--- a/artifacts/sift_agent_manifest.xlsx
+++ b/artifacts/sift_agent_manifest.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manifest" sheetId="1" r:id="R3de274992efd435a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Summary" sheetId="2" r:id="R8dd4aff7078945b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="3" r:id="R2a01efc58ca641a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA Notes" sheetId="4" r:id="R03e66533711c4084"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manifest" sheetId="1" r:id="R9efb3ece0c784c7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Summary" sheetId="2" r:id="R09b5300a35c04f6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="3" r:id="R30a4074ce2794b45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Path Notes" sheetId="4" r:id="Re6599acabe204149"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -58,7 +58,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="20">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -100,17 +100,20 @@
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="2">
+  <x:dxfs count="4">
     <x:dxf>
       <x:fill>
         <x:patternFill patternType="solid">
@@ -125,12 +128,26 @@
         </x:patternFill>
       </x:fill>
     </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF4CCCC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
   </x:dxfs>
 </x:styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SiftAgentManifestTable" displayName="SiftAgentManifestTable" ref="A1:Q214" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SiftAgentManifestRevisedPathsTable" displayName="SiftAgentManifestRevisedPathsTable" ref="A1:Q214" headerRowCount="1">
   <x:tableColumns count="17">
     <x:tableColumn id="1" name="Category"/>
     <x:tableColumn id="2" name="Domain"/>
@@ -178,10 +195,10 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="QANotesTable" displayName="QANotesTable" ref="A1:B9" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="PathNotesTable" displayName="PathNotesTable" ref="A1:B12" headerRowCount="1">
   <x:tableColumns count="2">
-    <x:tableColumn id="1" name="Check"/>
-    <x:tableColumn id="2" name="Value"/>
+    <x:tableColumn id="1" name="Item"/>
+    <x:tableColumn id="2" name="Note"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </x:table>
@@ -338,21 +355,21 @@
   <x:cols>
     <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="40" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="36" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="38" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="40" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="46" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="26" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="15" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="42" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="72" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="84" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="84" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="84" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="46" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="92" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="102" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="102" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="102" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="18" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="14" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="48" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="78" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -419,13 +436,13 @@
         <x:v>Some Basic Concepts in Chemistry</x:v>
       </x:c>
       <x:c r="D2" s="4" t="str">
-        <x:v>some-basic-concepts-chemistry</x:v>
+        <x:v>some-basic-concepts-in-chemistry</x:v>
       </x:c>
       <x:c r="E2" s="4" t="str">
         <x:v>01</x:v>
       </x:c>
       <x:c r="F2" s="4" t="str">
-        <x:v>some-basic-concepts-chemistry-lecture-01</x:v>
+        <x:v>some-basic-concepts-in-chemistry-lecture-01</x:v>
       </x:c>
       <x:c r="G2" s="4" t="str">
         <x:v>Laws of Chemical Combination</x:v>
@@ -440,16 +457,16 @@
         <x:v>comments-01-laws-of-chemical-combination</x:v>
       </x:c>
       <x:c r="K2" s="4" t="str">
-        <x:v>content/chemistry/physical/some-basic-concepts-chemistry/lectures/lecture-01-laws-of-chemical-combination</x:v>
+        <x:v>content/01-physical/01-some-basic-concepts-in-chemistry/lectures/lecture-01-laws-of-chemical-combination</x:v>
       </x:c>
       <x:c r="L2" s="4" t="str">
-        <x:v>content/chemistry/physical/some-basic-concepts-chemistry/lectures/lecture-01-laws-of-chemical-combination/comments/comments-01-laws-of-chemical-combination.raw.json</x:v>
+        <x:v>content/01-physical/01-some-basic-concepts-in-chemistry/lectures/lecture-01-laws-of-chemical-combination/comments/comments-01-laws-of-chemical-combination.raw.json</x:v>
       </x:c>
       <x:c r="M2" s="4" t="str">
-        <x:v>content/chemistry/physical/some-basic-concepts-chemistry/lectures/lecture-01-laws-of-chemical-combination/comments/comments-01-laws-of-chemical-combination.scrubbed.json</x:v>
+        <x:v>content/01-physical/01-some-basic-concepts-in-chemistry/lectures/lecture-01-laws-of-chemical-combination/comments/comments-01-laws-of-chemical-combination.scrubbed.json</x:v>
       </x:c>
       <x:c r="N2" s="4" t="str">
-        <x:v>content/chemistry/physical/some-basic-concepts-chemistry/lectures/lecture-01-laws-of-chemical-combination/comments/comments-01-laws-of-chemical-combination.final.md</x:v>
+        <x:v>content/01-physical/01-some-basic-concepts-in-chemistry/lectures/lecture-01-laws-of-chemical-combination/comments/comments-01-laws-of-chemical-combination.final.md</x:v>
       </x:c>
       <x:c r="O2" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -458,7 +475,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q2" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -472,13 +489,13 @@
         <x:v>Some Basic Concepts in Chemistry</x:v>
       </x:c>
       <x:c r="D3" s="4" t="str">
-        <x:v>some-basic-concepts-chemistry</x:v>
+        <x:v>some-basic-concepts-in-chemistry</x:v>
       </x:c>
       <x:c r="E3" s="4" t="str">
         <x:v>02</x:v>
       </x:c>
       <x:c r="F3" s="4" t="str">
-        <x:v>some-basic-concepts-chemistry-lecture-02</x:v>
+        <x:v>some-basic-concepts-in-chemistry-lecture-02</x:v>
       </x:c>
       <x:c r="G3" s="4" t="str">
         <x:v>Concentration terms: Mole Fraction</x:v>
@@ -493,16 +510,16 @@
         <x:v>comments-02-concentration-terms-mole-fraction</x:v>
       </x:c>
       <x:c r="K3" s="4" t="str">
-        <x:v>content/chemistry/physical/some-basic-concepts-chemistry/lectures/lecture-02-concentration-terms-mole-fraction</x:v>
+        <x:v>content/01-physical/01-some-basic-concepts-in-chemistry/lectures/lecture-02-concentration-terms-mole-fraction</x:v>
       </x:c>
       <x:c r="L3" s="4" t="str">
-        <x:v>content/chemistry/physical/some-basic-concepts-chemistry/lectures/lecture-02-concentration-terms-mole-fraction/comments/comments-02-concentration-terms-mole-fraction.raw.json</x:v>
+        <x:v>content/01-physical/01-some-basic-concepts-in-chemistry/lectures/lecture-02-concentration-terms-mole-fraction/comments/comments-02-concentration-terms-mole-fraction.raw.json</x:v>
       </x:c>
       <x:c r="M3" s="4" t="str">
-        <x:v>content/chemistry/physical/some-basic-concepts-chemistry/lectures/lecture-02-concentration-terms-mole-fraction/comments/comments-02-concentration-terms-mole-fraction.scrubbed.json</x:v>
+        <x:v>content/01-physical/01-some-basic-concepts-in-chemistry/lectures/lecture-02-concentration-terms-mole-fraction/comments/comments-02-concentration-terms-mole-fraction.scrubbed.json</x:v>
       </x:c>
       <x:c r="N3" s="4" t="str">
-        <x:v>content/chemistry/physical/some-basic-concepts-chemistry/lectures/lecture-02-concentration-terms-mole-fraction/comments/comments-02-concentration-terms-mole-fraction.final.md</x:v>
+        <x:v>content/01-physical/01-some-basic-concepts-in-chemistry/lectures/lecture-02-concentration-terms-mole-fraction/comments/comments-02-concentration-terms-mole-fraction.final.md</x:v>
       </x:c>
       <x:c r="O3" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -511,7 +528,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q3" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -525,13 +542,13 @@
         <x:v>Some Basic Concepts in Chemistry</x:v>
       </x:c>
       <x:c r="D4" s="4" t="str">
-        <x:v>some-basic-concepts-chemistry</x:v>
+        <x:v>some-basic-concepts-in-chemistry</x:v>
       </x:c>
       <x:c r="E4" s="4" t="str">
         <x:v>03</x:v>
       </x:c>
       <x:c r="F4" s="4" t="str">
-        <x:v>some-basic-concepts-chemistry-lecture-03</x:v>
+        <x:v>some-basic-concepts-in-chemistry-lecture-03</x:v>
       </x:c>
       <x:c r="G4" s="4" t="str">
         <x:v>Mole Concept, Stoichiometry, Percentage Composition</x:v>
@@ -546,16 +563,16 @@
         <x:v>comments-03-mole-concept-stoichiometry-percentage-composition</x:v>
       </x:c>
       <x:c r="K4" s="4" t="str">
-        <x:v>content/chemistry/physical/some-basic-concepts-chemistry/lectures/lecture-03-mole-concept-stoichiometry-percentage-composition</x:v>
+        <x:v>content/01-physical/01-some-basic-concepts-in-chemistry/lectures/lecture-03-mole-concept-stoichiometry-percentage-composition</x:v>
       </x:c>
       <x:c r="L4" s="4" t="str">
-        <x:v>content/chemistry/physical/some-basic-concepts-chemistry/lectures/lecture-03-mole-concept-stoichiometry-percentage-composition/comments/comments-03-mole-concept-stoichiometry-percentage-composition.raw.json</x:v>
+        <x:v>content/01-physical/01-some-basic-concepts-in-chemistry/lectures/lecture-03-mole-concept-stoichiometry-percentage-composition/comments/comments-03-mole-concept-stoichiometry-percentage-composition.raw.json</x:v>
       </x:c>
       <x:c r="M4" s="4" t="str">
-        <x:v>content/chemistry/physical/some-basic-concepts-chemistry/lectures/lecture-03-mole-concept-stoichiometry-percentage-composition/comments/comments-03-mole-concept-stoichiometry-percentage-composition.scrubbed.json</x:v>
+        <x:v>content/01-physical/01-some-basic-concepts-in-chemistry/lectures/lecture-03-mole-concept-stoichiometry-percentage-composition/comments/comments-03-mole-concept-stoichiometry-percentage-composition.scrubbed.json</x:v>
       </x:c>
       <x:c r="N4" s="4" t="str">
-        <x:v>content/chemistry/physical/some-basic-concepts-chemistry/lectures/lecture-03-mole-concept-stoichiometry-percentage-composition/comments/comments-03-mole-concept-stoichiometry-percentage-composition.final.md</x:v>
+        <x:v>content/01-physical/01-some-basic-concepts-in-chemistry/lectures/lecture-03-mole-concept-stoichiometry-percentage-composition/comments/comments-03-mole-concept-stoichiometry-percentage-composition.final.md</x:v>
       </x:c>
       <x:c r="O4" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -564,7 +581,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q4" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -578,13 +595,13 @@
         <x:v>Some Basic Concepts in Chemistry</x:v>
       </x:c>
       <x:c r="D5" s="4" t="str">
-        <x:v>some-basic-concepts-chemistry</x:v>
+        <x:v>some-basic-concepts-in-chemistry</x:v>
       </x:c>
       <x:c r="E5" s="4" t="str">
         <x:v>04</x:v>
       </x:c>
       <x:c r="F5" s="4" t="str">
-        <x:v>some-basic-concepts-chemistry-lecture-04</x:v>
+        <x:v>some-basic-concepts-in-chemistry-lecture-04</x:v>
       </x:c>
       <x:c r="G5" s="4" t="str">
         <x:v>Molarity and Molality</x:v>
@@ -599,16 +616,16 @@
         <x:v>comments-04-molarity-and-molality</x:v>
       </x:c>
       <x:c r="K5" s="4" t="str">
-        <x:v>content/chemistry/physical/some-basic-concepts-chemistry/lectures/lecture-04-molarity-and-molality</x:v>
+        <x:v>content/01-physical/01-some-basic-concepts-in-chemistry/lectures/lecture-04-molarity-and-molality</x:v>
       </x:c>
       <x:c r="L5" s="4" t="str">
-        <x:v>content/chemistry/physical/some-basic-concepts-chemistry/lectures/lecture-04-molarity-and-molality/comments/comments-04-molarity-and-molality.raw.json</x:v>
+        <x:v>content/01-physical/01-some-basic-concepts-in-chemistry/lectures/lecture-04-molarity-and-molality/comments/comments-04-molarity-and-molality.raw.json</x:v>
       </x:c>
       <x:c r="M5" s="4" t="str">
-        <x:v>content/chemistry/physical/some-basic-concepts-chemistry/lectures/lecture-04-molarity-and-molality/comments/comments-04-molarity-and-molality.scrubbed.json</x:v>
+        <x:v>content/01-physical/01-some-basic-concepts-in-chemistry/lectures/lecture-04-molarity-and-molality/comments/comments-04-molarity-and-molality.scrubbed.json</x:v>
       </x:c>
       <x:c r="N5" s="4" t="str">
-        <x:v>content/chemistry/physical/some-basic-concepts-chemistry/lectures/lecture-04-molarity-and-molality/comments/comments-04-molarity-and-molality.final.md</x:v>
+        <x:v>content/01-physical/01-some-basic-concepts-in-chemistry/lectures/lecture-04-molarity-and-molality/comments/comments-04-molarity-and-molality.final.md</x:v>
       </x:c>
       <x:c r="O5" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -617,7 +634,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q5" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -631,13 +648,13 @@
         <x:v>Some Basic Concepts in Chemistry</x:v>
       </x:c>
       <x:c r="D6" s="4" t="str">
-        <x:v>some-basic-concepts-chemistry</x:v>
+        <x:v>some-basic-concepts-in-chemistry</x:v>
       </x:c>
       <x:c r="E6" s="4" t="str">
         <x:v>05</x:v>
       </x:c>
       <x:c r="F6" s="4" t="str">
-        <x:v>some-basic-concepts-chemistry-lecture-05</x:v>
+        <x:v>some-basic-concepts-in-chemistry-lecture-05</x:v>
       </x:c>
       <x:c r="G6" s="4" t="str">
         <x:v>Equivalent Weight and Gram Equivalent part 1</x:v>
@@ -652,16 +669,16 @@
         <x:v>comments-05-equivalent-weight-and-gram-equivalent-part-1</x:v>
       </x:c>
       <x:c r="K6" s="4" t="str">
-        <x:v>content/chemistry/physical/some-basic-concepts-chemistry/lectures/lecture-05-equivalent-weight-and-gram-equivalent-part-1</x:v>
+        <x:v>content/01-physical/01-some-basic-concepts-in-chemistry/lectures/lecture-05-equivalent-weight-and-gram-equivalent-part-1</x:v>
       </x:c>
       <x:c r="L6" s="4" t="str">
-        <x:v>content/chemistry/physical/some-basic-concepts-chemistry/lectures/lecture-05-equivalent-weight-and-gram-equivalent-part-1/comments/comments-05-equivalent-weight-and-gram-equivalent-part-1.raw.json</x:v>
+        <x:v>content/01-physical/01-some-basic-concepts-in-chemistry/lectures/lecture-05-equivalent-weight-and-gram-equivalent-part-1/comments/comments-05-equivalent-weight-and-gram-equivalent-part-1.raw.json</x:v>
       </x:c>
       <x:c r="M6" s="4" t="str">
-        <x:v>content/chemistry/physical/some-basic-concepts-chemistry/lectures/lecture-05-equivalent-weight-and-gram-equivalent-part-1/comments/comments-05-equivalent-weight-and-gram-equivalent-part-1.scrubbed.json</x:v>
+        <x:v>content/01-physical/01-some-basic-concepts-in-chemistry/lectures/lecture-05-equivalent-weight-and-gram-equivalent-part-1/comments/comments-05-equivalent-weight-and-gram-equivalent-part-1.scrubbed.json</x:v>
       </x:c>
       <x:c r="N6" s="4" t="str">
-        <x:v>content/chemistry/physical/some-basic-concepts-chemistry/lectures/lecture-05-equivalent-weight-and-gram-equivalent-part-1/comments/comments-05-equivalent-weight-and-gram-equivalent-part-1.final.md</x:v>
+        <x:v>content/01-physical/01-some-basic-concepts-in-chemistry/lectures/lecture-05-equivalent-weight-and-gram-equivalent-part-1/comments/comments-05-equivalent-weight-and-gram-equivalent-part-1.final.md</x:v>
       </x:c>
       <x:c r="O6" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -670,7 +687,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q6" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -684,13 +701,13 @@
         <x:v>Some Basic Concepts in Chemistry</x:v>
       </x:c>
       <x:c r="D7" s="4" t="str">
-        <x:v>some-basic-concepts-chemistry</x:v>
+        <x:v>some-basic-concepts-in-chemistry</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
         <x:v>06</x:v>
       </x:c>
       <x:c r="F7" s="4" t="str">
-        <x:v>some-basic-concepts-chemistry-lecture-06</x:v>
+        <x:v>some-basic-concepts-in-chemistry-lecture-06</x:v>
       </x:c>
       <x:c r="G7" s="4" t="str">
         <x:v>Normality</x:v>
@@ -705,16 +722,16 @@
         <x:v>comments-06-normality</x:v>
       </x:c>
       <x:c r="K7" s="4" t="str">
-        <x:v>content/chemistry/physical/some-basic-concepts-chemistry/lectures/lecture-06-normality</x:v>
+        <x:v>content/01-physical/01-some-basic-concepts-in-chemistry/lectures/lecture-06-normality</x:v>
       </x:c>
       <x:c r="L7" s="4" t="str">
-        <x:v>content/chemistry/physical/some-basic-concepts-chemistry/lectures/lecture-06-normality/comments/comments-06-normality.raw.json</x:v>
+        <x:v>content/01-physical/01-some-basic-concepts-in-chemistry/lectures/lecture-06-normality/comments/comments-06-normality.raw.json</x:v>
       </x:c>
       <x:c r="M7" s="4" t="str">
-        <x:v>content/chemistry/physical/some-basic-concepts-chemistry/lectures/lecture-06-normality/comments/comments-06-normality.scrubbed.json</x:v>
+        <x:v>content/01-physical/01-some-basic-concepts-in-chemistry/lectures/lecture-06-normality/comments/comments-06-normality.scrubbed.json</x:v>
       </x:c>
       <x:c r="N7" s="4" t="str">
-        <x:v>content/chemistry/physical/some-basic-concepts-chemistry/lectures/lecture-06-normality/comments/comments-06-normality.final.md</x:v>
+        <x:v>content/01-physical/01-some-basic-concepts-in-chemistry/lectures/lecture-06-normality/comments/comments-06-normality.final.md</x:v>
       </x:c>
       <x:c r="O7" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -723,7 +740,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q7" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -758,16 +775,16 @@
         <x:v>comments-01-cathode-ray-rutherford-alpha-particle-scattering-experiment</x:v>
       </x:c>
       <x:c r="K8" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-01-cathode-ray-rutherford-alpha-particle-scattering-experiment</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-01-cathode-ray-rutherford-alpha-particle-scattering-experiment</x:v>
       </x:c>
       <x:c r="L8" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-01-cathode-ray-rutherford-alpha-particle-scattering-experiment/comments/comments-01-cathode-ray-rutherford-alpha-particle-scattering-experiment.raw.json</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-01-cathode-ray-rutherford-alpha-particle-scattering-experiment/comments/comments-01-cathode-ray-rutherford-alpha-particle-scattering-experiment.raw.json</x:v>
       </x:c>
       <x:c r="M8" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-01-cathode-ray-rutherford-alpha-particle-scattering-experiment/comments/comments-01-cathode-ray-rutherford-alpha-particle-scattering-experiment.scrubbed.json</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-01-cathode-ray-rutherford-alpha-particle-scattering-experiment/comments/comments-01-cathode-ray-rutherford-alpha-particle-scattering-experiment.scrubbed.json</x:v>
       </x:c>
       <x:c r="N8" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-01-cathode-ray-rutherford-alpha-particle-scattering-experiment/comments/comments-01-cathode-ray-rutherford-alpha-particle-scattering-experiment.final.md</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-01-cathode-ray-rutherford-alpha-particle-scattering-experiment/comments/comments-01-cathode-ray-rutherford-alpha-particle-scattering-experiment.final.md</x:v>
       </x:c>
       <x:c r="O8" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -776,7 +793,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q8" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -811,16 +828,16 @@
         <x:v>comments-02-bohrs-atomic-model</x:v>
       </x:c>
       <x:c r="K9" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-02-bohrs-atomic-model</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-02-bohrs-atomic-model</x:v>
       </x:c>
       <x:c r="L9" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-02-bohrs-atomic-model/comments/comments-02-bohrs-atomic-model.raw.json</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-02-bohrs-atomic-model/comments/comments-02-bohrs-atomic-model.raw.json</x:v>
       </x:c>
       <x:c r="M9" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-02-bohrs-atomic-model/comments/comments-02-bohrs-atomic-model.scrubbed.json</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-02-bohrs-atomic-model/comments/comments-02-bohrs-atomic-model.scrubbed.json</x:v>
       </x:c>
       <x:c r="N9" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-02-bohrs-atomic-model/comments/comments-02-bohrs-atomic-model.final.md</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-02-bohrs-atomic-model/comments/comments-02-bohrs-atomic-model.final.md</x:v>
       </x:c>
       <x:c r="O9" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -829,7 +846,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q9" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -864,16 +881,16 @@
         <x:v>comments-03-atomic-spectrum-hydrogen-spectrum</x:v>
       </x:c>
       <x:c r="K10" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-03-atomic-spectrum-hydrogen-spectrum</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-03-atomic-spectrum-hydrogen-spectrum</x:v>
       </x:c>
       <x:c r="L10" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-03-atomic-spectrum-hydrogen-spectrum/comments/comments-03-atomic-spectrum-hydrogen-spectrum.raw.json</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-03-atomic-spectrum-hydrogen-spectrum/comments/comments-03-atomic-spectrum-hydrogen-spectrum.raw.json</x:v>
       </x:c>
       <x:c r="M10" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-03-atomic-spectrum-hydrogen-spectrum/comments/comments-03-atomic-spectrum-hydrogen-spectrum.scrubbed.json</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-03-atomic-spectrum-hydrogen-spectrum/comments/comments-03-atomic-spectrum-hydrogen-spectrum.scrubbed.json</x:v>
       </x:c>
       <x:c r="N10" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-03-atomic-spectrum-hydrogen-spectrum/comments/comments-03-atomic-spectrum-hydrogen-spectrum.final.md</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-03-atomic-spectrum-hydrogen-spectrum/comments/comments-03-atomic-spectrum-hydrogen-spectrum.final.md</x:v>
       </x:c>
       <x:c r="O10" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -882,7 +899,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q10" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -917,16 +934,16 @@
         <x:v>comments-04-de-broglie-wavelength-heisenbergs-uncertainty-principle</x:v>
       </x:c>
       <x:c r="K11" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-04-de-broglie-wavelength-heisenbergs-uncertainty-principle</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-04-de-broglie-wavelength-heisenbergs-uncertainty-principle</x:v>
       </x:c>
       <x:c r="L11" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-04-de-broglie-wavelength-heisenbergs-uncertainty-principle/comments/comments-04-de-broglie-wavelength-heisenbergs-uncertainty-principle.raw.json</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-04-de-broglie-wavelength-heisenbergs-uncertainty-principle/comments/comments-04-de-broglie-wavelength-heisenbergs-uncertainty-principle.raw.json</x:v>
       </x:c>
       <x:c r="M11" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-04-de-broglie-wavelength-heisenbergs-uncertainty-principle/comments/comments-04-de-broglie-wavelength-heisenbergs-uncertainty-principle.scrubbed.json</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-04-de-broglie-wavelength-heisenbergs-uncertainty-principle/comments/comments-04-de-broglie-wavelength-heisenbergs-uncertainty-principle.scrubbed.json</x:v>
       </x:c>
       <x:c r="N11" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-04-de-broglie-wavelength-heisenbergs-uncertainty-principle/comments/comments-04-de-broglie-wavelength-heisenbergs-uncertainty-principle.final.md</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-04-de-broglie-wavelength-heisenbergs-uncertainty-principle/comments/comments-04-de-broglie-wavelength-heisenbergs-uncertainty-principle.final.md</x:v>
       </x:c>
       <x:c r="O11" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -935,7 +952,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q11" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -970,16 +987,16 @@
         <x:v>comments-05-quantum-numbers-paulis-exclusion-principle</x:v>
       </x:c>
       <x:c r="K12" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-05-quantum-numbers-paulis-exclusion-principle</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-05-quantum-numbers-paulis-exclusion-principle</x:v>
       </x:c>
       <x:c r="L12" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-05-quantum-numbers-paulis-exclusion-principle/comments/comments-05-quantum-numbers-paulis-exclusion-principle.raw.json</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-05-quantum-numbers-paulis-exclusion-principle/comments/comments-05-quantum-numbers-paulis-exclusion-principle.raw.json</x:v>
       </x:c>
       <x:c r="M12" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-05-quantum-numbers-paulis-exclusion-principle/comments/comments-05-quantum-numbers-paulis-exclusion-principle.scrubbed.json</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-05-quantum-numbers-paulis-exclusion-principle/comments/comments-05-quantum-numbers-paulis-exclusion-principle.scrubbed.json</x:v>
       </x:c>
       <x:c r="N12" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-05-quantum-numbers-paulis-exclusion-principle/comments/comments-05-quantum-numbers-paulis-exclusion-principle.final.md</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-05-quantum-numbers-paulis-exclusion-principle/comments/comments-05-quantum-numbers-paulis-exclusion-principle.final.md</x:v>
       </x:c>
       <x:c r="O12" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -988,7 +1005,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q12" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1023,16 +1040,16 @@
         <x:v>comments-06-aufbaus-principle-rules-for-filling-electrons</x:v>
       </x:c>
       <x:c r="K13" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-06-aufbaus-principle-rules-for-filling-electrons</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-06-aufbaus-principle-rules-for-filling-electrons</x:v>
       </x:c>
       <x:c r="L13" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-06-aufbaus-principle-rules-for-filling-electrons/comments/comments-06-aufbaus-principle-rules-for-filling-electrons.raw.json</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-06-aufbaus-principle-rules-for-filling-electrons/comments/comments-06-aufbaus-principle-rules-for-filling-electrons.raw.json</x:v>
       </x:c>
       <x:c r="M13" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-06-aufbaus-principle-rules-for-filling-electrons/comments/comments-06-aufbaus-principle-rules-for-filling-electrons.scrubbed.json</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-06-aufbaus-principle-rules-for-filling-electrons/comments/comments-06-aufbaus-principle-rules-for-filling-electrons.scrubbed.json</x:v>
       </x:c>
       <x:c r="N13" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-06-aufbaus-principle-rules-for-filling-electrons/comments/comments-06-aufbaus-principle-rules-for-filling-electrons.final.md</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-06-aufbaus-principle-rules-for-filling-electrons/comments/comments-06-aufbaus-principle-rules-for-filling-electrons.final.md</x:v>
       </x:c>
       <x:c r="O13" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -1041,7 +1058,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q13" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1076,16 +1093,16 @@
         <x:v>comments-07-hunds-rule-for-maximum-multiplicity</x:v>
       </x:c>
       <x:c r="K14" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-07-hunds-rule-for-maximum-multiplicity</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-07-hunds-rule-for-maximum-multiplicity</x:v>
       </x:c>
       <x:c r="L14" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-07-hunds-rule-for-maximum-multiplicity/comments/comments-07-hunds-rule-for-maximum-multiplicity.raw.json</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-07-hunds-rule-for-maximum-multiplicity/comments/comments-07-hunds-rule-for-maximum-multiplicity.raw.json</x:v>
       </x:c>
       <x:c r="M14" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-07-hunds-rule-for-maximum-multiplicity/comments/comments-07-hunds-rule-for-maximum-multiplicity.scrubbed.json</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-07-hunds-rule-for-maximum-multiplicity/comments/comments-07-hunds-rule-for-maximum-multiplicity.scrubbed.json</x:v>
       </x:c>
       <x:c r="N14" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-07-hunds-rule-for-maximum-multiplicity/comments/comments-07-hunds-rule-for-maximum-multiplicity.final.md</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-07-hunds-rule-for-maximum-multiplicity/comments/comments-07-hunds-rule-for-maximum-multiplicity.final.md</x:v>
       </x:c>
       <x:c r="O14" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -1094,7 +1111,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q14" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1129,16 +1146,16 @@
         <x:v>comments-08-how-to-do-electronic-configuration</x:v>
       </x:c>
       <x:c r="K15" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-08-how-to-do-electronic-configuration</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-08-how-to-do-electronic-configuration</x:v>
       </x:c>
       <x:c r="L15" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-08-how-to-do-electronic-configuration/comments/comments-08-how-to-do-electronic-configuration.raw.json</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-08-how-to-do-electronic-configuration/comments/comments-08-how-to-do-electronic-configuration.raw.json</x:v>
       </x:c>
       <x:c r="M15" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-08-how-to-do-electronic-configuration/comments/comments-08-how-to-do-electronic-configuration.scrubbed.json</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-08-how-to-do-electronic-configuration/comments/comments-08-how-to-do-electronic-configuration.scrubbed.json</x:v>
       </x:c>
       <x:c r="N15" s="4" t="str">
-        <x:v>content/chemistry/physical/atomic-structure/lectures/lecture-08-how-to-do-electronic-configuration/comments/comments-08-how-to-do-electronic-configuration.final.md</x:v>
+        <x:v>content/01-physical/02-atomic-structure/lectures/lecture-08-how-to-do-electronic-configuration/comments/comments-08-how-to-do-electronic-configuration.final.md</x:v>
       </x:c>
       <x:c r="O15" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -1147,7 +1164,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q15" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1182,16 +1199,16 @@
         <x:v>comments-01-intro-to-chemical-bonds</x:v>
       </x:c>
       <x:c r="K16" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-01-intro-to-chemical-bonds</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-01-intro-to-chemical-bonds</x:v>
       </x:c>
       <x:c r="L16" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-01-intro-to-chemical-bonds/comments/comments-01-intro-to-chemical-bonds.raw.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-01-intro-to-chemical-bonds/comments/comments-01-intro-to-chemical-bonds.raw.json</x:v>
       </x:c>
       <x:c r="M16" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-01-intro-to-chemical-bonds/comments/comments-01-intro-to-chemical-bonds.scrubbed.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-01-intro-to-chemical-bonds/comments/comments-01-intro-to-chemical-bonds.scrubbed.json</x:v>
       </x:c>
       <x:c r="N16" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-01-intro-to-chemical-bonds/comments/comments-01-intro-to-chemical-bonds.final.md</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-01-intro-to-chemical-bonds/comments/comments-01-intro-to-chemical-bonds.final.md</x:v>
       </x:c>
       <x:c r="O16" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -1200,7 +1217,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q16" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1235,16 +1252,16 @@
         <x:v>comments-02-ionic-bonds</x:v>
       </x:c>
       <x:c r="K17" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-02-ionic-bonds</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-02-ionic-bonds</x:v>
       </x:c>
       <x:c r="L17" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-02-ionic-bonds/comments/comments-02-ionic-bonds.raw.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-02-ionic-bonds/comments/comments-02-ionic-bonds.raw.json</x:v>
       </x:c>
       <x:c r="M17" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-02-ionic-bonds/comments/comments-02-ionic-bonds.scrubbed.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-02-ionic-bonds/comments/comments-02-ionic-bonds.scrubbed.json</x:v>
       </x:c>
       <x:c r="N17" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-02-ionic-bonds/comments/comments-02-ionic-bonds.final.md</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-02-ionic-bonds/comments/comments-02-ionic-bonds.final.md</x:v>
       </x:c>
       <x:c r="O17" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -1253,7 +1270,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q17" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1288,16 +1305,16 @@
         <x:v>comments-03-lattice-energy-and-born-haber-cycle</x:v>
       </x:c>
       <x:c r="K18" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-03-lattice-energy-and-born-haber-cycle</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-03-lattice-energy-and-born-haber-cycle</x:v>
       </x:c>
       <x:c r="L18" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-03-lattice-energy-and-born-haber-cycle/comments/comments-03-lattice-energy-and-born-haber-cycle.raw.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-03-lattice-energy-and-born-haber-cycle/comments/comments-03-lattice-energy-and-born-haber-cycle.raw.json</x:v>
       </x:c>
       <x:c r="M18" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-03-lattice-energy-and-born-haber-cycle/comments/comments-03-lattice-energy-and-born-haber-cycle.scrubbed.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-03-lattice-energy-and-born-haber-cycle/comments/comments-03-lattice-energy-and-born-haber-cycle.scrubbed.json</x:v>
       </x:c>
       <x:c r="N18" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-03-lattice-energy-and-born-haber-cycle/comments/comments-03-lattice-energy-and-born-haber-cycle.final.md</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-03-lattice-energy-and-born-haber-cycle/comments/comments-03-lattice-energy-and-born-haber-cycle.final.md</x:v>
       </x:c>
       <x:c r="O18" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -1306,7 +1323,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q18" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1341,16 +1358,16 @@
         <x:v>comments-04-fajans-rule</x:v>
       </x:c>
       <x:c r="K19" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-04-fajans-rule</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-04-fajans-rule</x:v>
       </x:c>
       <x:c r="L19" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-04-fajans-rule/comments/comments-04-fajans-rule.raw.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-04-fajans-rule/comments/comments-04-fajans-rule.raw.json</x:v>
       </x:c>
       <x:c r="M19" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-04-fajans-rule/comments/comments-04-fajans-rule.scrubbed.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-04-fajans-rule/comments/comments-04-fajans-rule.scrubbed.json</x:v>
       </x:c>
       <x:c r="N19" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-04-fajans-rule/comments/comments-04-fajans-rule.final.md</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-04-fajans-rule/comments/comments-04-fajans-rule.final.md</x:v>
       </x:c>
       <x:c r="O19" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -1359,7 +1376,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q19" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1394,16 +1411,16 @@
         <x:v>comments-05-lewis-dot-structure</x:v>
       </x:c>
       <x:c r="K20" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-05-lewis-dot-structure</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-05-lewis-dot-structure</x:v>
       </x:c>
       <x:c r="L20" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-05-lewis-dot-structure/comments/comments-05-lewis-dot-structure.raw.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-05-lewis-dot-structure/comments/comments-05-lewis-dot-structure.raw.json</x:v>
       </x:c>
       <x:c r="M20" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-05-lewis-dot-structure/comments/comments-05-lewis-dot-structure.scrubbed.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-05-lewis-dot-structure/comments/comments-05-lewis-dot-structure.scrubbed.json</x:v>
       </x:c>
       <x:c r="N20" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-05-lewis-dot-structure/comments/comments-05-lewis-dot-structure.final.md</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-05-lewis-dot-structure/comments/comments-05-lewis-dot-structure.final.md</x:v>
       </x:c>
       <x:c r="O20" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -1412,7 +1429,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q20" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1447,16 +1464,16 @@
         <x:v>comments-06-vbt</x:v>
       </x:c>
       <x:c r="K21" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-06-vbt</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-06-vbt</x:v>
       </x:c>
       <x:c r="L21" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-06-vbt/comments/comments-06-vbt.raw.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-06-vbt/comments/comments-06-vbt.raw.json</x:v>
       </x:c>
       <x:c r="M21" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-06-vbt/comments/comments-06-vbt.scrubbed.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-06-vbt/comments/comments-06-vbt.scrubbed.json</x:v>
       </x:c>
       <x:c r="N21" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-06-vbt/comments/comments-06-vbt.final.md</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-06-vbt/comments/comments-06-vbt.final.md</x:v>
       </x:c>
       <x:c r="O21" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -1465,7 +1482,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q21" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1500,16 +1517,16 @@
         <x:v>comments-07-more-on-vbt-pi-bonds</x:v>
       </x:c>
       <x:c r="K22" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-07-more-on-vbt-pi-bonds</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-07-more-on-vbt-pi-bonds</x:v>
       </x:c>
       <x:c r="L22" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-07-more-on-vbt-pi-bonds/comments/comments-07-more-on-vbt-pi-bonds.raw.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-07-more-on-vbt-pi-bonds/comments/comments-07-more-on-vbt-pi-bonds.raw.json</x:v>
       </x:c>
       <x:c r="M22" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-07-more-on-vbt-pi-bonds/comments/comments-07-more-on-vbt-pi-bonds.scrubbed.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-07-more-on-vbt-pi-bonds/comments/comments-07-more-on-vbt-pi-bonds.scrubbed.json</x:v>
       </x:c>
       <x:c r="N22" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-07-more-on-vbt-pi-bonds/comments/comments-07-more-on-vbt-pi-bonds.final.md</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-07-more-on-vbt-pi-bonds/comments/comments-07-more-on-vbt-pi-bonds.final.md</x:v>
       </x:c>
       <x:c r="O22" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -1518,7 +1535,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q22" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1553,16 +1570,16 @@
         <x:v>comments-08-hybridisation</x:v>
       </x:c>
       <x:c r="K23" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-08-hybridisation</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-08-hybridisation</x:v>
       </x:c>
       <x:c r="L23" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-08-hybridisation/comments/comments-08-hybridisation.raw.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-08-hybridisation/comments/comments-08-hybridisation.raw.json</x:v>
       </x:c>
       <x:c r="M23" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-08-hybridisation/comments/comments-08-hybridisation.scrubbed.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-08-hybridisation/comments/comments-08-hybridisation.scrubbed.json</x:v>
       </x:c>
       <x:c r="N23" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-08-hybridisation/comments/comments-08-hybridisation.final.md</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-08-hybridisation/comments/comments-08-hybridisation.final.md</x:v>
       </x:c>
       <x:c r="O23" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -1571,7 +1588,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q23" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1606,16 +1623,16 @@
         <x:v>comments-09-vsepr</x:v>
       </x:c>
       <x:c r="K24" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-09-vsepr</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-09-vsepr</x:v>
       </x:c>
       <x:c r="L24" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-09-vsepr/comments/comments-09-vsepr.raw.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-09-vsepr/comments/comments-09-vsepr.raw.json</x:v>
       </x:c>
       <x:c r="M24" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-09-vsepr/comments/comments-09-vsepr.scrubbed.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-09-vsepr/comments/comments-09-vsepr.scrubbed.json</x:v>
       </x:c>
       <x:c r="N24" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-09-vsepr/comments/comments-09-vsepr.final.md</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-09-vsepr/comments/comments-09-vsepr.final.md</x:v>
       </x:c>
       <x:c r="O24" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -1624,7 +1641,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q24" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1659,16 +1676,16 @@
         <x:v>comments-10-mot-part-i</x:v>
       </x:c>
       <x:c r="K25" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-10-mot-part-i</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-10-mot-part-i</x:v>
       </x:c>
       <x:c r="L25" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-10-mot-part-i/comments/comments-10-mot-part-i.raw.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-10-mot-part-i/comments/comments-10-mot-part-i.raw.json</x:v>
       </x:c>
       <x:c r="M25" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-10-mot-part-i/comments/comments-10-mot-part-i.scrubbed.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-10-mot-part-i/comments/comments-10-mot-part-i.scrubbed.json</x:v>
       </x:c>
       <x:c r="N25" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-10-mot-part-i/comments/comments-10-mot-part-i.final.md</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-10-mot-part-i/comments/comments-10-mot-part-i.final.md</x:v>
       </x:c>
       <x:c r="O25" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -1677,7 +1694,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q25" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1712,16 +1729,16 @@
         <x:v>comments-11-mot-part-ii</x:v>
       </x:c>
       <x:c r="K26" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-11-mot-part-ii</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-11-mot-part-ii</x:v>
       </x:c>
       <x:c r="L26" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-11-mot-part-ii/comments/comments-11-mot-part-ii.raw.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-11-mot-part-ii/comments/comments-11-mot-part-ii.raw.json</x:v>
       </x:c>
       <x:c r="M26" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-11-mot-part-ii/comments/comments-11-mot-part-ii.scrubbed.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-11-mot-part-ii/comments/comments-11-mot-part-ii.scrubbed.json</x:v>
       </x:c>
       <x:c r="N26" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-11-mot-part-ii/comments/comments-11-mot-part-ii.final.md</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-11-mot-part-ii/comments/comments-11-mot-part-ii.final.md</x:v>
       </x:c>
       <x:c r="O26" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -1730,7 +1747,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q26" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1765,16 +1782,16 @@
         <x:v>comments-12-dipole-moment</x:v>
       </x:c>
       <x:c r="K27" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-12-dipole-moment</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-12-dipole-moment</x:v>
       </x:c>
       <x:c r="L27" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-12-dipole-moment/comments/comments-12-dipole-moment.raw.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-12-dipole-moment/comments/comments-12-dipole-moment.raw.json</x:v>
       </x:c>
       <x:c r="M27" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-12-dipole-moment/comments/comments-12-dipole-moment.scrubbed.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-12-dipole-moment/comments/comments-12-dipole-moment.scrubbed.json</x:v>
       </x:c>
       <x:c r="N27" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-12-dipole-moment/comments/comments-12-dipole-moment.final.md</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-12-dipole-moment/comments/comments-12-dipole-moment.final.md</x:v>
       </x:c>
       <x:c r="O27" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -1783,7 +1800,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q27" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -1818,16 +1835,16 @@
         <x:v>comments-13-bond-angle</x:v>
       </x:c>
       <x:c r="K28" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-13-bond-angle</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-13-bond-angle</x:v>
       </x:c>
       <x:c r="L28" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-13-bond-angle/comments/comments-13-bond-angle.raw.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-13-bond-angle/comments/comments-13-bond-angle.raw.json</x:v>
       </x:c>
       <x:c r="M28" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-13-bond-angle/comments/comments-13-bond-angle.scrubbed.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-13-bond-angle/comments/comments-13-bond-angle.scrubbed.json</x:v>
       </x:c>
       <x:c r="N28" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-13-bond-angle/comments/comments-13-bond-angle.final.md</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-13-bond-angle/comments/comments-13-bond-angle.final.md</x:v>
       </x:c>
       <x:c r="O28" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -1836,7 +1853,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q28" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -1871,16 +1888,16 @@
         <x:v>comments-14-dragos-rule</x:v>
       </x:c>
       <x:c r="K29" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-14-dragos-rule</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-14-dragos-rule</x:v>
       </x:c>
       <x:c r="L29" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-14-dragos-rule/comments/comments-14-dragos-rule.raw.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-14-dragos-rule/comments/comments-14-dragos-rule.raw.json</x:v>
       </x:c>
       <x:c r="M29" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-14-dragos-rule/comments/comments-14-dragos-rule.scrubbed.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-14-dragos-rule/comments/comments-14-dragos-rule.scrubbed.json</x:v>
       </x:c>
       <x:c r="N29" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-14-dragos-rule/comments/comments-14-dragos-rule.final.md</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-14-dragos-rule/comments/comments-14-dragos-rule.final.md</x:v>
       </x:c>
       <x:c r="O29" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -1889,7 +1906,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q29" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -1924,16 +1941,16 @@
         <x:v>comments-15-vanderwaals-force</x:v>
       </x:c>
       <x:c r="K30" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-15-vanderwaals-force</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-15-vanderwaals-force</x:v>
       </x:c>
       <x:c r="L30" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-15-vanderwaals-force/comments/comments-15-vanderwaals-force.raw.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-15-vanderwaals-force/comments/comments-15-vanderwaals-force.raw.json</x:v>
       </x:c>
       <x:c r="M30" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-15-vanderwaals-force/comments/comments-15-vanderwaals-force.scrubbed.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-15-vanderwaals-force/comments/comments-15-vanderwaals-force.scrubbed.json</x:v>
       </x:c>
       <x:c r="N30" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-15-vanderwaals-force/comments/comments-15-vanderwaals-force.final.md</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-15-vanderwaals-force/comments/comments-15-vanderwaals-force.final.md</x:v>
       </x:c>
       <x:c r="O30" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -1942,7 +1959,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q30" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -1977,16 +1994,16 @@
         <x:v>comments-16-hydrogen-bonding</x:v>
       </x:c>
       <x:c r="K31" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-16-hydrogen-bonding</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-16-hydrogen-bonding</x:v>
       </x:c>
       <x:c r="L31" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-16-hydrogen-bonding/comments/comments-16-hydrogen-bonding.raw.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-16-hydrogen-bonding/comments/comments-16-hydrogen-bonding.raw.json</x:v>
       </x:c>
       <x:c r="M31" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-16-hydrogen-bonding/comments/comments-16-hydrogen-bonding.scrubbed.json</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-16-hydrogen-bonding/comments/comments-16-hydrogen-bonding.scrubbed.json</x:v>
       </x:c>
       <x:c r="N31" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-bonding/lectures/lecture-16-hydrogen-bonding/comments/comments-16-hydrogen-bonding.final.md</x:v>
+        <x:v>content/01-physical/03-chemical-bonding-and-molecular-structure/lectures/lecture-16-hydrogen-bonding/comments/comments-16-hydrogen-bonding.final.md</x:v>
       </x:c>
       <x:c r="O31" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -1995,7 +2012,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q31" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -2030,16 +2047,16 @@
         <x:v>comments-01-basic-gas-laws</x:v>
       </x:c>
       <x:c r="K32" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-01-basic-gas-laws</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-01-basic-gas-laws</x:v>
       </x:c>
       <x:c r="L32" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-01-basic-gas-laws/comments/comments-01-basic-gas-laws.raw.json</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-01-basic-gas-laws/comments/comments-01-basic-gas-laws.raw.json</x:v>
       </x:c>
       <x:c r="M32" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-01-basic-gas-laws/comments/comments-01-basic-gas-laws.scrubbed.json</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-01-basic-gas-laws/comments/comments-01-basic-gas-laws.scrubbed.json</x:v>
       </x:c>
       <x:c r="N32" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-01-basic-gas-laws/comments/comments-01-basic-gas-laws.final.md</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-01-basic-gas-laws/comments/comments-01-basic-gas-laws.final.md</x:v>
       </x:c>
       <x:c r="O32" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -2048,7 +2065,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q32" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -2083,16 +2100,16 @@
         <x:v>comments-02-ideal-gas-equation</x:v>
       </x:c>
       <x:c r="K33" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-02-ideal-gas-equation</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-02-ideal-gas-equation</x:v>
       </x:c>
       <x:c r="L33" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-02-ideal-gas-equation/comments/comments-02-ideal-gas-equation.raw.json</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-02-ideal-gas-equation/comments/comments-02-ideal-gas-equation.raw.json</x:v>
       </x:c>
       <x:c r="M33" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-02-ideal-gas-equation/comments/comments-02-ideal-gas-equation.scrubbed.json</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-02-ideal-gas-equation/comments/comments-02-ideal-gas-equation.scrubbed.json</x:v>
       </x:c>
       <x:c r="N33" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-02-ideal-gas-equation/comments/comments-02-ideal-gas-equation.final.md</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-02-ideal-gas-equation/comments/comments-02-ideal-gas-equation.final.md</x:v>
       </x:c>
       <x:c r="O33" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -2101,7 +2118,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q33" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -2136,16 +2153,16 @@
         <x:v>comments-03-daltons-law-of-partial-pressure</x:v>
       </x:c>
       <x:c r="K34" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-03-daltons-law-of-partial-pressure</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-03-daltons-law-of-partial-pressure</x:v>
       </x:c>
       <x:c r="L34" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-03-daltons-law-of-partial-pressure/comments/comments-03-daltons-law-of-partial-pressure.raw.json</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-03-daltons-law-of-partial-pressure/comments/comments-03-daltons-law-of-partial-pressure.raw.json</x:v>
       </x:c>
       <x:c r="M34" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-03-daltons-law-of-partial-pressure/comments/comments-03-daltons-law-of-partial-pressure.scrubbed.json</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-03-daltons-law-of-partial-pressure/comments/comments-03-daltons-law-of-partial-pressure.scrubbed.json</x:v>
       </x:c>
       <x:c r="N34" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-03-daltons-law-of-partial-pressure/comments/comments-03-daltons-law-of-partial-pressure.final.md</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-03-daltons-law-of-partial-pressure/comments/comments-03-daltons-law-of-partial-pressure.final.md</x:v>
       </x:c>
       <x:c r="O34" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -2154,7 +2171,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q34" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -2189,16 +2206,16 @@
         <x:v>comments-04-grahams-law-of-diffusion</x:v>
       </x:c>
       <x:c r="K35" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-04-grahams-law-of-diffusion</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-04-grahams-law-of-diffusion</x:v>
       </x:c>
       <x:c r="L35" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-04-grahams-law-of-diffusion/comments/comments-04-grahams-law-of-diffusion.raw.json</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-04-grahams-law-of-diffusion/comments/comments-04-grahams-law-of-diffusion.raw.json</x:v>
       </x:c>
       <x:c r="M35" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-04-grahams-law-of-diffusion/comments/comments-04-grahams-law-of-diffusion.scrubbed.json</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-04-grahams-law-of-diffusion/comments/comments-04-grahams-law-of-diffusion.scrubbed.json</x:v>
       </x:c>
       <x:c r="N35" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-04-grahams-law-of-diffusion/comments/comments-04-grahams-law-of-diffusion.final.md</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-04-grahams-law-of-diffusion/comments/comments-04-grahams-law-of-diffusion.final.md</x:v>
       </x:c>
       <x:c r="O35" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -2207,7 +2224,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q35" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -2242,16 +2259,16 @@
         <x:v>comments-05-kinetic-theory-of-gases</x:v>
       </x:c>
       <x:c r="K36" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-05-kinetic-theory-of-gases</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-05-kinetic-theory-of-gases</x:v>
       </x:c>
       <x:c r="L36" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-05-kinetic-theory-of-gases/comments/comments-05-kinetic-theory-of-gases.raw.json</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-05-kinetic-theory-of-gases/comments/comments-05-kinetic-theory-of-gases.raw.json</x:v>
       </x:c>
       <x:c r="M36" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-05-kinetic-theory-of-gases/comments/comments-05-kinetic-theory-of-gases.scrubbed.json</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-05-kinetic-theory-of-gases/comments/comments-05-kinetic-theory-of-gases.scrubbed.json</x:v>
       </x:c>
       <x:c r="N36" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-05-kinetic-theory-of-gases/comments/comments-05-kinetic-theory-of-gases.final.md</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-05-kinetic-theory-of-gases/comments/comments-05-kinetic-theory-of-gases.final.md</x:v>
       </x:c>
       <x:c r="O36" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -2260,7 +2277,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q36" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -2295,16 +2312,16 @@
         <x:v>comments-06-types-of-speeds-of-gas-molecules</x:v>
       </x:c>
       <x:c r="K37" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-06-types-of-speeds-of-gas-molecules</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-06-types-of-speeds-of-gas-molecules</x:v>
       </x:c>
       <x:c r="L37" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-06-types-of-speeds-of-gas-molecules/comments/comments-06-types-of-speeds-of-gas-molecules.raw.json</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-06-types-of-speeds-of-gas-molecules/comments/comments-06-types-of-speeds-of-gas-molecules.raw.json</x:v>
       </x:c>
       <x:c r="M37" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-06-types-of-speeds-of-gas-molecules/comments/comments-06-types-of-speeds-of-gas-molecules.scrubbed.json</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-06-types-of-speeds-of-gas-molecules/comments/comments-06-types-of-speeds-of-gas-molecules.scrubbed.json</x:v>
       </x:c>
       <x:c r="N37" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-06-types-of-speeds-of-gas-molecules/comments/comments-06-types-of-speeds-of-gas-molecules.final.md</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-06-types-of-speeds-of-gas-molecules/comments/comments-06-types-of-speeds-of-gas-molecules.final.md</x:v>
       </x:c>
       <x:c r="O37" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -2313,7 +2330,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q37" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -2348,16 +2365,16 @@
         <x:v>comments-07-real-gas-and-ideal-gas-compressibility-factor-z</x:v>
       </x:c>
       <x:c r="K38" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-07-real-gas-and-ideal-gas-compressibility-factor-z</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-07-real-gas-and-ideal-gas-compressibility-factor-z</x:v>
       </x:c>
       <x:c r="L38" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-07-real-gas-and-ideal-gas-compressibility-factor-z/comments/comments-07-real-gas-and-ideal-gas-compressibility-factor-z.raw.json</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-07-real-gas-and-ideal-gas-compressibility-factor-z/comments/comments-07-real-gas-and-ideal-gas-compressibility-factor-z.raw.json</x:v>
       </x:c>
       <x:c r="M38" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-07-real-gas-and-ideal-gas-compressibility-factor-z/comments/comments-07-real-gas-and-ideal-gas-compressibility-factor-z.scrubbed.json</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-07-real-gas-and-ideal-gas-compressibility-factor-z/comments/comments-07-real-gas-and-ideal-gas-compressibility-factor-z.scrubbed.json</x:v>
       </x:c>
       <x:c r="N38" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-07-real-gas-and-ideal-gas-compressibility-factor-z/comments/comments-07-real-gas-and-ideal-gas-compressibility-factor-z.final.md</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-07-real-gas-and-ideal-gas-compressibility-factor-z/comments/comments-07-real-gas-and-ideal-gas-compressibility-factor-z.final.md</x:v>
       </x:c>
       <x:c r="O38" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -2366,7 +2383,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q38" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -2401,16 +2418,16 @@
         <x:v>comments-08-vander-waals-corrections</x:v>
       </x:c>
       <x:c r="K39" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-08-vander-waals-corrections</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-08-vander-waals-corrections</x:v>
       </x:c>
       <x:c r="L39" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-08-vander-waals-corrections/comments/comments-08-vander-waals-corrections.raw.json</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-08-vander-waals-corrections/comments/comments-08-vander-waals-corrections.raw.json</x:v>
       </x:c>
       <x:c r="M39" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-08-vander-waals-corrections/comments/comments-08-vander-waals-corrections.scrubbed.json</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-08-vander-waals-corrections/comments/comments-08-vander-waals-corrections.scrubbed.json</x:v>
       </x:c>
       <x:c r="N39" s="4" t="str">
-        <x:v>content/chemistry/physical/states-of-matter/lectures/lecture-08-vander-waals-corrections/comments/comments-08-vander-waals-corrections.final.md</x:v>
+        <x:v>content/01-physical/04-states-of-matter/lectures/lecture-08-vander-waals-corrections/comments/comments-08-vander-waals-corrections.final.md</x:v>
       </x:c>
       <x:c r="O39" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -2419,7 +2436,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q39" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -2433,13 +2450,13 @@
         <x:v>Chemical Thermodynamics</x:v>
       </x:c>
       <x:c r="D40" s="4" t="str">
-        <x:v>thermodynamics</x:v>
+        <x:v>chemical-thermodynamics</x:v>
       </x:c>
       <x:c r="E40" s="4" t="str">
         <x:v>01</x:v>
       </x:c>
       <x:c r="F40" s="4" t="str">
-        <x:v>thermodynamics-lecture-01</x:v>
+        <x:v>chemical-thermodynamics-lecture-01</x:v>
       </x:c>
       <x:c r="G40" s="4" t="str">
         <x:v>Reversible and Irreversible Process</x:v>
@@ -2454,16 +2471,16 @@
         <x:v>comments-01-reversible-and-irreversible-process</x:v>
       </x:c>
       <x:c r="K40" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-01-reversible-and-irreversible-process</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-01-reversible-and-irreversible-process</x:v>
       </x:c>
       <x:c r="L40" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-01-reversible-and-irreversible-process/comments/comments-01-reversible-and-irreversible-process.raw.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-01-reversible-and-irreversible-process/comments/comments-01-reversible-and-irreversible-process.raw.json</x:v>
       </x:c>
       <x:c r="M40" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-01-reversible-and-irreversible-process/comments/comments-01-reversible-and-irreversible-process.scrubbed.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-01-reversible-and-irreversible-process/comments/comments-01-reversible-and-irreversible-process.scrubbed.json</x:v>
       </x:c>
       <x:c r="N40" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-01-reversible-and-irreversible-process/comments/comments-01-reversible-and-irreversible-process.final.md</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-01-reversible-and-irreversible-process/comments/comments-01-reversible-and-irreversible-process.final.md</x:v>
       </x:c>
       <x:c r="O40" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -2472,7 +2489,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q40" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -2486,13 +2503,13 @@
         <x:v>Chemical Thermodynamics</x:v>
       </x:c>
       <x:c r="D41" s="4" t="str">
-        <x:v>thermodynamics</x:v>
+        <x:v>chemical-thermodynamics</x:v>
       </x:c>
       <x:c r="E41" s="4" t="str">
         <x:v>02</x:v>
       </x:c>
       <x:c r="F41" s="4" t="str">
-        <x:v>thermodynamics-lecture-02</x:v>
+        <x:v>chemical-thermodynamics-lecture-02</x:v>
       </x:c>
       <x:c r="G41" s="4" t="str">
         <x:v>Heat || Concept of Cp and Cv of a Gas</x:v>
@@ -2507,16 +2524,16 @@
         <x:v>comments-02-heat-concept-of-cp-and-cv-of-a-gas</x:v>
       </x:c>
       <x:c r="K41" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-02-heat-concept-of-cp-and-cv-of-a-gas</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-02-heat-concept-of-cp-and-cv-of-a-gas</x:v>
       </x:c>
       <x:c r="L41" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-02-heat-concept-of-cp-and-cv-of-a-gas/comments/comments-02-heat-concept-of-cp-and-cv-of-a-gas.raw.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-02-heat-concept-of-cp-and-cv-of-a-gas/comments/comments-02-heat-concept-of-cp-and-cv-of-a-gas.raw.json</x:v>
       </x:c>
       <x:c r="M41" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-02-heat-concept-of-cp-and-cv-of-a-gas/comments/comments-02-heat-concept-of-cp-and-cv-of-a-gas.scrubbed.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-02-heat-concept-of-cp-and-cv-of-a-gas/comments/comments-02-heat-concept-of-cp-and-cv-of-a-gas.scrubbed.json</x:v>
       </x:c>
       <x:c r="N41" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-02-heat-concept-of-cp-and-cv-of-a-gas/comments/comments-02-heat-concept-of-cp-and-cv-of-a-gas.final.md</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-02-heat-concept-of-cp-and-cv-of-a-gas/comments/comments-02-heat-concept-of-cp-and-cv-of-a-gas.final.md</x:v>
       </x:c>
       <x:c r="O41" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -2525,7 +2542,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q41" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -2539,13 +2556,13 @@
         <x:v>Chemical Thermodynamics</x:v>
       </x:c>
       <x:c r="D42" s="4" t="str">
-        <x:v>thermodynamics</x:v>
+        <x:v>chemical-thermodynamics</x:v>
       </x:c>
       <x:c r="E42" s="4" t="str">
         <x:v>03</x:v>
       </x:c>
       <x:c r="F42" s="4" t="str">
-        <x:v>thermodynamics-lecture-03</x:v>
+        <x:v>chemical-thermodynamics-lecture-03</x:v>
       </x:c>
       <x:c r="G42" s="4" t="str">
         <x:v>Work done on/by a Gas</x:v>
@@ -2560,16 +2577,16 @@
         <x:v>comments-03-work-done-on-by-a-gas</x:v>
       </x:c>
       <x:c r="K42" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-03-work-done-on-by-a-gas</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-03-work-done-on-by-a-gas</x:v>
       </x:c>
       <x:c r="L42" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-03-work-done-on-by-a-gas/comments/comments-03-work-done-on-by-a-gas.raw.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-03-work-done-on-by-a-gas/comments/comments-03-work-done-on-by-a-gas.raw.json</x:v>
       </x:c>
       <x:c r="M42" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-03-work-done-on-by-a-gas/comments/comments-03-work-done-on-by-a-gas.scrubbed.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-03-work-done-on-by-a-gas/comments/comments-03-work-done-on-by-a-gas.scrubbed.json</x:v>
       </x:c>
       <x:c r="N42" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-03-work-done-on-by-a-gas/comments/comments-03-work-done-on-by-a-gas.final.md</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-03-work-done-on-by-a-gas/comments/comments-03-work-done-on-by-a-gas.final.md</x:v>
       </x:c>
       <x:c r="O42" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -2578,7 +2595,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q42" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -2592,13 +2609,13 @@
         <x:v>Chemical Thermodynamics</x:v>
       </x:c>
       <x:c r="D43" s="4" t="str">
-        <x:v>thermodynamics</x:v>
+        <x:v>chemical-thermodynamics</x:v>
       </x:c>
       <x:c r="E43" s="4" t="str">
         <x:v>04</x:v>
       </x:c>
       <x:c r="F43" s="4" t="str">
-        <x:v>thermodynamics-lecture-04</x:v>
+        <x:v>chemical-thermodynamics-lecture-04</x:v>
       </x:c>
       <x:c r="G43" s="4" t="str">
         <x:v>Work done in Isothermal and Adiabatic Expansion of Gas</x:v>
@@ -2613,16 +2630,16 @@
         <x:v>comments-04-work-done-in-isothermal-and-adiabatic-expansion-of-gas</x:v>
       </x:c>
       <x:c r="K43" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-04-work-done-in-isothermal-and-adiabatic-expansion-of-gas</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-04-work-done-in-isothermal-and-adiabatic-expansion-of-gas</x:v>
       </x:c>
       <x:c r="L43" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-04-work-done-in-isothermal-and-adiabatic-expansion-of-gas/comments/comments-04-work-done-in-isothermal-and-adiabatic-expansion-of-gas.raw.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-04-work-done-in-isothermal-and-adiabatic-expansion-of-gas/comments/comments-04-work-done-in-isothermal-and-adiabatic-expansion-of-gas.raw.json</x:v>
       </x:c>
       <x:c r="M43" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-04-work-done-in-isothermal-and-adiabatic-expansion-of-gas/comments/comments-04-work-done-in-isothermal-and-adiabatic-expansion-of-gas.scrubbed.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-04-work-done-in-isothermal-and-adiabatic-expansion-of-gas/comments/comments-04-work-done-in-isothermal-and-adiabatic-expansion-of-gas.scrubbed.json</x:v>
       </x:c>
       <x:c r="N43" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-04-work-done-in-isothermal-and-adiabatic-expansion-of-gas/comments/comments-04-work-done-in-isothermal-and-adiabatic-expansion-of-gas.final.md</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-04-work-done-in-isothermal-and-adiabatic-expansion-of-gas/comments/comments-04-work-done-in-isothermal-and-adiabatic-expansion-of-gas.final.md</x:v>
       </x:c>
       <x:c r="O43" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -2631,7 +2648,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q43" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -2645,13 +2662,13 @@
         <x:v>Chemical Thermodynamics</x:v>
       </x:c>
       <x:c r="D44" s="4" t="str">
-        <x:v>thermodynamics</x:v>
+        <x:v>chemical-thermodynamics</x:v>
       </x:c>
       <x:c r="E44" s="4" t="str">
         <x:v>05</x:v>
       </x:c>
       <x:c r="F44" s="4" t="str">
-        <x:v>thermodynamics-lecture-05</x:v>
+        <x:v>chemical-thermodynamics-lecture-05</x:v>
       </x:c>
       <x:c r="G44" s="4" t="str">
         <x:v>First Law Of Thermodynamics</x:v>
@@ -2666,16 +2683,16 @@
         <x:v>comments-05-first-law-of-thermodynamics</x:v>
       </x:c>
       <x:c r="K44" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-05-first-law-of-thermodynamics</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-05-first-law-of-thermodynamics</x:v>
       </x:c>
       <x:c r="L44" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-05-first-law-of-thermodynamics/comments/comments-05-first-law-of-thermodynamics.raw.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-05-first-law-of-thermodynamics/comments/comments-05-first-law-of-thermodynamics.raw.json</x:v>
       </x:c>
       <x:c r="M44" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-05-first-law-of-thermodynamics/comments/comments-05-first-law-of-thermodynamics.scrubbed.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-05-first-law-of-thermodynamics/comments/comments-05-first-law-of-thermodynamics.scrubbed.json</x:v>
       </x:c>
       <x:c r="N44" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-05-first-law-of-thermodynamics/comments/comments-05-first-law-of-thermodynamics.final.md</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-05-first-law-of-thermodynamics/comments/comments-05-first-law-of-thermodynamics.final.md</x:v>
       </x:c>
       <x:c r="O44" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -2684,7 +2701,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q44" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -2698,13 +2715,13 @@
         <x:v>Chemical Thermodynamics</x:v>
       </x:c>
       <x:c r="D45" s="4" t="str">
-        <x:v>thermodynamics</x:v>
+        <x:v>chemical-thermodynamics</x:v>
       </x:c>
       <x:c r="E45" s="4" t="str">
         <x:v>06</x:v>
       </x:c>
       <x:c r="F45" s="4" t="str">
-        <x:v>thermodynamics-lecture-06</x:v>
+        <x:v>chemical-thermodynamics-lecture-06</x:v>
       </x:c>
       <x:c r="G45" s="4" t="str">
         <x:v>What is Enthalpy || Relation between Enthalpy and Internal Energy</x:v>
@@ -2719,16 +2736,16 @@
         <x:v>comments-06-what-is-enthalpy-relation-between-enthalpy-and-internal-energy</x:v>
       </x:c>
       <x:c r="K45" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-06-what-is-enthalpy-relation-between-enthalpy-and-internal-energy</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-06-what-is-enthalpy-relation-between-enthalpy-and-internal-energy</x:v>
       </x:c>
       <x:c r="L45" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-06-what-is-enthalpy-relation-between-enthalpy-and-internal-energy/comments/comments-06-what-is-enthalpy-relation-between-enthalpy-and-internal-energy.raw.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-06-what-is-enthalpy-relation-between-enthalpy-and-internal-energy/comments/comments-06-what-is-enthalpy-relation-between-enthalpy-and-internal-energy.raw.json</x:v>
       </x:c>
       <x:c r="M45" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-06-what-is-enthalpy-relation-between-enthalpy-and-internal-energy/comments/comments-06-what-is-enthalpy-relation-between-enthalpy-and-internal-energy.scrubbed.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-06-what-is-enthalpy-relation-between-enthalpy-and-internal-energy/comments/comments-06-what-is-enthalpy-relation-between-enthalpy-and-internal-energy.scrubbed.json</x:v>
       </x:c>
       <x:c r="N45" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-06-what-is-enthalpy-relation-between-enthalpy-and-internal-energy/comments/comments-06-what-is-enthalpy-relation-between-enthalpy-and-internal-energy.final.md</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-06-what-is-enthalpy-relation-between-enthalpy-and-internal-energy/comments/comments-06-what-is-enthalpy-relation-between-enthalpy-and-internal-energy.final.md</x:v>
       </x:c>
       <x:c r="O45" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -2737,7 +2754,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q45" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -2751,13 +2768,13 @@
         <x:v>Chemical Thermodynamics</x:v>
       </x:c>
       <x:c r="D46" s="4" t="str">
-        <x:v>thermodynamics</x:v>
+        <x:v>chemical-thermodynamics</x:v>
       </x:c>
       <x:c r="E46" s="4" t="str">
         <x:v>07</x:v>
       </x:c>
       <x:c r="F46" s="4" t="str">
-        <x:v>thermodynamics-lecture-07</x:v>
+        <x:v>chemical-thermodynamics-lecture-07</x:v>
       </x:c>
       <x:c r="G46" s="4" t="str">
         <x:v>Heat of Reaction | Enthalpy Of Formation || Enthalpy Of Combustion</x:v>
@@ -2772,16 +2789,16 @@
         <x:v>comments-07-heat-of-reaction-enthalpy-of-formation-enthalpy-of-combustion</x:v>
       </x:c>
       <x:c r="K46" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-07-heat-of-reaction-enthalpy-of-formation-enthalpy-of-combustion</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-07-heat-of-reaction-enthalpy-of-formation-enthalpy-of-combustion</x:v>
       </x:c>
       <x:c r="L46" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-07-heat-of-reaction-enthalpy-of-formation-enthalpy-of-combustion/comments/comments-07-heat-of-reaction-enthalpy-of-formation-enthalpy-of-combustion.raw.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-07-heat-of-reaction-enthalpy-of-formation-enthalpy-of-combustion/comments/comments-07-heat-of-reaction-enthalpy-of-formation-enthalpy-of-combustion.raw.json</x:v>
       </x:c>
       <x:c r="M46" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-07-heat-of-reaction-enthalpy-of-formation-enthalpy-of-combustion/comments/comments-07-heat-of-reaction-enthalpy-of-formation-enthalpy-of-combustion.scrubbed.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-07-heat-of-reaction-enthalpy-of-formation-enthalpy-of-combustion/comments/comments-07-heat-of-reaction-enthalpy-of-formation-enthalpy-of-combustion.scrubbed.json</x:v>
       </x:c>
       <x:c r="N46" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-07-heat-of-reaction-enthalpy-of-formation-enthalpy-of-combustion/comments/comments-07-heat-of-reaction-enthalpy-of-formation-enthalpy-of-combustion.final.md</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-07-heat-of-reaction-enthalpy-of-formation-enthalpy-of-combustion/comments/comments-07-heat-of-reaction-enthalpy-of-formation-enthalpy-of-combustion.final.md</x:v>
       </x:c>
       <x:c r="O46" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -2790,7 +2807,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q46" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -2804,13 +2821,13 @@
         <x:v>Chemical Thermodynamics</x:v>
       </x:c>
       <x:c r="D47" s="4" t="str">
-        <x:v>thermodynamics</x:v>
+        <x:v>chemical-thermodynamics</x:v>
       </x:c>
       <x:c r="E47" s="4" t="str">
         <x:v>08</x:v>
       </x:c>
       <x:c r="F47" s="4" t="str">
-        <x:v>thermodynamics-lecture-08</x:v>
+        <x:v>chemical-thermodynamics-lecture-08</x:v>
       </x:c>
       <x:c r="G47" s="4" t="str">
         <x:v>Hess's Law</x:v>
@@ -2825,16 +2842,16 @@
         <x:v>comments-08-hesss-law</x:v>
       </x:c>
       <x:c r="K47" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-08-hesss-law</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-08-hesss-law</x:v>
       </x:c>
       <x:c r="L47" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-08-hesss-law/comments/comments-08-hesss-law.raw.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-08-hesss-law/comments/comments-08-hesss-law.raw.json</x:v>
       </x:c>
       <x:c r="M47" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-08-hesss-law/comments/comments-08-hesss-law.scrubbed.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-08-hesss-law/comments/comments-08-hesss-law.scrubbed.json</x:v>
       </x:c>
       <x:c r="N47" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-08-hesss-law/comments/comments-08-hesss-law.final.md</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-08-hesss-law/comments/comments-08-hesss-law.final.md</x:v>
       </x:c>
       <x:c r="O47" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -2843,7 +2860,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q47" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -2857,13 +2874,13 @@
         <x:v>Chemical Thermodynamics</x:v>
       </x:c>
       <x:c r="D48" s="4" t="str">
-        <x:v>thermodynamics</x:v>
+        <x:v>chemical-thermodynamics</x:v>
       </x:c>
       <x:c r="E48" s="4" t="str">
         <x:v>09</x:v>
       </x:c>
       <x:c r="F48" s="4" t="str">
-        <x:v>thermodynamics-lecture-09</x:v>
+        <x:v>chemical-thermodynamics-lecture-09</x:v>
       </x:c>
       <x:c r="G48" s="4" t="str">
         <x:v>Second Law Of Thermodynamics Introduction</x:v>
@@ -2878,16 +2895,16 @@
         <x:v>comments-09-second-law-of-thermodynamics-introduction</x:v>
       </x:c>
       <x:c r="K48" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-09-second-law-of-thermodynamics-introduction</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-09-second-law-of-thermodynamics-introduction</x:v>
       </x:c>
       <x:c r="L48" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-09-second-law-of-thermodynamics-introduction/comments/comments-09-second-law-of-thermodynamics-introduction.raw.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-09-second-law-of-thermodynamics-introduction/comments/comments-09-second-law-of-thermodynamics-introduction.raw.json</x:v>
       </x:c>
       <x:c r="M48" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-09-second-law-of-thermodynamics-introduction/comments/comments-09-second-law-of-thermodynamics-introduction.scrubbed.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-09-second-law-of-thermodynamics-introduction/comments/comments-09-second-law-of-thermodynamics-introduction.scrubbed.json</x:v>
       </x:c>
       <x:c r="N48" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-09-second-law-of-thermodynamics-introduction/comments/comments-09-second-law-of-thermodynamics-introduction.final.md</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-09-second-law-of-thermodynamics-introduction/comments/comments-09-second-law-of-thermodynamics-introduction.final.md</x:v>
       </x:c>
       <x:c r="O48" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -2896,7 +2913,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q48" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -2910,13 +2927,13 @@
         <x:v>Chemical Thermodynamics</x:v>
       </x:c>
       <x:c r="D49" s="4" t="str">
-        <x:v>thermodynamics</x:v>
+        <x:v>chemical-thermodynamics</x:v>
       </x:c>
       <x:c r="E49" s="4" t="str">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F49" s="4" t="str">
-        <x:v>thermodynamics-lecture-10</x:v>
+        <x:v>chemical-thermodynamics-lecture-10</x:v>
       </x:c>
       <x:c r="G49" s="4" t="str">
         <x:v>What is ENTROPY ? || Spontaneity and Entropy</x:v>
@@ -2931,16 +2948,16 @@
         <x:v>comments-10-what-is-entropy-spontaneity-and-entropy</x:v>
       </x:c>
       <x:c r="K49" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-10-what-is-entropy-spontaneity-and-entropy</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-10-what-is-entropy-spontaneity-and-entropy</x:v>
       </x:c>
       <x:c r="L49" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-10-what-is-entropy-spontaneity-and-entropy/comments/comments-10-what-is-entropy-spontaneity-and-entropy.raw.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-10-what-is-entropy-spontaneity-and-entropy/comments/comments-10-what-is-entropy-spontaneity-and-entropy.raw.json</x:v>
       </x:c>
       <x:c r="M49" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-10-what-is-entropy-spontaneity-and-entropy/comments/comments-10-what-is-entropy-spontaneity-and-entropy.scrubbed.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-10-what-is-entropy-spontaneity-and-entropy/comments/comments-10-what-is-entropy-spontaneity-and-entropy.scrubbed.json</x:v>
       </x:c>
       <x:c r="N49" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-10-what-is-entropy-spontaneity-and-entropy/comments/comments-10-what-is-entropy-spontaneity-and-entropy.final.md</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-10-what-is-entropy-spontaneity-and-entropy/comments/comments-10-what-is-entropy-spontaneity-and-entropy.final.md</x:v>
       </x:c>
       <x:c r="O49" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -2949,7 +2966,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q49" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -2963,13 +2980,13 @@
         <x:v>Chemical Thermodynamics</x:v>
       </x:c>
       <x:c r="D50" s="4" t="str">
-        <x:v>thermodynamics</x:v>
+        <x:v>chemical-thermodynamics</x:v>
       </x:c>
       <x:c r="E50" s="4" t="str">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F50" s="4" t="str">
-        <x:v>thermodynamics-lecture-11</x:v>
+        <x:v>chemical-thermodynamics-lecture-11</x:v>
       </x:c>
       <x:c r="G50" s="4" t="str">
         <x:v>Entropy of different process | How to find Entropy</x:v>
@@ -2984,16 +3001,16 @@
         <x:v>comments-11-entropy-of-different-process-how-to-find-entropy</x:v>
       </x:c>
       <x:c r="K50" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-11-entropy-of-different-process-how-to-find-entropy</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-11-entropy-of-different-process-how-to-find-entropy</x:v>
       </x:c>
       <x:c r="L50" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-11-entropy-of-different-process-how-to-find-entropy/comments/comments-11-entropy-of-different-process-how-to-find-entropy.raw.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-11-entropy-of-different-process-how-to-find-entropy/comments/comments-11-entropy-of-different-process-how-to-find-entropy.raw.json</x:v>
       </x:c>
       <x:c r="M50" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-11-entropy-of-different-process-how-to-find-entropy/comments/comments-11-entropy-of-different-process-how-to-find-entropy.scrubbed.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-11-entropy-of-different-process-how-to-find-entropy/comments/comments-11-entropy-of-different-process-how-to-find-entropy.scrubbed.json</x:v>
       </x:c>
       <x:c r="N50" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-11-entropy-of-different-process-how-to-find-entropy/comments/comments-11-entropy-of-different-process-how-to-find-entropy.final.md</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-11-entropy-of-different-process-how-to-find-entropy/comments/comments-11-entropy-of-different-process-how-to-find-entropy.final.md</x:v>
       </x:c>
       <x:c r="O50" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -3002,7 +3019,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q50" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -3016,13 +3033,13 @@
         <x:v>Chemical Thermodynamics</x:v>
       </x:c>
       <x:c r="D51" s="4" t="str">
-        <x:v>thermodynamics</x:v>
+        <x:v>chemical-thermodynamics</x:v>
       </x:c>
       <x:c r="E51" s="4" t="str">
         <x:v>12</x:v>
       </x:c>
       <x:c r="F51" s="4" t="str">
-        <x:v>thermodynamics-lecture-12</x:v>
+        <x:v>chemical-thermodynamics-lecture-12</x:v>
       </x:c>
       <x:c r="G51" s="4" t="str">
         <x:v>Gibb's Free Energy</x:v>
@@ -3037,16 +3054,16 @@
         <x:v>comments-12-gibbs-free-energy</x:v>
       </x:c>
       <x:c r="K51" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-12-gibbs-free-energy</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-12-gibbs-free-energy</x:v>
       </x:c>
       <x:c r="L51" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-12-gibbs-free-energy/comments/comments-12-gibbs-free-energy.raw.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-12-gibbs-free-energy/comments/comments-12-gibbs-free-energy.raw.json</x:v>
       </x:c>
       <x:c r="M51" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-12-gibbs-free-energy/comments/comments-12-gibbs-free-energy.scrubbed.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-12-gibbs-free-energy/comments/comments-12-gibbs-free-energy.scrubbed.json</x:v>
       </x:c>
       <x:c r="N51" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-12-gibbs-free-energy/comments/comments-12-gibbs-free-energy.final.md</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-12-gibbs-free-energy/comments/comments-12-gibbs-free-energy.final.md</x:v>
       </x:c>
       <x:c r="O51" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -3055,7 +3072,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q51" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -3069,13 +3086,13 @@
         <x:v>Chemical Thermodynamics</x:v>
       </x:c>
       <x:c r="D52" s="4" t="str">
-        <x:v>thermodynamics</x:v>
+        <x:v>chemical-thermodynamics</x:v>
       </x:c>
       <x:c r="E52" s="4" t="str">
         <x:v>13</x:v>
       </x:c>
       <x:c r="F52" s="4" t="str">
-        <x:v>thermodynamics-lecture-13</x:v>
+        <x:v>chemical-thermodynamics-lecture-13</x:v>
       </x:c>
       <x:c r="G52" s="4" t="str">
         <x:v>Standard Gibb's Free Energy and Equilibrium Constant</x:v>
@@ -3090,16 +3107,16 @@
         <x:v>comments-13-standard-gibbs-free-energy-and-equilibrium-constant</x:v>
       </x:c>
       <x:c r="K52" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-13-standard-gibbs-free-energy-and-equilibrium-constant</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-13-standard-gibbs-free-energy-and-equilibrium-constant</x:v>
       </x:c>
       <x:c r="L52" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-13-standard-gibbs-free-energy-and-equilibrium-constant/comments/comments-13-standard-gibbs-free-energy-and-equilibrium-constant.raw.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-13-standard-gibbs-free-energy-and-equilibrium-constant/comments/comments-13-standard-gibbs-free-energy-and-equilibrium-constant.raw.json</x:v>
       </x:c>
       <x:c r="M52" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-13-standard-gibbs-free-energy-and-equilibrium-constant/comments/comments-13-standard-gibbs-free-energy-and-equilibrium-constant.scrubbed.json</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-13-standard-gibbs-free-energy-and-equilibrium-constant/comments/comments-13-standard-gibbs-free-energy-and-equilibrium-constant.scrubbed.json</x:v>
       </x:c>
       <x:c r="N52" s="4" t="str">
-        <x:v>content/chemistry/physical/thermodynamics/lectures/lecture-13-standard-gibbs-free-energy-and-equilibrium-constant/comments/comments-13-standard-gibbs-free-energy-and-equilibrium-constant.final.md</x:v>
+        <x:v>content/01-physical/05-chemical-thermodynamics/lectures/lecture-13-standard-gibbs-free-energy-and-equilibrium-constant/comments/comments-13-standard-gibbs-free-energy-and-equilibrium-constant.final.md</x:v>
       </x:c>
       <x:c r="O52" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -3108,7 +3125,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q52" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -3143,16 +3160,16 @@
         <x:v>comments-01-introduction-to-equilibrium</x:v>
       </x:c>
       <x:c r="K53" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-01-introduction-to-equilibrium</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-01-introduction-to-equilibrium</x:v>
       </x:c>
       <x:c r="L53" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-01-introduction-to-equilibrium/comments/comments-01-introduction-to-equilibrium.raw.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-01-introduction-to-equilibrium/comments/comments-01-introduction-to-equilibrium.raw.json</x:v>
       </x:c>
       <x:c r="M53" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-01-introduction-to-equilibrium/comments/comments-01-introduction-to-equilibrium.scrubbed.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-01-introduction-to-equilibrium/comments/comments-01-introduction-to-equilibrium.scrubbed.json</x:v>
       </x:c>
       <x:c r="N53" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-01-introduction-to-equilibrium/comments/comments-01-introduction-to-equilibrium.final.md</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-01-introduction-to-equilibrium/comments/comments-01-introduction-to-equilibrium.final.md</x:v>
       </x:c>
       <x:c r="O53" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -3161,7 +3178,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q53" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -3196,16 +3213,16 @@
         <x:v>comments-02-equilibrium-constant-kp-and-kc</x:v>
       </x:c>
       <x:c r="K54" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-02-equilibrium-constant-kp-and-kc</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-02-equilibrium-constant-kp-and-kc</x:v>
       </x:c>
       <x:c r="L54" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-02-equilibrium-constant-kp-and-kc/comments/comments-02-equilibrium-constant-kp-and-kc.raw.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-02-equilibrium-constant-kp-and-kc/comments/comments-02-equilibrium-constant-kp-and-kc.raw.json</x:v>
       </x:c>
       <x:c r="M54" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-02-equilibrium-constant-kp-and-kc/comments/comments-02-equilibrium-constant-kp-and-kc.scrubbed.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-02-equilibrium-constant-kp-and-kc/comments/comments-02-equilibrium-constant-kp-and-kc.scrubbed.json</x:v>
       </x:c>
       <x:c r="N54" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-02-equilibrium-constant-kp-and-kc/comments/comments-02-equilibrium-constant-kp-and-kc.final.md</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-02-equilibrium-constant-kp-and-kc/comments/comments-02-equilibrium-constant-kp-and-kc.final.md</x:v>
       </x:c>
       <x:c r="O54" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -3214,7 +3231,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q54" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -3249,16 +3266,16 @@
         <x:v>comments-03-law-of-chemical-equilibrium-numericals</x:v>
       </x:c>
       <x:c r="K55" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-03-law-of-chemical-equilibrium-numericals</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-03-law-of-chemical-equilibrium-numericals</x:v>
       </x:c>
       <x:c r="L55" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-03-law-of-chemical-equilibrium-numericals/comments/comments-03-law-of-chemical-equilibrium-numericals.raw.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-03-law-of-chemical-equilibrium-numericals/comments/comments-03-law-of-chemical-equilibrium-numericals.raw.json</x:v>
       </x:c>
       <x:c r="M55" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-03-law-of-chemical-equilibrium-numericals/comments/comments-03-law-of-chemical-equilibrium-numericals.scrubbed.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-03-law-of-chemical-equilibrium-numericals/comments/comments-03-law-of-chemical-equilibrium-numericals.scrubbed.json</x:v>
       </x:c>
       <x:c r="N55" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-03-law-of-chemical-equilibrium-numericals/comments/comments-03-law-of-chemical-equilibrium-numericals.final.md</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-03-law-of-chemical-equilibrium-numericals/comments/comments-03-law-of-chemical-equilibrium-numericals.final.md</x:v>
       </x:c>
       <x:c r="O55" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -3267,7 +3284,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q55" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -3302,16 +3319,16 @@
         <x:v>comments-04-degree-of-dissociation-and-observed-density</x:v>
       </x:c>
       <x:c r="K56" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-04-degree-of-dissociation-and-observed-density</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-04-degree-of-dissociation-and-observed-density</x:v>
       </x:c>
       <x:c r="L56" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-04-degree-of-dissociation-and-observed-density/comments/comments-04-degree-of-dissociation-and-observed-density.raw.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-04-degree-of-dissociation-and-observed-density/comments/comments-04-degree-of-dissociation-and-observed-density.raw.json</x:v>
       </x:c>
       <x:c r="M56" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-04-degree-of-dissociation-and-observed-density/comments/comments-04-degree-of-dissociation-and-observed-density.scrubbed.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-04-degree-of-dissociation-and-observed-density/comments/comments-04-degree-of-dissociation-and-observed-density.scrubbed.json</x:v>
       </x:c>
       <x:c r="N56" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-04-degree-of-dissociation-and-observed-density/comments/comments-04-degree-of-dissociation-and-observed-density.final.md</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-04-degree-of-dissociation-and-observed-density/comments/comments-04-degree-of-dissociation-and-observed-density.final.md</x:v>
       </x:c>
       <x:c r="O56" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -3320,7 +3337,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q56" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -3355,16 +3372,16 @@
         <x:v>comments-05-le-chateliers-principle</x:v>
       </x:c>
       <x:c r="K57" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-05-le-chateliers-principle</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-05-le-chateliers-principle</x:v>
       </x:c>
       <x:c r="L57" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-05-le-chateliers-principle/comments/comments-05-le-chateliers-principle.raw.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-05-le-chateliers-principle/comments/comments-05-le-chateliers-principle.raw.json</x:v>
       </x:c>
       <x:c r="M57" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-05-le-chateliers-principle/comments/comments-05-le-chateliers-principle.scrubbed.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-05-le-chateliers-principle/comments/comments-05-le-chateliers-principle.scrubbed.json</x:v>
       </x:c>
       <x:c r="N57" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-05-le-chateliers-principle/comments/comments-05-le-chateliers-principle.final.md</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-05-le-chateliers-principle/comments/comments-05-le-chateliers-principle.final.md</x:v>
       </x:c>
       <x:c r="O57" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -3373,7 +3390,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q57" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -3408,16 +3425,16 @@
         <x:v>comments-06-theories-of-acids-and-bases</x:v>
       </x:c>
       <x:c r="K58" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-06-theories-of-acids-and-bases</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-06-theories-of-acids-and-bases</x:v>
       </x:c>
       <x:c r="L58" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-06-theories-of-acids-and-bases/comments/comments-06-theories-of-acids-and-bases.raw.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-06-theories-of-acids-and-bases/comments/comments-06-theories-of-acids-and-bases.raw.json</x:v>
       </x:c>
       <x:c r="M58" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-06-theories-of-acids-and-bases/comments/comments-06-theories-of-acids-and-bases.scrubbed.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-06-theories-of-acids-and-bases/comments/comments-06-theories-of-acids-and-bases.scrubbed.json</x:v>
       </x:c>
       <x:c r="N58" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-06-theories-of-acids-and-bases/comments/comments-06-theories-of-acids-and-bases.final.md</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-06-theories-of-acids-and-bases/comments/comments-06-theories-of-acids-and-bases.final.md</x:v>
       </x:c>
       <x:c r="O58" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -3426,7 +3443,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q58" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -3461,16 +3478,16 @@
         <x:v>comments-07-ionisation-constant-of-weak-acid-and-base</x:v>
       </x:c>
       <x:c r="K59" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-07-ionisation-constant-of-weak-acid-and-base</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-07-ionisation-constant-of-weak-acid-and-base</x:v>
       </x:c>
       <x:c r="L59" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-07-ionisation-constant-of-weak-acid-and-base/comments/comments-07-ionisation-constant-of-weak-acid-and-base.raw.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-07-ionisation-constant-of-weak-acid-and-base/comments/comments-07-ionisation-constant-of-weak-acid-and-base.raw.json</x:v>
       </x:c>
       <x:c r="M59" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-07-ionisation-constant-of-weak-acid-and-base/comments/comments-07-ionisation-constant-of-weak-acid-and-base.scrubbed.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-07-ionisation-constant-of-weak-acid-and-base/comments/comments-07-ionisation-constant-of-weak-acid-and-base.scrubbed.json</x:v>
       </x:c>
       <x:c r="N59" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-07-ionisation-constant-of-weak-acid-and-base/comments/comments-07-ionisation-constant-of-weak-acid-and-base.final.md</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-07-ionisation-constant-of-weak-acid-and-base/comments/comments-07-ionisation-constant-of-weak-acid-and-base.final.md</x:v>
       </x:c>
       <x:c r="O59" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -3479,7 +3496,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q59" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -3514,16 +3531,16 @@
         <x:v>comments-08-ph-of-solutions-how-to-find-ph-how-to-calculate-ph-of-any-solution</x:v>
       </x:c>
       <x:c r="K60" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-08-ph-of-solutions-how-to-find-ph-how-to-calculate-ph-of-any-solution</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-08-ph-of-solutions-how-to-find-ph-how-to-calculate-ph-of-any-solution</x:v>
       </x:c>
       <x:c r="L60" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-08-ph-of-solutions-how-to-find-ph-how-to-calculate-ph-of-any-solution/comments/comments-08-ph-of-solutions-how-to-find-ph-how-to-calculate-ph-of-any-solution.raw.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-08-ph-of-solutions-how-to-find-ph-how-to-calculate-ph-of-any-solution/comments/comments-08-ph-of-solutions-how-to-find-ph-how-to-calculate-ph-of-any-solution.raw.json</x:v>
       </x:c>
       <x:c r="M60" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-08-ph-of-solutions-how-to-find-ph-how-to-calculate-ph-of-any-solution/comments/comments-08-ph-of-solutions-how-to-find-ph-how-to-calculate-ph-of-any-solution.scrubbed.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-08-ph-of-solutions-how-to-find-ph-how-to-calculate-ph-of-any-solution/comments/comments-08-ph-of-solutions-how-to-find-ph-how-to-calculate-ph-of-any-solution.scrubbed.json</x:v>
       </x:c>
       <x:c r="N60" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-08-ph-of-solutions-how-to-find-ph-how-to-calculate-ph-of-any-solution/comments/comments-08-ph-of-solutions-how-to-find-ph-how-to-calculate-ph-of-any-solution.final.md</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-08-ph-of-solutions-how-to-find-ph-how-to-calculate-ph-of-any-solution/comments/comments-08-ph-of-solutions-how-to-find-ph-how-to-calculate-ph-of-any-solution.final.md</x:v>
       </x:c>
       <x:c r="O60" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -3532,7 +3549,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q60" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -3567,16 +3584,16 @@
         <x:v>comments-09-common-ion-effect</x:v>
       </x:c>
       <x:c r="K61" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-09-common-ion-effect</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-09-common-ion-effect</x:v>
       </x:c>
       <x:c r="L61" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-09-common-ion-effect/comments/comments-09-common-ion-effect.raw.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-09-common-ion-effect/comments/comments-09-common-ion-effect.raw.json</x:v>
       </x:c>
       <x:c r="M61" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-09-common-ion-effect/comments/comments-09-common-ion-effect.scrubbed.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-09-common-ion-effect/comments/comments-09-common-ion-effect.scrubbed.json</x:v>
       </x:c>
       <x:c r="N61" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-09-common-ion-effect/comments/comments-09-common-ion-effect.final.md</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-09-common-ion-effect/comments/comments-09-common-ion-effect.final.md</x:v>
       </x:c>
       <x:c r="O61" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -3585,7 +3602,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q61" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -3620,16 +3637,16 @@
         <x:v>comments-10-buffer-solutions-part-1-of-2</x:v>
       </x:c>
       <x:c r="K62" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-10-buffer-solutions-part-1-of-2</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-10-buffer-solutions-part-1-of-2</x:v>
       </x:c>
       <x:c r="L62" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-10-buffer-solutions-part-1-of-2/comments/comments-10-buffer-solutions-part-1-of-2.raw.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-10-buffer-solutions-part-1-of-2/comments/comments-10-buffer-solutions-part-1-of-2.raw.json</x:v>
       </x:c>
       <x:c r="M62" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-10-buffer-solutions-part-1-of-2/comments/comments-10-buffer-solutions-part-1-of-2.scrubbed.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-10-buffer-solutions-part-1-of-2/comments/comments-10-buffer-solutions-part-1-of-2.scrubbed.json</x:v>
       </x:c>
       <x:c r="N62" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-10-buffer-solutions-part-1-of-2/comments/comments-10-buffer-solutions-part-1-of-2.final.md</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-10-buffer-solutions-part-1-of-2/comments/comments-10-buffer-solutions-part-1-of-2.final.md</x:v>
       </x:c>
       <x:c r="O62" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -3638,7 +3655,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q62" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -3673,16 +3690,16 @@
         <x:v>comments-11-buffer-solutions-part-2-of-2</x:v>
       </x:c>
       <x:c r="K63" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-11-buffer-solutions-part-2-of-2</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-11-buffer-solutions-part-2-of-2</x:v>
       </x:c>
       <x:c r="L63" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-11-buffer-solutions-part-2-of-2/comments/comments-11-buffer-solutions-part-2-of-2.raw.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-11-buffer-solutions-part-2-of-2/comments/comments-11-buffer-solutions-part-2-of-2.raw.json</x:v>
       </x:c>
       <x:c r="M63" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-11-buffer-solutions-part-2-of-2/comments/comments-11-buffer-solutions-part-2-of-2.scrubbed.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-11-buffer-solutions-part-2-of-2/comments/comments-11-buffer-solutions-part-2-of-2.scrubbed.json</x:v>
       </x:c>
       <x:c r="N63" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-11-buffer-solutions-part-2-of-2/comments/comments-11-buffer-solutions-part-2-of-2.final.md</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-11-buffer-solutions-part-2-of-2/comments/comments-11-buffer-solutions-part-2-of-2.final.md</x:v>
       </x:c>
       <x:c r="O63" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -3691,7 +3708,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q63" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -3726,16 +3743,16 @@
         <x:v>comments-12-salt-hydrolysis</x:v>
       </x:c>
       <x:c r="K64" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-12-salt-hydrolysis</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-12-salt-hydrolysis</x:v>
       </x:c>
       <x:c r="L64" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-12-salt-hydrolysis/comments/comments-12-salt-hydrolysis.raw.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-12-salt-hydrolysis/comments/comments-12-salt-hydrolysis.raw.json</x:v>
       </x:c>
       <x:c r="M64" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-12-salt-hydrolysis/comments/comments-12-salt-hydrolysis.scrubbed.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-12-salt-hydrolysis/comments/comments-12-salt-hydrolysis.scrubbed.json</x:v>
       </x:c>
       <x:c r="N64" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-12-salt-hydrolysis/comments/comments-12-salt-hydrolysis.final.md</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-12-salt-hydrolysis/comments/comments-12-salt-hydrolysis.final.md</x:v>
       </x:c>
       <x:c r="O64" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -3744,7 +3761,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q64" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -3779,16 +3796,16 @@
         <x:v>comments-13-solubility-and-solubility-product</x:v>
       </x:c>
       <x:c r="K65" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-13-solubility-and-solubility-product</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-13-solubility-and-solubility-product</x:v>
       </x:c>
       <x:c r="L65" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-13-solubility-and-solubility-product/comments/comments-13-solubility-and-solubility-product.raw.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-13-solubility-and-solubility-product/comments/comments-13-solubility-and-solubility-product.raw.json</x:v>
       </x:c>
       <x:c r="M65" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-13-solubility-and-solubility-product/comments/comments-13-solubility-and-solubility-product.scrubbed.json</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-13-solubility-and-solubility-product/comments/comments-13-solubility-and-solubility-product.scrubbed.json</x:v>
       </x:c>
       <x:c r="N65" s="4" t="str">
-        <x:v>content/chemistry/physical/equilibrium/lectures/lecture-13-solubility-and-solubility-product/comments/comments-13-solubility-and-solubility-product.final.md</x:v>
+        <x:v>content/01-physical/06-equilibrium/lectures/lecture-13-solubility-and-solubility-product/comments/comments-13-solubility-and-solubility-product.final.md</x:v>
       </x:c>
       <x:c r="O65" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -3797,7 +3814,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q65" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -3811,13 +3828,13 @@
         <x:v>Redox Reactions and Electrochemistry</x:v>
       </x:c>
       <x:c r="D66" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry</x:v>
+        <x:v>redox-reactions-and-electrochemistry</x:v>
       </x:c>
       <x:c r="E66" s="4" t="str">
         <x:v>01</x:v>
       </x:c>
       <x:c r="F66" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry-lecture-01</x:v>
+        <x:v>redox-reactions-and-electrochemistry-lecture-01</x:v>
       </x:c>
       <x:c r="G66" s="4" t="str">
         <x:v>How to Find Oxidation Number - Methods &amp; Tricks</x:v>
@@ -3832,16 +3849,16 @@
         <x:v>comments-01-how-to-find-oxidation-number-methods-and-tricks</x:v>
       </x:c>
       <x:c r="K66" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-01-how-to-find-oxidation-number-methods-and-tricks</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-01-how-to-find-oxidation-number-methods-and-tricks</x:v>
       </x:c>
       <x:c r="L66" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-01-how-to-find-oxidation-number-methods-and-tricks/comments/comments-01-how-to-find-oxidation-number-methods-and-tricks.raw.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-01-how-to-find-oxidation-number-methods-and-tricks/comments/comments-01-how-to-find-oxidation-number-methods-and-tricks.raw.json</x:v>
       </x:c>
       <x:c r="M66" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-01-how-to-find-oxidation-number-methods-and-tricks/comments/comments-01-how-to-find-oxidation-number-methods-and-tricks.scrubbed.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-01-how-to-find-oxidation-number-methods-and-tricks/comments/comments-01-how-to-find-oxidation-number-methods-and-tricks.scrubbed.json</x:v>
       </x:c>
       <x:c r="N66" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-01-how-to-find-oxidation-number-methods-and-tricks/comments/comments-01-how-to-find-oxidation-number-methods-and-tricks.final.md</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-01-how-to-find-oxidation-number-methods-and-tricks/comments/comments-01-how-to-find-oxidation-number-methods-and-tricks.final.md</x:v>
       </x:c>
       <x:c r="O66" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -3850,7 +3867,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q66" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -3864,13 +3881,13 @@
         <x:v>Redox Reactions and Electrochemistry</x:v>
       </x:c>
       <x:c r="D67" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry</x:v>
+        <x:v>redox-reactions-and-electrochemistry</x:v>
       </x:c>
       <x:c r="E67" s="4" t="str">
         <x:v>02</x:v>
       </x:c>
       <x:c r="F67" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry-lecture-02</x:v>
+        <x:v>redox-reactions-and-electrochemistry-lecture-02</x:v>
       </x:c>
       <x:c r="G67" s="4" t="str">
         <x:v>Oxidation and Reduction &amp; Types of Redox Reactions</x:v>
@@ -3885,16 +3902,16 @@
         <x:v>comments-02-oxidation-and-reduction-and-types-of-redox-reactions</x:v>
       </x:c>
       <x:c r="K67" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-02-oxidation-and-reduction-and-types-of-redox-reactions</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-02-oxidation-and-reduction-and-types-of-redox-reactions</x:v>
       </x:c>
       <x:c r="L67" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-02-oxidation-and-reduction-and-types-of-redox-reactions/comments/comments-02-oxidation-and-reduction-and-types-of-redox-reactions.raw.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-02-oxidation-and-reduction-and-types-of-redox-reactions/comments/comments-02-oxidation-and-reduction-and-types-of-redox-reactions.raw.json</x:v>
       </x:c>
       <x:c r="M67" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-02-oxidation-and-reduction-and-types-of-redox-reactions/comments/comments-02-oxidation-and-reduction-and-types-of-redox-reactions.scrubbed.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-02-oxidation-and-reduction-and-types-of-redox-reactions/comments/comments-02-oxidation-and-reduction-and-types-of-redox-reactions.scrubbed.json</x:v>
       </x:c>
       <x:c r="N67" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-02-oxidation-and-reduction-and-types-of-redox-reactions/comments/comments-02-oxidation-and-reduction-and-types-of-redox-reactions.final.md</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-02-oxidation-and-reduction-and-types-of-redox-reactions/comments/comments-02-oxidation-and-reduction-and-types-of-redox-reactions.final.md</x:v>
       </x:c>
       <x:c r="O67" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -3903,7 +3920,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q67" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -3917,13 +3934,13 @@
         <x:v>Redox Reactions and Electrochemistry</x:v>
       </x:c>
       <x:c r="D68" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry</x:v>
+        <x:v>redox-reactions-and-electrochemistry</x:v>
       </x:c>
       <x:c r="E68" s="4" t="str">
         <x:v>03</x:v>
       </x:c>
       <x:c r="F68" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry-lecture-03</x:v>
+        <x:v>redox-reactions-and-electrochemistry-lecture-03</x:v>
       </x:c>
       <x:c r="G68" s="4" t="str">
         <x:v>Balancing a Chemical Equation By Ion-Electron Method or Half Reaction Method</x:v>
@@ -3938,16 +3955,16 @@
         <x:v>comments-03-balancing-a-chemical-equation-by-ion-electron-method-or-half-reaction-method</x:v>
       </x:c>
       <x:c r="K68" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-03-balancing-a-chemical-equation-by-ion-electron-method-or-half-reaction-method</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-03-balancing-a-chemical-equation-by-ion-electron-method-or-half-reaction-method</x:v>
       </x:c>
       <x:c r="L68" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-03-balancing-a-chemical-equation-by-ion-electron-method-or-half-reaction-method/comments/comments-03-balancing-a-chemical-equation-by-ion-electron-method-or-half-reaction-method.raw.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-03-balancing-a-chemical-equation-by-ion-electron-method-or-half-reaction-method/comments/comments-03-balancing-a-chemical-equation-by-ion-electron-method-or-half-reaction-method.raw.json</x:v>
       </x:c>
       <x:c r="M68" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-03-balancing-a-chemical-equation-by-ion-electron-method-or-half-reaction-method/comments/comments-03-balancing-a-chemical-equation-by-ion-electron-method-or-half-reaction-method.scrubbed.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-03-balancing-a-chemical-equation-by-ion-electron-method-or-half-reaction-method/comments/comments-03-balancing-a-chemical-equation-by-ion-electron-method-or-half-reaction-method.scrubbed.json</x:v>
       </x:c>
       <x:c r="N68" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-03-balancing-a-chemical-equation-by-ion-electron-method-or-half-reaction-method/comments/comments-03-balancing-a-chemical-equation-by-ion-electron-method-or-half-reaction-method.final.md</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-03-balancing-a-chemical-equation-by-ion-electron-method-or-half-reaction-method/comments/comments-03-balancing-a-chemical-equation-by-ion-electron-method-or-half-reaction-method.final.md</x:v>
       </x:c>
       <x:c r="O68" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -3956,7 +3973,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q68" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -3970,13 +3987,13 @@
         <x:v>Redox Reactions and Electrochemistry</x:v>
       </x:c>
       <x:c r="D69" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry</x:v>
+        <x:v>redox-reactions-and-electrochemistry</x:v>
       </x:c>
       <x:c r="E69" s="4" t="str">
         <x:v>04</x:v>
       </x:c>
       <x:c r="F69" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry-lecture-04</x:v>
+        <x:v>redox-reactions-and-electrochemistry-lecture-04</x:v>
       </x:c>
       <x:c r="G69" s="4" t="str">
         <x:v>Balancing a Chemical Equation By Oxidation Number Method</x:v>
@@ -3991,16 +4008,16 @@
         <x:v>comments-04-balancing-a-chemical-equation-by-oxidation-number-method</x:v>
       </x:c>
       <x:c r="K69" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-04-balancing-a-chemical-equation-by-oxidation-number-method</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-04-balancing-a-chemical-equation-by-oxidation-number-method</x:v>
       </x:c>
       <x:c r="L69" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-04-balancing-a-chemical-equation-by-oxidation-number-method/comments/comments-04-balancing-a-chemical-equation-by-oxidation-number-method.raw.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-04-balancing-a-chemical-equation-by-oxidation-number-method/comments/comments-04-balancing-a-chemical-equation-by-oxidation-number-method.raw.json</x:v>
       </x:c>
       <x:c r="M69" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-04-balancing-a-chemical-equation-by-oxidation-number-method/comments/comments-04-balancing-a-chemical-equation-by-oxidation-number-method.scrubbed.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-04-balancing-a-chemical-equation-by-oxidation-number-method/comments/comments-04-balancing-a-chemical-equation-by-oxidation-number-method.scrubbed.json</x:v>
       </x:c>
       <x:c r="N69" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-04-balancing-a-chemical-equation-by-oxidation-number-method/comments/comments-04-balancing-a-chemical-equation-by-oxidation-number-method.final.md</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-04-balancing-a-chemical-equation-by-oxidation-number-method/comments/comments-04-balancing-a-chemical-equation-by-oxidation-number-method.final.md</x:v>
       </x:c>
       <x:c r="O69" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -4009,7 +4026,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q69" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -4023,13 +4040,13 @@
         <x:v>Redox Reactions and Electrochemistry</x:v>
       </x:c>
       <x:c r="D70" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry</x:v>
+        <x:v>redox-reactions-and-electrochemistry</x:v>
       </x:c>
       <x:c r="E70" s="4" t="str">
         <x:v>05</x:v>
       </x:c>
       <x:c r="F70" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry-lecture-05</x:v>
+        <x:v>redox-reactions-and-electrochemistry-lecture-05</x:v>
       </x:c>
       <x:c r="G70" s="4" t="str">
         <x:v>Daniell Cell - Electrochemical / Galvanic / Voltaic Cell</x:v>
@@ -4044,16 +4061,16 @@
         <x:v>comments-05-daniell-cell-electrochemical-galvanic-voltaic-cell</x:v>
       </x:c>
       <x:c r="K70" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-05-daniell-cell-electrochemical-galvanic-voltaic-cell</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-05-daniell-cell-electrochemical-galvanic-voltaic-cell</x:v>
       </x:c>
       <x:c r="L70" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-05-daniell-cell-electrochemical-galvanic-voltaic-cell/comments/comments-05-daniell-cell-electrochemical-galvanic-voltaic-cell.raw.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-05-daniell-cell-electrochemical-galvanic-voltaic-cell/comments/comments-05-daniell-cell-electrochemical-galvanic-voltaic-cell.raw.json</x:v>
       </x:c>
       <x:c r="M70" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-05-daniell-cell-electrochemical-galvanic-voltaic-cell/comments/comments-05-daniell-cell-electrochemical-galvanic-voltaic-cell.scrubbed.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-05-daniell-cell-electrochemical-galvanic-voltaic-cell/comments/comments-05-daniell-cell-electrochemical-galvanic-voltaic-cell.scrubbed.json</x:v>
       </x:c>
       <x:c r="N70" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-05-daniell-cell-electrochemical-galvanic-voltaic-cell/comments/comments-05-daniell-cell-electrochemical-galvanic-voltaic-cell.final.md</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-05-daniell-cell-electrochemical-galvanic-voltaic-cell/comments/comments-05-daniell-cell-electrochemical-galvanic-voltaic-cell.final.md</x:v>
       </x:c>
       <x:c r="O70" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -4062,7 +4079,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q70" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -4076,13 +4093,13 @@
         <x:v>Redox Reactions and Electrochemistry</x:v>
       </x:c>
       <x:c r="D71" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry</x:v>
+        <x:v>redox-reactions-and-electrochemistry</x:v>
       </x:c>
       <x:c r="E71" s="4" t="str">
         <x:v>06</x:v>
       </x:c>
       <x:c r="F71" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry-lecture-06</x:v>
+        <x:v>redox-reactions-and-electrochemistry-lecture-06</x:v>
       </x:c>
       <x:c r="G71" s="4" t="str">
         <x:v>Electrode Potential and EMF Of Cell - Basics</x:v>
@@ -4097,16 +4114,16 @@
         <x:v>comments-06-electrode-potential-and-emf-of-cell-basics</x:v>
       </x:c>
       <x:c r="K71" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-06-electrode-potential-and-emf-of-cell-basics</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-06-electrode-potential-and-emf-of-cell-basics</x:v>
       </x:c>
       <x:c r="L71" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-06-electrode-potential-and-emf-of-cell-basics/comments/comments-06-electrode-potential-and-emf-of-cell-basics.raw.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-06-electrode-potential-and-emf-of-cell-basics/comments/comments-06-electrode-potential-and-emf-of-cell-basics.raw.json</x:v>
       </x:c>
       <x:c r="M71" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-06-electrode-potential-and-emf-of-cell-basics/comments/comments-06-electrode-potential-and-emf-of-cell-basics.scrubbed.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-06-electrode-potential-and-emf-of-cell-basics/comments/comments-06-electrode-potential-and-emf-of-cell-basics.scrubbed.json</x:v>
       </x:c>
       <x:c r="N71" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-06-electrode-potential-and-emf-of-cell-basics/comments/comments-06-electrode-potential-and-emf-of-cell-basics.final.md</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-06-electrode-potential-and-emf-of-cell-basics/comments/comments-06-electrode-potential-and-emf-of-cell-basics.final.md</x:v>
       </x:c>
       <x:c r="O71" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -4115,7 +4132,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q71" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -4129,13 +4146,13 @@
         <x:v>Redox Reactions and Electrochemistry</x:v>
       </x:c>
       <x:c r="D72" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry</x:v>
+        <x:v>redox-reactions-and-electrochemistry</x:v>
       </x:c>
       <x:c r="E72" s="4" t="str">
         <x:v>07</x:v>
       </x:c>
       <x:c r="F72" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry-lecture-07</x:v>
+        <x:v>redox-reactions-and-electrochemistry-lecture-07</x:v>
       </x:c>
       <x:c r="G72" s="4" t="str">
         <x:v>NERNST Equation for Electrode Potential and EMF of Cell</x:v>
@@ -4150,16 +4167,16 @@
         <x:v>comments-07-nernst-equation-for-electrode-potential-and-emf-of-cell</x:v>
       </x:c>
       <x:c r="K72" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-07-nernst-equation-for-electrode-potential-and-emf-of-cell</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-07-nernst-equation-for-electrode-potential-and-emf-of-cell</x:v>
       </x:c>
       <x:c r="L72" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-07-nernst-equation-for-electrode-potential-and-emf-of-cell/comments/comments-07-nernst-equation-for-electrode-potential-and-emf-of-cell.raw.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-07-nernst-equation-for-electrode-potential-and-emf-of-cell/comments/comments-07-nernst-equation-for-electrode-potential-and-emf-of-cell.raw.json</x:v>
       </x:c>
       <x:c r="M72" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-07-nernst-equation-for-electrode-potential-and-emf-of-cell/comments/comments-07-nernst-equation-for-electrode-potential-and-emf-of-cell.scrubbed.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-07-nernst-equation-for-electrode-potential-and-emf-of-cell/comments/comments-07-nernst-equation-for-electrode-potential-and-emf-of-cell.scrubbed.json</x:v>
       </x:c>
       <x:c r="N72" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-07-nernst-equation-for-electrode-potential-and-emf-of-cell/comments/comments-07-nernst-equation-for-electrode-potential-and-emf-of-cell.final.md</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-07-nernst-equation-for-electrode-potential-and-emf-of-cell/comments/comments-07-nernst-equation-for-electrode-potential-and-emf-of-cell.final.md</x:v>
       </x:c>
       <x:c r="O72" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -4168,7 +4185,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q72" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -4182,13 +4199,13 @@
         <x:v>Redox Reactions and Electrochemistry</x:v>
       </x:c>
       <x:c r="D73" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry</x:v>
+        <x:v>redox-reactions-and-electrochemistry</x:v>
       </x:c>
       <x:c r="E73" s="4" t="str">
         <x:v>08</x:v>
       </x:c>
       <x:c r="F73" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry-lecture-08</x:v>
+        <x:v>redox-reactions-and-electrochemistry-lecture-08</x:v>
       </x:c>
       <x:c r="G73" s="4" t="str">
         <x:v>Standard Hydrogen Electrode (SHE): Theory and Numericals</x:v>
@@ -4203,16 +4220,16 @@
         <x:v>comments-08-standard-hydrogen-electrode-she-theory-and-numericals</x:v>
       </x:c>
       <x:c r="K73" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-08-standard-hydrogen-electrode-she-theory-and-numericals</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-08-standard-hydrogen-electrode-she-theory-and-numericals</x:v>
       </x:c>
       <x:c r="L73" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-08-standard-hydrogen-electrode-she-theory-and-numericals/comments/comments-08-standard-hydrogen-electrode-she-theory-and-numericals.raw.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-08-standard-hydrogen-electrode-she-theory-and-numericals/comments/comments-08-standard-hydrogen-electrode-she-theory-and-numericals.raw.json</x:v>
       </x:c>
       <x:c r="M73" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-08-standard-hydrogen-electrode-she-theory-and-numericals/comments/comments-08-standard-hydrogen-electrode-she-theory-and-numericals.scrubbed.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-08-standard-hydrogen-electrode-she-theory-and-numericals/comments/comments-08-standard-hydrogen-electrode-she-theory-and-numericals.scrubbed.json</x:v>
       </x:c>
       <x:c r="N73" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-08-standard-hydrogen-electrode-she-theory-and-numericals/comments/comments-08-standard-hydrogen-electrode-she-theory-and-numericals.final.md</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-08-standard-hydrogen-electrode-she-theory-and-numericals/comments/comments-08-standard-hydrogen-electrode-she-theory-and-numericals.final.md</x:v>
       </x:c>
       <x:c r="O73" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -4221,7 +4238,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q73" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -4235,13 +4252,13 @@
         <x:v>Redox Reactions and Electrochemistry</x:v>
       </x:c>
       <x:c r="D74" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry</x:v>
+        <x:v>redox-reactions-and-electrochemistry</x:v>
       </x:c>
       <x:c r="E74" s="4" t="str">
         <x:v>09</x:v>
       </x:c>
       <x:c r="F74" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry-lecture-09</x:v>
+        <x:v>redox-reactions-and-electrochemistry-lecture-09</x:v>
       </x:c>
       <x:c r="G74" s="4" t="str">
         <x:v>Electrochemical Series</x:v>
@@ -4256,16 +4273,16 @@
         <x:v>comments-09-electrochemical-series</x:v>
       </x:c>
       <x:c r="K74" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-09-electrochemical-series</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-09-electrochemical-series</x:v>
       </x:c>
       <x:c r="L74" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-09-electrochemical-series/comments/comments-09-electrochemical-series.raw.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-09-electrochemical-series/comments/comments-09-electrochemical-series.raw.json</x:v>
       </x:c>
       <x:c r="M74" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-09-electrochemical-series/comments/comments-09-electrochemical-series.scrubbed.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-09-electrochemical-series/comments/comments-09-electrochemical-series.scrubbed.json</x:v>
       </x:c>
       <x:c r="N74" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-09-electrochemical-series/comments/comments-09-electrochemical-series.final.md</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-09-electrochemical-series/comments/comments-09-electrochemical-series.final.md</x:v>
       </x:c>
       <x:c r="O74" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -4274,7 +4291,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q74" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -4288,13 +4305,13 @@
         <x:v>Redox Reactions and Electrochemistry</x:v>
       </x:c>
       <x:c r="D75" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry</x:v>
+        <x:v>redox-reactions-and-electrochemistry</x:v>
       </x:c>
       <x:c r="E75" s="4" t="str">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F75" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry-lecture-10</x:v>
+        <x:v>redox-reactions-and-electrochemistry-lecture-10</x:v>
       </x:c>
       <x:c r="G75" s="4" t="str">
         <x:v>Electrolysis OR Electrochemical Cell: Introduction - Product at Electrode</x:v>
@@ -4309,16 +4326,16 @@
         <x:v>comments-10-electrolysis-or-electrochemical-cell-introduction-product-at-electrode</x:v>
       </x:c>
       <x:c r="K75" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-10-electrolysis-or-electrochemical-cell-introduction-product-at-electrode</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-10-electrolysis-or-electrochemical-cell-introduction-product-at-electrode</x:v>
       </x:c>
       <x:c r="L75" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-10-electrolysis-or-electrochemical-cell-introduction-product-at-electrode/comments/comments-10-electrolysis-or-electrochemical-cell-introduction-product-at-electrode.raw.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-10-electrolysis-or-electrochemical-cell-introduction-product-at-electrode/comments/comments-10-electrolysis-or-electrochemical-cell-introduction-product-at-electrode.raw.json</x:v>
       </x:c>
       <x:c r="M75" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-10-electrolysis-or-electrochemical-cell-introduction-product-at-electrode/comments/comments-10-electrolysis-or-electrochemical-cell-introduction-product-at-electrode.scrubbed.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-10-electrolysis-or-electrochemical-cell-introduction-product-at-electrode/comments/comments-10-electrolysis-or-electrochemical-cell-introduction-product-at-electrode.scrubbed.json</x:v>
       </x:c>
       <x:c r="N75" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-10-electrolysis-or-electrochemical-cell-introduction-product-at-electrode/comments/comments-10-electrolysis-or-electrochemical-cell-introduction-product-at-electrode.final.md</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-10-electrolysis-or-electrochemical-cell-introduction-product-at-electrode/comments/comments-10-electrolysis-or-electrochemical-cell-introduction-product-at-electrode.final.md</x:v>
       </x:c>
       <x:c r="O75" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -4327,7 +4344,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q75" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -4341,13 +4358,13 @@
         <x:v>Redox Reactions and Electrochemistry</x:v>
       </x:c>
       <x:c r="D76" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry</x:v>
+        <x:v>redox-reactions-and-electrochemistry</x:v>
       </x:c>
       <x:c r="E76" s="4" t="str">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F76" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry-lecture-11</x:v>
+        <x:v>redox-reactions-and-electrochemistry-lecture-11</x:v>
       </x:c>
       <x:c r="G76" s="4" t="str">
         <x:v>Faraday's Laws Of Electrolysis</x:v>
@@ -4362,16 +4379,16 @@
         <x:v>comments-11-faradays-laws-of-electrolysis</x:v>
       </x:c>
       <x:c r="K76" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-11-faradays-laws-of-electrolysis</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-11-faradays-laws-of-electrolysis</x:v>
       </x:c>
       <x:c r="L76" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-11-faradays-laws-of-electrolysis/comments/comments-11-faradays-laws-of-electrolysis.raw.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-11-faradays-laws-of-electrolysis/comments/comments-11-faradays-laws-of-electrolysis.raw.json</x:v>
       </x:c>
       <x:c r="M76" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-11-faradays-laws-of-electrolysis/comments/comments-11-faradays-laws-of-electrolysis.scrubbed.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-11-faradays-laws-of-electrolysis/comments/comments-11-faradays-laws-of-electrolysis.scrubbed.json</x:v>
       </x:c>
       <x:c r="N76" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-11-faradays-laws-of-electrolysis/comments/comments-11-faradays-laws-of-electrolysis.final.md</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-11-faradays-laws-of-electrolysis/comments/comments-11-faradays-laws-of-electrolysis.final.md</x:v>
       </x:c>
       <x:c r="O76" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -4380,7 +4397,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q76" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -4394,13 +4411,13 @@
         <x:v>Redox Reactions and Electrochemistry</x:v>
       </x:c>
       <x:c r="D77" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry</x:v>
+        <x:v>redox-reactions-and-electrochemistry</x:v>
       </x:c>
       <x:c r="E77" s="4" t="str">
         <x:v>12</x:v>
       </x:c>
       <x:c r="F77" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry-lecture-12</x:v>
+        <x:v>redox-reactions-and-electrochemistry-lecture-12</x:v>
       </x:c>
       <x:c r="G77" s="4" t="str">
         <x:v>Electrolytic Conductance - Conductivity - Molar and Equivalent Conductivity</x:v>
@@ -4415,16 +4432,16 @@
         <x:v>comments-12-electrolytic-conductance-conductivity-molar-and-equivalent-conductivity</x:v>
       </x:c>
       <x:c r="K77" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-12-electrolytic-conductance-conductivity-molar-and-equivalent-conductivity</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-12-electrolytic-conductance-conductivity-molar-and-equivalent-conductivity</x:v>
       </x:c>
       <x:c r="L77" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-12-electrolytic-conductance-conductivity-molar-and-equivalent-conductivity/comments/comments-12-electrolytic-conductance-conductivity-molar-and-equivalent-conductivity.raw.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-12-electrolytic-conductance-conductivity-molar-and-equivalent-conductivity/comments/comments-12-electrolytic-conductance-conductivity-molar-and-equivalent-conductivity.raw.json</x:v>
       </x:c>
       <x:c r="M77" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-12-electrolytic-conductance-conductivity-molar-and-equivalent-conductivity/comments/comments-12-electrolytic-conductance-conductivity-molar-and-equivalent-conductivity.scrubbed.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-12-electrolytic-conductance-conductivity-molar-and-equivalent-conductivity/comments/comments-12-electrolytic-conductance-conductivity-molar-and-equivalent-conductivity.scrubbed.json</x:v>
       </x:c>
       <x:c r="N77" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-12-electrolytic-conductance-conductivity-molar-and-equivalent-conductivity/comments/comments-12-electrolytic-conductance-conductivity-molar-and-equivalent-conductivity.final.md</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-12-electrolytic-conductance-conductivity-molar-and-equivalent-conductivity/comments/comments-12-electrolytic-conductance-conductivity-molar-and-equivalent-conductivity.final.md</x:v>
       </x:c>
       <x:c r="O77" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -4433,7 +4450,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q77" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -4447,13 +4464,13 @@
         <x:v>Redox Reactions and Electrochemistry</x:v>
       </x:c>
       <x:c r="D78" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry</x:v>
+        <x:v>redox-reactions-and-electrochemistry</x:v>
       </x:c>
       <x:c r="E78" s="4" t="str">
         <x:v>13</x:v>
       </x:c>
       <x:c r="F78" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry-lecture-13</x:v>
+        <x:v>redox-reactions-and-electrochemistry-lecture-13</x:v>
       </x:c>
       <x:c r="G78" s="4" t="str">
         <x:v>Variation of Molar Conductivity with Concentration - KOHLRAUSCH'S LAW</x:v>
@@ -4468,16 +4485,16 @@
         <x:v>comments-13-variation-of-molar-conductivity-with-concentration-kohlrauschs-law</x:v>
       </x:c>
       <x:c r="K78" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-13-variation-of-molar-conductivity-with-concentration-kohlrauschs-law</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-13-variation-of-molar-conductivity-with-concentration-kohlrauschs-law</x:v>
       </x:c>
       <x:c r="L78" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-13-variation-of-molar-conductivity-with-concentration-kohlrauschs-law/comments/comments-13-variation-of-molar-conductivity-with-concentration-kohlrauschs-law.raw.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-13-variation-of-molar-conductivity-with-concentration-kohlrauschs-law/comments/comments-13-variation-of-molar-conductivity-with-concentration-kohlrauschs-law.raw.json</x:v>
       </x:c>
       <x:c r="M78" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-13-variation-of-molar-conductivity-with-concentration-kohlrauschs-law/comments/comments-13-variation-of-molar-conductivity-with-concentration-kohlrauschs-law.scrubbed.json</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-13-variation-of-molar-conductivity-with-concentration-kohlrauschs-law/comments/comments-13-variation-of-molar-conductivity-with-concentration-kohlrauschs-law.scrubbed.json</x:v>
       </x:c>
       <x:c r="N78" s="4" t="str">
-        <x:v>content/chemistry/physical/redox-reactions-electrochemistry/lectures/lecture-13-variation-of-molar-conductivity-with-concentration-kohlrauschs-law/comments/comments-13-variation-of-molar-conductivity-with-concentration-kohlrauschs-law.final.md</x:v>
+        <x:v>content/01-physical/07-redox-reactions-and-electrochemistry/lectures/lecture-13-variation-of-molar-conductivity-with-concentration-kohlrauschs-law/comments/comments-13-variation-of-molar-conductivity-with-concentration-kohlrauschs-law.final.md</x:v>
       </x:c>
       <x:c r="O78" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -4486,7 +4503,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q78" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -4521,16 +4538,16 @@
         <x:v>comments-01-solutions-01-ii-introduction-and-concentration-terms</x:v>
       </x:c>
       <x:c r="K79" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-01-solutions-01-ii-introduction-and-concentration-terms</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-01-solutions-01-ii-introduction-and-concentration-terms</x:v>
       </x:c>
       <x:c r="L79" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-01-solutions-01-ii-introduction-and-concentration-terms/comments/comments-01-solutions-01-ii-introduction-and-concentration-terms.raw.json</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-01-solutions-01-ii-introduction-and-concentration-terms/comments/comments-01-solutions-01-ii-introduction-and-concentration-terms.raw.json</x:v>
       </x:c>
       <x:c r="M79" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-01-solutions-01-ii-introduction-and-concentration-terms/comments/comments-01-solutions-01-ii-introduction-and-concentration-terms.scrubbed.json</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-01-solutions-01-ii-introduction-and-concentration-terms/comments/comments-01-solutions-01-ii-introduction-and-concentration-terms.scrubbed.json</x:v>
       </x:c>
       <x:c r="N79" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-01-solutions-01-ii-introduction-and-concentration-terms/comments/comments-01-solutions-01-ii-introduction-and-concentration-terms.final.md</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-01-solutions-01-ii-introduction-and-concentration-terms/comments/comments-01-solutions-01-ii-introduction-and-concentration-terms.final.md</x:v>
       </x:c>
       <x:c r="O79" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -4539,7 +4556,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q79" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -4574,16 +4591,16 @@
         <x:v>comments-02-vapour-pressure-of-solution-of-two-volatile-liquids-raoults-law</x:v>
       </x:c>
       <x:c r="K80" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-02-vapour-pressure-of-solution-of-two-volatile-liquids-raoults-law</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-02-vapour-pressure-of-solution-of-two-volatile-liquids-raoults-law</x:v>
       </x:c>
       <x:c r="L80" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-02-vapour-pressure-of-solution-of-two-volatile-liquids-raoults-law/comments/comments-02-vapour-pressure-of-solution-of-two-volatile-liquids-raoults-law.raw.json</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-02-vapour-pressure-of-solution-of-two-volatile-liquids-raoults-law/comments/comments-02-vapour-pressure-of-solution-of-two-volatile-liquids-raoults-law.raw.json</x:v>
       </x:c>
       <x:c r="M80" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-02-vapour-pressure-of-solution-of-two-volatile-liquids-raoults-law/comments/comments-02-vapour-pressure-of-solution-of-two-volatile-liquids-raoults-law.scrubbed.json</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-02-vapour-pressure-of-solution-of-two-volatile-liquids-raoults-law/comments/comments-02-vapour-pressure-of-solution-of-two-volatile-liquids-raoults-law.scrubbed.json</x:v>
       </x:c>
       <x:c r="N80" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-02-vapour-pressure-of-solution-of-two-volatile-liquids-raoults-law/comments/comments-02-vapour-pressure-of-solution-of-two-volatile-liquids-raoults-law.final.md</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-02-vapour-pressure-of-solution-of-two-volatile-liquids-raoults-law/comments/comments-02-vapour-pressure-of-solution-of-two-volatile-liquids-raoults-law.final.md</x:v>
       </x:c>
       <x:c r="O80" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -4592,7 +4609,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q80" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -4627,16 +4644,16 @@
         <x:v>comments-03-relative-lowering-of-vapour-pressure-due-to-non-volatile-solute-colligative-property</x:v>
       </x:c>
       <x:c r="K81" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-03-relative-lowering-of-vapour-pressure-due-to-non-volatile-solute-colligative-property</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-03-relative-lowering-of-vapour-pressure-due-to-non-volatile-solute-colligative-property</x:v>
       </x:c>
       <x:c r="L81" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-03-relative-lowering-of-vapour-pressure-due-to-non-volatile-solute-colligative-property/comments/comments-03-relative-lowering-of-vapour-pressure-due-to-non-volatile-solute-colligative-property.raw.json</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-03-relative-lowering-of-vapour-pressure-due-to-non-volatile-solute-colligative-property/comments/comments-03-relative-lowering-of-vapour-pressure-due-to-non-volatile-solute-colligative-property.raw.json</x:v>
       </x:c>
       <x:c r="M81" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-03-relative-lowering-of-vapour-pressure-due-to-non-volatile-solute-colligative-property/comments/comments-03-relative-lowering-of-vapour-pressure-due-to-non-volatile-solute-colligative-property.scrubbed.json</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-03-relative-lowering-of-vapour-pressure-due-to-non-volatile-solute-colligative-property/comments/comments-03-relative-lowering-of-vapour-pressure-due-to-non-volatile-solute-colligative-property.scrubbed.json</x:v>
       </x:c>
       <x:c r="N81" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-03-relative-lowering-of-vapour-pressure-due-to-non-volatile-solute-colligative-property/comments/comments-03-relative-lowering-of-vapour-pressure-due-to-non-volatile-solute-colligative-property.final.md</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-03-relative-lowering-of-vapour-pressure-due-to-non-volatile-solute-colligative-property/comments/comments-03-relative-lowering-of-vapour-pressure-due-to-non-volatile-solute-colligative-property.final.md</x:v>
       </x:c>
       <x:c r="O81" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -4645,7 +4662,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q81" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -4680,16 +4697,16 @@
         <x:v>comments-04-ideal-and-non-ideal-solutions-raoults-law-plus-ve-deviation-and-ve-deviation</x:v>
       </x:c>
       <x:c r="K82" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-04-ideal-and-non-ideal-solutions-raoults-law-plus-ve-deviation-and-ve-deviation</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-04-ideal-and-non-ideal-solutions-raoults-law-plus-ve-deviation-and-ve-deviation</x:v>
       </x:c>
       <x:c r="L82" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-04-ideal-and-non-ideal-solutions-raoults-law-plus-ve-deviation-and-ve-deviation/comments/comments-04-ideal-and-non-ideal-solutions-raoults-law-plus-ve-deviation-and-ve-deviation.raw.json</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-04-ideal-and-non-ideal-solutions-raoults-law-plus-ve-deviation-and-ve-deviation/comments/comments-04-ideal-and-non-ideal-solutions-raoults-law-plus-ve-deviation-and-ve-deviation.raw.json</x:v>
       </x:c>
       <x:c r="M82" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-04-ideal-and-non-ideal-solutions-raoults-law-plus-ve-deviation-and-ve-deviation/comments/comments-04-ideal-and-non-ideal-solutions-raoults-law-plus-ve-deviation-and-ve-deviation.scrubbed.json</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-04-ideal-and-non-ideal-solutions-raoults-law-plus-ve-deviation-and-ve-deviation/comments/comments-04-ideal-and-non-ideal-solutions-raoults-law-plus-ve-deviation-and-ve-deviation.scrubbed.json</x:v>
       </x:c>
       <x:c r="N82" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-04-ideal-and-non-ideal-solutions-raoults-law-plus-ve-deviation-and-ve-deviation/comments/comments-04-ideal-and-non-ideal-solutions-raoults-law-plus-ve-deviation-and-ve-deviation.final.md</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-04-ideal-and-non-ideal-solutions-raoults-law-plus-ve-deviation-and-ve-deviation/comments/comments-04-ideal-and-non-ideal-solutions-raoults-law-plus-ve-deviation-and-ve-deviation.final.md</x:v>
       </x:c>
       <x:c r="O82" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -4698,7 +4715,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q82" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -4733,16 +4750,16 @@
         <x:v>comments-05-colligative-property-elevation-in-boiling-point</x:v>
       </x:c>
       <x:c r="K83" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-05-colligative-property-elevation-in-boiling-point</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-05-colligative-property-elevation-in-boiling-point</x:v>
       </x:c>
       <x:c r="L83" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-05-colligative-property-elevation-in-boiling-point/comments/comments-05-colligative-property-elevation-in-boiling-point.raw.json</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-05-colligative-property-elevation-in-boiling-point/comments/comments-05-colligative-property-elevation-in-boiling-point.raw.json</x:v>
       </x:c>
       <x:c r="M83" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-05-colligative-property-elevation-in-boiling-point/comments/comments-05-colligative-property-elevation-in-boiling-point.scrubbed.json</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-05-colligative-property-elevation-in-boiling-point/comments/comments-05-colligative-property-elevation-in-boiling-point.scrubbed.json</x:v>
       </x:c>
       <x:c r="N83" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-05-colligative-property-elevation-in-boiling-point/comments/comments-05-colligative-property-elevation-in-boiling-point.final.md</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-05-colligative-property-elevation-in-boiling-point/comments/comments-05-colligative-property-elevation-in-boiling-point.final.md</x:v>
       </x:c>
       <x:c r="O83" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -4751,7 +4768,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q83" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -4786,16 +4803,16 @@
         <x:v>comments-06-colligative-property-depression-in-freezing-point</x:v>
       </x:c>
       <x:c r="K84" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-06-colligative-property-depression-in-freezing-point</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-06-colligative-property-depression-in-freezing-point</x:v>
       </x:c>
       <x:c r="L84" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-06-colligative-property-depression-in-freezing-point/comments/comments-06-colligative-property-depression-in-freezing-point.raw.json</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-06-colligative-property-depression-in-freezing-point/comments/comments-06-colligative-property-depression-in-freezing-point.raw.json</x:v>
       </x:c>
       <x:c r="M84" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-06-colligative-property-depression-in-freezing-point/comments/comments-06-colligative-property-depression-in-freezing-point.scrubbed.json</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-06-colligative-property-depression-in-freezing-point/comments/comments-06-colligative-property-depression-in-freezing-point.scrubbed.json</x:v>
       </x:c>
       <x:c r="N84" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-06-colligative-property-depression-in-freezing-point/comments/comments-06-colligative-property-depression-in-freezing-point.final.md</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-06-colligative-property-depression-in-freezing-point/comments/comments-06-colligative-property-depression-in-freezing-point.final.md</x:v>
       </x:c>
       <x:c r="O84" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -4804,7 +4821,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q84" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -4839,16 +4856,16 @@
         <x:v>comments-07-colligative-property-osmotic-pressure</x:v>
       </x:c>
       <x:c r="K85" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-07-colligative-property-osmotic-pressure</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-07-colligative-property-osmotic-pressure</x:v>
       </x:c>
       <x:c r="L85" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-07-colligative-property-osmotic-pressure/comments/comments-07-colligative-property-osmotic-pressure.raw.json</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-07-colligative-property-osmotic-pressure/comments/comments-07-colligative-property-osmotic-pressure.raw.json</x:v>
       </x:c>
       <x:c r="M85" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-07-colligative-property-osmotic-pressure/comments/comments-07-colligative-property-osmotic-pressure.scrubbed.json</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-07-colligative-property-osmotic-pressure/comments/comments-07-colligative-property-osmotic-pressure.scrubbed.json</x:v>
       </x:c>
       <x:c r="N85" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-07-colligative-property-osmotic-pressure/comments/comments-07-colligative-property-osmotic-pressure.final.md</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-07-colligative-property-osmotic-pressure/comments/comments-07-colligative-property-osmotic-pressure.final.md</x:v>
       </x:c>
       <x:c r="O85" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -4857,7 +4874,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q85" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -4892,16 +4909,16 @@
         <x:v>comments-08-vant-hoff-factor-and-abnormal-molar-masses</x:v>
       </x:c>
       <x:c r="K86" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-08-vant-hoff-factor-and-abnormal-molar-masses</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-08-vant-hoff-factor-and-abnormal-molar-masses</x:v>
       </x:c>
       <x:c r="L86" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-08-vant-hoff-factor-and-abnormal-molar-masses/comments/comments-08-vant-hoff-factor-and-abnormal-molar-masses.raw.json</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-08-vant-hoff-factor-and-abnormal-molar-masses/comments/comments-08-vant-hoff-factor-and-abnormal-molar-masses.raw.json</x:v>
       </x:c>
       <x:c r="M86" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-08-vant-hoff-factor-and-abnormal-molar-masses/comments/comments-08-vant-hoff-factor-and-abnormal-molar-masses.scrubbed.json</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-08-vant-hoff-factor-and-abnormal-molar-masses/comments/comments-08-vant-hoff-factor-and-abnormal-molar-masses.scrubbed.json</x:v>
       </x:c>
       <x:c r="N86" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-08-vant-hoff-factor-and-abnormal-molar-masses/comments/comments-08-vant-hoff-factor-and-abnormal-molar-masses.final.md</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-08-vant-hoff-factor-and-abnormal-molar-masses/comments/comments-08-vant-hoff-factor-and-abnormal-molar-masses.final.md</x:v>
       </x:c>
       <x:c r="O86" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -4910,7 +4927,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q86" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -4945,16 +4962,16 @@
         <x:v>comments-09-previous-year-iit-questions-on-colligative-properties</x:v>
       </x:c>
       <x:c r="K87" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-09-previous-year-iit-questions-on-colligative-properties</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-09-previous-year-iit-questions-on-colligative-properties</x:v>
       </x:c>
       <x:c r="L87" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-09-previous-year-iit-questions-on-colligative-properties/comments/comments-09-previous-year-iit-questions-on-colligative-properties.raw.json</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-09-previous-year-iit-questions-on-colligative-properties/comments/comments-09-previous-year-iit-questions-on-colligative-properties.raw.json</x:v>
       </x:c>
       <x:c r="M87" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-09-previous-year-iit-questions-on-colligative-properties/comments/comments-09-previous-year-iit-questions-on-colligative-properties.scrubbed.json</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-09-previous-year-iit-questions-on-colligative-properties/comments/comments-09-previous-year-iit-questions-on-colligative-properties.scrubbed.json</x:v>
       </x:c>
       <x:c r="N87" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-09-previous-year-iit-questions-on-colligative-properties/comments/comments-09-previous-year-iit-questions-on-colligative-properties.final.md</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-09-previous-year-iit-questions-on-colligative-properties/comments/comments-09-previous-year-iit-questions-on-colligative-properties.final.md</x:v>
       </x:c>
       <x:c r="O87" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -4963,7 +4980,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q87" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -4998,16 +5015,16 @@
         <x:v>comments-10-solubility-and-henrys-law</x:v>
       </x:c>
       <x:c r="K88" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-10-solubility-and-henrys-law</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-10-solubility-and-henrys-law</x:v>
       </x:c>
       <x:c r="L88" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-10-solubility-and-henrys-law/comments/comments-10-solubility-and-henrys-law.raw.json</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-10-solubility-and-henrys-law/comments/comments-10-solubility-and-henrys-law.raw.json</x:v>
       </x:c>
       <x:c r="M88" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-10-solubility-and-henrys-law/comments/comments-10-solubility-and-henrys-law.scrubbed.json</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-10-solubility-and-henrys-law/comments/comments-10-solubility-and-henrys-law.scrubbed.json</x:v>
       </x:c>
       <x:c r="N88" s="4" t="str">
-        <x:v>content/chemistry/physical/solutions/lectures/lecture-10-solubility-and-henrys-law/comments/comments-10-solubility-and-henrys-law.final.md</x:v>
+        <x:v>content/01-physical/08-solutions/lectures/lecture-10-solubility-and-henrys-law/comments/comments-10-solubility-and-henrys-law.final.md</x:v>
       </x:c>
       <x:c r="O88" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -5016,7 +5033,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q88" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -5051,16 +5068,16 @@
         <x:v>comments-01-introduction-rate-of-reaction</x:v>
       </x:c>
       <x:c r="K89" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-01-introduction-rate-of-reaction</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-01-introduction-rate-of-reaction</x:v>
       </x:c>
       <x:c r="L89" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-01-introduction-rate-of-reaction/comments/comments-01-introduction-rate-of-reaction.raw.json</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-01-introduction-rate-of-reaction/comments/comments-01-introduction-rate-of-reaction.raw.json</x:v>
       </x:c>
       <x:c r="M89" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-01-introduction-rate-of-reaction/comments/comments-01-introduction-rate-of-reaction.scrubbed.json</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-01-introduction-rate-of-reaction/comments/comments-01-introduction-rate-of-reaction.scrubbed.json</x:v>
       </x:c>
       <x:c r="N89" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-01-introduction-rate-of-reaction/comments/comments-01-introduction-rate-of-reaction.final.md</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-01-introduction-rate-of-reaction/comments/comments-01-introduction-rate-of-reaction.final.md</x:v>
       </x:c>
       <x:c r="O89" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -5069,7 +5086,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q89" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -5104,16 +5121,16 @@
         <x:v>comments-02-factors-affecting-rate-of-reaction-7-factors</x:v>
       </x:c>
       <x:c r="K90" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-02-factors-affecting-rate-of-reaction-7-factors</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-02-factors-affecting-rate-of-reaction-7-factors</x:v>
       </x:c>
       <x:c r="L90" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-02-factors-affecting-rate-of-reaction-7-factors/comments/comments-02-factors-affecting-rate-of-reaction-7-factors.raw.json</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-02-factors-affecting-rate-of-reaction-7-factors/comments/comments-02-factors-affecting-rate-of-reaction-7-factors.raw.json</x:v>
       </x:c>
       <x:c r="M90" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-02-factors-affecting-rate-of-reaction-7-factors/comments/comments-02-factors-affecting-rate-of-reaction-7-factors.scrubbed.json</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-02-factors-affecting-rate-of-reaction-7-factors/comments/comments-02-factors-affecting-rate-of-reaction-7-factors.scrubbed.json</x:v>
       </x:c>
       <x:c r="N90" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-02-factors-affecting-rate-of-reaction-7-factors/comments/comments-02-factors-affecting-rate-of-reaction-7-factors.final.md</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-02-factors-affecting-rate-of-reaction-7-factors/comments/comments-02-factors-affecting-rate-of-reaction-7-factors.final.md</x:v>
       </x:c>
       <x:c r="O90" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -5122,7 +5139,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q90" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -5157,16 +5174,16 @@
         <x:v>comments-03-rate-law-and-order-of-reaction</x:v>
       </x:c>
       <x:c r="K91" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-03-rate-law-and-order-of-reaction</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-03-rate-law-and-order-of-reaction</x:v>
       </x:c>
       <x:c r="L91" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-03-rate-law-and-order-of-reaction/comments/comments-03-rate-law-and-order-of-reaction.raw.json</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-03-rate-law-and-order-of-reaction/comments/comments-03-rate-law-and-order-of-reaction.raw.json</x:v>
       </x:c>
       <x:c r="M91" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-03-rate-law-and-order-of-reaction/comments/comments-03-rate-law-and-order-of-reaction.scrubbed.json</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-03-rate-law-and-order-of-reaction/comments/comments-03-rate-law-and-order-of-reaction.scrubbed.json</x:v>
       </x:c>
       <x:c r="N91" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-03-rate-law-and-order-of-reaction/comments/comments-03-rate-law-and-order-of-reaction.final.md</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-03-rate-law-and-order-of-reaction/comments/comments-03-rate-law-and-order-of-reaction.final.md</x:v>
       </x:c>
       <x:c r="O91" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -5175,7 +5192,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q91" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -5210,16 +5227,16 @@
         <x:v>comments-04-initial-rate-method-to-determine-order-of-reaction-and-rate-law</x:v>
       </x:c>
       <x:c r="K92" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-04-initial-rate-method-to-determine-order-of-reaction-and-rate-law</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-04-initial-rate-method-to-determine-order-of-reaction-and-rate-law</x:v>
       </x:c>
       <x:c r="L92" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-04-initial-rate-method-to-determine-order-of-reaction-and-rate-law/comments/comments-04-initial-rate-method-to-determine-order-of-reaction-and-rate-law.raw.json</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-04-initial-rate-method-to-determine-order-of-reaction-and-rate-law/comments/comments-04-initial-rate-method-to-determine-order-of-reaction-and-rate-law.raw.json</x:v>
       </x:c>
       <x:c r="M92" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-04-initial-rate-method-to-determine-order-of-reaction-and-rate-law/comments/comments-04-initial-rate-method-to-determine-order-of-reaction-and-rate-law.scrubbed.json</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-04-initial-rate-method-to-determine-order-of-reaction-and-rate-law/comments/comments-04-initial-rate-method-to-determine-order-of-reaction-and-rate-law.scrubbed.json</x:v>
       </x:c>
       <x:c r="N92" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-04-initial-rate-method-to-determine-order-of-reaction-and-rate-law/comments/comments-04-initial-rate-method-to-determine-order-of-reaction-and-rate-law.final.md</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-04-initial-rate-method-to-determine-order-of-reaction-and-rate-law/comments/comments-04-initial-rate-method-to-determine-order-of-reaction-and-rate-law.final.md</x:v>
       </x:c>
       <x:c r="O92" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -5228,7 +5245,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q92" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -5263,16 +5280,16 @@
         <x:v>comments-05-zero-order-kinetics-rate-law-and-half-life-of-zero-order</x:v>
       </x:c>
       <x:c r="K93" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-05-zero-order-kinetics-rate-law-and-half-life-of-zero-order</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-05-zero-order-kinetics-rate-law-and-half-life-of-zero-order</x:v>
       </x:c>
       <x:c r="L93" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-05-zero-order-kinetics-rate-law-and-half-life-of-zero-order/comments/comments-05-zero-order-kinetics-rate-law-and-half-life-of-zero-order.raw.json</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-05-zero-order-kinetics-rate-law-and-half-life-of-zero-order/comments/comments-05-zero-order-kinetics-rate-law-and-half-life-of-zero-order.raw.json</x:v>
       </x:c>
       <x:c r="M93" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-05-zero-order-kinetics-rate-law-and-half-life-of-zero-order/comments/comments-05-zero-order-kinetics-rate-law-and-half-life-of-zero-order.scrubbed.json</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-05-zero-order-kinetics-rate-law-and-half-life-of-zero-order/comments/comments-05-zero-order-kinetics-rate-law-and-half-life-of-zero-order.scrubbed.json</x:v>
       </x:c>
       <x:c r="N93" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-05-zero-order-kinetics-rate-law-and-half-life-of-zero-order/comments/comments-05-zero-order-kinetics-rate-law-and-half-life-of-zero-order.final.md</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-05-zero-order-kinetics-rate-law-and-half-life-of-zero-order/comments/comments-05-zero-order-kinetics-rate-law-and-half-life-of-zero-order.final.md</x:v>
       </x:c>
       <x:c r="O93" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -5281,7 +5298,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q93" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -5316,16 +5333,16 @@
         <x:v>comments-06-first-order-kinetics-complete-first-order-reaction</x:v>
       </x:c>
       <x:c r="K94" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-06-first-order-kinetics-complete-first-order-reaction</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-06-first-order-kinetics-complete-first-order-reaction</x:v>
       </x:c>
       <x:c r="L94" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-06-first-order-kinetics-complete-first-order-reaction/comments/comments-06-first-order-kinetics-complete-first-order-reaction.raw.json</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-06-first-order-kinetics-complete-first-order-reaction/comments/comments-06-first-order-kinetics-complete-first-order-reaction.raw.json</x:v>
       </x:c>
       <x:c r="M94" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-06-first-order-kinetics-complete-first-order-reaction/comments/comments-06-first-order-kinetics-complete-first-order-reaction.scrubbed.json</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-06-first-order-kinetics-complete-first-order-reaction/comments/comments-06-first-order-kinetics-complete-first-order-reaction.scrubbed.json</x:v>
       </x:c>
       <x:c r="N94" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-06-first-order-kinetics-complete-first-order-reaction/comments/comments-06-first-order-kinetics-complete-first-order-reaction.final.md</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-06-first-order-kinetics-complete-first-order-reaction/comments/comments-06-first-order-kinetics-complete-first-order-reaction.final.md</x:v>
       </x:c>
       <x:c r="O94" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -5334,7 +5351,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q94" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -5369,16 +5386,16 @@
         <x:v>comments-07-second-third-and-nth-order-reaction-and-kinetics-all-formulae</x:v>
       </x:c>
       <x:c r="K95" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-07-second-third-and-nth-order-reaction-and-kinetics-all-formulae</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-07-second-third-and-nth-order-reaction-and-kinetics-all-formulae</x:v>
       </x:c>
       <x:c r="L95" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-07-second-third-and-nth-order-reaction-and-kinetics-all-formulae/comments/comments-07-second-third-and-nth-order-reaction-and-kinetics-all-formulae.raw.json</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-07-second-third-and-nth-order-reaction-and-kinetics-all-formulae/comments/comments-07-second-third-and-nth-order-reaction-and-kinetics-all-formulae.raw.json</x:v>
       </x:c>
       <x:c r="M95" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-07-second-third-and-nth-order-reaction-and-kinetics-all-formulae/comments/comments-07-second-third-and-nth-order-reaction-and-kinetics-all-formulae.scrubbed.json</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-07-second-third-and-nth-order-reaction-and-kinetics-all-formulae/comments/comments-07-second-third-and-nth-order-reaction-and-kinetics-all-formulae.scrubbed.json</x:v>
       </x:c>
       <x:c r="N95" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-07-second-third-and-nth-order-reaction-and-kinetics-all-formulae/comments/comments-07-second-third-and-nth-order-reaction-and-kinetics-all-formulae.final.md</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-07-second-third-and-nth-order-reaction-and-kinetics-all-formulae/comments/comments-07-second-third-and-nth-order-reaction-and-kinetics-all-formulae.final.md</x:v>
       </x:c>
       <x:c r="O95" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -5387,7 +5404,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q95" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -5422,16 +5439,16 @@
         <x:v>comments-08-how-to-determine-order-of-reaction-half-life-method-and-other-methods</x:v>
       </x:c>
       <x:c r="K96" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-08-how-to-determine-order-of-reaction-half-life-method-and-other-methods</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-08-how-to-determine-order-of-reaction-half-life-method-and-other-methods</x:v>
       </x:c>
       <x:c r="L96" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-08-how-to-determine-order-of-reaction-half-life-method-and-other-methods/comments/comments-08-how-to-determine-order-of-reaction-half-life-method-and-other-methods.raw.json</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-08-how-to-determine-order-of-reaction-half-life-method-and-other-methods/comments/comments-08-how-to-determine-order-of-reaction-half-life-method-and-other-methods.raw.json</x:v>
       </x:c>
       <x:c r="M96" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-08-how-to-determine-order-of-reaction-half-life-method-and-other-methods/comments/comments-08-how-to-determine-order-of-reaction-half-life-method-and-other-methods.scrubbed.json</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-08-how-to-determine-order-of-reaction-half-life-method-and-other-methods/comments/comments-08-how-to-determine-order-of-reaction-half-life-method-and-other-methods.scrubbed.json</x:v>
       </x:c>
       <x:c r="N96" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-08-how-to-determine-order-of-reaction-half-life-method-and-other-methods/comments/comments-08-how-to-determine-order-of-reaction-half-life-method-and-other-methods.final.md</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-08-how-to-determine-order-of-reaction-half-life-method-and-other-methods/comments/comments-08-how-to-determine-order-of-reaction-half-life-method-and-other-methods.final.md</x:v>
       </x:c>
       <x:c r="O96" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -5440,7 +5457,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q96" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -5475,16 +5492,16 @@
         <x:v>comments-09-molecularity-of-reaction-pseudo-order-reaction-molecularity</x:v>
       </x:c>
       <x:c r="K97" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-09-molecularity-of-reaction-pseudo-order-reaction-molecularity</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-09-molecularity-of-reaction-pseudo-order-reaction-molecularity</x:v>
       </x:c>
       <x:c r="L97" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-09-molecularity-of-reaction-pseudo-order-reaction-molecularity/comments/comments-09-molecularity-of-reaction-pseudo-order-reaction-molecularity.raw.json</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-09-molecularity-of-reaction-pseudo-order-reaction-molecularity/comments/comments-09-molecularity-of-reaction-pseudo-order-reaction-molecularity.raw.json</x:v>
       </x:c>
       <x:c r="M97" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-09-molecularity-of-reaction-pseudo-order-reaction-molecularity/comments/comments-09-molecularity-of-reaction-pseudo-order-reaction-molecularity.scrubbed.json</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-09-molecularity-of-reaction-pseudo-order-reaction-molecularity/comments/comments-09-molecularity-of-reaction-pseudo-order-reaction-molecularity.scrubbed.json</x:v>
       </x:c>
       <x:c r="N97" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-09-molecularity-of-reaction-pseudo-order-reaction-molecularity/comments/comments-09-molecularity-of-reaction-pseudo-order-reaction-molecularity.final.md</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-09-molecularity-of-reaction-pseudo-order-reaction-molecularity/comments/comments-09-molecularity-of-reaction-pseudo-order-reaction-molecularity.final.md</x:v>
       </x:c>
       <x:c r="O97" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -5493,7 +5510,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q97" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -5528,16 +5545,16 @@
         <x:v>comments-10-arrhenius-equation-effect-of-temperature-on-rate-of-reaction</x:v>
       </x:c>
       <x:c r="K98" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-10-arrhenius-equation-effect-of-temperature-on-rate-of-reaction</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-10-arrhenius-equation-effect-of-temperature-on-rate-of-reaction</x:v>
       </x:c>
       <x:c r="L98" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-10-arrhenius-equation-effect-of-temperature-on-rate-of-reaction/comments/comments-10-arrhenius-equation-effect-of-temperature-on-rate-of-reaction.raw.json</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-10-arrhenius-equation-effect-of-temperature-on-rate-of-reaction/comments/comments-10-arrhenius-equation-effect-of-temperature-on-rate-of-reaction.raw.json</x:v>
       </x:c>
       <x:c r="M98" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-10-arrhenius-equation-effect-of-temperature-on-rate-of-reaction/comments/comments-10-arrhenius-equation-effect-of-temperature-on-rate-of-reaction.scrubbed.json</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-10-arrhenius-equation-effect-of-temperature-on-rate-of-reaction/comments/comments-10-arrhenius-equation-effect-of-temperature-on-rate-of-reaction.scrubbed.json</x:v>
       </x:c>
       <x:c r="N98" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-10-arrhenius-equation-effect-of-temperature-on-rate-of-reaction/comments/comments-10-arrhenius-equation-effect-of-temperature-on-rate-of-reaction.final.md</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-10-arrhenius-equation-effect-of-temperature-on-rate-of-reaction/comments/comments-10-arrhenius-equation-effect-of-temperature-on-rate-of-reaction.final.md</x:v>
       </x:c>
       <x:c r="O98" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -5546,7 +5563,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q98" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -5581,16 +5598,16 @@
         <x:v>comments-11-complex-reaction-mechanism-of-reaction-steady-state-approximation</x:v>
       </x:c>
       <x:c r="K99" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-11-complex-reaction-mechanism-of-reaction-steady-state-approximation</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-11-complex-reaction-mechanism-of-reaction-steady-state-approximation</x:v>
       </x:c>
       <x:c r="L99" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-11-complex-reaction-mechanism-of-reaction-steady-state-approximation/comments/comments-11-complex-reaction-mechanism-of-reaction-steady-state-approximation.raw.json</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-11-complex-reaction-mechanism-of-reaction-steady-state-approximation/comments/comments-11-complex-reaction-mechanism-of-reaction-steady-state-approximation.raw.json</x:v>
       </x:c>
       <x:c r="M99" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-11-complex-reaction-mechanism-of-reaction-steady-state-approximation/comments/comments-11-complex-reaction-mechanism-of-reaction-steady-state-approximation.scrubbed.json</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-11-complex-reaction-mechanism-of-reaction-steady-state-approximation/comments/comments-11-complex-reaction-mechanism-of-reaction-steady-state-approximation.scrubbed.json</x:v>
       </x:c>
       <x:c r="N99" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-11-complex-reaction-mechanism-of-reaction-steady-state-approximation/comments/comments-11-complex-reaction-mechanism-of-reaction-steady-state-approximation.final.md</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-11-complex-reaction-mechanism-of-reaction-steady-state-approximation/comments/comments-11-complex-reaction-mechanism-of-reaction-steady-state-approximation.final.md</x:v>
       </x:c>
       <x:c r="O99" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -5599,7 +5616,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q99" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -5634,16 +5651,16 @@
         <x:v>comments-12-parallel-first-order-reaction-kinetics</x:v>
       </x:c>
       <x:c r="K100" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-12-parallel-first-order-reaction-kinetics</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-12-parallel-first-order-reaction-kinetics</x:v>
       </x:c>
       <x:c r="L100" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-12-parallel-first-order-reaction-kinetics/comments/comments-12-parallel-first-order-reaction-kinetics.raw.json</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-12-parallel-first-order-reaction-kinetics/comments/comments-12-parallel-first-order-reaction-kinetics.raw.json</x:v>
       </x:c>
       <x:c r="M100" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-12-parallel-first-order-reaction-kinetics/comments/comments-12-parallel-first-order-reaction-kinetics.scrubbed.json</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-12-parallel-first-order-reaction-kinetics/comments/comments-12-parallel-first-order-reaction-kinetics.scrubbed.json</x:v>
       </x:c>
       <x:c r="N100" s="4" t="str">
-        <x:v>content/chemistry/physical/chemical-kinetics/lectures/lecture-12-parallel-first-order-reaction-kinetics/comments/comments-12-parallel-first-order-reaction-kinetics.final.md</x:v>
+        <x:v>content/01-physical/09-chemical-kinetics/lectures/lecture-12-parallel-first-order-reaction-kinetics/comments/comments-12-parallel-first-order-reaction-kinetics.final.md</x:v>
       </x:c>
       <x:c r="O100" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -5652,7 +5669,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q100" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -5687,16 +5704,16 @@
         <x:v>comments-01-historical-development</x:v>
       </x:c>
       <x:c r="K101" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-01-historical-development</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-01-historical-development</x:v>
       </x:c>
       <x:c r="L101" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-01-historical-development/comments/comments-01-historical-development.raw.json</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-01-historical-development/comments/comments-01-historical-development.raw.json</x:v>
       </x:c>
       <x:c r="M101" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-01-historical-development/comments/comments-01-historical-development.scrubbed.json</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-01-historical-development/comments/comments-01-historical-development.scrubbed.json</x:v>
       </x:c>
       <x:c r="N101" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-01-historical-development/comments/comments-01-historical-development.final.md</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-01-historical-development/comments/comments-01-historical-development.final.md</x:v>
       </x:c>
       <x:c r="O101" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -5705,7 +5722,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q101" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -5740,16 +5757,16 @@
         <x:v>comments-02-modern-periodic-table</x:v>
       </x:c>
       <x:c r="K102" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-02-modern-periodic-table</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-02-modern-periodic-table</x:v>
       </x:c>
       <x:c r="L102" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-02-modern-periodic-table/comments/comments-02-modern-periodic-table.raw.json</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-02-modern-periodic-table/comments/comments-02-modern-periodic-table.raw.json</x:v>
       </x:c>
       <x:c r="M102" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-02-modern-periodic-table/comments/comments-02-modern-periodic-table.scrubbed.json</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-02-modern-periodic-table/comments/comments-02-modern-periodic-table.scrubbed.json</x:v>
       </x:c>
       <x:c r="N102" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-02-modern-periodic-table/comments/comments-02-modern-periodic-table.final.md</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-02-modern-periodic-table/comments/comments-02-modern-periodic-table.final.md</x:v>
       </x:c>
       <x:c r="O102" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -5758,7 +5775,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q102" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -5793,16 +5810,16 @@
         <x:v>comments-03-how-to-find-group-period-and-block-of-any-element-spdf-trick</x:v>
       </x:c>
       <x:c r="K103" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-03-how-to-find-group-period-and-block-of-any-element-spdf-trick</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-03-how-to-find-group-period-and-block-of-any-element-spdf-trick</x:v>
       </x:c>
       <x:c r="L103" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-03-how-to-find-group-period-and-block-of-any-element-spdf-trick/comments/comments-03-how-to-find-group-period-and-block-of-any-element-spdf-trick.raw.json</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-03-how-to-find-group-period-and-block-of-any-element-spdf-trick/comments/comments-03-how-to-find-group-period-and-block-of-any-element-spdf-trick.raw.json</x:v>
       </x:c>
       <x:c r="M103" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-03-how-to-find-group-period-and-block-of-any-element-spdf-trick/comments/comments-03-how-to-find-group-period-and-block-of-any-element-spdf-trick.scrubbed.json</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-03-how-to-find-group-period-and-block-of-any-element-spdf-trick/comments/comments-03-how-to-find-group-period-and-block-of-any-element-spdf-trick.scrubbed.json</x:v>
       </x:c>
       <x:c r="N103" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-03-how-to-find-group-period-and-block-of-any-element-spdf-trick/comments/comments-03-how-to-find-group-period-and-block-of-any-element-spdf-trick.final.md</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-03-how-to-find-group-period-and-block-of-any-element-spdf-trick/comments/comments-03-how-to-find-group-period-and-block-of-any-element-spdf-trick.final.md</x:v>
       </x:c>
       <x:c r="O103" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -5811,7 +5828,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q103" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -5846,16 +5863,16 @@
         <x:v>comments-04-atomic-radius-ionic-radius-and-its-variation</x:v>
       </x:c>
       <x:c r="K104" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-04-atomic-radius-ionic-radius-and-its-variation</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-04-atomic-radius-ionic-radius-and-its-variation</x:v>
       </x:c>
       <x:c r="L104" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-04-atomic-radius-ionic-radius-and-its-variation/comments/comments-04-atomic-radius-ionic-radius-and-its-variation.raw.json</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-04-atomic-radius-ionic-radius-and-its-variation/comments/comments-04-atomic-radius-ionic-radius-and-its-variation.raw.json</x:v>
       </x:c>
       <x:c r="M104" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-04-atomic-radius-ionic-radius-and-its-variation/comments/comments-04-atomic-radius-ionic-radius-and-its-variation.scrubbed.json</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-04-atomic-radius-ionic-radius-and-its-variation/comments/comments-04-atomic-radius-ionic-radius-and-its-variation.scrubbed.json</x:v>
       </x:c>
       <x:c r="N104" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-04-atomic-radius-ionic-radius-and-its-variation/comments/comments-04-atomic-radius-ionic-radius-and-its-variation.final.md</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-04-atomic-radius-ionic-radius-and-its-variation/comments/comments-04-atomic-radius-ionic-radius-and-its-variation.final.md</x:v>
       </x:c>
       <x:c r="O104" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -5864,7 +5881,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q104" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -5899,16 +5916,16 @@
         <x:v>comments-05-ionization-energy-ionization-potential</x:v>
       </x:c>
       <x:c r="K105" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-05-ionization-energy-ionization-potential</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-05-ionization-energy-ionization-potential</x:v>
       </x:c>
       <x:c r="L105" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-05-ionization-energy-ionization-potential/comments/comments-05-ionization-energy-ionization-potential.raw.json</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-05-ionization-energy-ionization-potential/comments/comments-05-ionization-energy-ionization-potential.raw.json</x:v>
       </x:c>
       <x:c r="M105" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-05-ionization-energy-ionization-potential/comments/comments-05-ionization-energy-ionization-potential.scrubbed.json</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-05-ionization-energy-ionization-potential/comments/comments-05-ionization-energy-ionization-potential.scrubbed.json</x:v>
       </x:c>
       <x:c r="N105" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-05-ionization-energy-ionization-potential/comments/comments-05-ionization-energy-ionization-potential.final.md</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-05-ionization-energy-ionization-potential/comments/comments-05-ionization-energy-ionization-potential.final.md</x:v>
       </x:c>
       <x:c r="O105" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -5917,7 +5934,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q105" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -5952,16 +5969,16 @@
         <x:v>comments-06-electron-affinity-electron-gain-enthalpy</x:v>
       </x:c>
       <x:c r="K106" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-06-electron-affinity-electron-gain-enthalpy</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-06-electron-affinity-electron-gain-enthalpy</x:v>
       </x:c>
       <x:c r="L106" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-06-electron-affinity-electron-gain-enthalpy/comments/comments-06-electron-affinity-electron-gain-enthalpy.raw.json</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-06-electron-affinity-electron-gain-enthalpy/comments/comments-06-electron-affinity-electron-gain-enthalpy.raw.json</x:v>
       </x:c>
       <x:c r="M106" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-06-electron-affinity-electron-gain-enthalpy/comments/comments-06-electron-affinity-electron-gain-enthalpy.scrubbed.json</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-06-electron-affinity-electron-gain-enthalpy/comments/comments-06-electron-affinity-electron-gain-enthalpy.scrubbed.json</x:v>
       </x:c>
       <x:c r="N106" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-06-electron-affinity-electron-gain-enthalpy/comments/comments-06-electron-affinity-electron-gain-enthalpy.final.md</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-06-electron-affinity-electron-gain-enthalpy/comments/comments-06-electron-affinity-electron-gain-enthalpy.final.md</x:v>
       </x:c>
       <x:c r="O106" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -5970,7 +5987,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q106" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
@@ -6005,16 +6022,16 @@
         <x:v>comments-07-electronegativity</x:v>
       </x:c>
       <x:c r="K107" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-07-electronegativity</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-07-electronegativity</x:v>
       </x:c>
       <x:c r="L107" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-07-electronegativity/comments/comments-07-electronegativity.raw.json</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-07-electronegativity/comments/comments-07-electronegativity.raw.json</x:v>
       </x:c>
       <x:c r="M107" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-07-electronegativity/comments/comments-07-electronegativity.scrubbed.json</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-07-electronegativity/comments/comments-07-electronegativity.scrubbed.json</x:v>
       </x:c>
       <x:c r="N107" s="4" t="str">
-        <x:v>content/chemistry/inorganic/periodic-classification/lectures/lecture-07-electronegativity/comments/comments-07-electronegativity.final.md</x:v>
+        <x:v>content/02-inorganic/01-periodic-classification/lectures/lecture-07-electronegativity/comments/comments-07-electronegativity.final.md</x:v>
       </x:c>
       <x:c r="O107" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -6023,7 +6040,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q107" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -6058,16 +6075,16 @@
         <x:v>comments-01-p-block-elements</x:v>
       </x:c>
       <x:c r="K108" s="4" t="str">
-        <x:v>content/chemistry/inorganic/p-block-elements/lectures/lecture-01-p-block-elements</x:v>
+        <x:v>content/02-inorganic/02-p-block-elements/lectures/lecture-01-p-block-elements</x:v>
       </x:c>
       <x:c r="L108" s="4" t="str">
-        <x:v>content/chemistry/inorganic/p-block-elements/lectures/lecture-01-p-block-elements/comments/comments-01-p-block-elements.raw.json</x:v>
+        <x:v>content/02-inorganic/02-p-block-elements/lectures/lecture-01-p-block-elements/comments/comments-01-p-block-elements.raw.json</x:v>
       </x:c>
       <x:c r="M108" s="4" t="str">
-        <x:v>content/chemistry/inorganic/p-block-elements/lectures/lecture-01-p-block-elements/comments/comments-01-p-block-elements.scrubbed.json</x:v>
+        <x:v>content/02-inorganic/02-p-block-elements/lectures/lecture-01-p-block-elements/comments/comments-01-p-block-elements.scrubbed.json</x:v>
       </x:c>
       <x:c r="N108" s="4" t="str">
-        <x:v>content/chemistry/inorganic/p-block-elements/lectures/lecture-01-p-block-elements/comments/comments-01-p-block-elements.final.md</x:v>
+        <x:v>content/02-inorganic/02-p-block-elements/lectures/lecture-01-p-block-elements/comments/comments-01-p-block-elements.final.md</x:v>
       </x:c>
       <x:c r="O108" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -6076,7 +6093,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q108" s="4" t="str">
-        <x:v>One-shot/timestamped chapter collapsed from 33 same-video links.</x:v>
+        <x:v>One-shot/timestamped chapter collapsed from 33 same-video links. New one-shot lecture folder proposed.</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -6111,16 +6128,16 @@
         <x:v>comments-01-d-and-f-block-elements</x:v>
       </x:c>
       <x:c r="K109" s="4" t="str">
-        <x:v>content/chemistry/inorganic/d-and-f-block-elements/lectures/lecture-01-d-and-f-block-elements</x:v>
+        <x:v>content/02-inorganic/03-d-and-f-block-elements/lectures/lecture-01-d-and-f-block-elements</x:v>
       </x:c>
       <x:c r="L109" s="4" t="str">
-        <x:v>content/chemistry/inorganic/d-and-f-block-elements/lectures/lecture-01-d-and-f-block-elements/comments/comments-01-d-and-f-block-elements.raw.json</x:v>
+        <x:v>content/02-inorganic/03-d-and-f-block-elements/lectures/lecture-01-d-and-f-block-elements/comments/comments-01-d-and-f-block-elements.raw.json</x:v>
       </x:c>
       <x:c r="M109" s="4" t="str">
-        <x:v>content/chemistry/inorganic/d-and-f-block-elements/lectures/lecture-01-d-and-f-block-elements/comments/comments-01-d-and-f-block-elements.scrubbed.json</x:v>
+        <x:v>content/02-inorganic/03-d-and-f-block-elements/lectures/lecture-01-d-and-f-block-elements/comments/comments-01-d-and-f-block-elements.scrubbed.json</x:v>
       </x:c>
       <x:c r="N109" s="4" t="str">
-        <x:v>content/chemistry/inorganic/d-and-f-block-elements/lectures/lecture-01-d-and-f-block-elements/comments/comments-01-d-and-f-block-elements.final.md</x:v>
+        <x:v>content/02-inorganic/03-d-and-f-block-elements/lectures/lecture-01-d-and-f-block-elements/comments/comments-01-d-and-f-block-elements.final.md</x:v>
       </x:c>
       <x:c r="O109" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -6129,7 +6146,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q109" s="4" t="str">
-        <x:v>One-shot/timestamped chapter collapsed from 30 same-video links.</x:v>
+        <x:v>One-shot/timestamped chapter collapsed from 30 same-video links. New one-shot lecture folder proposed.</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -6164,16 +6181,16 @@
         <x:v>comments-01-coordination-compounds</x:v>
       </x:c>
       <x:c r="K110" s="4" t="str">
-        <x:v>content/chemistry/inorganic/coordination-compounds/lectures/lecture-01-coordination-compounds</x:v>
+        <x:v>content/02-inorganic/04-coordination-compounds/lectures/lecture-01-coordination-compounds</x:v>
       </x:c>
       <x:c r="L110" s="4" t="str">
-        <x:v>content/chemistry/inorganic/coordination-compounds/lectures/lecture-01-coordination-compounds/comments/comments-01-coordination-compounds.raw.json</x:v>
+        <x:v>content/02-inorganic/04-coordination-compounds/lectures/lecture-01-coordination-compounds/comments/comments-01-coordination-compounds.raw.json</x:v>
       </x:c>
       <x:c r="M110" s="4" t="str">
-        <x:v>content/chemistry/inorganic/coordination-compounds/lectures/lecture-01-coordination-compounds/comments/comments-01-coordination-compounds.scrubbed.json</x:v>
+        <x:v>content/02-inorganic/04-coordination-compounds/lectures/lecture-01-coordination-compounds/comments/comments-01-coordination-compounds.scrubbed.json</x:v>
       </x:c>
       <x:c r="N110" s="4" t="str">
-        <x:v>content/chemistry/inorganic/coordination-compounds/lectures/lecture-01-coordination-compounds/comments/comments-01-coordination-compounds.final.md</x:v>
+        <x:v>content/02-inorganic/04-coordination-compounds/lectures/lecture-01-coordination-compounds/comments/comments-01-coordination-compounds.final.md</x:v>
       </x:c>
       <x:c r="O110" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -6182,7 +6199,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q110" s="4" t="str">
-        <x:v>One-shot/timestamped chapter collapsed from 30 same-video links.</x:v>
+        <x:v>One-shot/timestamped chapter collapsed from 30 same-video links. New one-shot lecture folder proposed.</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -6196,13 +6213,13 @@
         <x:v>Organic Chemistry: IUPAC nomenclature</x:v>
       </x:c>
       <x:c r="D111" s="4" t="str">
-        <x:v>iupac</x:v>
+        <x:v>organic-chemistry-iupac-nomenclature</x:v>
       </x:c>
       <x:c r="E111" s="4" t="str">
         <x:v>01</x:v>
       </x:c>
       <x:c r="F111" s="4" t="str">
-        <x:v>iupac-lecture-01</x:v>
+        <x:v>organic-chemistry-iupac-nomenclature-lecture-01</x:v>
       </x:c>
       <x:c r="G111" s="4" t="str">
         <x:v>Some Basic Principles and Naming of Alkanes</x:v>
@@ -6217,16 +6234,16 @@
         <x:v>comments-01-some-basic-principles-and-naming-of-alkanes</x:v>
       </x:c>
       <x:c r="K111" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-01-some-basic-principles-and-naming-of-alkanes</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-01-some-basic-principles-and-naming-of-alkanes</x:v>
       </x:c>
       <x:c r="L111" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-01-some-basic-principles-and-naming-of-alkanes/comments/comments-01-some-basic-principles-and-naming-of-alkanes.raw.json</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-01-some-basic-principles-and-naming-of-alkanes/comments/comments-01-some-basic-principles-and-naming-of-alkanes.raw.json</x:v>
       </x:c>
       <x:c r="M111" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-01-some-basic-principles-and-naming-of-alkanes/comments/comments-01-some-basic-principles-and-naming-of-alkanes.scrubbed.json</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-01-some-basic-principles-and-naming-of-alkanes/comments/comments-01-some-basic-principles-and-naming-of-alkanes.scrubbed.json</x:v>
       </x:c>
       <x:c r="N111" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-01-some-basic-principles-and-naming-of-alkanes/comments/comments-01-some-basic-principles-and-naming-of-alkanes.final.md</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-01-some-basic-principles-and-naming-of-alkanes/comments/comments-01-some-basic-principles-and-naming-of-alkanes.final.md</x:v>
       </x:c>
       <x:c r="O111" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -6235,7 +6252,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q111" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -6249,13 +6266,13 @@
         <x:v>Organic Chemistry: IUPAC nomenclature</x:v>
       </x:c>
       <x:c r="D112" s="4" t="str">
-        <x:v>iupac</x:v>
+        <x:v>organic-chemistry-iupac-nomenclature</x:v>
       </x:c>
       <x:c r="E112" s="4" t="str">
         <x:v>02</x:v>
       </x:c>
       <x:c r="F112" s="4" t="str">
-        <x:v>iupac-lecture-02</x:v>
+        <x:v>organic-chemistry-iupac-nomenclature-lecture-02</x:v>
       </x:c>
       <x:c r="G112" s="4" t="str">
         <x:v>Complex Substituents and Cycloalkanes</x:v>
@@ -6270,16 +6287,16 @@
         <x:v>comments-02-complex-substituents-and-cycloalkanes</x:v>
       </x:c>
       <x:c r="K112" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-02-complex-substituents-and-cycloalkanes</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-02-complex-substituents-and-cycloalkanes</x:v>
       </x:c>
       <x:c r="L112" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-02-complex-substituents-and-cycloalkanes/comments/comments-02-complex-substituents-and-cycloalkanes.raw.json</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-02-complex-substituents-and-cycloalkanes/comments/comments-02-complex-substituents-and-cycloalkanes.raw.json</x:v>
       </x:c>
       <x:c r="M112" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-02-complex-substituents-and-cycloalkanes/comments/comments-02-complex-substituents-and-cycloalkanes.scrubbed.json</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-02-complex-substituents-and-cycloalkanes/comments/comments-02-complex-substituents-and-cycloalkanes.scrubbed.json</x:v>
       </x:c>
       <x:c r="N112" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-02-complex-substituents-and-cycloalkanes/comments/comments-02-complex-substituents-and-cycloalkanes.final.md</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-02-complex-substituents-and-cycloalkanes/comments/comments-02-complex-substituents-and-cycloalkanes.final.md</x:v>
       </x:c>
       <x:c r="O112" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -6288,7 +6305,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q112" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -6302,13 +6319,13 @@
         <x:v>Organic Chemistry: IUPAC nomenclature</x:v>
       </x:c>
       <x:c r="D113" s="4" t="str">
-        <x:v>iupac</x:v>
+        <x:v>organic-chemistry-iupac-nomenclature</x:v>
       </x:c>
       <x:c r="E113" s="4" t="str">
         <x:v>03</x:v>
       </x:c>
       <x:c r="F113" s="4" t="str">
-        <x:v>iupac-lecture-03</x:v>
+        <x:v>organic-chemistry-iupac-nomenclature-lecture-03</x:v>
       </x:c>
       <x:c r="G113" s="4" t="str">
         <x:v>Naming of Alkenes and Alkynes</x:v>
@@ -6323,16 +6340,16 @@
         <x:v>comments-03-naming-of-alkenes-and-alkynes</x:v>
       </x:c>
       <x:c r="K113" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-03-naming-of-alkenes-and-alkynes</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-03-naming-of-alkenes-and-alkynes</x:v>
       </x:c>
       <x:c r="L113" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-03-naming-of-alkenes-and-alkynes/comments/comments-03-naming-of-alkenes-and-alkynes.raw.json</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-03-naming-of-alkenes-and-alkynes/comments/comments-03-naming-of-alkenes-and-alkynes.raw.json</x:v>
       </x:c>
       <x:c r="M113" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-03-naming-of-alkenes-and-alkynes/comments/comments-03-naming-of-alkenes-and-alkynes.scrubbed.json</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-03-naming-of-alkenes-and-alkynes/comments/comments-03-naming-of-alkenes-and-alkynes.scrubbed.json</x:v>
       </x:c>
       <x:c r="N113" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-03-naming-of-alkenes-and-alkynes/comments/comments-03-naming-of-alkenes-and-alkynes.final.md</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-03-naming-of-alkenes-and-alkynes/comments/comments-03-naming-of-alkenes-and-alkynes.final.md</x:v>
       </x:c>
       <x:c r="O113" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -6341,7 +6358,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q113" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -6355,13 +6372,13 @@
         <x:v>Organic Chemistry: IUPAC nomenclature</x:v>
       </x:c>
       <x:c r="D114" s="4" t="str">
-        <x:v>iupac</x:v>
+        <x:v>organic-chemistry-iupac-nomenclature</x:v>
       </x:c>
       <x:c r="E114" s="4" t="str">
         <x:v>04</x:v>
       </x:c>
       <x:c r="F114" s="4" t="str">
-        <x:v>iupac-lecture-04</x:v>
+        <x:v>organic-chemistry-iupac-nomenclature-lecture-04</x:v>
       </x:c>
       <x:c r="G114" s="4" t="str">
         <x:v>Functional Groups with Secondary Suffix</x:v>
@@ -6376,16 +6393,16 @@
         <x:v>comments-04-functional-groups-with-secondary-suffix</x:v>
       </x:c>
       <x:c r="K114" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-04-functional-groups-with-secondary-suffix</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-04-functional-groups-with-secondary-suffix</x:v>
       </x:c>
       <x:c r="L114" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-04-functional-groups-with-secondary-suffix/comments/comments-04-functional-groups-with-secondary-suffix.raw.json</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-04-functional-groups-with-secondary-suffix/comments/comments-04-functional-groups-with-secondary-suffix.raw.json</x:v>
       </x:c>
       <x:c r="M114" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-04-functional-groups-with-secondary-suffix/comments/comments-04-functional-groups-with-secondary-suffix.scrubbed.json</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-04-functional-groups-with-secondary-suffix/comments/comments-04-functional-groups-with-secondary-suffix.scrubbed.json</x:v>
       </x:c>
       <x:c r="N114" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-04-functional-groups-with-secondary-suffix/comments/comments-04-functional-groups-with-secondary-suffix.final.md</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-04-functional-groups-with-secondary-suffix/comments/comments-04-functional-groups-with-secondary-suffix.final.md</x:v>
       </x:c>
       <x:c r="O114" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -6394,7 +6411,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q114" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -6408,13 +6425,13 @@
         <x:v>Organic Chemistry: IUPAC nomenclature</x:v>
       </x:c>
       <x:c r="D115" s="4" t="str">
-        <x:v>iupac</x:v>
+        <x:v>organic-chemistry-iupac-nomenclature</x:v>
       </x:c>
       <x:c r="E115" s="4" t="str">
         <x:v>05</x:v>
       </x:c>
       <x:c r="F115" s="4" t="str">
-        <x:v>iupac-lecture-05</x:v>
+        <x:v>organic-chemistry-iupac-nomenclature-lecture-05</x:v>
       </x:c>
       <x:c r="G115" s="4" t="str">
         <x:v>Naming of Alcohols</x:v>
@@ -6429,16 +6446,16 @@
         <x:v>comments-05-naming-of-alcohols</x:v>
       </x:c>
       <x:c r="K115" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-05-naming-of-alcohols</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-05-naming-of-alcohols</x:v>
       </x:c>
       <x:c r="L115" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-05-naming-of-alcohols/comments/comments-05-naming-of-alcohols.raw.json</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-05-naming-of-alcohols/comments/comments-05-naming-of-alcohols.raw.json</x:v>
       </x:c>
       <x:c r="M115" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-05-naming-of-alcohols/comments/comments-05-naming-of-alcohols.scrubbed.json</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-05-naming-of-alcohols/comments/comments-05-naming-of-alcohols.scrubbed.json</x:v>
       </x:c>
       <x:c r="N115" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-05-naming-of-alcohols/comments/comments-05-naming-of-alcohols.final.md</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-05-naming-of-alcohols/comments/comments-05-naming-of-alcohols.final.md</x:v>
       </x:c>
       <x:c r="O115" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -6447,7 +6464,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q115" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -6461,13 +6478,13 @@
         <x:v>Organic Chemistry: IUPAC nomenclature</x:v>
       </x:c>
       <x:c r="D116" s="4" t="str">
-        <x:v>iupac</x:v>
+        <x:v>organic-chemistry-iupac-nomenclature</x:v>
       </x:c>
       <x:c r="E116" s="4" t="str">
         <x:v>06</x:v>
       </x:c>
       <x:c r="F116" s="4" t="str">
-        <x:v>iupac-lecture-06</x:v>
+        <x:v>organic-chemistry-iupac-nomenclature-lecture-06</x:v>
       </x:c>
       <x:c r="G116" s="4" t="str">
         <x:v>Naming of Aldehydes and Ketones</x:v>
@@ -6482,16 +6499,16 @@
         <x:v>comments-06-naming-of-aldehydes-and-ketones</x:v>
       </x:c>
       <x:c r="K116" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-06-naming-of-aldehydes-and-ketones</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-06-naming-of-aldehydes-and-ketones</x:v>
       </x:c>
       <x:c r="L116" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-06-naming-of-aldehydes-and-ketones/comments/comments-06-naming-of-aldehydes-and-ketones.raw.json</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-06-naming-of-aldehydes-and-ketones/comments/comments-06-naming-of-aldehydes-and-ketones.raw.json</x:v>
       </x:c>
       <x:c r="M116" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-06-naming-of-aldehydes-and-ketones/comments/comments-06-naming-of-aldehydes-and-ketones.scrubbed.json</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-06-naming-of-aldehydes-and-ketones/comments/comments-06-naming-of-aldehydes-and-ketones.scrubbed.json</x:v>
       </x:c>
       <x:c r="N116" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-06-naming-of-aldehydes-and-ketones/comments/comments-06-naming-of-aldehydes-and-ketones.final.md</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-06-naming-of-aldehydes-and-ketones/comments/comments-06-naming-of-aldehydes-and-ketones.final.md</x:v>
       </x:c>
       <x:c r="O116" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -6500,7 +6517,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q116" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -6514,13 +6531,13 @@
         <x:v>Organic Chemistry: IUPAC nomenclature</x:v>
       </x:c>
       <x:c r="D117" s="4" t="str">
-        <x:v>iupac</x:v>
+        <x:v>organic-chemistry-iupac-nomenclature</x:v>
       </x:c>
       <x:c r="E117" s="4" t="str">
         <x:v>07</x:v>
       </x:c>
       <x:c r="F117" s="4" t="str">
-        <x:v>iupac-lecture-07</x:v>
+        <x:v>organic-chemistry-iupac-nomenclature-lecture-07</x:v>
       </x:c>
       <x:c r="G117" s="4" t="str">
         <x:v>Naming of Carboxylic Acid and Acid Halides</x:v>
@@ -6535,16 +6552,16 @@
         <x:v>comments-07-naming-of-carboxylic-acid-and-acid-halides</x:v>
       </x:c>
       <x:c r="K117" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-07-naming-of-carboxylic-acid-and-acid-halides</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-07-naming-of-carboxylic-acid-and-acid-halides</x:v>
       </x:c>
       <x:c r="L117" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-07-naming-of-carboxylic-acid-and-acid-halides/comments/comments-07-naming-of-carboxylic-acid-and-acid-halides.raw.json</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-07-naming-of-carboxylic-acid-and-acid-halides/comments/comments-07-naming-of-carboxylic-acid-and-acid-halides.raw.json</x:v>
       </x:c>
       <x:c r="M117" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-07-naming-of-carboxylic-acid-and-acid-halides/comments/comments-07-naming-of-carboxylic-acid-and-acid-halides.scrubbed.json</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-07-naming-of-carboxylic-acid-and-acid-halides/comments/comments-07-naming-of-carboxylic-acid-and-acid-halides.scrubbed.json</x:v>
       </x:c>
       <x:c r="N117" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-07-naming-of-carboxylic-acid-and-acid-halides/comments/comments-07-naming-of-carboxylic-acid-and-acid-halides.final.md</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-07-naming-of-carboxylic-acid-and-acid-halides/comments/comments-07-naming-of-carboxylic-acid-and-acid-halides.final.md</x:v>
       </x:c>
       <x:c r="O117" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -6553,7 +6570,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q117" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -6567,13 +6584,13 @@
         <x:v>Organic Chemistry: IUPAC nomenclature</x:v>
       </x:c>
       <x:c r="D118" s="4" t="str">
-        <x:v>iupac</x:v>
+        <x:v>organic-chemistry-iupac-nomenclature</x:v>
       </x:c>
       <x:c r="E118" s="4" t="str">
         <x:v>08</x:v>
       </x:c>
       <x:c r="F118" s="4" t="str">
-        <x:v>iupac-lecture-08</x:v>
+        <x:v>organic-chemistry-iupac-nomenclature-lecture-08</x:v>
       </x:c>
       <x:c r="G118" s="4" t="str">
         <x:v>Naming of Acid Amides and Esters</x:v>
@@ -6588,16 +6605,16 @@
         <x:v>comments-08-naming-of-acid-amides-and-esters</x:v>
       </x:c>
       <x:c r="K118" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-08-naming-of-acid-amides-and-esters</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-08-naming-of-acid-amides-and-esters</x:v>
       </x:c>
       <x:c r="L118" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-08-naming-of-acid-amides-and-esters/comments/comments-08-naming-of-acid-amides-and-esters.raw.json</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-08-naming-of-acid-amides-and-esters/comments/comments-08-naming-of-acid-amides-and-esters.raw.json</x:v>
       </x:c>
       <x:c r="M118" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-08-naming-of-acid-amides-and-esters/comments/comments-08-naming-of-acid-amides-and-esters.scrubbed.json</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-08-naming-of-acid-amides-and-esters/comments/comments-08-naming-of-acid-amides-and-esters.scrubbed.json</x:v>
       </x:c>
       <x:c r="N118" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-08-naming-of-acid-amides-and-esters/comments/comments-08-naming-of-acid-amides-and-esters.final.md</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-08-naming-of-acid-amides-and-esters/comments/comments-08-naming-of-acid-amides-and-esters.final.md</x:v>
       </x:c>
       <x:c r="O118" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -6606,7 +6623,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q118" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -6620,13 +6637,13 @@
         <x:v>Organic Chemistry: IUPAC nomenclature</x:v>
       </x:c>
       <x:c r="D119" s="4" t="str">
-        <x:v>iupac</x:v>
+        <x:v>organic-chemistry-iupac-nomenclature</x:v>
       </x:c>
       <x:c r="E119" s="4" t="str">
         <x:v>09</x:v>
       </x:c>
       <x:c r="F119" s="4" t="str">
-        <x:v>iupac-lecture-09</x:v>
+        <x:v>organic-chemistry-iupac-nomenclature-lecture-09</x:v>
       </x:c>
       <x:c r="G119" s="4" t="str">
         <x:v>Naming of Cyanides, Amines, and Ethers</x:v>
@@ -6641,16 +6658,16 @@
         <x:v>comments-09-naming-of-cyanides-amines-and-ethers</x:v>
       </x:c>
       <x:c r="K119" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-09-naming-of-cyanides-amines-and-ethers</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-09-naming-of-cyanides-amines-and-ethers</x:v>
       </x:c>
       <x:c r="L119" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-09-naming-of-cyanides-amines-and-ethers/comments/comments-09-naming-of-cyanides-amines-and-ethers.raw.json</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-09-naming-of-cyanides-amines-and-ethers/comments/comments-09-naming-of-cyanides-amines-and-ethers.raw.json</x:v>
       </x:c>
       <x:c r="M119" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-09-naming-of-cyanides-amines-and-ethers/comments/comments-09-naming-of-cyanides-amines-and-ethers.scrubbed.json</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-09-naming-of-cyanides-amines-and-ethers/comments/comments-09-naming-of-cyanides-amines-and-ethers.scrubbed.json</x:v>
       </x:c>
       <x:c r="N119" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-09-naming-of-cyanides-amines-and-ethers/comments/comments-09-naming-of-cyanides-amines-and-ethers.final.md</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-09-naming-of-cyanides-amines-and-ethers/comments/comments-09-naming-of-cyanides-amines-and-ethers.final.md</x:v>
       </x:c>
       <x:c r="O119" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -6659,7 +6676,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q119" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -6673,13 +6690,13 @@
         <x:v>Organic Chemistry: IUPAC nomenclature</x:v>
       </x:c>
       <x:c r="D120" s="4" t="str">
-        <x:v>iupac</x:v>
+        <x:v>organic-chemistry-iupac-nomenclature</x:v>
       </x:c>
       <x:c r="E120" s="4" t="str">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F120" s="4" t="str">
-        <x:v>iupac-lecture-10</x:v>
+        <x:v>organic-chemistry-iupac-nomenclature-lecture-10</x:v>
       </x:c>
       <x:c r="G120" s="4" t="str">
         <x:v>Naming of Polyfunctional Compounds</x:v>
@@ -6694,16 +6711,16 @@
         <x:v>comments-10-naming-of-polyfunctional-compounds</x:v>
       </x:c>
       <x:c r="K120" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-10-naming-of-polyfunctional-compounds</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-10-naming-of-polyfunctional-compounds</x:v>
       </x:c>
       <x:c r="L120" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-10-naming-of-polyfunctional-compounds/comments/comments-10-naming-of-polyfunctional-compounds.raw.json</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-10-naming-of-polyfunctional-compounds/comments/comments-10-naming-of-polyfunctional-compounds.raw.json</x:v>
       </x:c>
       <x:c r="M120" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-10-naming-of-polyfunctional-compounds/comments/comments-10-naming-of-polyfunctional-compounds.scrubbed.json</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-10-naming-of-polyfunctional-compounds/comments/comments-10-naming-of-polyfunctional-compounds.scrubbed.json</x:v>
       </x:c>
       <x:c r="N120" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-10-naming-of-polyfunctional-compounds/comments/comments-10-naming-of-polyfunctional-compounds.final.md</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-10-naming-of-polyfunctional-compounds/comments/comments-10-naming-of-polyfunctional-compounds.final.md</x:v>
       </x:c>
       <x:c r="O120" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -6712,7 +6729,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q120" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
@@ -6726,13 +6743,13 @@
         <x:v>Organic Chemistry: IUPAC nomenclature</x:v>
       </x:c>
       <x:c r="D121" s="4" t="str">
-        <x:v>iupac</x:v>
+        <x:v>organic-chemistry-iupac-nomenclature</x:v>
       </x:c>
       <x:c r="E121" s="4" t="str">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F121" s="4" t="str">
-        <x:v>iupac-lecture-11</x:v>
+        <x:v>organic-chemistry-iupac-nomenclature-lecture-11</x:v>
       </x:c>
       <x:c r="G121" s="4" t="str">
         <x:v>Naming of Aromatic Compounds - Benzene Rings</x:v>
@@ -6747,16 +6764,16 @@
         <x:v>comments-11-naming-of-aromatic-compounds-benzene-rings</x:v>
       </x:c>
       <x:c r="K121" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-11-naming-of-aromatic-compounds-benzene-rings</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-11-naming-of-aromatic-compounds-benzene-rings</x:v>
       </x:c>
       <x:c r="L121" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-11-naming-of-aromatic-compounds-benzene-rings/comments/comments-11-naming-of-aromatic-compounds-benzene-rings.raw.json</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-11-naming-of-aromatic-compounds-benzene-rings/comments/comments-11-naming-of-aromatic-compounds-benzene-rings.raw.json</x:v>
       </x:c>
       <x:c r="M121" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-11-naming-of-aromatic-compounds-benzene-rings/comments/comments-11-naming-of-aromatic-compounds-benzene-rings.scrubbed.json</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-11-naming-of-aromatic-compounds-benzene-rings/comments/comments-11-naming-of-aromatic-compounds-benzene-rings.scrubbed.json</x:v>
       </x:c>
       <x:c r="N121" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-11-naming-of-aromatic-compounds-benzene-rings/comments/comments-11-naming-of-aromatic-compounds-benzene-rings.final.md</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-11-naming-of-aromatic-compounds-benzene-rings/comments/comments-11-naming-of-aromatic-compounds-benzene-rings.final.md</x:v>
       </x:c>
       <x:c r="O121" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -6765,7 +6782,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q121" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
@@ -6779,13 +6796,13 @@
         <x:v>Organic Chemistry: IUPAC nomenclature</x:v>
       </x:c>
       <x:c r="D122" s="4" t="str">
-        <x:v>iupac</x:v>
+        <x:v>organic-chemistry-iupac-nomenclature</x:v>
       </x:c>
       <x:c r="E122" s="4" t="str">
         <x:v>12</x:v>
       </x:c>
       <x:c r="F122" s="4" t="str">
-        <x:v>iupac-lecture-12</x:v>
+        <x:v>organic-chemistry-iupac-nomenclature-lecture-12</x:v>
       </x:c>
       <x:c r="G122" s="4" t="str">
         <x:v>Naming of Bicyclo and Spiro Compounds</x:v>
@@ -6800,16 +6817,16 @@
         <x:v>comments-12-naming-of-bicyclo-and-spiro-compounds</x:v>
       </x:c>
       <x:c r="K122" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-12-naming-of-bicyclo-and-spiro-compounds</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-12-naming-of-bicyclo-and-spiro-compounds</x:v>
       </x:c>
       <x:c r="L122" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-12-naming-of-bicyclo-and-spiro-compounds/comments/comments-12-naming-of-bicyclo-and-spiro-compounds.raw.json</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-12-naming-of-bicyclo-and-spiro-compounds/comments/comments-12-naming-of-bicyclo-and-spiro-compounds.raw.json</x:v>
       </x:c>
       <x:c r="M122" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-12-naming-of-bicyclo-and-spiro-compounds/comments/comments-12-naming-of-bicyclo-and-spiro-compounds.scrubbed.json</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-12-naming-of-bicyclo-and-spiro-compounds/comments/comments-12-naming-of-bicyclo-and-spiro-compounds.scrubbed.json</x:v>
       </x:c>
       <x:c r="N122" s="4" t="str">
-        <x:v>content/chemistry/organic/iupac/lectures/lecture-12-naming-of-bicyclo-and-spiro-compounds/comments/comments-12-naming-of-bicyclo-and-spiro-compounds.final.md</x:v>
+        <x:v>content/03-organic/01-organic-chemistry-iupac-nomenclature/lectures/lecture-12-naming-of-bicyclo-and-spiro-compounds/comments/comments-12-naming-of-bicyclo-and-spiro-compounds.final.md</x:v>
       </x:c>
       <x:c r="O122" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -6818,7 +6835,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q122" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -6832,13 +6849,13 @@
         <x:v>Organic Chemistry: Isomerism</x:v>
       </x:c>
       <x:c r="D123" s="4" t="str">
-        <x:v>isomerism</x:v>
+        <x:v>organic-chemistry-isomerism</x:v>
       </x:c>
       <x:c r="E123" s="4" t="str">
         <x:v>01</x:v>
       </x:c>
       <x:c r="F123" s="4" t="str">
-        <x:v>isomerism-lecture-01</x:v>
+        <x:v>organic-chemistry-isomerism-lecture-01</x:v>
       </x:c>
       <x:c r="G123" s="4" t="str">
         <x:v>Introduction: Chain and Position Isomerism</x:v>
@@ -6853,16 +6870,16 @@
         <x:v>comments-01-introduction-chain-and-position-isomerism</x:v>
       </x:c>
       <x:c r="K123" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-01-introduction-chain-and-position-isomerism</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-01-introduction-chain-and-position-isomerism</x:v>
       </x:c>
       <x:c r="L123" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-01-introduction-chain-and-position-isomerism/comments/comments-01-introduction-chain-and-position-isomerism.raw.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-01-introduction-chain-and-position-isomerism/comments/comments-01-introduction-chain-and-position-isomerism.raw.json</x:v>
       </x:c>
       <x:c r="M123" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-01-introduction-chain-and-position-isomerism/comments/comments-01-introduction-chain-and-position-isomerism.scrubbed.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-01-introduction-chain-and-position-isomerism/comments/comments-01-introduction-chain-and-position-isomerism.scrubbed.json</x:v>
       </x:c>
       <x:c r="N123" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-01-introduction-chain-and-position-isomerism/comments/comments-01-introduction-chain-and-position-isomerism.final.md</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-01-introduction-chain-and-position-isomerism/comments/comments-01-introduction-chain-and-position-isomerism.final.md</x:v>
       </x:c>
       <x:c r="O123" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -6871,7 +6888,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q123" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="124">
@@ -6885,13 +6902,13 @@
         <x:v>Organic Chemistry: Isomerism</x:v>
       </x:c>
       <x:c r="D124" s="4" t="str">
-        <x:v>isomerism</x:v>
+        <x:v>organic-chemistry-isomerism</x:v>
       </x:c>
       <x:c r="E124" s="4" t="str">
         <x:v>02</x:v>
       </x:c>
       <x:c r="F124" s="4" t="str">
-        <x:v>isomerism-lecture-02</x:v>
+        <x:v>organic-chemistry-isomerism-lecture-02</x:v>
       </x:c>
       <x:c r="G124" s="4" t="str">
         <x:v>How to Find Total Structural Isomers</x:v>
@@ -6906,16 +6923,16 @@
         <x:v>comments-02-how-to-find-total-structural-isomers</x:v>
       </x:c>
       <x:c r="K124" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-02-how-to-find-total-structural-isomers</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-02-how-to-find-total-structural-isomers</x:v>
       </x:c>
       <x:c r="L124" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-02-how-to-find-total-structural-isomers/comments/comments-02-how-to-find-total-structural-isomers.raw.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-02-how-to-find-total-structural-isomers/comments/comments-02-how-to-find-total-structural-isomers.raw.json</x:v>
       </x:c>
       <x:c r="M124" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-02-how-to-find-total-structural-isomers/comments/comments-02-how-to-find-total-structural-isomers.scrubbed.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-02-how-to-find-total-structural-isomers/comments/comments-02-how-to-find-total-structural-isomers.scrubbed.json</x:v>
       </x:c>
       <x:c r="N124" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-02-how-to-find-total-structural-isomers/comments/comments-02-how-to-find-total-structural-isomers.final.md</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-02-how-to-find-total-structural-isomers/comments/comments-02-how-to-find-total-structural-isomers.final.md</x:v>
       </x:c>
       <x:c r="O124" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -6924,7 +6941,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q124" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="125">
@@ -6938,13 +6955,13 @@
         <x:v>Organic Chemistry: Isomerism</x:v>
       </x:c>
       <x:c r="D125" s="4" t="str">
-        <x:v>isomerism</x:v>
+        <x:v>organic-chemistry-isomerism</x:v>
       </x:c>
       <x:c r="E125" s="4" t="str">
         <x:v>03</x:v>
       </x:c>
       <x:c r="F125" s="4" t="str">
-        <x:v>isomerism-lecture-03</x:v>
+        <x:v>organic-chemistry-isomerism-lecture-03</x:v>
       </x:c>
       <x:c r="G125" s="4" t="str">
         <x:v>Functional Isomerism, Metamerism, Ring-Chain Isomerism</x:v>
@@ -6959,16 +6976,16 @@
         <x:v>comments-03-functional-isomerism-metamerism-ring-chain-isomerism</x:v>
       </x:c>
       <x:c r="K125" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-03-functional-isomerism-metamerism-ring-chain-isomerism</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-03-functional-isomerism-metamerism-ring-chain-isomerism</x:v>
       </x:c>
       <x:c r="L125" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-03-functional-isomerism-metamerism-ring-chain-isomerism/comments/comments-03-functional-isomerism-metamerism-ring-chain-isomerism.raw.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-03-functional-isomerism-metamerism-ring-chain-isomerism/comments/comments-03-functional-isomerism-metamerism-ring-chain-isomerism.raw.json</x:v>
       </x:c>
       <x:c r="M125" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-03-functional-isomerism-metamerism-ring-chain-isomerism/comments/comments-03-functional-isomerism-metamerism-ring-chain-isomerism.scrubbed.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-03-functional-isomerism-metamerism-ring-chain-isomerism/comments/comments-03-functional-isomerism-metamerism-ring-chain-isomerism.scrubbed.json</x:v>
       </x:c>
       <x:c r="N125" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-03-functional-isomerism-metamerism-ring-chain-isomerism/comments/comments-03-functional-isomerism-metamerism-ring-chain-isomerism.final.md</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-03-functional-isomerism-metamerism-ring-chain-isomerism/comments/comments-03-functional-isomerism-metamerism-ring-chain-isomerism.final.md</x:v>
       </x:c>
       <x:c r="O125" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -6977,7 +6994,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q125" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
@@ -6991,13 +7008,13 @@
         <x:v>Organic Chemistry: Isomerism</x:v>
       </x:c>
       <x:c r="D126" s="4" t="str">
-        <x:v>isomerism</x:v>
+        <x:v>organic-chemistry-isomerism</x:v>
       </x:c>
       <x:c r="E126" s="4" t="str">
         <x:v>04</x:v>
       </x:c>
       <x:c r="F126" s="4" t="str">
-        <x:v>isomerism-lecture-04</x:v>
+        <x:v>organic-chemistry-isomerism-lecture-04</x:v>
       </x:c>
       <x:c r="G126" s="4" t="str">
         <x:v>Tautomerism 01: Condition to Show Tautomerism and Special Cases</x:v>
@@ -7012,16 +7029,16 @@
         <x:v>comments-04-tautomerism-01-condition-to-show-tautomerism-and-special-cases</x:v>
       </x:c>
       <x:c r="K126" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-04-tautomerism-01-condition-to-show-tautomerism-and-special-cases</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-04-tautomerism-01-condition-to-show-tautomerism-and-special-cases</x:v>
       </x:c>
       <x:c r="L126" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-04-tautomerism-01-condition-to-show-tautomerism-and-special-cases/comments/comments-04-tautomerism-01-condition-to-show-tautomerism-and-special-cases.raw.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-04-tautomerism-01-condition-to-show-tautomerism-and-special-cases/comments/comments-04-tautomerism-01-condition-to-show-tautomerism-and-special-cases.raw.json</x:v>
       </x:c>
       <x:c r="M126" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-04-tautomerism-01-condition-to-show-tautomerism-and-special-cases/comments/comments-04-tautomerism-01-condition-to-show-tautomerism-and-special-cases.scrubbed.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-04-tautomerism-01-condition-to-show-tautomerism-and-special-cases/comments/comments-04-tautomerism-01-condition-to-show-tautomerism-and-special-cases.scrubbed.json</x:v>
       </x:c>
       <x:c r="N126" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-04-tautomerism-01-condition-to-show-tautomerism-and-special-cases/comments/comments-04-tautomerism-01-condition-to-show-tautomerism-and-special-cases.final.md</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-04-tautomerism-01-condition-to-show-tautomerism-and-special-cases/comments/comments-04-tautomerism-01-condition-to-show-tautomerism-and-special-cases.final.md</x:v>
       </x:c>
       <x:c r="O126" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -7030,7 +7047,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q126" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
@@ -7044,13 +7061,13 @@
         <x:v>Organic Chemistry: Isomerism</x:v>
       </x:c>
       <x:c r="D127" s="4" t="str">
-        <x:v>isomerism</x:v>
+        <x:v>organic-chemistry-isomerism</x:v>
       </x:c>
       <x:c r="E127" s="4" t="str">
         <x:v>05</x:v>
       </x:c>
       <x:c r="F127" s="4" t="str">
-        <x:v>isomerism-lecture-05</x:v>
+        <x:v>organic-chemistry-isomerism-lecture-05</x:v>
       </x:c>
       <x:c r="G127" s="4" t="str">
         <x:v>Tautomerism 02: Percentage of Enol Content &amp; Stability of Enol</x:v>
@@ -7065,16 +7082,16 @@
         <x:v>comments-05-tautomerism-02-percentage-of-enol-content-and-stability-of-enol</x:v>
       </x:c>
       <x:c r="K127" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-05-tautomerism-02-percentage-of-enol-content-and-stability-of-enol</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-05-tautomerism-02-percentage-of-enol-content-and-stability-of-enol</x:v>
       </x:c>
       <x:c r="L127" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-05-tautomerism-02-percentage-of-enol-content-and-stability-of-enol/comments/comments-05-tautomerism-02-percentage-of-enol-content-and-stability-of-enol.raw.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-05-tautomerism-02-percentage-of-enol-content-and-stability-of-enol/comments/comments-05-tautomerism-02-percentage-of-enol-content-and-stability-of-enol.raw.json</x:v>
       </x:c>
       <x:c r="M127" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-05-tautomerism-02-percentage-of-enol-content-and-stability-of-enol/comments/comments-05-tautomerism-02-percentage-of-enol-content-and-stability-of-enol.scrubbed.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-05-tautomerism-02-percentage-of-enol-content-and-stability-of-enol/comments/comments-05-tautomerism-02-percentage-of-enol-content-and-stability-of-enol.scrubbed.json</x:v>
       </x:c>
       <x:c r="N127" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-05-tautomerism-02-percentage-of-enol-content-and-stability-of-enol/comments/comments-05-tautomerism-02-percentage-of-enol-content-and-stability-of-enol.final.md</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-05-tautomerism-02-percentage-of-enol-content-and-stability-of-enol/comments/comments-05-tautomerism-02-percentage-of-enol-content-and-stability-of-enol.final.md</x:v>
       </x:c>
       <x:c r="O127" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -7083,7 +7100,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q127" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
@@ -7097,13 +7114,13 @@
         <x:v>Organic Chemistry: Isomerism</x:v>
       </x:c>
       <x:c r="D128" s="4" t="str">
-        <x:v>isomerism</x:v>
+        <x:v>organic-chemistry-isomerism</x:v>
       </x:c>
       <x:c r="E128" s="4" t="str">
         <x:v>06</x:v>
       </x:c>
       <x:c r="F128" s="4" t="str">
-        <x:v>isomerism-lecture-06</x:v>
+        <x:v>organic-chemistry-isomerism-lecture-06</x:v>
       </x:c>
       <x:c r="G128" s="4" t="str">
         <x:v>Stereoisomerism: Geometrical Isomers 01 | Cis-Trans / E-Z / Syn-Anti</x:v>
@@ -7118,16 +7135,16 @@
         <x:v>comments-06-stereoisomerism-geometrical-isomers-01-cis-trans-e-z-syn-anti</x:v>
       </x:c>
       <x:c r="K128" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-06-stereoisomerism-geometrical-isomers-01-cis-trans-e-z-syn-anti</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-06-stereoisomerism-geometrical-isomers-01-cis-trans-e-z-syn-anti</x:v>
       </x:c>
       <x:c r="L128" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-06-stereoisomerism-geometrical-isomers-01-cis-trans-e-z-syn-anti/comments/comments-06-stereoisomerism-geometrical-isomers-01-cis-trans-e-z-syn-anti.raw.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-06-stereoisomerism-geometrical-isomers-01-cis-trans-e-z-syn-anti/comments/comments-06-stereoisomerism-geometrical-isomers-01-cis-trans-e-z-syn-anti.raw.json</x:v>
       </x:c>
       <x:c r="M128" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-06-stereoisomerism-geometrical-isomers-01-cis-trans-e-z-syn-anti/comments/comments-06-stereoisomerism-geometrical-isomers-01-cis-trans-e-z-syn-anti.scrubbed.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-06-stereoisomerism-geometrical-isomers-01-cis-trans-e-z-syn-anti/comments/comments-06-stereoisomerism-geometrical-isomers-01-cis-trans-e-z-syn-anti.scrubbed.json</x:v>
       </x:c>
       <x:c r="N128" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-06-stereoisomerism-geometrical-isomers-01-cis-trans-e-z-syn-anti/comments/comments-06-stereoisomerism-geometrical-isomers-01-cis-trans-e-z-syn-anti.final.md</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-06-stereoisomerism-geometrical-isomers-01-cis-trans-e-z-syn-anti/comments/comments-06-stereoisomerism-geometrical-isomers-01-cis-trans-e-z-syn-anti.final.md</x:v>
       </x:c>
       <x:c r="O128" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -7136,7 +7153,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q128" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
@@ -7150,13 +7167,13 @@
         <x:v>Organic Chemistry: Isomerism</x:v>
       </x:c>
       <x:c r="D129" s="4" t="str">
-        <x:v>isomerism</x:v>
+        <x:v>organic-chemistry-isomerism</x:v>
       </x:c>
       <x:c r="E129" s="4" t="str">
         <x:v>07</x:v>
       </x:c>
       <x:c r="F129" s="4" t="str">
-        <x:v>isomerism-lecture-07</x:v>
+        <x:v>organic-chemistry-isomerism-lecture-07</x:v>
       </x:c>
       <x:c r="G129" s="4" t="str">
         <x:v>Geometrical Isomers 02: Cycloalkanes, Allenes, Spiro, Biphenyl</x:v>
@@ -7171,16 +7188,16 @@
         <x:v>comments-07-geometrical-isomers-02-cycloalkanes-allenes-spiro-biphenyl</x:v>
       </x:c>
       <x:c r="K129" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-07-geometrical-isomers-02-cycloalkanes-allenes-spiro-biphenyl</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-07-geometrical-isomers-02-cycloalkanes-allenes-spiro-biphenyl</x:v>
       </x:c>
       <x:c r="L129" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-07-geometrical-isomers-02-cycloalkanes-allenes-spiro-biphenyl/comments/comments-07-geometrical-isomers-02-cycloalkanes-allenes-spiro-biphenyl.raw.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-07-geometrical-isomers-02-cycloalkanes-allenes-spiro-biphenyl/comments/comments-07-geometrical-isomers-02-cycloalkanes-allenes-spiro-biphenyl.raw.json</x:v>
       </x:c>
       <x:c r="M129" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-07-geometrical-isomers-02-cycloalkanes-allenes-spiro-biphenyl/comments/comments-07-geometrical-isomers-02-cycloalkanes-allenes-spiro-biphenyl.scrubbed.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-07-geometrical-isomers-02-cycloalkanes-allenes-spiro-biphenyl/comments/comments-07-geometrical-isomers-02-cycloalkanes-allenes-spiro-biphenyl.scrubbed.json</x:v>
       </x:c>
       <x:c r="N129" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-07-geometrical-isomers-02-cycloalkanes-allenes-spiro-biphenyl/comments/comments-07-geometrical-isomers-02-cycloalkanes-allenes-spiro-biphenyl.final.md</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-07-geometrical-isomers-02-cycloalkanes-allenes-spiro-biphenyl/comments/comments-07-geometrical-isomers-02-cycloalkanes-allenes-spiro-biphenyl.final.md</x:v>
       </x:c>
       <x:c r="O129" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -7189,7 +7206,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q129" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
@@ -7203,13 +7220,13 @@
         <x:v>Organic Chemistry: Isomerism</x:v>
       </x:c>
       <x:c r="D130" s="4" t="str">
-        <x:v>isomerism</x:v>
+        <x:v>organic-chemistry-isomerism</x:v>
       </x:c>
       <x:c r="E130" s="4" t="str">
         <x:v>08</x:v>
       </x:c>
       <x:c r="F130" s="4" t="str">
-        <x:v>isomerism-lecture-08</x:v>
+        <x:v>organic-chemistry-isomerism-lecture-08</x:v>
       </x:c>
       <x:c r="G130" s="4" t="str">
         <x:v>Geometrical Isomers 03: Number of Geometrical Isomers</x:v>
@@ -7224,16 +7241,16 @@
         <x:v>comments-08-geometrical-isomers-03-number-of-geometrical-isomers</x:v>
       </x:c>
       <x:c r="K130" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-08-geometrical-isomers-03-number-of-geometrical-isomers</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-08-geometrical-isomers-03-number-of-geometrical-isomers</x:v>
       </x:c>
       <x:c r="L130" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-08-geometrical-isomers-03-number-of-geometrical-isomers/comments/comments-08-geometrical-isomers-03-number-of-geometrical-isomers.raw.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-08-geometrical-isomers-03-number-of-geometrical-isomers/comments/comments-08-geometrical-isomers-03-number-of-geometrical-isomers.raw.json</x:v>
       </x:c>
       <x:c r="M130" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-08-geometrical-isomers-03-number-of-geometrical-isomers/comments/comments-08-geometrical-isomers-03-number-of-geometrical-isomers.scrubbed.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-08-geometrical-isomers-03-number-of-geometrical-isomers/comments/comments-08-geometrical-isomers-03-number-of-geometrical-isomers.scrubbed.json</x:v>
       </x:c>
       <x:c r="N130" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-08-geometrical-isomers-03-number-of-geometrical-isomers/comments/comments-08-geometrical-isomers-03-number-of-geometrical-isomers.final.md</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-08-geometrical-isomers-03-number-of-geometrical-isomers/comments/comments-08-geometrical-isomers-03-number-of-geometrical-isomers.final.md</x:v>
       </x:c>
       <x:c r="O130" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -7242,7 +7259,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q130" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
@@ -7256,13 +7273,13 @@
         <x:v>Organic Chemistry: Isomerism</x:v>
       </x:c>
       <x:c r="D131" s="4" t="str">
-        <x:v>isomerism</x:v>
+        <x:v>organic-chemistry-isomerism</x:v>
       </x:c>
       <x:c r="E131" s="4" t="str">
         <x:v>09</x:v>
       </x:c>
       <x:c r="F131" s="4" t="str">
-        <x:v>isomerism-lecture-09</x:v>
+        <x:v>organic-chemistry-isomerism-lecture-09</x:v>
       </x:c>
       <x:c r="G131" s="4" t="str">
         <x:v>Optical Isomers 01: Introduction - Chiral Centre and Enantiomers</x:v>
@@ -7277,16 +7294,16 @@
         <x:v>comments-09-optical-isomers-01-introduction-chiral-centre-and-enantiomers</x:v>
       </x:c>
       <x:c r="K131" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-09-optical-isomers-01-introduction-chiral-centre-and-enantiomers</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-09-optical-isomers-01-introduction-chiral-centre-and-enantiomers</x:v>
       </x:c>
       <x:c r="L131" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-09-optical-isomers-01-introduction-chiral-centre-and-enantiomers/comments/comments-09-optical-isomers-01-introduction-chiral-centre-and-enantiomers.raw.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-09-optical-isomers-01-introduction-chiral-centre-and-enantiomers/comments/comments-09-optical-isomers-01-introduction-chiral-centre-and-enantiomers.raw.json</x:v>
       </x:c>
       <x:c r="M131" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-09-optical-isomers-01-introduction-chiral-centre-and-enantiomers/comments/comments-09-optical-isomers-01-introduction-chiral-centre-and-enantiomers.scrubbed.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-09-optical-isomers-01-introduction-chiral-centre-and-enantiomers/comments/comments-09-optical-isomers-01-introduction-chiral-centre-and-enantiomers.scrubbed.json</x:v>
       </x:c>
       <x:c r="N131" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-09-optical-isomers-01-introduction-chiral-centre-and-enantiomers/comments/comments-09-optical-isomers-01-introduction-chiral-centre-and-enantiomers.final.md</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-09-optical-isomers-01-introduction-chiral-centre-and-enantiomers/comments/comments-09-optical-isomers-01-introduction-chiral-centre-and-enantiomers.final.md</x:v>
       </x:c>
       <x:c r="O131" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -7295,7 +7312,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q131" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
@@ -7309,13 +7326,13 @@
         <x:v>Organic Chemistry: Isomerism</x:v>
       </x:c>
       <x:c r="D132" s="4" t="str">
-        <x:v>isomerism</x:v>
+        <x:v>organic-chemistry-isomerism</x:v>
       </x:c>
       <x:c r="E132" s="4" t="str">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F132" s="4" t="str">
-        <x:v>isomerism-lecture-10</x:v>
+        <x:v>organic-chemistry-isomerism-lecture-10</x:v>
       </x:c>
       <x:c r="G132" s="4" t="str">
         <x:v>Optical Isomers 02: Plane of Symmetry and Centre of Symmetry</x:v>
@@ -7330,16 +7347,16 @@
         <x:v>comments-10-optical-isomers-02-plane-of-symmetry-and-centre-of-symmetry</x:v>
       </x:c>
       <x:c r="K132" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-10-optical-isomers-02-plane-of-symmetry-and-centre-of-symmetry</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-10-optical-isomers-02-plane-of-symmetry-and-centre-of-symmetry</x:v>
       </x:c>
       <x:c r="L132" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-10-optical-isomers-02-plane-of-symmetry-and-centre-of-symmetry/comments/comments-10-optical-isomers-02-plane-of-symmetry-and-centre-of-symmetry.raw.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-10-optical-isomers-02-plane-of-symmetry-and-centre-of-symmetry/comments/comments-10-optical-isomers-02-plane-of-symmetry-and-centre-of-symmetry.raw.json</x:v>
       </x:c>
       <x:c r="M132" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-10-optical-isomers-02-plane-of-symmetry-and-centre-of-symmetry/comments/comments-10-optical-isomers-02-plane-of-symmetry-and-centre-of-symmetry.scrubbed.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-10-optical-isomers-02-plane-of-symmetry-and-centre-of-symmetry/comments/comments-10-optical-isomers-02-plane-of-symmetry-and-centre-of-symmetry.scrubbed.json</x:v>
       </x:c>
       <x:c r="N132" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-10-optical-isomers-02-plane-of-symmetry-and-centre-of-symmetry/comments/comments-10-optical-isomers-02-plane-of-symmetry-and-centre-of-symmetry.final.md</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-10-optical-isomers-02-plane-of-symmetry-and-centre-of-symmetry/comments/comments-10-optical-isomers-02-plane-of-symmetry-and-centre-of-symmetry.final.md</x:v>
       </x:c>
       <x:c r="O132" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -7348,7 +7365,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q132" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="133">
@@ -7362,13 +7379,13 @@
         <x:v>Organic Chemistry: Isomerism</x:v>
       </x:c>
       <x:c r="D133" s="4" t="str">
-        <x:v>isomerism</x:v>
+        <x:v>organic-chemistry-isomerism</x:v>
       </x:c>
       <x:c r="E133" s="4" t="str">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F133" s="4" t="str">
-        <x:v>isomerism-lecture-11</x:v>
+        <x:v>organic-chemistry-isomerism-lecture-11</x:v>
       </x:c>
       <x:c r="G133" s="4" t="str">
         <x:v>Optical Isomers 03: Enantiomers, Diastereomers, Meso, Total Isomers</x:v>
@@ -7383,16 +7400,16 @@
         <x:v>comments-11-optical-isomers-03-enantiomers-diastereomers-meso-total-isomers</x:v>
       </x:c>
       <x:c r="K133" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-11-optical-isomers-03-enantiomers-diastereomers-meso-total-isomers</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-11-optical-isomers-03-enantiomers-diastereomers-meso-total-isomers</x:v>
       </x:c>
       <x:c r="L133" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-11-optical-isomers-03-enantiomers-diastereomers-meso-total-isomers/comments/comments-11-optical-isomers-03-enantiomers-diastereomers-meso-total-isomers.raw.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-11-optical-isomers-03-enantiomers-diastereomers-meso-total-isomers/comments/comments-11-optical-isomers-03-enantiomers-diastereomers-meso-total-isomers.raw.json</x:v>
       </x:c>
       <x:c r="M133" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-11-optical-isomers-03-enantiomers-diastereomers-meso-total-isomers/comments/comments-11-optical-isomers-03-enantiomers-diastereomers-meso-total-isomers.scrubbed.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-11-optical-isomers-03-enantiomers-diastereomers-meso-total-isomers/comments/comments-11-optical-isomers-03-enantiomers-diastereomers-meso-total-isomers.scrubbed.json</x:v>
       </x:c>
       <x:c r="N133" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-11-optical-isomers-03-enantiomers-diastereomers-meso-total-isomers/comments/comments-11-optical-isomers-03-enantiomers-diastereomers-meso-total-isomers.final.md</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-11-optical-isomers-03-enantiomers-diastereomers-meso-total-isomers/comments/comments-11-optical-isomers-03-enantiomers-diastereomers-meso-total-isomers.final.md</x:v>
       </x:c>
       <x:c r="O133" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -7401,7 +7418,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q133" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="134">
@@ -7415,13 +7432,13 @@
         <x:v>Organic Chemistry: Isomerism</x:v>
       </x:c>
       <x:c r="D134" s="4" t="str">
-        <x:v>isomerism</x:v>
+        <x:v>organic-chemistry-isomerism</x:v>
       </x:c>
       <x:c r="E134" s="4" t="str">
         <x:v>12</x:v>
       </x:c>
       <x:c r="F134" s="4" t="str">
-        <x:v>isomerism-lecture-12</x:v>
+        <x:v>organic-chemistry-isomerism-lecture-12</x:v>
       </x:c>
       <x:c r="G134" s="4" t="str">
         <x:v>Optical Isomers 04: Wedge Dash and Fischer Projections with R-S Configurations</x:v>
@@ -7436,16 +7453,16 @@
         <x:v>comments-12-optical-isomers-04-wedge-dash-and-fischer-projections-with-r-s-configurations</x:v>
       </x:c>
       <x:c r="K134" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-12-optical-isomers-04-wedge-dash-and-fischer-projections-with-r-s-configurations</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-12-optical-isomers-04-wedge-dash-and-fischer-projections-with-r-s-configurations</x:v>
       </x:c>
       <x:c r="L134" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-12-optical-isomers-04-wedge-dash-and-fischer-projections-with-r-s-configurations/comments/comments-12-optical-isomers-04-wedge-dash-and-fischer-projections-with-r-s-configurations.raw.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-12-optical-isomers-04-wedge-dash-and-fischer-projections-with-r-s-configurations/comments/comments-12-optical-isomers-04-wedge-dash-and-fischer-projections-with-r-s-configurations.raw.json</x:v>
       </x:c>
       <x:c r="M134" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-12-optical-isomers-04-wedge-dash-and-fischer-projections-with-r-s-configurations/comments/comments-12-optical-isomers-04-wedge-dash-and-fischer-projections-with-r-s-configurations.scrubbed.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-12-optical-isomers-04-wedge-dash-and-fischer-projections-with-r-s-configurations/comments/comments-12-optical-isomers-04-wedge-dash-and-fischer-projections-with-r-s-configurations.scrubbed.json</x:v>
       </x:c>
       <x:c r="N134" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-12-optical-isomers-04-wedge-dash-and-fischer-projections-with-r-s-configurations/comments/comments-12-optical-isomers-04-wedge-dash-and-fischer-projections-with-r-s-configurations.final.md</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-12-optical-isomers-04-wedge-dash-and-fischer-projections-with-r-s-configurations/comments/comments-12-optical-isomers-04-wedge-dash-and-fischer-projections-with-r-s-configurations.final.md</x:v>
       </x:c>
       <x:c r="O134" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -7454,7 +7471,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q134" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="135">
@@ -7468,13 +7485,13 @@
         <x:v>Organic Chemistry: Isomerism</x:v>
       </x:c>
       <x:c r="D135" s="4" t="str">
-        <x:v>isomerism</x:v>
+        <x:v>organic-chemistry-isomerism</x:v>
       </x:c>
       <x:c r="E135" s="4" t="str">
         <x:v>13</x:v>
       </x:c>
       <x:c r="F135" s="4" t="str">
-        <x:v>isomerism-lecture-13</x:v>
+        <x:v>organic-chemistry-isomerism-lecture-13</x:v>
       </x:c>
       <x:c r="G135" s="4" t="str">
         <x:v>Optical Isomers 05: Optical Isomerism in Allene, Spiro and Biphenyl</x:v>
@@ -7489,16 +7506,16 @@
         <x:v>comments-13-optical-isomers-05-optical-isomerism-in-allene-spiro-and-biphenyl</x:v>
       </x:c>
       <x:c r="K135" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-13-optical-isomers-05-optical-isomerism-in-allene-spiro-and-biphenyl</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-13-optical-isomers-05-optical-isomerism-in-allene-spiro-and-biphenyl</x:v>
       </x:c>
       <x:c r="L135" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-13-optical-isomers-05-optical-isomerism-in-allene-spiro-and-biphenyl/comments/comments-13-optical-isomers-05-optical-isomerism-in-allene-spiro-and-biphenyl.raw.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-13-optical-isomers-05-optical-isomerism-in-allene-spiro-and-biphenyl/comments/comments-13-optical-isomers-05-optical-isomerism-in-allene-spiro-and-biphenyl.raw.json</x:v>
       </x:c>
       <x:c r="M135" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-13-optical-isomers-05-optical-isomerism-in-allene-spiro-and-biphenyl/comments/comments-13-optical-isomers-05-optical-isomerism-in-allene-spiro-and-biphenyl.scrubbed.json</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-13-optical-isomers-05-optical-isomerism-in-allene-spiro-and-biphenyl/comments/comments-13-optical-isomers-05-optical-isomerism-in-allene-spiro-and-biphenyl.scrubbed.json</x:v>
       </x:c>
       <x:c r="N135" s="4" t="str">
-        <x:v>content/chemistry/organic/isomerism/lectures/lecture-13-optical-isomers-05-optical-isomerism-in-allene-spiro-and-biphenyl/comments/comments-13-optical-isomers-05-optical-isomerism-in-allene-spiro-and-biphenyl.final.md</x:v>
+        <x:v>content/03-organic/02-organic-chemistry-isomerism/lectures/lecture-13-optical-isomers-05-optical-isomerism-in-allene-spiro-and-biphenyl/comments/comments-13-optical-isomers-05-optical-isomerism-in-allene-spiro-and-biphenyl.final.md</x:v>
       </x:c>
       <x:c r="O135" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -7507,7 +7524,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q135" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="136">
@@ -7521,13 +7538,13 @@
         <x:v>Organic Chemistry: GOC</x:v>
       </x:c>
       <x:c r="D136" s="4" t="str">
-        <x:v>goc</x:v>
+        <x:v>organic-chemistry-goc</x:v>
       </x:c>
       <x:c r="E136" s="4" t="str">
         <x:v>01</x:v>
       </x:c>
       <x:c r="F136" s="4" t="str">
-        <x:v>goc-lecture-01</x:v>
+        <x:v>organic-chemistry-goc-lecture-01</x:v>
       </x:c>
       <x:c r="G136" s="4" t="str">
         <x:v>Inductive Effect and Acidic Strength</x:v>
@@ -7542,16 +7559,16 @@
         <x:v>comments-01-inductive-effect-and-acidic-strength</x:v>
       </x:c>
       <x:c r="K136" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-01-inductive-effect-and-acidic-strength</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-01-inductive-effect-and-acidic-strength</x:v>
       </x:c>
       <x:c r="L136" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-01-inductive-effect-and-acidic-strength/comments/comments-01-inductive-effect-and-acidic-strength.raw.json</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-01-inductive-effect-and-acidic-strength/comments/comments-01-inductive-effect-and-acidic-strength.raw.json</x:v>
       </x:c>
       <x:c r="M136" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-01-inductive-effect-and-acidic-strength/comments/comments-01-inductive-effect-and-acidic-strength.scrubbed.json</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-01-inductive-effect-and-acidic-strength/comments/comments-01-inductive-effect-and-acidic-strength.scrubbed.json</x:v>
       </x:c>
       <x:c r="N136" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-01-inductive-effect-and-acidic-strength/comments/comments-01-inductive-effect-and-acidic-strength.final.md</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-01-inductive-effect-and-acidic-strength/comments/comments-01-inductive-effect-and-acidic-strength.final.md</x:v>
       </x:c>
       <x:c r="O136" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -7560,7 +7577,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q136" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="137">
@@ -7574,13 +7591,13 @@
         <x:v>Organic Chemistry: GOC</x:v>
       </x:c>
       <x:c r="D137" s="4" t="str">
-        <x:v>goc</x:v>
+        <x:v>organic-chemistry-goc</x:v>
       </x:c>
       <x:c r="E137" s="4" t="str">
         <x:v>02</x:v>
       </x:c>
       <x:c r="F137" s="4" t="str">
-        <x:v>goc-lecture-02</x:v>
+        <x:v>organic-chemistry-goc-lecture-02</x:v>
       </x:c>
       <x:c r="G137" s="4" t="str">
         <x:v>Resonance 01: How to Draw Resonance Structures</x:v>
@@ -7595,16 +7612,16 @@
         <x:v>comments-02-resonance-01-how-to-draw-resonance-structures</x:v>
       </x:c>
       <x:c r="K137" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-02-resonance-01-how-to-draw-resonance-structures</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-02-resonance-01-how-to-draw-resonance-structures</x:v>
       </x:c>
       <x:c r="L137" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-02-resonance-01-how-to-draw-resonance-structures/comments/comments-02-resonance-01-how-to-draw-resonance-structures.raw.json</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-02-resonance-01-how-to-draw-resonance-structures/comments/comments-02-resonance-01-how-to-draw-resonance-structures.raw.json</x:v>
       </x:c>
       <x:c r="M137" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-02-resonance-01-how-to-draw-resonance-structures/comments/comments-02-resonance-01-how-to-draw-resonance-structures.scrubbed.json</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-02-resonance-01-how-to-draw-resonance-structures/comments/comments-02-resonance-01-how-to-draw-resonance-structures.scrubbed.json</x:v>
       </x:c>
       <x:c r="N137" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-02-resonance-01-how-to-draw-resonance-structures/comments/comments-02-resonance-01-how-to-draw-resonance-structures.final.md</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-02-resonance-01-how-to-draw-resonance-structures/comments/comments-02-resonance-01-how-to-draw-resonance-structures.final.md</x:v>
       </x:c>
       <x:c r="O137" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -7613,7 +7630,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q137" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="138">
@@ -7627,13 +7644,13 @@
         <x:v>Organic Chemistry: GOC</x:v>
       </x:c>
       <x:c r="D138" s="4" t="str">
-        <x:v>goc</x:v>
+        <x:v>organic-chemistry-goc</x:v>
       </x:c>
       <x:c r="E138" s="4" t="str">
         <x:v>03</x:v>
       </x:c>
       <x:c r="F138" s="4" t="str">
-        <x:v>goc-lecture-03</x:v>
+        <x:v>organic-chemistry-goc-lecture-03</x:v>
       </x:c>
       <x:c r="G138" s="4" t="str">
         <x:v>Resonance 02: Stability of Resonance Structures</x:v>
@@ -7648,16 +7665,16 @@
         <x:v>comments-03-resonance-02-stability-of-resonance-structures</x:v>
       </x:c>
       <x:c r="K138" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-03-resonance-02-stability-of-resonance-structures</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-03-resonance-02-stability-of-resonance-structures</x:v>
       </x:c>
       <x:c r="L138" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-03-resonance-02-stability-of-resonance-structures/comments/comments-03-resonance-02-stability-of-resonance-structures.raw.json</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-03-resonance-02-stability-of-resonance-structures/comments/comments-03-resonance-02-stability-of-resonance-structures.raw.json</x:v>
       </x:c>
       <x:c r="M138" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-03-resonance-02-stability-of-resonance-structures/comments/comments-03-resonance-02-stability-of-resonance-structures.scrubbed.json</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-03-resonance-02-stability-of-resonance-structures/comments/comments-03-resonance-02-stability-of-resonance-structures.scrubbed.json</x:v>
       </x:c>
       <x:c r="N138" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-03-resonance-02-stability-of-resonance-structures/comments/comments-03-resonance-02-stability-of-resonance-structures.final.md</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-03-resonance-02-stability-of-resonance-structures/comments/comments-03-resonance-02-stability-of-resonance-structures.final.md</x:v>
       </x:c>
       <x:c r="O138" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -7666,7 +7683,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q138" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
@@ -7680,13 +7697,13 @@
         <x:v>Organic Chemistry: GOC</x:v>
       </x:c>
       <x:c r="D139" s="4" t="str">
-        <x:v>goc</x:v>
+        <x:v>organic-chemistry-goc</x:v>
       </x:c>
       <x:c r="E139" s="4" t="str">
         <x:v>04</x:v>
       </x:c>
       <x:c r="F139" s="4" t="str">
-        <x:v>goc-lecture-04</x:v>
+        <x:v>organic-chemistry-goc-lecture-04</x:v>
       </x:c>
       <x:c r="G139" s="4" t="str">
         <x:v>Resonance 03: Mesomeric Effect Complete Topic</x:v>
@@ -7701,16 +7718,16 @@
         <x:v>comments-04-resonance-03-mesomeric-effect-complete-topic</x:v>
       </x:c>
       <x:c r="K139" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-04-resonance-03-mesomeric-effect-complete-topic</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-04-resonance-03-mesomeric-effect-complete-topic</x:v>
       </x:c>
       <x:c r="L139" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-04-resonance-03-mesomeric-effect-complete-topic/comments/comments-04-resonance-03-mesomeric-effect-complete-topic.raw.json</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-04-resonance-03-mesomeric-effect-complete-topic/comments/comments-04-resonance-03-mesomeric-effect-complete-topic.raw.json</x:v>
       </x:c>
       <x:c r="M139" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-04-resonance-03-mesomeric-effect-complete-topic/comments/comments-04-resonance-03-mesomeric-effect-complete-topic.scrubbed.json</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-04-resonance-03-mesomeric-effect-complete-topic/comments/comments-04-resonance-03-mesomeric-effect-complete-topic.scrubbed.json</x:v>
       </x:c>
       <x:c r="N139" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-04-resonance-03-mesomeric-effect-complete-topic/comments/comments-04-resonance-03-mesomeric-effect-complete-topic.final.md</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-04-resonance-03-mesomeric-effect-complete-topic/comments/comments-04-resonance-03-mesomeric-effect-complete-topic.final.md</x:v>
       </x:c>
       <x:c r="O139" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -7719,7 +7736,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q139" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -7733,13 +7750,13 @@
         <x:v>Organic Chemistry: GOC</x:v>
       </x:c>
       <x:c r="D140" s="4" t="str">
-        <x:v>goc</x:v>
+        <x:v>organic-chemistry-goc</x:v>
       </x:c>
       <x:c r="E140" s="4" t="str">
         <x:v>05</x:v>
       </x:c>
       <x:c r="F140" s="4" t="str">
-        <x:v>goc-lecture-05</x:v>
+        <x:v>organic-chemistry-goc-lecture-05</x:v>
       </x:c>
       <x:c r="G140" s="4" t="str">
         <x:v>Hyperconjugation Effect in Carbocation, Free Radical</x:v>
@@ -7754,16 +7771,16 @@
         <x:v>comments-05-hyperconjugation-effect-in-carbocation-free-radical</x:v>
       </x:c>
       <x:c r="K140" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-05-hyperconjugation-effect-in-carbocation-free-radical</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-05-hyperconjugation-effect-in-carbocation-free-radical</x:v>
       </x:c>
       <x:c r="L140" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-05-hyperconjugation-effect-in-carbocation-free-radical/comments/comments-05-hyperconjugation-effect-in-carbocation-free-radical.raw.json</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-05-hyperconjugation-effect-in-carbocation-free-radical/comments/comments-05-hyperconjugation-effect-in-carbocation-free-radical.raw.json</x:v>
       </x:c>
       <x:c r="M140" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-05-hyperconjugation-effect-in-carbocation-free-radical/comments/comments-05-hyperconjugation-effect-in-carbocation-free-radical.scrubbed.json</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-05-hyperconjugation-effect-in-carbocation-free-radical/comments/comments-05-hyperconjugation-effect-in-carbocation-free-radical.scrubbed.json</x:v>
       </x:c>
       <x:c r="N140" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-05-hyperconjugation-effect-in-carbocation-free-radical/comments/comments-05-hyperconjugation-effect-in-carbocation-free-radical.final.md</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-05-hyperconjugation-effect-in-carbocation-free-radical/comments/comments-05-hyperconjugation-effect-in-carbocation-free-radical.final.md</x:v>
       </x:c>
       <x:c r="O140" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -7772,7 +7789,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q140" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
@@ -7786,13 +7803,13 @@
         <x:v>Organic Chemistry: GOC</x:v>
       </x:c>
       <x:c r="D141" s="4" t="str">
-        <x:v>goc</x:v>
+        <x:v>organic-chemistry-goc</x:v>
       </x:c>
       <x:c r="E141" s="4" t="str">
         <x:v>06</x:v>
       </x:c>
       <x:c r="F141" s="4" t="str">
-        <x:v>goc-lecture-06</x:v>
+        <x:v>organic-chemistry-goc-lecture-06</x:v>
       </x:c>
       <x:c r="G141" s="4" t="str">
         <x:v>Aromatic, Anti-Aromatic, and Non-Aromatic Compounds</x:v>
@@ -7807,16 +7824,16 @@
         <x:v>comments-06-aromatic-anti-aromatic-and-non-aromatic-compounds</x:v>
       </x:c>
       <x:c r="K141" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-06-aromatic-anti-aromatic-and-non-aromatic-compounds</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-06-aromatic-anti-aromatic-and-non-aromatic-compounds</x:v>
       </x:c>
       <x:c r="L141" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-06-aromatic-anti-aromatic-and-non-aromatic-compounds/comments/comments-06-aromatic-anti-aromatic-and-non-aromatic-compounds.raw.json</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-06-aromatic-anti-aromatic-and-non-aromatic-compounds/comments/comments-06-aromatic-anti-aromatic-and-non-aromatic-compounds.raw.json</x:v>
       </x:c>
       <x:c r="M141" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-06-aromatic-anti-aromatic-and-non-aromatic-compounds/comments/comments-06-aromatic-anti-aromatic-and-non-aromatic-compounds.scrubbed.json</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-06-aromatic-anti-aromatic-and-non-aromatic-compounds/comments/comments-06-aromatic-anti-aromatic-and-non-aromatic-compounds.scrubbed.json</x:v>
       </x:c>
       <x:c r="N141" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-06-aromatic-anti-aromatic-and-non-aromatic-compounds/comments/comments-06-aromatic-anti-aromatic-and-non-aromatic-compounds.final.md</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-06-aromatic-anti-aromatic-and-non-aromatic-compounds/comments/comments-06-aromatic-anti-aromatic-and-non-aromatic-compounds.final.md</x:v>
       </x:c>
       <x:c r="O141" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -7825,7 +7842,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q141" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
@@ -7839,13 +7856,13 @@
         <x:v>Organic Chemistry: GOC</x:v>
       </x:c>
       <x:c r="D142" s="4" t="str">
-        <x:v>goc</x:v>
+        <x:v>organic-chemistry-goc</x:v>
       </x:c>
       <x:c r="E142" s="4" t="str">
         <x:v>07</x:v>
       </x:c>
       <x:c r="F142" s="4" t="str">
-        <x:v>goc-lecture-07</x:v>
+        <x:v>organic-chemistry-goc-lecture-07</x:v>
       </x:c>
       <x:c r="G142" s="4" t="str">
         <x:v>Carbocation - Reaction Intermediate 01</x:v>
@@ -7860,16 +7877,16 @@
         <x:v>comments-07-carbocation-reaction-intermediate-01</x:v>
       </x:c>
       <x:c r="K142" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-07-carbocation-reaction-intermediate-01</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-07-carbocation-reaction-intermediate-01</x:v>
       </x:c>
       <x:c r="L142" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-07-carbocation-reaction-intermediate-01/comments/comments-07-carbocation-reaction-intermediate-01.raw.json</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-07-carbocation-reaction-intermediate-01/comments/comments-07-carbocation-reaction-intermediate-01.raw.json</x:v>
       </x:c>
       <x:c r="M142" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-07-carbocation-reaction-intermediate-01/comments/comments-07-carbocation-reaction-intermediate-01.scrubbed.json</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-07-carbocation-reaction-intermediate-01/comments/comments-07-carbocation-reaction-intermediate-01.scrubbed.json</x:v>
       </x:c>
       <x:c r="N142" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-07-carbocation-reaction-intermediate-01/comments/comments-07-carbocation-reaction-intermediate-01.final.md</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-07-carbocation-reaction-intermediate-01/comments/comments-07-carbocation-reaction-intermediate-01.final.md</x:v>
       </x:c>
       <x:c r="O142" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -7878,7 +7895,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q142" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
@@ -7892,13 +7909,13 @@
         <x:v>Organic Chemistry: GOC</x:v>
       </x:c>
       <x:c r="D143" s="4" t="str">
-        <x:v>goc</x:v>
+        <x:v>organic-chemistry-goc</x:v>
       </x:c>
       <x:c r="E143" s="4" t="str">
         <x:v>08</x:v>
       </x:c>
       <x:c r="F143" s="4" t="str">
-        <x:v>goc-lecture-08</x:v>
+        <x:v>organic-chemistry-goc-lecture-08</x:v>
       </x:c>
       <x:c r="G143" s="4" t="str">
         <x:v>Free Radical and Carbanion - Reaction Intermediate 02</x:v>
@@ -7913,16 +7930,16 @@
         <x:v>comments-08-free-radical-and-carbanion-reaction-intermediate-02</x:v>
       </x:c>
       <x:c r="K143" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-08-free-radical-and-carbanion-reaction-intermediate-02</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-08-free-radical-and-carbanion-reaction-intermediate-02</x:v>
       </x:c>
       <x:c r="L143" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-08-free-radical-and-carbanion-reaction-intermediate-02/comments/comments-08-free-radical-and-carbanion-reaction-intermediate-02.raw.json</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-08-free-radical-and-carbanion-reaction-intermediate-02/comments/comments-08-free-radical-and-carbanion-reaction-intermediate-02.raw.json</x:v>
       </x:c>
       <x:c r="M143" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-08-free-radical-and-carbanion-reaction-intermediate-02/comments/comments-08-free-radical-and-carbanion-reaction-intermediate-02.scrubbed.json</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-08-free-radical-and-carbanion-reaction-intermediate-02/comments/comments-08-free-radical-and-carbanion-reaction-intermediate-02.scrubbed.json</x:v>
       </x:c>
       <x:c r="N143" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-08-free-radical-and-carbanion-reaction-intermediate-02/comments/comments-08-free-radical-and-carbanion-reaction-intermediate-02.final.md</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-08-free-radical-and-carbanion-reaction-intermediate-02/comments/comments-08-free-radical-and-carbanion-reaction-intermediate-02.final.md</x:v>
       </x:c>
       <x:c r="O143" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -7931,7 +7948,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q143" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -7945,13 +7962,13 @@
         <x:v>Organic Chemistry: GOC</x:v>
       </x:c>
       <x:c r="D144" s="4" t="str">
-        <x:v>goc</x:v>
+        <x:v>organic-chemistry-goc</x:v>
       </x:c>
       <x:c r="E144" s="4" t="str">
         <x:v>09</x:v>
       </x:c>
       <x:c r="F144" s="4" t="str">
-        <x:v>goc-lecture-09</x:v>
+        <x:v>organic-chemistry-goc-lecture-09</x:v>
       </x:c>
       <x:c r="G144" s="4" t="str">
         <x:v>Carbene || Singlet and Triplet Carbene - Reaction Intermediate 03</x:v>
@@ -7966,16 +7983,16 @@
         <x:v>comments-09-carbene-singlet-and-triplet-carbene-reaction-intermediate-03</x:v>
       </x:c>
       <x:c r="K144" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-09-carbene-singlet-and-triplet-carbene-reaction-intermediate-03</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-09-carbene-singlet-and-triplet-carbene-reaction-intermediate-03</x:v>
       </x:c>
       <x:c r="L144" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-09-carbene-singlet-and-triplet-carbene-reaction-intermediate-03/comments/comments-09-carbene-singlet-and-triplet-carbene-reaction-intermediate-03.raw.json</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-09-carbene-singlet-and-triplet-carbene-reaction-intermediate-03/comments/comments-09-carbene-singlet-and-triplet-carbene-reaction-intermediate-03.raw.json</x:v>
       </x:c>
       <x:c r="M144" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-09-carbene-singlet-and-triplet-carbene-reaction-intermediate-03/comments/comments-09-carbene-singlet-and-triplet-carbene-reaction-intermediate-03.scrubbed.json</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-09-carbene-singlet-and-triplet-carbene-reaction-intermediate-03/comments/comments-09-carbene-singlet-and-triplet-carbene-reaction-intermediate-03.scrubbed.json</x:v>
       </x:c>
       <x:c r="N144" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-09-carbene-singlet-and-triplet-carbene-reaction-intermediate-03/comments/comments-09-carbene-singlet-and-triplet-carbene-reaction-intermediate-03.final.md</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-09-carbene-singlet-and-triplet-carbene-reaction-intermediate-03/comments/comments-09-carbene-singlet-and-triplet-carbene-reaction-intermediate-03.final.md</x:v>
       </x:c>
       <x:c r="O144" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -7984,7 +8001,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q144" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -7998,13 +8015,13 @@
         <x:v>Organic Chemistry: GOC</x:v>
       </x:c>
       <x:c r="D145" s="4" t="str">
-        <x:v>goc</x:v>
+        <x:v>organic-chemistry-goc</x:v>
       </x:c>
       <x:c r="E145" s="4" t="str">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F145" s="4" t="str">
-        <x:v>goc-lecture-10</x:v>
+        <x:v>organic-chemistry-goc-lecture-10</x:v>
       </x:c>
       <x:c r="G145" s="4" t="str">
         <x:v>Rearrangement of Carbocation | Hydride, Methyl, and Phenyl Shifting</x:v>
@@ -8019,16 +8036,16 @@
         <x:v>comments-10-rearrangement-of-carbocation-hydride-methyl-and-phenyl-shifting</x:v>
       </x:c>
       <x:c r="K145" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-10-rearrangement-of-carbocation-hydride-methyl-and-phenyl-shifting</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-10-rearrangement-of-carbocation-hydride-methyl-and-phenyl-shifting</x:v>
       </x:c>
       <x:c r="L145" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-10-rearrangement-of-carbocation-hydride-methyl-and-phenyl-shifting/comments/comments-10-rearrangement-of-carbocation-hydride-methyl-and-phenyl-shifting.raw.json</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-10-rearrangement-of-carbocation-hydride-methyl-and-phenyl-shifting/comments/comments-10-rearrangement-of-carbocation-hydride-methyl-and-phenyl-shifting.raw.json</x:v>
       </x:c>
       <x:c r="M145" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-10-rearrangement-of-carbocation-hydride-methyl-and-phenyl-shifting/comments/comments-10-rearrangement-of-carbocation-hydride-methyl-and-phenyl-shifting.scrubbed.json</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-10-rearrangement-of-carbocation-hydride-methyl-and-phenyl-shifting/comments/comments-10-rearrangement-of-carbocation-hydride-methyl-and-phenyl-shifting.scrubbed.json</x:v>
       </x:c>
       <x:c r="N145" s="4" t="str">
-        <x:v>content/chemistry/organic/goc/lectures/lecture-10-rearrangement-of-carbocation-hydride-methyl-and-phenyl-shifting/comments/comments-10-rearrangement-of-carbocation-hydride-methyl-and-phenyl-shifting.final.md</x:v>
+        <x:v>content/03-organic/03-organic-chemistry-goc/lectures/lecture-10-rearrangement-of-carbocation-hydride-methyl-and-phenyl-shifting/comments/comments-10-rearrangement-of-carbocation-hydride-methyl-and-phenyl-shifting.final.md</x:v>
       </x:c>
       <x:c r="O145" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -8037,7 +8054,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q145" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
@@ -8051,13 +8068,13 @@
         <x:v>Purification and Characterisation of Organic Compounds</x:v>
       </x:c>
       <x:c r="D146" s="4" t="str">
-        <x:v>purification-and-characterisation-organic-compounds</x:v>
+        <x:v>purification-and-characterisation-of-organic-compounds</x:v>
       </x:c>
       <x:c r="E146" s="4" t="str">
         <x:v>01</x:v>
       </x:c>
       <x:c r="F146" s="4" t="str">
-        <x:v>purification-and-characterisation-organic-compounds-lecture-01</x:v>
+        <x:v>purification-and-characterisation-of-organic-compounds-lecture-01</x:v>
       </x:c>
       <x:c r="G146" s="4" t="str">
         <x:v>Purification and Characterisation of Organic Compounds</x:v>
@@ -8072,16 +8089,16 @@
         <x:v>comments-01-purification-and-characterisation-of-organic-compounds</x:v>
       </x:c>
       <x:c r="K146" s="4" t="str">
-        <x:v>content/chemistry/organic/purification-and-characterisation-organic-compounds/lectures/lecture-01-purification-and-characterisation-of-organic-compounds</x:v>
+        <x:v>content/03-organic/12-purification-and-characterisation-of-organic-compounds/lectures/lecture-01-purification-and-characterisation-of-organic-compounds</x:v>
       </x:c>
       <x:c r="L146" s="4" t="str">
-        <x:v>content/chemistry/organic/purification-and-characterisation-organic-compounds/lectures/lecture-01-purification-and-characterisation-of-organic-compounds/comments/comments-01-purification-and-characterisation-of-organic-compounds.raw.json</x:v>
+        <x:v>content/03-organic/12-purification-and-characterisation-of-organic-compounds/lectures/lecture-01-purification-and-characterisation-of-organic-compounds/comments/comments-01-purification-and-characterisation-of-organic-compounds.raw.json</x:v>
       </x:c>
       <x:c r="M146" s="4" t="str">
-        <x:v>content/chemistry/organic/purification-and-characterisation-organic-compounds/lectures/lecture-01-purification-and-characterisation-of-organic-compounds/comments/comments-01-purification-and-characterisation-of-organic-compounds.scrubbed.json</x:v>
+        <x:v>content/03-organic/12-purification-and-characterisation-of-organic-compounds/lectures/lecture-01-purification-and-characterisation-of-organic-compounds/comments/comments-01-purification-and-characterisation-of-organic-compounds.scrubbed.json</x:v>
       </x:c>
       <x:c r="N146" s="4" t="str">
-        <x:v>content/chemistry/organic/purification-and-characterisation-organic-compounds/lectures/lecture-01-purification-and-characterisation-of-organic-compounds/comments/comments-01-purification-and-characterisation-of-organic-compounds.final.md</x:v>
+        <x:v>content/03-organic/12-purification-and-characterisation-of-organic-compounds/lectures/lecture-01-purification-and-characterisation-of-organic-compounds/comments/comments-01-purification-and-characterisation-of-organic-compounds.final.md</x:v>
       </x:c>
       <x:c r="O146" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -8090,7 +8107,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q146" s="4" t="str">
-        <x:v>One-shot/timestamped chapter collapsed from 16 same-video links.</x:v>
+        <x:v>One-shot/timestamped chapter collapsed from 16 same-video links. New one-shot lecture folder proposed.</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
@@ -8104,13 +8121,13 @@
         <x:v>Organic Chemistry: Reaction Mechanism</x:v>
       </x:c>
       <x:c r="D147" s="4" t="str">
-        <x:v>reaction-mechanism</x:v>
+        <x:v>organic-chemistry-reaction-mechanism</x:v>
       </x:c>
       <x:c r="E147" s="4" t="str">
         <x:v>01</x:v>
       </x:c>
       <x:c r="F147" s="4" t="str">
-        <x:v>reaction-mechanism-lecture-01</x:v>
+        <x:v>organic-chemistry-reaction-mechanism-lecture-01</x:v>
       </x:c>
       <x:c r="G147" s="4" t="str">
         <x:v>Types of Attacking Reagents: Electrophile &amp; Nucleophile</x:v>
@@ -8125,16 +8142,16 @@
         <x:v>comments-01-types-of-attacking-reagents-electrophile-and-nucleophile</x:v>
       </x:c>
       <x:c r="K147" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-01-types-of-attacking-reagents-electrophile-and-nucleophile</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-01-types-of-attacking-reagents-electrophile-and-nucleophile</x:v>
       </x:c>
       <x:c r="L147" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-01-types-of-attacking-reagents-electrophile-and-nucleophile/comments/comments-01-types-of-attacking-reagents-electrophile-and-nucleophile.raw.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-01-types-of-attacking-reagents-electrophile-and-nucleophile/comments/comments-01-types-of-attacking-reagents-electrophile-and-nucleophile.raw.json</x:v>
       </x:c>
       <x:c r="M147" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-01-types-of-attacking-reagents-electrophile-and-nucleophile/comments/comments-01-types-of-attacking-reagents-electrophile-and-nucleophile.scrubbed.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-01-types-of-attacking-reagents-electrophile-and-nucleophile/comments/comments-01-types-of-attacking-reagents-electrophile-and-nucleophile.scrubbed.json</x:v>
       </x:c>
       <x:c r="N147" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-01-types-of-attacking-reagents-electrophile-and-nucleophile/comments/comments-01-types-of-attacking-reagents-electrophile-and-nucleophile.final.md</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-01-types-of-attacking-reagents-electrophile-and-nucleophile/comments/comments-01-types-of-attacking-reagents-electrophile-and-nucleophile.final.md</x:v>
       </x:c>
       <x:c r="O147" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -8143,7 +8160,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q147" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
@@ -8157,13 +8174,13 @@
         <x:v>Organic Chemistry: Reaction Mechanism</x:v>
       </x:c>
       <x:c r="D148" s="4" t="str">
-        <x:v>reaction-mechanism</x:v>
+        <x:v>organic-chemistry-reaction-mechanism</x:v>
       </x:c>
       <x:c r="E148" s="4" t="str">
         <x:v>02</x:v>
       </x:c>
       <x:c r="F148" s="4" t="str">
-        <x:v>reaction-mechanism-lecture-02</x:v>
+        <x:v>organic-chemistry-reaction-mechanism-lecture-02</x:v>
       </x:c>
       <x:c r="G148" s="4" t="str">
         <x:v>Free Radical Substitution 01 | Halogenation of Alkane</x:v>
@@ -8178,16 +8195,16 @@
         <x:v>comments-02-free-radical-substitution-01-halogenation-of-alkane</x:v>
       </x:c>
       <x:c r="K148" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-02-free-radical-substitution-01-halogenation-of-alkane</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-02-free-radical-substitution-01-halogenation-of-alkane</x:v>
       </x:c>
       <x:c r="L148" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-02-free-radical-substitution-01-halogenation-of-alkane/comments/comments-02-free-radical-substitution-01-halogenation-of-alkane.raw.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-02-free-radical-substitution-01-halogenation-of-alkane/comments/comments-02-free-radical-substitution-01-halogenation-of-alkane.raw.json</x:v>
       </x:c>
       <x:c r="M148" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-02-free-radical-substitution-01-halogenation-of-alkane/comments/comments-02-free-radical-substitution-01-halogenation-of-alkane.scrubbed.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-02-free-radical-substitution-01-halogenation-of-alkane/comments/comments-02-free-radical-substitution-01-halogenation-of-alkane.scrubbed.json</x:v>
       </x:c>
       <x:c r="N148" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-02-free-radical-substitution-01-halogenation-of-alkane/comments/comments-02-free-radical-substitution-01-halogenation-of-alkane.final.md</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-02-free-radical-substitution-01-halogenation-of-alkane/comments/comments-02-free-radical-substitution-01-halogenation-of-alkane.final.md</x:v>
       </x:c>
       <x:c r="O148" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -8196,7 +8213,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q148" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
@@ -8210,13 +8227,13 @@
         <x:v>Organic Chemistry: Reaction Mechanism</x:v>
       </x:c>
       <x:c r="D149" s="4" t="str">
-        <x:v>reaction-mechanism</x:v>
+        <x:v>organic-chemistry-reaction-mechanism</x:v>
       </x:c>
       <x:c r="E149" s="4" t="str">
         <x:v>03</x:v>
       </x:c>
       <x:c r="F149" s="4" t="str">
-        <x:v>reaction-mechanism-lecture-03</x:v>
+        <x:v>organic-chemistry-reaction-mechanism-lecture-03</x:v>
       </x:c>
       <x:c r="G149" s="4" t="str">
         <x:v>Free Radical Substitution 02 | Selectivity in Halogenation</x:v>
@@ -8231,16 +8248,16 @@
         <x:v>comments-03-free-radical-substitution-02-selectivity-in-halogenation</x:v>
       </x:c>
       <x:c r="K149" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-03-free-radical-substitution-02-selectivity-in-halogenation</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-03-free-radical-substitution-02-selectivity-in-halogenation</x:v>
       </x:c>
       <x:c r="L149" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-03-free-radical-substitution-02-selectivity-in-halogenation/comments/comments-03-free-radical-substitution-02-selectivity-in-halogenation.raw.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-03-free-radical-substitution-02-selectivity-in-halogenation/comments/comments-03-free-radical-substitution-02-selectivity-in-halogenation.raw.json</x:v>
       </x:c>
       <x:c r="M149" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-03-free-radical-substitution-02-selectivity-in-halogenation/comments/comments-03-free-radical-substitution-02-selectivity-in-halogenation.scrubbed.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-03-free-radical-substitution-02-selectivity-in-halogenation/comments/comments-03-free-radical-substitution-02-selectivity-in-halogenation.scrubbed.json</x:v>
       </x:c>
       <x:c r="N149" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-03-free-radical-substitution-02-selectivity-in-halogenation/comments/comments-03-free-radical-substitution-02-selectivity-in-halogenation.final.md</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-03-free-radical-substitution-02-selectivity-in-halogenation/comments/comments-03-free-radical-substitution-02-selectivity-in-halogenation.final.md</x:v>
       </x:c>
       <x:c r="O149" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -8249,7 +8266,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q149" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
@@ -8263,13 +8280,13 @@
         <x:v>Organic Chemistry: Reaction Mechanism</x:v>
       </x:c>
       <x:c r="D150" s="4" t="str">
-        <x:v>reaction-mechanism</x:v>
+        <x:v>organic-chemistry-reaction-mechanism</x:v>
       </x:c>
       <x:c r="E150" s="4" t="str">
         <x:v>04</x:v>
       </x:c>
       <x:c r="F150" s="4" t="str">
-        <x:v>reaction-mechanism-lecture-04</x:v>
+        <x:v>organic-chemistry-reaction-mechanism-lecture-04</x:v>
       </x:c>
       <x:c r="G150" s="4" t="str">
         <x:v>Free Radical Substitution 03 | Allylic Substitution</x:v>
@@ -8284,16 +8301,16 @@
         <x:v>comments-04-free-radical-substitution-03-allylic-substitution</x:v>
       </x:c>
       <x:c r="K150" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-04-free-radical-substitution-03-allylic-substitution</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-04-free-radical-substitution-03-allylic-substitution</x:v>
       </x:c>
       <x:c r="L150" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-04-free-radical-substitution-03-allylic-substitution/comments/comments-04-free-radical-substitution-03-allylic-substitution.raw.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-04-free-radical-substitution-03-allylic-substitution/comments/comments-04-free-radical-substitution-03-allylic-substitution.raw.json</x:v>
       </x:c>
       <x:c r="M150" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-04-free-radical-substitution-03-allylic-substitution/comments/comments-04-free-radical-substitution-03-allylic-substitution.scrubbed.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-04-free-radical-substitution-03-allylic-substitution/comments/comments-04-free-radical-substitution-03-allylic-substitution.scrubbed.json</x:v>
       </x:c>
       <x:c r="N150" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-04-free-radical-substitution-03-allylic-substitution/comments/comments-04-free-radical-substitution-03-allylic-substitution.final.md</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-04-free-radical-substitution-03-allylic-substitution/comments/comments-04-free-radical-substitution-03-allylic-substitution.final.md</x:v>
       </x:c>
       <x:c r="O150" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -8302,7 +8319,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q150" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
@@ -8316,13 +8333,13 @@
         <x:v>Organic Chemistry: Reaction Mechanism</x:v>
       </x:c>
       <x:c r="D151" s="4" t="str">
-        <x:v>reaction-mechanism</x:v>
+        <x:v>organic-chemistry-reaction-mechanism</x:v>
       </x:c>
       <x:c r="E151" s="4" t="str">
         <x:v>05</x:v>
       </x:c>
       <x:c r="F151" s="4" t="str">
-        <x:v>reaction-mechanism-lecture-05</x:v>
+        <x:v>organic-chemistry-reaction-mechanism-lecture-05</x:v>
       </x:c>
       <x:c r="G151" s="4" t="str">
         <x:v>Electrophilic Substitution 01: Chlorination, Nitration in Benzene</x:v>
@@ -8337,16 +8354,16 @@
         <x:v>comments-05-electrophilic-substitution-01-chlorination-nitration-in-benzene</x:v>
       </x:c>
       <x:c r="K151" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-05-electrophilic-substitution-01-chlorination-nitration-in-benzene</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-05-electrophilic-substitution-01-chlorination-nitration-in-benzene</x:v>
       </x:c>
       <x:c r="L151" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-05-electrophilic-substitution-01-chlorination-nitration-in-benzene/comments/comments-05-electrophilic-substitution-01-chlorination-nitration-in-benzene.raw.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-05-electrophilic-substitution-01-chlorination-nitration-in-benzene/comments/comments-05-electrophilic-substitution-01-chlorination-nitration-in-benzene.raw.json</x:v>
       </x:c>
       <x:c r="M151" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-05-electrophilic-substitution-01-chlorination-nitration-in-benzene/comments/comments-05-electrophilic-substitution-01-chlorination-nitration-in-benzene.scrubbed.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-05-electrophilic-substitution-01-chlorination-nitration-in-benzene/comments/comments-05-electrophilic-substitution-01-chlorination-nitration-in-benzene.scrubbed.json</x:v>
       </x:c>
       <x:c r="N151" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-05-electrophilic-substitution-01-chlorination-nitration-in-benzene/comments/comments-05-electrophilic-substitution-01-chlorination-nitration-in-benzene.final.md</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-05-electrophilic-substitution-01-chlorination-nitration-in-benzene/comments/comments-05-electrophilic-substitution-01-chlorination-nitration-in-benzene.final.md</x:v>
       </x:c>
       <x:c r="O151" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -8355,7 +8372,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q151" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
@@ -8369,13 +8386,13 @@
         <x:v>Organic Chemistry: Reaction Mechanism</x:v>
       </x:c>
       <x:c r="D152" s="4" t="str">
-        <x:v>reaction-mechanism</x:v>
+        <x:v>organic-chemistry-reaction-mechanism</x:v>
       </x:c>
       <x:c r="E152" s="4" t="str">
         <x:v>06</x:v>
       </x:c>
       <x:c r="F152" s="4" t="str">
-        <x:v>reaction-mechanism-lecture-06</x:v>
+        <x:v>organic-chemistry-reaction-mechanism-lecture-06</x:v>
       </x:c>
       <x:c r="G152" s="4" t="str">
         <x:v>Electrophilic Substitution 02: Friedel-Crafts Reaction</x:v>
@@ -8390,16 +8407,16 @@
         <x:v>comments-06-electrophilic-substitution-02-friedel-crafts-reaction</x:v>
       </x:c>
       <x:c r="K152" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-06-electrophilic-substitution-02-friedel-crafts-reaction</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-06-electrophilic-substitution-02-friedel-crafts-reaction</x:v>
       </x:c>
       <x:c r="L152" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-06-electrophilic-substitution-02-friedel-crafts-reaction/comments/comments-06-electrophilic-substitution-02-friedel-crafts-reaction.raw.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-06-electrophilic-substitution-02-friedel-crafts-reaction/comments/comments-06-electrophilic-substitution-02-friedel-crafts-reaction.raw.json</x:v>
       </x:c>
       <x:c r="M152" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-06-electrophilic-substitution-02-friedel-crafts-reaction/comments/comments-06-electrophilic-substitution-02-friedel-crafts-reaction.scrubbed.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-06-electrophilic-substitution-02-friedel-crafts-reaction/comments/comments-06-electrophilic-substitution-02-friedel-crafts-reaction.scrubbed.json</x:v>
       </x:c>
       <x:c r="N152" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-06-electrophilic-substitution-02-friedel-crafts-reaction/comments/comments-06-electrophilic-substitution-02-friedel-crafts-reaction.final.md</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-06-electrophilic-substitution-02-friedel-crafts-reaction/comments/comments-06-electrophilic-substitution-02-friedel-crafts-reaction.final.md</x:v>
       </x:c>
       <x:c r="O152" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -8408,7 +8425,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q152" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
@@ -8422,13 +8439,13 @@
         <x:v>Organic Chemistry: Reaction Mechanism</x:v>
       </x:c>
       <x:c r="D153" s="4" t="str">
-        <x:v>reaction-mechanism</x:v>
+        <x:v>organic-chemistry-reaction-mechanism</x:v>
       </x:c>
       <x:c r="E153" s="4" t="str">
         <x:v>07</x:v>
       </x:c>
       <x:c r="F153" s="4" t="str">
-        <x:v>reaction-mechanism-lecture-07</x:v>
+        <x:v>organic-chemistry-reaction-mechanism-lecture-07</x:v>
       </x:c>
       <x:c r="G153" s="4" t="str">
         <x:v>Electrophilic Substitution 03: Effect of Substituent on Reactivity of Benzene</x:v>
@@ -8443,16 +8460,16 @@
         <x:v>comments-07-electrophilic-substitution-03-effect-of-substituent-on-reactivity-of-benzene</x:v>
       </x:c>
       <x:c r="K153" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-07-electrophilic-substitution-03-effect-of-substituent-on-reactivity-of-benzene</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-07-electrophilic-substitution-03-effect-of-substituent-on-reactivity-of-benzene</x:v>
       </x:c>
       <x:c r="L153" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-07-electrophilic-substitution-03-effect-of-substituent-on-reactivity-of-benzene/comments/comments-07-electrophilic-substitution-03-effect-of-substituent-on-reactivity-of-benzene.raw.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-07-electrophilic-substitution-03-effect-of-substituent-on-reactivity-of-benzene/comments/comments-07-electrophilic-substitution-03-effect-of-substituent-on-reactivity-of-benzene.raw.json</x:v>
       </x:c>
       <x:c r="M153" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-07-electrophilic-substitution-03-effect-of-substituent-on-reactivity-of-benzene/comments/comments-07-electrophilic-substitution-03-effect-of-substituent-on-reactivity-of-benzene.scrubbed.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-07-electrophilic-substitution-03-effect-of-substituent-on-reactivity-of-benzene/comments/comments-07-electrophilic-substitution-03-effect-of-substituent-on-reactivity-of-benzene.scrubbed.json</x:v>
       </x:c>
       <x:c r="N153" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-07-electrophilic-substitution-03-effect-of-substituent-on-reactivity-of-benzene/comments/comments-07-electrophilic-substitution-03-effect-of-substituent-on-reactivity-of-benzene.final.md</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-07-electrophilic-substitution-03-effect-of-substituent-on-reactivity-of-benzene/comments/comments-07-electrophilic-substitution-03-effect-of-substituent-on-reactivity-of-benzene.final.md</x:v>
       </x:c>
       <x:c r="O153" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -8461,7 +8478,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q153" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
@@ -8475,13 +8492,13 @@
         <x:v>Organic Chemistry: Reaction Mechanism</x:v>
       </x:c>
       <x:c r="D154" s="4" t="str">
-        <x:v>reaction-mechanism</x:v>
+        <x:v>organic-chemistry-reaction-mechanism</x:v>
       </x:c>
       <x:c r="E154" s="4" t="str">
         <x:v>08</x:v>
       </x:c>
       <x:c r="F154" s="4" t="str">
-        <x:v>reaction-mechanism-lecture-08</x:v>
+        <x:v>organic-chemistry-reaction-mechanism-lecture-08</x:v>
       </x:c>
       <x:c r="G154" s="4" t="str">
         <x:v>Nucleophilic Substitution 01: Leaving Group Tendency</x:v>
@@ -8496,16 +8513,16 @@
         <x:v>comments-08-nucleophilic-substitution-01-leaving-group-tendency</x:v>
       </x:c>
       <x:c r="K154" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-08-nucleophilic-substitution-01-leaving-group-tendency</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-08-nucleophilic-substitution-01-leaving-group-tendency</x:v>
       </x:c>
       <x:c r="L154" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-08-nucleophilic-substitution-01-leaving-group-tendency/comments/comments-08-nucleophilic-substitution-01-leaving-group-tendency.raw.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-08-nucleophilic-substitution-01-leaving-group-tendency/comments/comments-08-nucleophilic-substitution-01-leaving-group-tendency.raw.json</x:v>
       </x:c>
       <x:c r="M154" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-08-nucleophilic-substitution-01-leaving-group-tendency/comments/comments-08-nucleophilic-substitution-01-leaving-group-tendency.scrubbed.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-08-nucleophilic-substitution-01-leaving-group-tendency/comments/comments-08-nucleophilic-substitution-01-leaving-group-tendency.scrubbed.json</x:v>
       </x:c>
       <x:c r="N154" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-08-nucleophilic-substitution-01-leaving-group-tendency/comments/comments-08-nucleophilic-substitution-01-leaving-group-tendency.final.md</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-08-nucleophilic-substitution-01-leaving-group-tendency/comments/comments-08-nucleophilic-substitution-01-leaving-group-tendency.final.md</x:v>
       </x:c>
       <x:c r="O154" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -8514,7 +8531,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q154" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
@@ -8528,13 +8545,13 @@
         <x:v>Organic Chemistry: Reaction Mechanism</x:v>
       </x:c>
       <x:c r="D155" s="4" t="str">
-        <x:v>reaction-mechanism</x:v>
+        <x:v>organic-chemistry-reaction-mechanism</x:v>
       </x:c>
       <x:c r="E155" s="4" t="str">
         <x:v>09</x:v>
       </x:c>
       <x:c r="F155" s="4" t="str">
-        <x:v>reaction-mechanism-lecture-09</x:v>
+        <x:v>organic-chemistry-reaction-mechanism-lecture-09</x:v>
       </x:c>
       <x:c r="G155" s="4" t="str">
         <x:v>Nucleophilic Substitution 02: SN1 Reaction and Mechanism</x:v>
@@ -8549,16 +8566,16 @@
         <x:v>comments-09-nucleophilic-substitution-02-sn1-reaction-and-mechanism</x:v>
       </x:c>
       <x:c r="K155" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-09-nucleophilic-substitution-02-sn1-reaction-and-mechanism</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-09-nucleophilic-substitution-02-sn1-reaction-and-mechanism</x:v>
       </x:c>
       <x:c r="L155" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-09-nucleophilic-substitution-02-sn1-reaction-and-mechanism/comments/comments-09-nucleophilic-substitution-02-sn1-reaction-and-mechanism.raw.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-09-nucleophilic-substitution-02-sn1-reaction-and-mechanism/comments/comments-09-nucleophilic-substitution-02-sn1-reaction-and-mechanism.raw.json</x:v>
       </x:c>
       <x:c r="M155" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-09-nucleophilic-substitution-02-sn1-reaction-and-mechanism/comments/comments-09-nucleophilic-substitution-02-sn1-reaction-and-mechanism.scrubbed.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-09-nucleophilic-substitution-02-sn1-reaction-and-mechanism/comments/comments-09-nucleophilic-substitution-02-sn1-reaction-and-mechanism.scrubbed.json</x:v>
       </x:c>
       <x:c r="N155" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-09-nucleophilic-substitution-02-sn1-reaction-and-mechanism/comments/comments-09-nucleophilic-substitution-02-sn1-reaction-and-mechanism.final.md</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-09-nucleophilic-substitution-02-sn1-reaction-and-mechanism/comments/comments-09-nucleophilic-substitution-02-sn1-reaction-and-mechanism.final.md</x:v>
       </x:c>
       <x:c r="O155" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -8567,7 +8584,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q155" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
@@ -8581,13 +8598,13 @@
         <x:v>Organic Chemistry: Reaction Mechanism</x:v>
       </x:c>
       <x:c r="D156" s="4" t="str">
-        <x:v>reaction-mechanism</x:v>
+        <x:v>organic-chemistry-reaction-mechanism</x:v>
       </x:c>
       <x:c r="E156" s="4" t="str">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F156" s="4" t="str">
-        <x:v>reaction-mechanism-lecture-10</x:v>
+        <x:v>organic-chemistry-reaction-mechanism-lecture-10</x:v>
       </x:c>
       <x:c r="G156" s="4" t="str">
         <x:v>Nucleophilic Substitution 03: SN2 Reaction and Mechanism</x:v>
@@ -8602,16 +8619,16 @@
         <x:v>comments-10-nucleophilic-substitution-03-sn2-reaction-and-mechanism</x:v>
       </x:c>
       <x:c r="K156" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-10-nucleophilic-substitution-03-sn2-reaction-and-mechanism</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-10-nucleophilic-substitution-03-sn2-reaction-and-mechanism</x:v>
       </x:c>
       <x:c r="L156" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-10-nucleophilic-substitution-03-sn2-reaction-and-mechanism/comments/comments-10-nucleophilic-substitution-03-sn2-reaction-and-mechanism.raw.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-10-nucleophilic-substitution-03-sn2-reaction-and-mechanism/comments/comments-10-nucleophilic-substitution-03-sn2-reaction-and-mechanism.raw.json</x:v>
       </x:c>
       <x:c r="M156" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-10-nucleophilic-substitution-03-sn2-reaction-and-mechanism/comments/comments-10-nucleophilic-substitution-03-sn2-reaction-and-mechanism.scrubbed.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-10-nucleophilic-substitution-03-sn2-reaction-and-mechanism/comments/comments-10-nucleophilic-substitution-03-sn2-reaction-and-mechanism.scrubbed.json</x:v>
       </x:c>
       <x:c r="N156" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-10-nucleophilic-substitution-03-sn2-reaction-and-mechanism/comments/comments-10-nucleophilic-substitution-03-sn2-reaction-and-mechanism.final.md</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-10-nucleophilic-substitution-03-sn2-reaction-and-mechanism/comments/comments-10-nucleophilic-substitution-03-sn2-reaction-and-mechanism.final.md</x:v>
       </x:c>
       <x:c r="O156" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -8620,7 +8637,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q156" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
@@ -8634,13 +8651,13 @@
         <x:v>Organic Chemistry: Reaction Mechanism</x:v>
       </x:c>
       <x:c r="D157" s="4" t="str">
-        <x:v>reaction-mechanism</x:v>
+        <x:v>organic-chemistry-reaction-mechanism</x:v>
       </x:c>
       <x:c r="E157" s="4" t="str">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F157" s="4" t="str">
-        <x:v>reaction-mechanism-lecture-11</x:v>
+        <x:v>organic-chemistry-reaction-mechanism-lecture-11</x:v>
       </x:c>
       <x:c r="G157" s="4" t="str">
         <x:v>Electrophilic Addition 01: Addition of HX to Alkene - Markovnikov's Rule</x:v>
@@ -8655,16 +8672,16 @@
         <x:v>comments-11-electrophilic-addition-01-addition-of-hx-to-alkene-markovnikovs-rule</x:v>
       </x:c>
       <x:c r="K157" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-11-electrophilic-addition-01-addition-of-hx-to-alkene-markovnikovs-rule</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-11-electrophilic-addition-01-addition-of-hx-to-alkene-markovnikovs-rule</x:v>
       </x:c>
       <x:c r="L157" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-11-electrophilic-addition-01-addition-of-hx-to-alkene-markovnikovs-rule/comments/comments-11-electrophilic-addition-01-addition-of-hx-to-alkene-markovnikovs-rule.raw.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-11-electrophilic-addition-01-addition-of-hx-to-alkene-markovnikovs-rule/comments/comments-11-electrophilic-addition-01-addition-of-hx-to-alkene-markovnikovs-rule.raw.json</x:v>
       </x:c>
       <x:c r="M157" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-11-electrophilic-addition-01-addition-of-hx-to-alkene-markovnikovs-rule/comments/comments-11-electrophilic-addition-01-addition-of-hx-to-alkene-markovnikovs-rule.scrubbed.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-11-electrophilic-addition-01-addition-of-hx-to-alkene-markovnikovs-rule/comments/comments-11-electrophilic-addition-01-addition-of-hx-to-alkene-markovnikovs-rule.scrubbed.json</x:v>
       </x:c>
       <x:c r="N157" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-11-electrophilic-addition-01-addition-of-hx-to-alkene-markovnikovs-rule/comments/comments-11-electrophilic-addition-01-addition-of-hx-to-alkene-markovnikovs-rule.final.md</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-11-electrophilic-addition-01-addition-of-hx-to-alkene-markovnikovs-rule/comments/comments-11-electrophilic-addition-01-addition-of-hx-to-alkene-markovnikovs-rule.final.md</x:v>
       </x:c>
       <x:c r="O157" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -8673,7 +8690,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q157" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="158">
@@ -8687,13 +8704,13 @@
         <x:v>Organic Chemistry: Reaction Mechanism</x:v>
       </x:c>
       <x:c r="D158" s="4" t="str">
-        <x:v>reaction-mechanism</x:v>
+        <x:v>organic-chemistry-reaction-mechanism</x:v>
       </x:c>
       <x:c r="E158" s="4" t="str">
         <x:v>12</x:v>
       </x:c>
       <x:c r="F158" s="4" t="str">
-        <x:v>reaction-mechanism-lecture-12</x:v>
+        <x:v>organic-chemistry-reaction-mechanism-lecture-12</x:v>
       </x:c>
       <x:c r="G158" s="4" t="str">
         <x:v>Free Radical Addition: Anti-Markovnikov's Rule</x:v>
@@ -8708,16 +8725,16 @@
         <x:v>comments-12-free-radical-addition-anti-markovnikovs-rule</x:v>
       </x:c>
       <x:c r="K158" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-12-free-radical-addition-anti-markovnikovs-rule</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-12-free-radical-addition-anti-markovnikovs-rule</x:v>
       </x:c>
       <x:c r="L158" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-12-free-radical-addition-anti-markovnikovs-rule/comments/comments-12-free-radical-addition-anti-markovnikovs-rule.raw.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-12-free-radical-addition-anti-markovnikovs-rule/comments/comments-12-free-radical-addition-anti-markovnikovs-rule.raw.json</x:v>
       </x:c>
       <x:c r="M158" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-12-free-radical-addition-anti-markovnikovs-rule/comments/comments-12-free-radical-addition-anti-markovnikovs-rule.scrubbed.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-12-free-radical-addition-anti-markovnikovs-rule/comments/comments-12-free-radical-addition-anti-markovnikovs-rule.scrubbed.json</x:v>
       </x:c>
       <x:c r="N158" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-12-free-radical-addition-anti-markovnikovs-rule/comments/comments-12-free-radical-addition-anti-markovnikovs-rule.final.md</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-12-free-radical-addition-anti-markovnikovs-rule/comments/comments-12-free-radical-addition-anti-markovnikovs-rule.final.md</x:v>
       </x:c>
       <x:c r="O158" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -8726,7 +8743,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q158" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
@@ -8740,13 +8757,13 @@
         <x:v>Organic Chemistry: Reaction Mechanism</x:v>
       </x:c>
       <x:c r="D159" s="4" t="str">
-        <x:v>reaction-mechanism</x:v>
+        <x:v>organic-chemistry-reaction-mechanism</x:v>
       </x:c>
       <x:c r="E159" s="4" t="str">
         <x:v>13</x:v>
       </x:c>
       <x:c r="F159" s="4" t="str">
-        <x:v>reaction-mechanism-lecture-13</x:v>
+        <x:v>organic-chemistry-reaction-mechanism-lecture-13</x:v>
       </x:c>
       <x:c r="G159" s="4" t="str">
         <x:v>Electrophilic Addition 02: Anti Addition of Bromine</x:v>
@@ -8761,16 +8778,16 @@
         <x:v>comments-13-electrophilic-addition-02-anti-addition-of-bromine</x:v>
       </x:c>
       <x:c r="K159" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-13-electrophilic-addition-02-anti-addition-of-bromine</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-13-electrophilic-addition-02-anti-addition-of-bromine</x:v>
       </x:c>
       <x:c r="L159" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-13-electrophilic-addition-02-anti-addition-of-bromine/comments/comments-13-electrophilic-addition-02-anti-addition-of-bromine.raw.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-13-electrophilic-addition-02-anti-addition-of-bromine/comments/comments-13-electrophilic-addition-02-anti-addition-of-bromine.raw.json</x:v>
       </x:c>
       <x:c r="M159" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-13-electrophilic-addition-02-anti-addition-of-bromine/comments/comments-13-electrophilic-addition-02-anti-addition-of-bromine.scrubbed.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-13-electrophilic-addition-02-anti-addition-of-bromine/comments/comments-13-electrophilic-addition-02-anti-addition-of-bromine.scrubbed.json</x:v>
       </x:c>
       <x:c r="N159" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-13-electrophilic-addition-02-anti-addition-of-bromine/comments/comments-13-electrophilic-addition-02-anti-addition-of-bromine.final.md</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-13-electrophilic-addition-02-anti-addition-of-bromine/comments/comments-13-electrophilic-addition-02-anti-addition-of-bromine.final.md</x:v>
       </x:c>
       <x:c r="O159" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -8779,7 +8796,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q159" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
@@ -8793,13 +8810,13 @@
         <x:v>Organic Chemistry: Reaction Mechanism</x:v>
       </x:c>
       <x:c r="D160" s="4" t="str">
-        <x:v>reaction-mechanism</x:v>
+        <x:v>organic-chemistry-reaction-mechanism</x:v>
       </x:c>
       <x:c r="E160" s="4" t="str">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F160" s="4" t="str">
-        <x:v>reaction-mechanism-lecture-14</x:v>
+        <x:v>organic-chemistry-reaction-mechanism-lecture-14</x:v>
       </x:c>
       <x:c r="G160" s="4" t="str">
         <x:v>Elimination Reaction 01 || E1 Reaction</x:v>
@@ -8814,16 +8831,16 @@
         <x:v>comments-14-elimination-reaction-01-e1-reaction</x:v>
       </x:c>
       <x:c r="K160" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-14-elimination-reaction-01-e1-reaction</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-14-elimination-reaction-01-e1-reaction</x:v>
       </x:c>
       <x:c r="L160" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-14-elimination-reaction-01-e1-reaction/comments/comments-14-elimination-reaction-01-e1-reaction.raw.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-14-elimination-reaction-01-e1-reaction/comments/comments-14-elimination-reaction-01-e1-reaction.raw.json</x:v>
       </x:c>
       <x:c r="M160" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-14-elimination-reaction-01-e1-reaction/comments/comments-14-elimination-reaction-01-e1-reaction.scrubbed.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-14-elimination-reaction-01-e1-reaction/comments/comments-14-elimination-reaction-01-e1-reaction.scrubbed.json</x:v>
       </x:c>
       <x:c r="N160" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-14-elimination-reaction-01-e1-reaction/comments/comments-14-elimination-reaction-01-e1-reaction.final.md</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-14-elimination-reaction-01-e1-reaction/comments/comments-14-elimination-reaction-01-e1-reaction.final.md</x:v>
       </x:c>
       <x:c r="O160" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -8832,7 +8849,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q160" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
@@ -8846,13 +8863,13 @@
         <x:v>Organic Chemistry: Reaction Mechanism</x:v>
       </x:c>
       <x:c r="D161" s="4" t="str">
-        <x:v>reaction-mechanism</x:v>
+        <x:v>organic-chemistry-reaction-mechanism</x:v>
       </x:c>
       <x:c r="E161" s="4" t="str">
         <x:v>15</x:v>
       </x:c>
       <x:c r="F161" s="4" t="str">
-        <x:v>reaction-mechanism-lecture-15</x:v>
+        <x:v>organic-chemistry-reaction-mechanism-lecture-15</x:v>
       </x:c>
       <x:c r="G161" s="4" t="str">
         <x:v>Elimination Reaction 02 || E2 Reaction</x:v>
@@ -8867,16 +8884,16 @@
         <x:v>comments-15-elimination-reaction-02-e2-reaction</x:v>
       </x:c>
       <x:c r="K161" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-15-elimination-reaction-02-e2-reaction</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-15-elimination-reaction-02-e2-reaction</x:v>
       </x:c>
       <x:c r="L161" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-15-elimination-reaction-02-e2-reaction/comments/comments-15-elimination-reaction-02-e2-reaction.raw.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-15-elimination-reaction-02-e2-reaction/comments/comments-15-elimination-reaction-02-e2-reaction.raw.json</x:v>
       </x:c>
       <x:c r="M161" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-15-elimination-reaction-02-e2-reaction/comments/comments-15-elimination-reaction-02-e2-reaction.scrubbed.json</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-15-elimination-reaction-02-e2-reaction/comments/comments-15-elimination-reaction-02-e2-reaction.scrubbed.json</x:v>
       </x:c>
       <x:c r="N161" s="4" t="str">
-        <x:v>content/chemistry/organic/reaction-mechanism/lectures/lecture-15-elimination-reaction-02-e2-reaction/comments/comments-15-elimination-reaction-02-e2-reaction.final.md</x:v>
+        <x:v>content/03-organic/04-organic-chemistry-reaction-mechanism/lectures/lecture-15-elimination-reaction-02-e2-reaction/comments/comments-15-elimination-reaction-02-e2-reaction.final.md</x:v>
       </x:c>
       <x:c r="O161" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -8885,7 +8902,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q161" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
@@ -8920,16 +8937,16 @@
         <x:v>comments-01-preparation-of-alkanes-01-reduction-of-alkene-alkyne-and-alkyl-halides</x:v>
       </x:c>
       <x:c r="K162" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-01-preparation-of-alkanes-01-reduction-of-alkene-alkyne-and-alkyl-halides</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-01-preparation-of-alkanes-01-reduction-of-alkene-alkyne-and-alkyl-halides</x:v>
       </x:c>
       <x:c r="L162" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-01-preparation-of-alkanes-01-reduction-of-alkene-alkyne-and-alkyl-halides/comments/comments-01-preparation-of-alkanes-01-reduction-of-alkene-alkyne-and-alkyl-halides.raw.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-01-preparation-of-alkanes-01-reduction-of-alkene-alkyne-and-alkyl-halides/comments/comments-01-preparation-of-alkanes-01-reduction-of-alkene-alkyne-and-alkyl-halides.raw.json</x:v>
       </x:c>
       <x:c r="M162" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-01-preparation-of-alkanes-01-reduction-of-alkene-alkyne-and-alkyl-halides/comments/comments-01-preparation-of-alkanes-01-reduction-of-alkene-alkyne-and-alkyl-halides.scrubbed.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-01-preparation-of-alkanes-01-reduction-of-alkene-alkyne-and-alkyl-halides/comments/comments-01-preparation-of-alkanes-01-reduction-of-alkene-alkyne-and-alkyl-halides.scrubbed.json</x:v>
       </x:c>
       <x:c r="N162" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-01-preparation-of-alkanes-01-reduction-of-alkene-alkyne-and-alkyl-halides/comments/comments-01-preparation-of-alkanes-01-reduction-of-alkene-alkyne-and-alkyl-halides.final.md</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-01-preparation-of-alkanes-01-reduction-of-alkene-alkyne-and-alkyl-halides/comments/comments-01-preparation-of-alkanes-01-reduction-of-alkene-alkyne-and-alkyl-halides.final.md</x:v>
       </x:c>
       <x:c r="O162" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -8938,7 +8955,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q162" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
@@ -8973,16 +8990,16 @@
         <x:v>comments-02-preparation-of-alkanes-02-wurtz-reaction-and-frankland-reaction</x:v>
       </x:c>
       <x:c r="K163" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-02-preparation-of-alkanes-02-wurtz-reaction-and-frankland-reaction</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-02-preparation-of-alkanes-02-wurtz-reaction-and-frankland-reaction</x:v>
       </x:c>
       <x:c r="L163" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-02-preparation-of-alkanes-02-wurtz-reaction-and-frankland-reaction/comments/comments-02-preparation-of-alkanes-02-wurtz-reaction-and-frankland-reaction.raw.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-02-preparation-of-alkanes-02-wurtz-reaction-and-frankland-reaction/comments/comments-02-preparation-of-alkanes-02-wurtz-reaction-and-frankland-reaction.raw.json</x:v>
       </x:c>
       <x:c r="M163" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-02-preparation-of-alkanes-02-wurtz-reaction-and-frankland-reaction/comments/comments-02-preparation-of-alkanes-02-wurtz-reaction-and-frankland-reaction.scrubbed.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-02-preparation-of-alkanes-02-wurtz-reaction-and-frankland-reaction/comments/comments-02-preparation-of-alkanes-02-wurtz-reaction-and-frankland-reaction.scrubbed.json</x:v>
       </x:c>
       <x:c r="N163" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-02-preparation-of-alkanes-02-wurtz-reaction-and-frankland-reaction/comments/comments-02-preparation-of-alkanes-02-wurtz-reaction-and-frankland-reaction.final.md</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-02-preparation-of-alkanes-02-wurtz-reaction-and-frankland-reaction/comments/comments-02-preparation-of-alkanes-02-wurtz-reaction-and-frankland-reaction.final.md</x:v>
       </x:c>
       <x:c r="O163" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -8991,7 +9008,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q163" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
@@ -9026,16 +9043,16 @@
         <x:v>comments-03-preparation-of-alkanes-03-kolbes-electrolytic-method</x:v>
       </x:c>
       <x:c r="K164" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-03-preparation-of-alkanes-03-kolbes-electrolytic-method</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-03-preparation-of-alkanes-03-kolbes-electrolytic-method</x:v>
       </x:c>
       <x:c r="L164" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-03-preparation-of-alkanes-03-kolbes-electrolytic-method/comments/comments-03-preparation-of-alkanes-03-kolbes-electrolytic-method.raw.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-03-preparation-of-alkanes-03-kolbes-electrolytic-method/comments/comments-03-preparation-of-alkanes-03-kolbes-electrolytic-method.raw.json</x:v>
       </x:c>
       <x:c r="M164" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-03-preparation-of-alkanes-03-kolbes-electrolytic-method/comments/comments-03-preparation-of-alkanes-03-kolbes-electrolytic-method.scrubbed.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-03-preparation-of-alkanes-03-kolbes-electrolytic-method/comments/comments-03-preparation-of-alkanes-03-kolbes-electrolytic-method.scrubbed.json</x:v>
       </x:c>
       <x:c r="N164" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-03-preparation-of-alkanes-03-kolbes-electrolytic-method/comments/comments-03-preparation-of-alkanes-03-kolbes-electrolytic-method.final.md</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-03-preparation-of-alkanes-03-kolbes-electrolytic-method/comments/comments-03-preparation-of-alkanes-03-kolbes-electrolytic-method.final.md</x:v>
       </x:c>
       <x:c r="O164" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -9044,7 +9061,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q164" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="165">
@@ -9079,16 +9096,16 @@
         <x:v>comments-04-preparation-of-alkanes-04-soda-lime-decarboxylation</x:v>
       </x:c>
       <x:c r="K165" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-04-preparation-of-alkanes-04-soda-lime-decarboxylation</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-04-preparation-of-alkanes-04-soda-lime-decarboxylation</x:v>
       </x:c>
       <x:c r="L165" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-04-preparation-of-alkanes-04-soda-lime-decarboxylation/comments/comments-04-preparation-of-alkanes-04-soda-lime-decarboxylation.raw.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-04-preparation-of-alkanes-04-soda-lime-decarboxylation/comments/comments-04-preparation-of-alkanes-04-soda-lime-decarboxylation.raw.json</x:v>
       </x:c>
       <x:c r="M165" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-04-preparation-of-alkanes-04-soda-lime-decarboxylation/comments/comments-04-preparation-of-alkanes-04-soda-lime-decarboxylation.scrubbed.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-04-preparation-of-alkanes-04-soda-lime-decarboxylation/comments/comments-04-preparation-of-alkanes-04-soda-lime-decarboxylation.scrubbed.json</x:v>
       </x:c>
       <x:c r="N165" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-04-preparation-of-alkanes-04-soda-lime-decarboxylation/comments/comments-04-preparation-of-alkanes-04-soda-lime-decarboxylation.final.md</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-04-preparation-of-alkanes-04-soda-lime-decarboxylation/comments/comments-04-preparation-of-alkanes-04-soda-lime-decarboxylation.final.md</x:v>
       </x:c>
       <x:c r="O165" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -9097,7 +9114,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q165" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="166">
@@ -9132,16 +9149,16 @@
         <x:v>comments-05-preparation-of-alkanes-05-clemenson-and-wolf-kishner-reduction-red-p-hi-method</x:v>
       </x:c>
       <x:c r="K166" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-05-preparation-of-alkanes-05-clemenson-and-wolf-kishner-reduction-red-p-hi-method</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-05-preparation-of-alkanes-05-clemenson-and-wolf-kishner-reduction-red-p-hi-method</x:v>
       </x:c>
       <x:c r="L166" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-05-preparation-of-alkanes-05-clemenson-and-wolf-kishner-reduction-red-p-hi-method/comments/comments-05-preparation-of-alkanes-05-clemenson-and-wolf-kishner-reduction-red-p-hi-method.raw.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-05-preparation-of-alkanes-05-clemenson-and-wolf-kishner-reduction-red-p-hi-method/comments/comments-05-preparation-of-alkanes-05-clemenson-and-wolf-kishner-reduction-red-p-hi-method.raw.json</x:v>
       </x:c>
       <x:c r="M166" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-05-preparation-of-alkanes-05-clemenson-and-wolf-kishner-reduction-red-p-hi-method/comments/comments-05-preparation-of-alkanes-05-clemenson-and-wolf-kishner-reduction-red-p-hi-method.scrubbed.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-05-preparation-of-alkanes-05-clemenson-and-wolf-kishner-reduction-red-p-hi-method/comments/comments-05-preparation-of-alkanes-05-clemenson-and-wolf-kishner-reduction-red-p-hi-method.scrubbed.json</x:v>
       </x:c>
       <x:c r="N166" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-05-preparation-of-alkanes-05-clemenson-and-wolf-kishner-reduction-red-p-hi-method/comments/comments-05-preparation-of-alkanes-05-clemenson-and-wolf-kishner-reduction-red-p-hi-method.final.md</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-05-preparation-of-alkanes-05-clemenson-and-wolf-kishner-reduction-red-p-hi-method/comments/comments-05-preparation-of-alkanes-05-clemenson-and-wolf-kishner-reduction-red-p-hi-method.final.md</x:v>
       </x:c>
       <x:c r="O166" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -9150,7 +9167,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q166" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
@@ -9185,16 +9202,16 @@
         <x:v>comments-06-preparation-of-alkanes-06-from-grignards-reagant-and-corey-house-synthesis-jee</x:v>
       </x:c>
       <x:c r="K167" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-06-preparation-of-alkanes-06-from-grignards-reagant-and-corey-house-synthesis-jee</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-06-preparation-of-alkanes-06-from-grignards-reagant-and-corey-house-synthesis-jee</x:v>
       </x:c>
       <x:c r="L167" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-06-preparation-of-alkanes-06-from-grignards-reagant-and-corey-house-synthesis-jee/comments/comments-06-preparation-of-alkanes-06-from-grignards-reagant-and-corey-house-synthesis-jee.raw.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-06-preparation-of-alkanes-06-from-grignards-reagant-and-corey-house-synthesis-jee/comments/comments-06-preparation-of-alkanes-06-from-grignards-reagant-and-corey-house-synthesis-jee.raw.json</x:v>
       </x:c>
       <x:c r="M167" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-06-preparation-of-alkanes-06-from-grignards-reagant-and-corey-house-synthesis-jee/comments/comments-06-preparation-of-alkanes-06-from-grignards-reagant-and-corey-house-synthesis-jee.scrubbed.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-06-preparation-of-alkanes-06-from-grignards-reagant-and-corey-house-synthesis-jee/comments/comments-06-preparation-of-alkanes-06-from-grignards-reagant-and-corey-house-synthesis-jee.scrubbed.json</x:v>
       </x:c>
       <x:c r="N167" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-06-preparation-of-alkanes-06-from-grignards-reagant-and-corey-house-synthesis-jee/comments/comments-06-preparation-of-alkanes-06-from-grignards-reagant-and-corey-house-synthesis-jee.final.md</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-06-preparation-of-alkanes-06-from-grignards-reagant-and-corey-house-synthesis-jee/comments/comments-06-preparation-of-alkanes-06-from-grignards-reagant-and-corey-house-synthesis-jee.final.md</x:v>
       </x:c>
       <x:c r="O167" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -9203,7 +9220,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q167" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
@@ -9238,16 +9255,16 @@
         <x:v>comments-07-properties-of-alkanes-01-halogenation-of-alkane-compilation-of-previous-videos</x:v>
       </x:c>
       <x:c r="K168" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-07-properties-of-alkanes-01-halogenation-of-alkane-compilation-of-previous-videos</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-07-properties-of-alkanes-01-halogenation-of-alkane-compilation-of-previous-videos</x:v>
       </x:c>
       <x:c r="L168" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-07-properties-of-alkanes-01-halogenation-of-alkane-compilation-of-previous-videos/comments/comments-07-properties-of-alkanes-01-halogenation-of-alkane-compilation-of-previous-videos.raw.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-07-properties-of-alkanes-01-halogenation-of-alkane-compilation-of-previous-videos/comments/comments-07-properties-of-alkanes-01-halogenation-of-alkane-compilation-of-previous-videos.raw.json</x:v>
       </x:c>
       <x:c r="M168" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-07-properties-of-alkanes-01-halogenation-of-alkane-compilation-of-previous-videos/comments/comments-07-properties-of-alkanes-01-halogenation-of-alkane-compilation-of-previous-videos.scrubbed.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-07-properties-of-alkanes-01-halogenation-of-alkane-compilation-of-previous-videos/comments/comments-07-properties-of-alkanes-01-halogenation-of-alkane-compilation-of-previous-videos.scrubbed.json</x:v>
       </x:c>
       <x:c r="N168" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-07-properties-of-alkanes-01-halogenation-of-alkane-compilation-of-previous-videos/comments/comments-07-properties-of-alkanes-01-halogenation-of-alkane-compilation-of-previous-videos.final.md</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-07-properties-of-alkanes-01-halogenation-of-alkane-compilation-of-previous-videos/comments/comments-07-properties-of-alkanes-01-halogenation-of-alkane-compilation-of-previous-videos.final.md</x:v>
       </x:c>
       <x:c r="O168" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -9256,7 +9273,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q168" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="169">
@@ -9291,16 +9308,16 @@
         <x:v>comments-08-properties-of-alkanes-02-nitration-sulphonation-pyrolysis-aromatization</x:v>
       </x:c>
       <x:c r="K169" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-08-properties-of-alkanes-02-nitration-sulphonation-pyrolysis-aromatization</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-08-properties-of-alkanes-02-nitration-sulphonation-pyrolysis-aromatization</x:v>
       </x:c>
       <x:c r="L169" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-08-properties-of-alkanes-02-nitration-sulphonation-pyrolysis-aromatization/comments/comments-08-properties-of-alkanes-02-nitration-sulphonation-pyrolysis-aromatization.raw.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-08-properties-of-alkanes-02-nitration-sulphonation-pyrolysis-aromatization/comments/comments-08-properties-of-alkanes-02-nitration-sulphonation-pyrolysis-aromatization.raw.json</x:v>
       </x:c>
       <x:c r="M169" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-08-properties-of-alkanes-02-nitration-sulphonation-pyrolysis-aromatization/comments/comments-08-properties-of-alkanes-02-nitration-sulphonation-pyrolysis-aromatization.scrubbed.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-08-properties-of-alkanes-02-nitration-sulphonation-pyrolysis-aromatization/comments/comments-08-properties-of-alkanes-02-nitration-sulphonation-pyrolysis-aromatization.scrubbed.json</x:v>
       </x:c>
       <x:c r="N169" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-08-properties-of-alkanes-02-nitration-sulphonation-pyrolysis-aromatization/comments/comments-08-properties-of-alkanes-02-nitration-sulphonation-pyrolysis-aromatization.final.md</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-08-properties-of-alkanes-02-nitration-sulphonation-pyrolysis-aromatization/comments/comments-08-properties-of-alkanes-02-nitration-sulphonation-pyrolysis-aromatization.final.md</x:v>
       </x:c>
       <x:c r="O169" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -9309,7 +9326,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q169" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="170">
@@ -9344,16 +9361,16 @@
         <x:v>comments-09-properties-of-alkanes-03-oxidation-catalytic-oxidation-and-combustion</x:v>
       </x:c>
       <x:c r="K170" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-09-properties-of-alkanes-03-oxidation-catalytic-oxidation-and-combustion</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-09-properties-of-alkanes-03-oxidation-catalytic-oxidation-and-combustion</x:v>
       </x:c>
       <x:c r="L170" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-09-properties-of-alkanes-03-oxidation-catalytic-oxidation-and-combustion/comments/comments-09-properties-of-alkanes-03-oxidation-catalytic-oxidation-and-combustion.raw.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-09-properties-of-alkanes-03-oxidation-catalytic-oxidation-and-combustion/comments/comments-09-properties-of-alkanes-03-oxidation-catalytic-oxidation-and-combustion.raw.json</x:v>
       </x:c>
       <x:c r="M170" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-09-properties-of-alkanes-03-oxidation-catalytic-oxidation-and-combustion/comments/comments-09-properties-of-alkanes-03-oxidation-catalytic-oxidation-and-combustion.scrubbed.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-09-properties-of-alkanes-03-oxidation-catalytic-oxidation-and-combustion/comments/comments-09-properties-of-alkanes-03-oxidation-catalytic-oxidation-and-combustion.scrubbed.json</x:v>
       </x:c>
       <x:c r="N170" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-09-properties-of-alkanes-03-oxidation-catalytic-oxidation-and-combustion/comments/comments-09-properties-of-alkanes-03-oxidation-catalytic-oxidation-and-combustion.final.md</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-09-properties-of-alkanes-03-oxidation-catalytic-oxidation-and-combustion/comments/comments-09-properties-of-alkanes-03-oxidation-catalytic-oxidation-and-combustion.final.md</x:v>
       </x:c>
       <x:c r="O170" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -9362,7 +9379,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q170" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="171">
@@ -9397,16 +9414,16 @@
         <x:v>comments-10-preparation-of-alkenes-1-dehydration-of-alcohols-and-from-alkyl-halide</x:v>
       </x:c>
       <x:c r="K171" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-10-preparation-of-alkenes-1-dehydration-of-alcohols-and-from-alkyl-halide</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-10-preparation-of-alkenes-1-dehydration-of-alcohols-and-from-alkyl-halide</x:v>
       </x:c>
       <x:c r="L171" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-10-preparation-of-alkenes-1-dehydration-of-alcohols-and-from-alkyl-halide/comments/comments-10-preparation-of-alkenes-1-dehydration-of-alcohols-and-from-alkyl-halide.raw.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-10-preparation-of-alkenes-1-dehydration-of-alcohols-and-from-alkyl-halide/comments/comments-10-preparation-of-alkenes-1-dehydration-of-alcohols-and-from-alkyl-halide.raw.json</x:v>
       </x:c>
       <x:c r="M171" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-10-preparation-of-alkenes-1-dehydration-of-alcohols-and-from-alkyl-halide/comments/comments-10-preparation-of-alkenes-1-dehydration-of-alcohols-and-from-alkyl-halide.scrubbed.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-10-preparation-of-alkenes-1-dehydration-of-alcohols-and-from-alkyl-halide/comments/comments-10-preparation-of-alkenes-1-dehydration-of-alcohols-and-from-alkyl-halide.scrubbed.json</x:v>
       </x:c>
       <x:c r="N171" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-10-preparation-of-alkenes-1-dehydration-of-alcohols-and-from-alkyl-halide/comments/comments-10-preparation-of-alkenes-1-dehydration-of-alcohols-and-from-alkyl-halide.final.md</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-10-preparation-of-alkenes-1-dehydration-of-alcohols-and-from-alkyl-halide/comments/comments-10-preparation-of-alkenes-1-dehydration-of-alcohols-and-from-alkyl-halide.final.md</x:v>
       </x:c>
       <x:c r="O171" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -9415,7 +9432,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q171" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
@@ -9450,16 +9467,16 @@
         <x:v>comments-11-preparation-of-alkenes-2-from-alkyne-birch-reduction-and-lindlars-catalyst</x:v>
       </x:c>
       <x:c r="K172" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-11-preparation-of-alkenes-2-from-alkyne-birch-reduction-and-lindlars-catalyst</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-11-preparation-of-alkenes-2-from-alkyne-birch-reduction-and-lindlars-catalyst</x:v>
       </x:c>
       <x:c r="L172" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-11-preparation-of-alkenes-2-from-alkyne-birch-reduction-and-lindlars-catalyst/comments/comments-11-preparation-of-alkenes-2-from-alkyne-birch-reduction-and-lindlars-catalyst.raw.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-11-preparation-of-alkenes-2-from-alkyne-birch-reduction-and-lindlars-catalyst/comments/comments-11-preparation-of-alkenes-2-from-alkyne-birch-reduction-and-lindlars-catalyst.raw.json</x:v>
       </x:c>
       <x:c r="M172" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-11-preparation-of-alkenes-2-from-alkyne-birch-reduction-and-lindlars-catalyst/comments/comments-11-preparation-of-alkenes-2-from-alkyne-birch-reduction-and-lindlars-catalyst.scrubbed.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-11-preparation-of-alkenes-2-from-alkyne-birch-reduction-and-lindlars-catalyst/comments/comments-11-preparation-of-alkenes-2-from-alkyne-birch-reduction-and-lindlars-catalyst.scrubbed.json</x:v>
       </x:c>
       <x:c r="N172" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-11-preparation-of-alkenes-2-from-alkyne-birch-reduction-and-lindlars-catalyst/comments/comments-11-preparation-of-alkenes-2-from-alkyne-birch-reduction-and-lindlars-catalyst.final.md</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-11-preparation-of-alkenes-2-from-alkyne-birch-reduction-and-lindlars-catalyst/comments/comments-11-preparation-of-alkenes-2-from-alkyne-birch-reduction-and-lindlars-catalyst.final.md</x:v>
       </x:c>
       <x:c r="O172" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -9468,7 +9485,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q172" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="173">
@@ -9503,16 +9520,16 @@
         <x:v>comments-12-properties-of-alkenes-1-addition-of-hydrogen-halogen-and-halogen-acid</x:v>
       </x:c>
       <x:c r="K173" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-12-properties-of-alkenes-1-addition-of-hydrogen-halogen-and-halogen-acid</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-12-properties-of-alkenes-1-addition-of-hydrogen-halogen-and-halogen-acid</x:v>
       </x:c>
       <x:c r="L173" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-12-properties-of-alkenes-1-addition-of-hydrogen-halogen-and-halogen-acid/comments/comments-12-properties-of-alkenes-1-addition-of-hydrogen-halogen-and-halogen-acid.raw.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-12-properties-of-alkenes-1-addition-of-hydrogen-halogen-and-halogen-acid/comments/comments-12-properties-of-alkenes-1-addition-of-hydrogen-halogen-and-halogen-acid.raw.json</x:v>
       </x:c>
       <x:c r="M173" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-12-properties-of-alkenes-1-addition-of-hydrogen-halogen-and-halogen-acid/comments/comments-12-properties-of-alkenes-1-addition-of-hydrogen-halogen-and-halogen-acid.scrubbed.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-12-properties-of-alkenes-1-addition-of-hydrogen-halogen-and-halogen-acid/comments/comments-12-properties-of-alkenes-1-addition-of-hydrogen-halogen-and-halogen-acid.scrubbed.json</x:v>
       </x:c>
       <x:c r="N173" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-12-properties-of-alkenes-1-addition-of-hydrogen-halogen-and-halogen-acid/comments/comments-12-properties-of-alkenes-1-addition-of-hydrogen-halogen-and-halogen-acid.final.md</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-12-properties-of-alkenes-1-addition-of-hydrogen-halogen-and-halogen-acid/comments/comments-12-properties-of-alkenes-1-addition-of-hydrogen-halogen-and-halogen-acid.final.md</x:v>
       </x:c>
       <x:c r="O173" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -9521,7 +9538,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q173" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="174">
@@ -9556,16 +9573,16 @@
         <x:v>comments-13-properties-of-alkenes-2-addition-of-water-acid-catalyzed-hydration-of-alkene</x:v>
       </x:c>
       <x:c r="K174" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-13-properties-of-alkenes-2-addition-of-water-acid-catalyzed-hydration-of-alkene</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-13-properties-of-alkenes-2-addition-of-water-acid-catalyzed-hydration-of-alkene</x:v>
       </x:c>
       <x:c r="L174" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-13-properties-of-alkenes-2-addition-of-water-acid-catalyzed-hydration-of-alkene/comments/comments-13-properties-of-alkenes-2-addition-of-water-acid-catalyzed-hydration-of-alkene.raw.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-13-properties-of-alkenes-2-addition-of-water-acid-catalyzed-hydration-of-alkene/comments/comments-13-properties-of-alkenes-2-addition-of-water-acid-catalyzed-hydration-of-alkene.raw.json</x:v>
       </x:c>
       <x:c r="M174" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-13-properties-of-alkenes-2-addition-of-water-acid-catalyzed-hydration-of-alkene/comments/comments-13-properties-of-alkenes-2-addition-of-water-acid-catalyzed-hydration-of-alkene.scrubbed.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-13-properties-of-alkenes-2-addition-of-water-acid-catalyzed-hydration-of-alkene/comments/comments-13-properties-of-alkenes-2-addition-of-water-acid-catalyzed-hydration-of-alkene.scrubbed.json</x:v>
       </x:c>
       <x:c r="N174" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-13-properties-of-alkenes-2-addition-of-water-acid-catalyzed-hydration-of-alkene/comments/comments-13-properties-of-alkenes-2-addition-of-water-acid-catalyzed-hydration-of-alkene.final.md</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-13-properties-of-alkenes-2-addition-of-water-acid-catalyzed-hydration-of-alkene/comments/comments-13-properties-of-alkenes-2-addition-of-water-acid-catalyzed-hydration-of-alkene.final.md</x:v>
       </x:c>
       <x:c r="O174" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -9574,7 +9591,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q174" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
@@ -9609,16 +9626,16 @@
         <x:v>comments-14-properties-of-alkenes-3-addition-of-water-hydroboration-oxidation</x:v>
       </x:c>
       <x:c r="K175" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-14-properties-of-alkenes-3-addition-of-water-hydroboration-oxidation</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-14-properties-of-alkenes-3-addition-of-water-hydroboration-oxidation</x:v>
       </x:c>
       <x:c r="L175" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-14-properties-of-alkenes-3-addition-of-water-hydroboration-oxidation/comments/comments-14-properties-of-alkenes-3-addition-of-water-hydroboration-oxidation.raw.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-14-properties-of-alkenes-3-addition-of-water-hydroboration-oxidation/comments/comments-14-properties-of-alkenes-3-addition-of-water-hydroboration-oxidation.raw.json</x:v>
       </x:c>
       <x:c r="M175" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-14-properties-of-alkenes-3-addition-of-water-hydroboration-oxidation/comments/comments-14-properties-of-alkenes-3-addition-of-water-hydroboration-oxidation.scrubbed.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-14-properties-of-alkenes-3-addition-of-water-hydroboration-oxidation/comments/comments-14-properties-of-alkenes-3-addition-of-water-hydroboration-oxidation.scrubbed.json</x:v>
       </x:c>
       <x:c r="N175" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-14-properties-of-alkenes-3-addition-of-water-hydroboration-oxidation/comments/comments-14-properties-of-alkenes-3-addition-of-water-hydroboration-oxidation.final.md</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-14-properties-of-alkenes-3-addition-of-water-hydroboration-oxidation/comments/comments-14-properties-of-alkenes-3-addition-of-water-hydroboration-oxidation.final.md</x:v>
       </x:c>
       <x:c r="O175" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -9627,7 +9644,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q175" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="176">
@@ -9662,16 +9679,16 @@
         <x:v>comments-15-properties-of-alkenes-4-addition-of-water-oxymercuration-demercuration</x:v>
       </x:c>
       <x:c r="K176" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-15-properties-of-alkenes-4-addition-of-water-oxymercuration-demercuration</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-15-properties-of-alkenes-4-addition-of-water-oxymercuration-demercuration</x:v>
       </x:c>
       <x:c r="L176" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-15-properties-of-alkenes-4-addition-of-water-oxymercuration-demercuration/comments/comments-15-properties-of-alkenes-4-addition-of-water-oxymercuration-demercuration.raw.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-15-properties-of-alkenes-4-addition-of-water-oxymercuration-demercuration/comments/comments-15-properties-of-alkenes-4-addition-of-water-oxymercuration-demercuration.raw.json</x:v>
       </x:c>
       <x:c r="M176" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-15-properties-of-alkenes-4-addition-of-water-oxymercuration-demercuration/comments/comments-15-properties-of-alkenes-4-addition-of-water-oxymercuration-demercuration.scrubbed.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-15-properties-of-alkenes-4-addition-of-water-oxymercuration-demercuration/comments/comments-15-properties-of-alkenes-4-addition-of-water-oxymercuration-demercuration.scrubbed.json</x:v>
       </x:c>
       <x:c r="N176" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-15-properties-of-alkenes-4-addition-of-water-oxymercuration-demercuration/comments/comments-15-properties-of-alkenes-4-addition-of-water-oxymercuration-demercuration.final.md</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-15-properties-of-alkenes-4-addition-of-water-oxymercuration-demercuration/comments/comments-15-properties-of-alkenes-4-addition-of-water-oxymercuration-demercuration.final.md</x:v>
       </x:c>
       <x:c r="O176" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -9680,7 +9697,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q176" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="177">
@@ -9715,16 +9732,16 @@
         <x:v>comments-16-properties-of-alkenes-5-ozonolysis-addition-of-ozone</x:v>
       </x:c>
       <x:c r="K177" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-16-properties-of-alkenes-5-ozonolysis-addition-of-ozone</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-16-properties-of-alkenes-5-ozonolysis-addition-of-ozone</x:v>
       </x:c>
       <x:c r="L177" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-16-properties-of-alkenes-5-ozonolysis-addition-of-ozone/comments/comments-16-properties-of-alkenes-5-ozonolysis-addition-of-ozone.raw.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-16-properties-of-alkenes-5-ozonolysis-addition-of-ozone/comments/comments-16-properties-of-alkenes-5-ozonolysis-addition-of-ozone.raw.json</x:v>
       </x:c>
       <x:c r="M177" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-16-properties-of-alkenes-5-ozonolysis-addition-of-ozone/comments/comments-16-properties-of-alkenes-5-ozonolysis-addition-of-ozone.scrubbed.json</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-16-properties-of-alkenes-5-ozonolysis-addition-of-ozone/comments/comments-16-properties-of-alkenes-5-ozonolysis-addition-of-ozone.scrubbed.json</x:v>
       </x:c>
       <x:c r="N177" s="4" t="str">
-        <x:v>content/chemistry/organic/hydrocarbons/lectures/lecture-16-properties-of-alkenes-5-ozonolysis-addition-of-ozone/comments/comments-16-properties-of-alkenes-5-ozonolysis-addition-of-ozone.final.md</x:v>
+        <x:v>content/03-organic/05-hydrocarbons/lectures/lecture-16-properties-of-alkenes-5-ozonolysis-addition-of-ozone/comments/comments-16-properties-of-alkenes-5-ozonolysis-addition-of-ozone.final.md</x:v>
       </x:c>
       <x:c r="O177" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -9733,7 +9750,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q177" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="178">
@@ -9747,13 +9764,13 @@
         <x:v>Haloalkanes and Haloarenes (Organic Compounds containing Halogens)</x:v>
       </x:c>
       <x:c r="D178" s="4" t="str">
-        <x:v>haloalkanes-and-haloarenes</x:v>
+        <x:v>haloalkanes-and-haloarenes-organic-compounds-containing-halogens</x:v>
       </x:c>
       <x:c r="E178" s="4" t="str">
         <x:v>01</x:v>
       </x:c>
       <x:c r="F178" s="4" t="str">
-        <x:v>haloalkanes-and-haloarenes-lecture-01</x:v>
+        <x:v>haloalkanes-and-haloarenes-organic-compounds-containing-halogens-lecture-01</x:v>
       </x:c>
       <x:c r="G178" s="4" t="str">
         <x:v>Preparation Of HaloAlkanes 1 - From Alkanes and Alkene</x:v>
@@ -9768,16 +9785,16 @@
         <x:v>comments-01-preparation-of-haloalkanes-1-from-alkanes-and-alkene</x:v>
       </x:c>
       <x:c r="K178" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-01-preparation-of-haloalkanes-1-from-alkanes-and-alkene</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-01-preparation-of-haloalkanes-1-from-alkanes-and-alkene</x:v>
       </x:c>
       <x:c r="L178" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-01-preparation-of-haloalkanes-1-from-alkanes-and-alkene/comments/comments-01-preparation-of-haloalkanes-1-from-alkanes-and-alkene.raw.json</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-01-preparation-of-haloalkanes-1-from-alkanes-and-alkene/comments/comments-01-preparation-of-haloalkanes-1-from-alkanes-and-alkene.raw.json</x:v>
       </x:c>
       <x:c r="M178" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-01-preparation-of-haloalkanes-1-from-alkanes-and-alkene/comments/comments-01-preparation-of-haloalkanes-1-from-alkanes-and-alkene.scrubbed.json</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-01-preparation-of-haloalkanes-1-from-alkanes-and-alkene/comments/comments-01-preparation-of-haloalkanes-1-from-alkanes-and-alkene.scrubbed.json</x:v>
       </x:c>
       <x:c r="N178" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-01-preparation-of-haloalkanes-1-from-alkanes-and-alkene/comments/comments-01-preparation-of-haloalkanes-1-from-alkanes-and-alkene.final.md</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-01-preparation-of-haloalkanes-1-from-alkanes-and-alkene/comments/comments-01-preparation-of-haloalkanes-1-from-alkanes-and-alkene.final.md</x:v>
       </x:c>
       <x:c r="O178" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -9786,7 +9803,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q178" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="179">
@@ -9800,13 +9817,13 @@
         <x:v>Haloalkanes and Haloarenes (Organic Compounds containing Halogens)</x:v>
       </x:c>
       <x:c r="D179" s="4" t="str">
-        <x:v>haloalkanes-and-haloarenes</x:v>
+        <x:v>haloalkanes-and-haloarenes-organic-compounds-containing-halogens</x:v>
       </x:c>
       <x:c r="E179" s="4" t="str">
         <x:v>02</x:v>
       </x:c>
       <x:c r="F179" s="4" t="str">
-        <x:v>haloalkanes-and-haloarenes-lecture-02</x:v>
+        <x:v>haloalkanes-and-haloarenes-organic-compounds-containing-halogens-lecture-02</x:v>
       </x:c>
       <x:c r="G179" s="4" t="str">
         <x:v>Preparation Of HaloAlkanes 2 - From Alcohols: Lucas Reagent and Others</x:v>
@@ -9821,16 +9838,16 @@
         <x:v>comments-02-preparation-of-haloalkanes-2-from-alcohols-lucas-reagent-and-others</x:v>
       </x:c>
       <x:c r="K179" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-02-preparation-of-haloalkanes-2-from-alcohols-lucas-reagent-and-others</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-02-preparation-of-haloalkanes-2-from-alcohols-lucas-reagent-and-others</x:v>
       </x:c>
       <x:c r="L179" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-02-preparation-of-haloalkanes-2-from-alcohols-lucas-reagent-and-others/comments/comments-02-preparation-of-haloalkanes-2-from-alcohols-lucas-reagent-and-others.raw.json</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-02-preparation-of-haloalkanes-2-from-alcohols-lucas-reagent-and-others/comments/comments-02-preparation-of-haloalkanes-2-from-alcohols-lucas-reagent-and-others.raw.json</x:v>
       </x:c>
       <x:c r="M179" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-02-preparation-of-haloalkanes-2-from-alcohols-lucas-reagent-and-others/comments/comments-02-preparation-of-haloalkanes-2-from-alcohols-lucas-reagent-and-others.scrubbed.json</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-02-preparation-of-haloalkanes-2-from-alcohols-lucas-reagent-and-others/comments/comments-02-preparation-of-haloalkanes-2-from-alcohols-lucas-reagent-and-others.scrubbed.json</x:v>
       </x:c>
       <x:c r="N179" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-02-preparation-of-haloalkanes-2-from-alcohols-lucas-reagent-and-others/comments/comments-02-preparation-of-haloalkanes-2-from-alcohols-lucas-reagent-and-others.final.md</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-02-preparation-of-haloalkanes-2-from-alcohols-lucas-reagent-and-others/comments/comments-02-preparation-of-haloalkanes-2-from-alcohols-lucas-reagent-and-others.final.md</x:v>
       </x:c>
       <x:c r="O179" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -9839,7 +9856,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q179" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
@@ -9853,13 +9870,13 @@
         <x:v>Haloalkanes and Haloarenes (Organic Compounds containing Halogens)</x:v>
       </x:c>
       <x:c r="D180" s="4" t="str">
-        <x:v>haloalkanes-and-haloarenes</x:v>
+        <x:v>haloalkanes-and-haloarenes-organic-compounds-containing-halogens</x:v>
       </x:c>
       <x:c r="E180" s="4" t="str">
         <x:v>03</x:v>
       </x:c>
       <x:c r="F180" s="4" t="str">
-        <x:v>haloalkanes-and-haloarenes-lecture-03</x:v>
+        <x:v>haloalkanes-and-haloarenes-organic-compounds-containing-halogens-lecture-03</x:v>
       </x:c>
       <x:c r="G180" s="4" t="str">
         <x:v>Preparation Of HaloAlkanes 3 - Halogen Exchange &amp; Hunsdiecker Method</x:v>
@@ -9874,16 +9891,16 @@
         <x:v>comments-03-preparation-of-haloalkanes-3-halogen-exchange-and-hunsdiecker-method</x:v>
       </x:c>
       <x:c r="K180" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-03-preparation-of-haloalkanes-3-halogen-exchange-and-hunsdiecker-method</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-03-preparation-of-haloalkanes-3-halogen-exchange-and-hunsdiecker-method</x:v>
       </x:c>
       <x:c r="L180" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-03-preparation-of-haloalkanes-3-halogen-exchange-and-hunsdiecker-method/comments/comments-03-preparation-of-haloalkanes-3-halogen-exchange-and-hunsdiecker-method.raw.json</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-03-preparation-of-haloalkanes-3-halogen-exchange-and-hunsdiecker-method/comments/comments-03-preparation-of-haloalkanes-3-halogen-exchange-and-hunsdiecker-method.raw.json</x:v>
       </x:c>
       <x:c r="M180" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-03-preparation-of-haloalkanes-3-halogen-exchange-and-hunsdiecker-method/comments/comments-03-preparation-of-haloalkanes-3-halogen-exchange-and-hunsdiecker-method.scrubbed.json</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-03-preparation-of-haloalkanes-3-halogen-exchange-and-hunsdiecker-method/comments/comments-03-preparation-of-haloalkanes-3-halogen-exchange-and-hunsdiecker-method.scrubbed.json</x:v>
       </x:c>
       <x:c r="N180" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-03-preparation-of-haloalkanes-3-halogen-exchange-and-hunsdiecker-method/comments/comments-03-preparation-of-haloalkanes-3-halogen-exchange-and-hunsdiecker-method.final.md</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-03-preparation-of-haloalkanes-3-halogen-exchange-and-hunsdiecker-method/comments/comments-03-preparation-of-haloalkanes-3-halogen-exchange-and-hunsdiecker-method.final.md</x:v>
       </x:c>
       <x:c r="O180" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -9892,7 +9909,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q180" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="181">
@@ -9906,13 +9923,13 @@
         <x:v>Haloalkanes and Haloarenes (Organic Compounds containing Halogens)</x:v>
       </x:c>
       <x:c r="D181" s="4" t="str">
-        <x:v>haloalkanes-and-haloarenes</x:v>
+        <x:v>haloalkanes-and-haloarenes-organic-compounds-containing-halogens</x:v>
       </x:c>
       <x:c r="E181" s="4" t="str">
         <x:v>04</x:v>
       </x:c>
       <x:c r="F181" s="4" t="str">
-        <x:v>haloalkanes-and-haloarenes-lecture-04</x:v>
+        <x:v>haloalkanes-and-haloarenes-organic-compounds-containing-halogens-lecture-04</x:v>
       </x:c>
       <x:c r="G181" s="4" t="str">
         <x:v>Properties of HaloAlkanes 1: SN1 and SN2 Reaction</x:v>
@@ -9927,16 +9944,16 @@
         <x:v>comments-04-properties-of-haloalkanes-1-sn1-and-sn2-reaction</x:v>
       </x:c>
       <x:c r="K181" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-04-properties-of-haloalkanes-1-sn1-and-sn2-reaction</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-04-properties-of-haloalkanes-1-sn1-and-sn2-reaction</x:v>
       </x:c>
       <x:c r="L181" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-04-properties-of-haloalkanes-1-sn1-and-sn2-reaction/comments/comments-04-properties-of-haloalkanes-1-sn1-and-sn2-reaction.raw.json</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-04-properties-of-haloalkanes-1-sn1-and-sn2-reaction/comments/comments-04-properties-of-haloalkanes-1-sn1-and-sn2-reaction.raw.json</x:v>
       </x:c>
       <x:c r="M181" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-04-properties-of-haloalkanes-1-sn1-and-sn2-reaction/comments/comments-04-properties-of-haloalkanes-1-sn1-and-sn2-reaction.scrubbed.json</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-04-properties-of-haloalkanes-1-sn1-and-sn2-reaction/comments/comments-04-properties-of-haloalkanes-1-sn1-and-sn2-reaction.scrubbed.json</x:v>
       </x:c>
       <x:c r="N181" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-04-properties-of-haloalkanes-1-sn1-and-sn2-reaction/comments/comments-04-properties-of-haloalkanes-1-sn1-and-sn2-reaction.final.md</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-04-properties-of-haloalkanes-1-sn1-and-sn2-reaction/comments/comments-04-properties-of-haloalkanes-1-sn1-and-sn2-reaction.final.md</x:v>
       </x:c>
       <x:c r="O181" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -9945,7 +9962,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q181" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="182">
@@ -9959,13 +9976,13 @@
         <x:v>Haloalkanes and Haloarenes (Organic Compounds containing Halogens)</x:v>
       </x:c>
       <x:c r="D182" s="4" t="str">
-        <x:v>haloalkanes-and-haloarenes</x:v>
+        <x:v>haloalkanes-and-haloarenes-organic-compounds-containing-halogens</x:v>
       </x:c>
       <x:c r="E182" s="4" t="str">
         <x:v>05</x:v>
       </x:c>
       <x:c r="F182" s="4" t="str">
-        <x:v>haloalkanes-and-haloarenes-lecture-05</x:v>
+        <x:v>haloalkanes-and-haloarenes-organic-compounds-containing-halogens-lecture-05</x:v>
       </x:c>
       <x:c r="G182" s="4" t="str">
         <x:v>Reaction with KOH / AgOH / KCN / AgCN / KNO2 / AgNO2 / NH3 / RONa / H2O</x:v>
@@ -9980,16 +9997,16 @@
         <x:v>comments-05-reaction-with-koh-agoh-kcn-agcn-kno2-agno2-nh3-rona-h2o</x:v>
       </x:c>
       <x:c r="K182" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-05-reaction-with-koh-agoh-kcn-agcn-kno2-agno2-nh3-rona-h2o</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-05-reaction-with-koh-agoh-kcn-agcn-kno2-agno2-nh3-rona-h2o</x:v>
       </x:c>
       <x:c r="L182" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-05-reaction-with-koh-agoh-kcn-agcn-kno2-agno2-nh3-rona-h2o/comments/comments-05-reaction-with-koh-agoh-kcn-agcn-kno2-agno2-nh3-rona-h2o.raw.json</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-05-reaction-with-koh-agoh-kcn-agcn-kno2-agno2-nh3-rona-h2o/comments/comments-05-reaction-with-koh-agoh-kcn-agcn-kno2-agno2-nh3-rona-h2o.raw.json</x:v>
       </x:c>
       <x:c r="M182" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-05-reaction-with-koh-agoh-kcn-agcn-kno2-agno2-nh3-rona-h2o/comments/comments-05-reaction-with-koh-agoh-kcn-agcn-kno2-agno2-nh3-rona-h2o.scrubbed.json</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-05-reaction-with-koh-agoh-kcn-agcn-kno2-agno2-nh3-rona-h2o/comments/comments-05-reaction-with-koh-agoh-kcn-agcn-kno2-agno2-nh3-rona-h2o.scrubbed.json</x:v>
       </x:c>
       <x:c r="N182" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-05-reaction-with-koh-agoh-kcn-agcn-kno2-agno2-nh3-rona-h2o/comments/comments-05-reaction-with-koh-agoh-kcn-agcn-kno2-agno2-nh3-rona-h2o.final.md</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-05-reaction-with-koh-agoh-kcn-agcn-kno2-agno2-nh3-rona-h2o/comments/comments-05-reaction-with-koh-agoh-kcn-agcn-kno2-agno2-nh3-rona-h2o.final.md</x:v>
       </x:c>
       <x:c r="O182" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -9998,7 +10015,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q182" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="183">
@@ -10012,13 +10029,13 @@
         <x:v>Haloalkanes and Haloarenes (Organic Compounds containing Halogens)</x:v>
       </x:c>
       <x:c r="D183" s="4" t="str">
-        <x:v>haloalkanes-and-haloarenes</x:v>
+        <x:v>haloalkanes-and-haloarenes-organic-compounds-containing-halogens</x:v>
       </x:c>
       <x:c r="E183" s="4" t="str">
         <x:v>06</x:v>
       </x:c>
       <x:c r="F183" s="4" t="str">
-        <x:v>haloalkanes-and-haloarenes-lecture-06</x:v>
+        <x:v>haloalkanes-and-haloarenes-organic-compounds-containing-halogens-lecture-06</x:v>
       </x:c>
       <x:c r="G183" s="4" t="str">
         <x:v>Properties of HaloAlkanes 3: Elimination Reaction - E1 &amp; E2</x:v>
@@ -10033,16 +10050,16 @@
         <x:v>comments-06-properties-of-haloalkanes-3-elimination-reaction-e1-and-e2</x:v>
       </x:c>
       <x:c r="K183" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-06-properties-of-haloalkanes-3-elimination-reaction-e1-and-e2</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-06-properties-of-haloalkanes-3-elimination-reaction-e1-and-e2</x:v>
       </x:c>
       <x:c r="L183" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-06-properties-of-haloalkanes-3-elimination-reaction-e1-and-e2/comments/comments-06-properties-of-haloalkanes-3-elimination-reaction-e1-and-e2.raw.json</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-06-properties-of-haloalkanes-3-elimination-reaction-e1-and-e2/comments/comments-06-properties-of-haloalkanes-3-elimination-reaction-e1-and-e2.raw.json</x:v>
       </x:c>
       <x:c r="M183" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-06-properties-of-haloalkanes-3-elimination-reaction-e1-and-e2/comments/comments-06-properties-of-haloalkanes-3-elimination-reaction-e1-and-e2.scrubbed.json</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-06-properties-of-haloalkanes-3-elimination-reaction-e1-and-e2/comments/comments-06-properties-of-haloalkanes-3-elimination-reaction-e1-and-e2.scrubbed.json</x:v>
       </x:c>
       <x:c r="N183" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-06-properties-of-haloalkanes-3-elimination-reaction-e1-and-e2/comments/comments-06-properties-of-haloalkanes-3-elimination-reaction-e1-and-e2.final.md</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-06-properties-of-haloalkanes-3-elimination-reaction-e1-and-e2/comments/comments-06-properties-of-haloalkanes-3-elimination-reaction-e1-and-e2.final.md</x:v>
       </x:c>
       <x:c r="O183" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -10051,7 +10068,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q183" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="184">
@@ -10065,13 +10082,13 @@
         <x:v>Haloalkanes and Haloarenes (Organic Compounds containing Halogens)</x:v>
       </x:c>
       <x:c r="D184" s="4" t="str">
-        <x:v>haloalkanes-and-haloarenes</x:v>
+        <x:v>haloalkanes-and-haloarenes-organic-compounds-containing-halogens</x:v>
       </x:c>
       <x:c r="E184" s="4" t="str">
         <x:v>07</x:v>
       </x:c>
       <x:c r="F184" s="4" t="str">
-        <x:v>haloalkanes-and-haloarenes-lecture-07</x:v>
+        <x:v>haloalkanes-and-haloarenes-organic-compounds-containing-halogens-lecture-07</x:v>
       </x:c>
       <x:c r="G184" s="4" t="str">
         <x:v>Properties of HaloAlkanes 4: Reaction with Metals</x:v>
@@ -10086,16 +10103,16 @@
         <x:v>comments-07-properties-of-haloalkanes-4-reaction-with-metals</x:v>
       </x:c>
       <x:c r="K184" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-07-properties-of-haloalkanes-4-reaction-with-metals</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-07-properties-of-haloalkanes-4-reaction-with-metals</x:v>
       </x:c>
       <x:c r="L184" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-07-properties-of-haloalkanes-4-reaction-with-metals/comments/comments-07-properties-of-haloalkanes-4-reaction-with-metals.raw.json</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-07-properties-of-haloalkanes-4-reaction-with-metals/comments/comments-07-properties-of-haloalkanes-4-reaction-with-metals.raw.json</x:v>
       </x:c>
       <x:c r="M184" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-07-properties-of-haloalkanes-4-reaction-with-metals/comments/comments-07-properties-of-haloalkanes-4-reaction-with-metals.scrubbed.json</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-07-properties-of-haloalkanes-4-reaction-with-metals/comments/comments-07-properties-of-haloalkanes-4-reaction-with-metals.scrubbed.json</x:v>
       </x:c>
       <x:c r="N184" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-07-properties-of-haloalkanes-4-reaction-with-metals/comments/comments-07-properties-of-haloalkanes-4-reaction-with-metals.final.md</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-07-properties-of-haloalkanes-4-reaction-with-metals/comments/comments-07-properties-of-haloalkanes-4-reaction-with-metals.final.md</x:v>
       </x:c>
       <x:c r="O184" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -10104,7 +10121,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q184" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
@@ -10118,13 +10135,13 @@
         <x:v>Haloalkanes and Haloarenes (Organic Compounds containing Halogens)</x:v>
       </x:c>
       <x:c r="D185" s="4" t="str">
-        <x:v>haloalkanes-and-haloarenes</x:v>
+        <x:v>haloalkanes-and-haloarenes-organic-compounds-containing-halogens</x:v>
       </x:c>
       <x:c r="E185" s="4" t="str">
         <x:v>08</x:v>
       </x:c>
       <x:c r="F185" s="4" t="str">
-        <x:v>haloalkanes-and-haloarenes-lecture-08</x:v>
+        <x:v>haloalkanes-and-haloarenes-organic-compounds-containing-halogens-lecture-08</x:v>
       </x:c>
       <x:c r="G185" s="4" t="str">
         <x:v>Preparation of HaloArenes - Sandmeyer &amp; Gattermann Reaction</x:v>
@@ -10139,16 +10156,16 @@
         <x:v>comments-08-preparation-of-haloarenes-sandmeyer-and-gattermann-reaction</x:v>
       </x:c>
       <x:c r="K185" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-08-preparation-of-haloarenes-sandmeyer-and-gattermann-reaction</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-08-preparation-of-haloarenes-sandmeyer-and-gattermann-reaction</x:v>
       </x:c>
       <x:c r="L185" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-08-preparation-of-haloarenes-sandmeyer-and-gattermann-reaction/comments/comments-08-preparation-of-haloarenes-sandmeyer-and-gattermann-reaction.raw.json</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-08-preparation-of-haloarenes-sandmeyer-and-gattermann-reaction/comments/comments-08-preparation-of-haloarenes-sandmeyer-and-gattermann-reaction.raw.json</x:v>
       </x:c>
       <x:c r="M185" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-08-preparation-of-haloarenes-sandmeyer-and-gattermann-reaction/comments/comments-08-preparation-of-haloarenes-sandmeyer-and-gattermann-reaction.scrubbed.json</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-08-preparation-of-haloarenes-sandmeyer-and-gattermann-reaction/comments/comments-08-preparation-of-haloarenes-sandmeyer-and-gattermann-reaction.scrubbed.json</x:v>
       </x:c>
       <x:c r="N185" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-08-preparation-of-haloarenes-sandmeyer-and-gattermann-reaction/comments/comments-08-preparation-of-haloarenes-sandmeyer-and-gattermann-reaction.final.md</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-08-preparation-of-haloarenes-sandmeyer-and-gattermann-reaction/comments/comments-08-preparation-of-haloarenes-sandmeyer-and-gattermann-reaction.final.md</x:v>
       </x:c>
       <x:c r="O185" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -10157,7 +10174,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q185" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="186">
@@ -10171,13 +10188,13 @@
         <x:v>Haloalkanes and Haloarenes (Organic Compounds containing Halogens)</x:v>
       </x:c>
       <x:c r="D186" s="4" t="str">
-        <x:v>haloalkanes-and-haloarenes</x:v>
+        <x:v>haloalkanes-and-haloarenes-organic-compounds-containing-halogens</x:v>
       </x:c>
       <x:c r="E186" s="4" t="str">
         <x:v>09</x:v>
       </x:c>
       <x:c r="F186" s="4" t="str">
-        <x:v>haloalkanes-and-haloarenes-lecture-09</x:v>
+        <x:v>haloalkanes-and-haloarenes-organic-compounds-containing-halogens-lecture-09</x:v>
       </x:c>
       <x:c r="G186" s="4" t="str">
         <x:v>Chemical Properties of HaloArenes</x:v>
@@ -10192,16 +10209,16 @@
         <x:v>comments-09-chemical-properties-of-haloarenes</x:v>
       </x:c>
       <x:c r="K186" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-09-chemical-properties-of-haloarenes</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-09-chemical-properties-of-haloarenes</x:v>
       </x:c>
       <x:c r="L186" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-09-chemical-properties-of-haloarenes/comments/comments-09-chemical-properties-of-haloarenes.raw.json</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-09-chemical-properties-of-haloarenes/comments/comments-09-chemical-properties-of-haloarenes.raw.json</x:v>
       </x:c>
       <x:c r="M186" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-09-chemical-properties-of-haloarenes/comments/comments-09-chemical-properties-of-haloarenes.scrubbed.json</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-09-chemical-properties-of-haloarenes/comments/comments-09-chemical-properties-of-haloarenes.scrubbed.json</x:v>
       </x:c>
       <x:c r="N186" s="4" t="str">
-        <x:v>content/chemistry/organic/haloalkanes-and-haloarenes/lectures/lecture-09-chemical-properties-of-haloarenes/comments/comments-09-chemical-properties-of-haloarenes.final.md</x:v>
+        <x:v>content/03-organic/06-haloalkanes-and-haloarenes-organic-compounds-containing-halogens/lectures/lecture-09-chemical-properties-of-haloarenes/comments/comments-09-chemical-properties-of-haloarenes.final.md</x:v>
       </x:c>
       <x:c r="O186" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -10210,7 +10227,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q186" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="187">
@@ -10224,13 +10241,13 @@
         <x:v>Alcohols, Phenols and Ethers (Organic Compounds containing Oxygen 1/3)</x:v>
       </x:c>
       <x:c r="D187" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3</x:v>
       </x:c>
       <x:c r="E187" s="4" t="str">
         <x:v>01</x:v>
       </x:c>
       <x:c r="F187" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers-lecture-01</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3-lecture-01</x:v>
       </x:c>
       <x:c r="G187" s="4" t="str">
         <x:v>Introduction, Classification &amp; Nomenclature</x:v>
@@ -10245,16 +10262,16 @@
         <x:v>comments-01-introduction-classification-and-nomenclature</x:v>
       </x:c>
       <x:c r="K187" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-01-introduction-classification-and-nomenclature</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-01-introduction-classification-and-nomenclature</x:v>
       </x:c>
       <x:c r="L187" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-01-introduction-classification-and-nomenclature/comments/comments-01-introduction-classification-and-nomenclature.raw.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-01-introduction-classification-and-nomenclature/comments/comments-01-introduction-classification-and-nomenclature.raw.json</x:v>
       </x:c>
       <x:c r="M187" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-01-introduction-classification-and-nomenclature/comments/comments-01-introduction-classification-and-nomenclature.scrubbed.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-01-introduction-classification-and-nomenclature/comments/comments-01-introduction-classification-and-nomenclature.scrubbed.json</x:v>
       </x:c>
       <x:c r="N187" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-01-introduction-classification-and-nomenclature/comments/comments-01-introduction-classification-and-nomenclature.final.md</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-01-introduction-classification-and-nomenclature/comments/comments-01-introduction-classification-and-nomenclature.final.md</x:v>
       </x:c>
       <x:c r="O187" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -10263,7 +10280,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q187" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="188">
@@ -10277,13 +10294,13 @@
         <x:v>Alcohols, Phenols and Ethers (Organic Compounds containing Oxygen 1/3)</x:v>
       </x:c>
       <x:c r="D188" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3</x:v>
       </x:c>
       <x:c r="E188" s="4" t="str">
         <x:v>02</x:v>
       </x:c>
       <x:c r="F188" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers-lecture-02</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3-lecture-02</x:v>
       </x:c>
       <x:c r="G188" s="4" t="str">
         <x:v>Preparation of Alcohols 1: From Alkenes</x:v>
@@ -10298,16 +10315,16 @@
         <x:v>comments-02-preparation-of-alcohols-1-from-alkenes</x:v>
       </x:c>
       <x:c r="K188" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-02-preparation-of-alcohols-1-from-alkenes</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-02-preparation-of-alcohols-1-from-alkenes</x:v>
       </x:c>
       <x:c r="L188" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-02-preparation-of-alcohols-1-from-alkenes/comments/comments-02-preparation-of-alcohols-1-from-alkenes.raw.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-02-preparation-of-alcohols-1-from-alkenes/comments/comments-02-preparation-of-alcohols-1-from-alkenes.raw.json</x:v>
       </x:c>
       <x:c r="M188" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-02-preparation-of-alcohols-1-from-alkenes/comments/comments-02-preparation-of-alcohols-1-from-alkenes.scrubbed.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-02-preparation-of-alcohols-1-from-alkenes/comments/comments-02-preparation-of-alcohols-1-from-alkenes.scrubbed.json</x:v>
       </x:c>
       <x:c r="N188" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-02-preparation-of-alcohols-1-from-alkenes/comments/comments-02-preparation-of-alcohols-1-from-alkenes.final.md</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-02-preparation-of-alcohols-1-from-alkenes/comments/comments-02-preparation-of-alcohols-1-from-alkenes.final.md</x:v>
       </x:c>
       <x:c r="O188" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -10316,7 +10333,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q188" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="189">
@@ -10330,13 +10347,13 @@
         <x:v>Alcohols, Phenols and Ethers (Organic Compounds containing Oxygen 1/3)</x:v>
       </x:c>
       <x:c r="D189" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3</x:v>
       </x:c>
       <x:c r="E189" s="4" t="str">
         <x:v>03</x:v>
       </x:c>
       <x:c r="F189" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers-lecture-03</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3-lecture-03</x:v>
       </x:c>
       <x:c r="G189" s="4" t="str">
         <x:v>Preparation of Alcohols 2: From Carbonyl Compounds &amp; Carboxylic Acid</x:v>
@@ -10351,16 +10368,16 @@
         <x:v>comments-03-preparation-of-alcohols-2-from-carbonyl-compounds-and-carboxylic-acid</x:v>
       </x:c>
       <x:c r="K189" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-03-preparation-of-alcohols-2-from-carbonyl-compounds-and-carboxylic-acid</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-03-preparation-of-alcohols-2-from-carbonyl-compounds-and-carboxylic-acid</x:v>
       </x:c>
       <x:c r="L189" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-03-preparation-of-alcohols-2-from-carbonyl-compounds-and-carboxylic-acid/comments/comments-03-preparation-of-alcohols-2-from-carbonyl-compounds-and-carboxylic-acid.raw.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-03-preparation-of-alcohols-2-from-carbonyl-compounds-and-carboxylic-acid/comments/comments-03-preparation-of-alcohols-2-from-carbonyl-compounds-and-carboxylic-acid.raw.json</x:v>
       </x:c>
       <x:c r="M189" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-03-preparation-of-alcohols-2-from-carbonyl-compounds-and-carboxylic-acid/comments/comments-03-preparation-of-alcohols-2-from-carbonyl-compounds-and-carboxylic-acid.scrubbed.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-03-preparation-of-alcohols-2-from-carbonyl-compounds-and-carboxylic-acid/comments/comments-03-preparation-of-alcohols-2-from-carbonyl-compounds-and-carboxylic-acid.scrubbed.json</x:v>
       </x:c>
       <x:c r="N189" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-03-preparation-of-alcohols-2-from-carbonyl-compounds-and-carboxylic-acid/comments/comments-03-preparation-of-alcohols-2-from-carbonyl-compounds-and-carboxylic-acid.final.md</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-03-preparation-of-alcohols-2-from-carbonyl-compounds-and-carboxylic-acid/comments/comments-03-preparation-of-alcohols-2-from-carbonyl-compounds-and-carboxylic-acid.final.md</x:v>
       </x:c>
       <x:c r="O189" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -10369,7 +10386,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q189" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
@@ -10383,13 +10400,13 @@
         <x:v>Alcohols, Phenols and Ethers (Organic Compounds containing Oxygen 1/3)</x:v>
       </x:c>
       <x:c r="D190" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3</x:v>
       </x:c>
       <x:c r="E190" s="4" t="str">
         <x:v>04</x:v>
       </x:c>
       <x:c r="F190" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers-lecture-04</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3-lecture-04</x:v>
       </x:c>
       <x:c r="G190" s="4" t="str">
         <x:v>Preparation of Alcohols 3: From Grignard's Reagent</x:v>
@@ -10404,16 +10421,16 @@
         <x:v>comments-04-preparation-of-alcohols-3-from-grignards-reagent</x:v>
       </x:c>
       <x:c r="K190" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-04-preparation-of-alcohols-3-from-grignards-reagent</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-04-preparation-of-alcohols-3-from-grignards-reagent</x:v>
       </x:c>
       <x:c r="L190" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-04-preparation-of-alcohols-3-from-grignards-reagent/comments/comments-04-preparation-of-alcohols-3-from-grignards-reagent.raw.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-04-preparation-of-alcohols-3-from-grignards-reagent/comments/comments-04-preparation-of-alcohols-3-from-grignards-reagent.raw.json</x:v>
       </x:c>
       <x:c r="M190" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-04-preparation-of-alcohols-3-from-grignards-reagent/comments/comments-04-preparation-of-alcohols-3-from-grignards-reagent.scrubbed.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-04-preparation-of-alcohols-3-from-grignards-reagent/comments/comments-04-preparation-of-alcohols-3-from-grignards-reagent.scrubbed.json</x:v>
       </x:c>
       <x:c r="N190" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-04-preparation-of-alcohols-3-from-grignards-reagent/comments/comments-04-preparation-of-alcohols-3-from-grignards-reagent.final.md</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-04-preparation-of-alcohols-3-from-grignards-reagent/comments/comments-04-preparation-of-alcohols-3-from-grignards-reagent.final.md</x:v>
       </x:c>
       <x:c r="O190" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -10422,7 +10439,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q190" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="191">
@@ -10436,13 +10453,13 @@
         <x:v>Alcohols, Phenols and Ethers (Organic Compounds containing Oxygen 1/3)</x:v>
       </x:c>
       <x:c r="D191" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3</x:v>
       </x:c>
       <x:c r="E191" s="4" t="str">
         <x:v>05</x:v>
       </x:c>
       <x:c r="F191" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers-lecture-05</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3-lecture-05</x:v>
       </x:c>
       <x:c r="G191" s="4" t="str">
         <x:v>Properties of Alcohols 1: Acidic Nature - Esterification</x:v>
@@ -10457,16 +10474,16 @@
         <x:v>comments-05-properties-of-alcohols-1-acidic-nature-esterification</x:v>
       </x:c>
       <x:c r="K191" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-05-properties-of-alcohols-1-acidic-nature-esterification</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-05-properties-of-alcohols-1-acidic-nature-esterification</x:v>
       </x:c>
       <x:c r="L191" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-05-properties-of-alcohols-1-acidic-nature-esterification/comments/comments-05-properties-of-alcohols-1-acidic-nature-esterification.raw.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-05-properties-of-alcohols-1-acidic-nature-esterification/comments/comments-05-properties-of-alcohols-1-acidic-nature-esterification.raw.json</x:v>
       </x:c>
       <x:c r="M191" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-05-properties-of-alcohols-1-acidic-nature-esterification/comments/comments-05-properties-of-alcohols-1-acidic-nature-esterification.scrubbed.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-05-properties-of-alcohols-1-acidic-nature-esterification/comments/comments-05-properties-of-alcohols-1-acidic-nature-esterification.scrubbed.json</x:v>
       </x:c>
       <x:c r="N191" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-05-properties-of-alcohols-1-acidic-nature-esterification/comments/comments-05-properties-of-alcohols-1-acidic-nature-esterification.final.md</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-05-properties-of-alcohols-1-acidic-nature-esterification/comments/comments-05-properties-of-alcohols-1-acidic-nature-esterification.final.md</x:v>
       </x:c>
       <x:c r="O191" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -10475,7 +10492,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q191" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="192">
@@ -10489,13 +10506,13 @@
         <x:v>Alcohols, Phenols and Ethers (Organic Compounds containing Oxygen 1/3)</x:v>
       </x:c>
       <x:c r="D192" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3</x:v>
       </x:c>
       <x:c r="E192" s="4" t="str">
         <x:v>06</x:v>
       </x:c>
       <x:c r="F192" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers-lecture-06</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3-lecture-06</x:v>
       </x:c>
       <x:c r="G192" s="4" t="str">
         <x:v>Properties of Alcohols 2: Lucas Test</x:v>
@@ -10510,16 +10527,16 @@
         <x:v>comments-06-properties-of-alcohols-2-lucas-test</x:v>
       </x:c>
       <x:c r="K192" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-06-properties-of-alcohols-2-lucas-test</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-06-properties-of-alcohols-2-lucas-test</x:v>
       </x:c>
       <x:c r="L192" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-06-properties-of-alcohols-2-lucas-test/comments/comments-06-properties-of-alcohols-2-lucas-test.raw.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-06-properties-of-alcohols-2-lucas-test/comments/comments-06-properties-of-alcohols-2-lucas-test.raw.json</x:v>
       </x:c>
       <x:c r="M192" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-06-properties-of-alcohols-2-lucas-test/comments/comments-06-properties-of-alcohols-2-lucas-test.scrubbed.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-06-properties-of-alcohols-2-lucas-test/comments/comments-06-properties-of-alcohols-2-lucas-test.scrubbed.json</x:v>
       </x:c>
       <x:c r="N192" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-06-properties-of-alcohols-2-lucas-test/comments/comments-06-properties-of-alcohols-2-lucas-test.final.md</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-06-properties-of-alcohols-2-lucas-test/comments/comments-06-properties-of-alcohols-2-lucas-test.final.md</x:v>
       </x:c>
       <x:c r="O192" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -10528,7 +10545,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q192" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="193">
@@ -10542,13 +10559,13 @@
         <x:v>Alcohols, Phenols and Ethers (Organic Compounds containing Oxygen 1/3)</x:v>
       </x:c>
       <x:c r="D193" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3</x:v>
       </x:c>
       <x:c r="E193" s="4" t="str">
         <x:v>07</x:v>
       </x:c>
       <x:c r="F193" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers-lecture-07</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3-lecture-07</x:v>
       </x:c>
       <x:c r="G193" s="4" t="str">
         <x:v>Properties of Alcohols 3: Dehydration of Alcohols</x:v>
@@ -10563,16 +10580,16 @@
         <x:v>comments-07-properties-of-alcohols-3-dehydration-of-alcohols</x:v>
       </x:c>
       <x:c r="K193" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-07-properties-of-alcohols-3-dehydration-of-alcohols</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-07-properties-of-alcohols-3-dehydration-of-alcohols</x:v>
       </x:c>
       <x:c r="L193" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-07-properties-of-alcohols-3-dehydration-of-alcohols/comments/comments-07-properties-of-alcohols-3-dehydration-of-alcohols.raw.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-07-properties-of-alcohols-3-dehydration-of-alcohols/comments/comments-07-properties-of-alcohols-3-dehydration-of-alcohols.raw.json</x:v>
       </x:c>
       <x:c r="M193" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-07-properties-of-alcohols-3-dehydration-of-alcohols/comments/comments-07-properties-of-alcohols-3-dehydration-of-alcohols.scrubbed.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-07-properties-of-alcohols-3-dehydration-of-alcohols/comments/comments-07-properties-of-alcohols-3-dehydration-of-alcohols.scrubbed.json</x:v>
       </x:c>
       <x:c r="N193" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-07-properties-of-alcohols-3-dehydration-of-alcohols/comments/comments-07-properties-of-alcohols-3-dehydration-of-alcohols.final.md</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-07-properties-of-alcohols-3-dehydration-of-alcohols/comments/comments-07-properties-of-alcohols-3-dehydration-of-alcohols.final.md</x:v>
       </x:c>
       <x:c r="O193" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -10581,7 +10598,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q193" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="194">
@@ -10595,13 +10612,13 @@
         <x:v>Alcohols, Phenols and Ethers (Organic Compounds containing Oxygen 1/3)</x:v>
       </x:c>
       <x:c r="D194" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3</x:v>
       </x:c>
       <x:c r="E194" s="4" t="str">
         <x:v>08</x:v>
       </x:c>
       <x:c r="F194" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers-lecture-08</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3-lecture-08</x:v>
       </x:c>
       <x:c r="G194" s="4" t="str">
         <x:v>Properties of Alcohols 4: Oxidation of Alcohols</x:v>
@@ -10616,16 +10633,16 @@
         <x:v>comments-08-properties-of-alcohols-4-oxidation-of-alcohols</x:v>
       </x:c>
       <x:c r="K194" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-08-properties-of-alcohols-4-oxidation-of-alcohols</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-08-properties-of-alcohols-4-oxidation-of-alcohols</x:v>
       </x:c>
       <x:c r="L194" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-08-properties-of-alcohols-4-oxidation-of-alcohols/comments/comments-08-properties-of-alcohols-4-oxidation-of-alcohols.raw.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-08-properties-of-alcohols-4-oxidation-of-alcohols/comments/comments-08-properties-of-alcohols-4-oxidation-of-alcohols.raw.json</x:v>
       </x:c>
       <x:c r="M194" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-08-properties-of-alcohols-4-oxidation-of-alcohols/comments/comments-08-properties-of-alcohols-4-oxidation-of-alcohols.scrubbed.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-08-properties-of-alcohols-4-oxidation-of-alcohols/comments/comments-08-properties-of-alcohols-4-oxidation-of-alcohols.scrubbed.json</x:v>
       </x:c>
       <x:c r="N194" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-08-properties-of-alcohols-4-oxidation-of-alcohols/comments/comments-08-properties-of-alcohols-4-oxidation-of-alcohols.final.md</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-08-properties-of-alcohols-4-oxidation-of-alcohols/comments/comments-08-properties-of-alcohols-4-oxidation-of-alcohols.final.md</x:v>
       </x:c>
       <x:c r="O194" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -10634,7 +10651,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q194" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
@@ -10648,13 +10665,13 @@
         <x:v>Alcohols, Phenols and Ethers (Organic Compounds containing Oxygen 1/3)</x:v>
       </x:c>
       <x:c r="D195" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3</x:v>
       </x:c>
       <x:c r="E195" s="4" t="str">
         <x:v>09</x:v>
       </x:c>
       <x:c r="F195" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers-lecture-09</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3-lecture-09</x:v>
       </x:c>
       <x:c r="G195" s="4" t="str">
         <x:v>Preparation of Phenols - All Methods</x:v>
@@ -10669,16 +10686,16 @@
         <x:v>comments-09-preparation-of-phenols-all-methods</x:v>
       </x:c>
       <x:c r="K195" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-09-preparation-of-phenols-all-methods</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-09-preparation-of-phenols-all-methods</x:v>
       </x:c>
       <x:c r="L195" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-09-preparation-of-phenols-all-methods/comments/comments-09-preparation-of-phenols-all-methods.raw.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-09-preparation-of-phenols-all-methods/comments/comments-09-preparation-of-phenols-all-methods.raw.json</x:v>
       </x:c>
       <x:c r="M195" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-09-preparation-of-phenols-all-methods/comments/comments-09-preparation-of-phenols-all-methods.scrubbed.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-09-preparation-of-phenols-all-methods/comments/comments-09-preparation-of-phenols-all-methods.scrubbed.json</x:v>
       </x:c>
       <x:c r="N195" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-09-preparation-of-phenols-all-methods/comments/comments-09-preparation-of-phenols-all-methods.final.md</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-09-preparation-of-phenols-all-methods/comments/comments-09-preparation-of-phenols-all-methods.final.md</x:v>
       </x:c>
       <x:c r="O195" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -10687,7 +10704,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q195" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
@@ -10701,13 +10718,13 @@
         <x:v>Alcohols, Phenols and Ethers (Organic Compounds containing Oxygen 1/3)</x:v>
       </x:c>
       <x:c r="D196" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3</x:v>
       </x:c>
       <x:c r="E196" s="4" t="str">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F196" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers-lecture-10</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3-lecture-10</x:v>
       </x:c>
       <x:c r="G196" s="4" t="str">
         <x:v>Properties of Phenols 1: Acidic Nature of Phenols</x:v>
@@ -10722,16 +10739,16 @@
         <x:v>comments-10-properties-of-phenols-1-acidic-nature-of-phenols</x:v>
       </x:c>
       <x:c r="K196" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-10-properties-of-phenols-1-acidic-nature-of-phenols</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-10-properties-of-phenols-1-acidic-nature-of-phenols</x:v>
       </x:c>
       <x:c r="L196" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-10-properties-of-phenols-1-acidic-nature-of-phenols/comments/comments-10-properties-of-phenols-1-acidic-nature-of-phenols.raw.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-10-properties-of-phenols-1-acidic-nature-of-phenols/comments/comments-10-properties-of-phenols-1-acidic-nature-of-phenols.raw.json</x:v>
       </x:c>
       <x:c r="M196" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-10-properties-of-phenols-1-acidic-nature-of-phenols/comments/comments-10-properties-of-phenols-1-acidic-nature-of-phenols.scrubbed.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-10-properties-of-phenols-1-acidic-nature-of-phenols/comments/comments-10-properties-of-phenols-1-acidic-nature-of-phenols.scrubbed.json</x:v>
       </x:c>
       <x:c r="N196" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-10-properties-of-phenols-1-acidic-nature-of-phenols/comments/comments-10-properties-of-phenols-1-acidic-nature-of-phenols.final.md</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-10-properties-of-phenols-1-acidic-nature-of-phenols/comments/comments-10-properties-of-phenols-1-acidic-nature-of-phenols.final.md</x:v>
       </x:c>
       <x:c r="O196" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -10740,7 +10757,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q196" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
@@ -10754,13 +10771,13 @@
         <x:v>Alcohols, Phenols and Ethers (Organic Compounds containing Oxygen 1/3)</x:v>
       </x:c>
       <x:c r="D197" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3</x:v>
       </x:c>
       <x:c r="E197" s="4" t="str">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F197" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers-lecture-11</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3-lecture-11</x:v>
       </x:c>
       <x:c r="G197" s="4" t="str">
         <x:v>Properties of Phenols 2: Esterification &amp; Reactions of Benzene Ring</x:v>
@@ -10775,16 +10792,16 @@
         <x:v>comments-11-properties-of-phenols-2-esterification-and-reactions-of-benzene-ring</x:v>
       </x:c>
       <x:c r="K197" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-11-properties-of-phenols-2-esterification-and-reactions-of-benzene-ring</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-11-properties-of-phenols-2-esterification-and-reactions-of-benzene-ring</x:v>
       </x:c>
       <x:c r="L197" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-11-properties-of-phenols-2-esterification-and-reactions-of-benzene-ring/comments/comments-11-properties-of-phenols-2-esterification-and-reactions-of-benzene-ring.raw.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-11-properties-of-phenols-2-esterification-and-reactions-of-benzene-ring/comments/comments-11-properties-of-phenols-2-esterification-and-reactions-of-benzene-ring.raw.json</x:v>
       </x:c>
       <x:c r="M197" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-11-properties-of-phenols-2-esterification-and-reactions-of-benzene-ring/comments/comments-11-properties-of-phenols-2-esterification-and-reactions-of-benzene-ring.scrubbed.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-11-properties-of-phenols-2-esterification-and-reactions-of-benzene-ring/comments/comments-11-properties-of-phenols-2-esterification-and-reactions-of-benzene-ring.scrubbed.json</x:v>
       </x:c>
       <x:c r="N197" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-11-properties-of-phenols-2-esterification-and-reactions-of-benzene-ring/comments/comments-11-properties-of-phenols-2-esterification-and-reactions-of-benzene-ring.final.md</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-11-properties-of-phenols-2-esterification-and-reactions-of-benzene-ring/comments/comments-11-properties-of-phenols-2-esterification-and-reactions-of-benzene-ring.final.md</x:v>
       </x:c>
       <x:c r="O197" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -10793,7 +10810,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q197" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="198">
@@ -10807,13 +10824,13 @@
         <x:v>Alcohols, Phenols and Ethers (Organic Compounds containing Oxygen 1/3)</x:v>
       </x:c>
       <x:c r="D198" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3</x:v>
       </x:c>
       <x:c r="E198" s="4" t="str">
         <x:v>12</x:v>
       </x:c>
       <x:c r="F198" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers-lecture-12</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3-lecture-12</x:v>
       </x:c>
       <x:c r="G198" s="4" t="str">
         <x:v>Properties of Phenols 3: Reimer-Tiemann &amp; Kolbe's Reaction</x:v>
@@ -10828,16 +10845,16 @@
         <x:v>comments-12-properties-of-phenols-3-reimer-tiemann-and-kolbes-reaction</x:v>
       </x:c>
       <x:c r="K198" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-12-properties-of-phenols-3-reimer-tiemann-and-kolbes-reaction</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-12-properties-of-phenols-3-reimer-tiemann-and-kolbes-reaction</x:v>
       </x:c>
       <x:c r="L198" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-12-properties-of-phenols-3-reimer-tiemann-and-kolbes-reaction/comments/comments-12-properties-of-phenols-3-reimer-tiemann-and-kolbes-reaction.raw.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-12-properties-of-phenols-3-reimer-tiemann-and-kolbes-reaction/comments/comments-12-properties-of-phenols-3-reimer-tiemann-and-kolbes-reaction.raw.json</x:v>
       </x:c>
       <x:c r="M198" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-12-properties-of-phenols-3-reimer-tiemann-and-kolbes-reaction/comments/comments-12-properties-of-phenols-3-reimer-tiemann-and-kolbes-reaction.scrubbed.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-12-properties-of-phenols-3-reimer-tiemann-and-kolbes-reaction/comments/comments-12-properties-of-phenols-3-reimer-tiemann-and-kolbes-reaction.scrubbed.json</x:v>
       </x:c>
       <x:c r="N198" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-12-properties-of-phenols-3-reimer-tiemann-and-kolbes-reaction/comments/comments-12-properties-of-phenols-3-reimer-tiemann-and-kolbes-reaction.final.md</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-12-properties-of-phenols-3-reimer-tiemann-and-kolbes-reaction/comments/comments-12-properties-of-phenols-3-reimer-tiemann-and-kolbes-reaction.final.md</x:v>
       </x:c>
       <x:c r="O198" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -10846,7 +10863,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q198" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="199">
@@ -10860,13 +10877,13 @@
         <x:v>Alcohols, Phenols and Ethers (Organic Compounds containing Oxygen 1/3)</x:v>
       </x:c>
       <x:c r="D199" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3</x:v>
       </x:c>
       <x:c r="E199" s="4" t="str">
         <x:v>13</x:v>
       </x:c>
       <x:c r="F199" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers-lecture-13</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3-lecture-13</x:v>
       </x:c>
       <x:c r="G199" s="4" t="str">
         <x:v>Preparation of Ethers - Dehydration of Alcohol &amp; Williamson Synthesis</x:v>
@@ -10881,16 +10898,16 @@
         <x:v>comments-13-preparation-of-ethers-dehydration-of-alcohol-and-williamson-synthesis</x:v>
       </x:c>
       <x:c r="K199" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-13-preparation-of-ethers-dehydration-of-alcohol-and-williamson-synthesis</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-13-preparation-of-ethers-dehydration-of-alcohol-and-williamson-synthesis</x:v>
       </x:c>
       <x:c r="L199" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-13-preparation-of-ethers-dehydration-of-alcohol-and-williamson-synthesis/comments/comments-13-preparation-of-ethers-dehydration-of-alcohol-and-williamson-synthesis.raw.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-13-preparation-of-ethers-dehydration-of-alcohol-and-williamson-synthesis/comments/comments-13-preparation-of-ethers-dehydration-of-alcohol-and-williamson-synthesis.raw.json</x:v>
       </x:c>
       <x:c r="M199" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-13-preparation-of-ethers-dehydration-of-alcohol-and-williamson-synthesis/comments/comments-13-preparation-of-ethers-dehydration-of-alcohol-and-williamson-synthesis.scrubbed.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-13-preparation-of-ethers-dehydration-of-alcohol-and-williamson-synthesis/comments/comments-13-preparation-of-ethers-dehydration-of-alcohol-and-williamson-synthesis.scrubbed.json</x:v>
       </x:c>
       <x:c r="N199" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-13-preparation-of-ethers-dehydration-of-alcohol-and-williamson-synthesis/comments/comments-13-preparation-of-ethers-dehydration-of-alcohol-and-williamson-synthesis.final.md</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-13-preparation-of-ethers-dehydration-of-alcohol-and-williamson-synthesis/comments/comments-13-preparation-of-ethers-dehydration-of-alcohol-and-williamson-synthesis.final.md</x:v>
       </x:c>
       <x:c r="O199" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -10899,7 +10916,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q199" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="200">
@@ -10913,13 +10930,13 @@
         <x:v>Alcohols, Phenols and Ethers (Organic Compounds containing Oxygen 1/3)</x:v>
       </x:c>
       <x:c r="D200" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3</x:v>
       </x:c>
       <x:c r="E200" s="4" t="str">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F200" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers-lecture-14</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3-lecture-14</x:v>
       </x:c>
       <x:c r="G200" s="4" t="str">
         <x:v>Properties of Ethers: Reaction with HI &amp; Reaction of Aryl Ethers</x:v>
@@ -10934,16 +10951,16 @@
         <x:v>comments-14-properties-of-ethers-reaction-with-hi-and-reaction-of-aryl-ethers</x:v>
       </x:c>
       <x:c r="K200" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-14-properties-of-ethers-reaction-with-hi-and-reaction-of-aryl-ethers</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-14-properties-of-ethers-reaction-with-hi-and-reaction-of-aryl-ethers</x:v>
       </x:c>
       <x:c r="L200" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-14-properties-of-ethers-reaction-with-hi-and-reaction-of-aryl-ethers/comments/comments-14-properties-of-ethers-reaction-with-hi-and-reaction-of-aryl-ethers.raw.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-14-properties-of-ethers-reaction-with-hi-and-reaction-of-aryl-ethers/comments/comments-14-properties-of-ethers-reaction-with-hi-and-reaction-of-aryl-ethers.raw.json</x:v>
       </x:c>
       <x:c r="M200" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-14-properties-of-ethers-reaction-with-hi-and-reaction-of-aryl-ethers/comments/comments-14-properties-of-ethers-reaction-with-hi-and-reaction-of-aryl-ethers.scrubbed.json</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-14-properties-of-ethers-reaction-with-hi-and-reaction-of-aryl-ethers/comments/comments-14-properties-of-ethers-reaction-with-hi-and-reaction-of-aryl-ethers.scrubbed.json</x:v>
       </x:c>
       <x:c r="N200" s="4" t="str">
-        <x:v>content/chemistry/organic/alcohols-phenols-and-ethers/lectures/lecture-14-properties-of-ethers-reaction-with-hi-and-reaction-of-aryl-ethers/comments/comments-14-properties-of-ethers-reaction-with-hi-and-reaction-of-aryl-ethers.final.md</x:v>
+        <x:v>content/03-organic/07-alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3/lectures/lecture-14-properties-of-ethers-reaction-with-hi-and-reaction-of-aryl-ethers/comments/comments-14-properties-of-ethers-reaction-with-hi-and-reaction-of-aryl-ethers.final.md</x:v>
       </x:c>
       <x:c r="O200" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -10952,7 +10969,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q200" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="201">
@@ -10966,13 +10983,13 @@
         <x:v>Aldehydes and Ketones (Organic Compounds containing Oxygen 2/3)</x:v>
       </x:c>
       <x:c r="D201" s="4" t="str">
-        <x:v>aldehydes-and-ketones</x:v>
+        <x:v>aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3</x:v>
       </x:c>
       <x:c r="E201" s="4" t="str">
         <x:v>01</x:v>
       </x:c>
       <x:c r="F201" s="4" t="str">
-        <x:v>aldehydes-and-ketones-lecture-01</x:v>
+        <x:v>aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3-lecture-01</x:v>
       </x:c>
       <x:c r="G201" s="4" t="str">
         <x:v>Methods of Preparation of Aldehydes and Ketones</x:v>
@@ -10987,16 +11004,16 @@
         <x:v>comments-01-methods-of-preparation-of-aldehydes-and-ketones</x:v>
       </x:c>
       <x:c r="K201" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-01-methods-of-preparation-of-aldehydes-and-ketones</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-01-methods-of-preparation-of-aldehydes-and-ketones</x:v>
       </x:c>
       <x:c r="L201" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-01-methods-of-preparation-of-aldehydes-and-ketones/comments/comments-01-methods-of-preparation-of-aldehydes-and-ketones.raw.json</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-01-methods-of-preparation-of-aldehydes-and-ketones/comments/comments-01-methods-of-preparation-of-aldehydes-and-ketones.raw.json</x:v>
       </x:c>
       <x:c r="M201" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-01-methods-of-preparation-of-aldehydes-and-ketones/comments/comments-01-methods-of-preparation-of-aldehydes-and-ketones.scrubbed.json</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-01-methods-of-preparation-of-aldehydes-and-ketones/comments/comments-01-methods-of-preparation-of-aldehydes-and-ketones.scrubbed.json</x:v>
       </x:c>
       <x:c r="N201" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-01-methods-of-preparation-of-aldehydes-and-ketones/comments/comments-01-methods-of-preparation-of-aldehydes-and-ketones.final.md</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-01-methods-of-preparation-of-aldehydes-and-ketones/comments/comments-01-methods-of-preparation-of-aldehydes-and-ketones.final.md</x:v>
       </x:c>
       <x:c r="O201" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -11005,7 +11022,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q201" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="202">
@@ -11019,13 +11036,13 @@
         <x:v>Aldehydes and Ketones (Organic Compounds containing Oxygen 2/3)</x:v>
       </x:c>
       <x:c r="D202" s="4" t="str">
-        <x:v>aldehydes-and-ketones</x:v>
+        <x:v>aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3</x:v>
       </x:c>
       <x:c r="E202" s="4" t="str">
         <x:v>02</x:v>
       </x:c>
       <x:c r="F202" s="4" t="str">
-        <x:v>aldehydes-and-ketones-lecture-02</x:v>
+        <x:v>aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3-lecture-02</x:v>
       </x:c>
       <x:c r="G202" s="4" t="str">
         <x:v>Preparation of Aldehydes &amp; Ketones - Dry Distillation of Carboxylic Acids</x:v>
@@ -11040,16 +11057,16 @@
         <x:v>comments-02-preparation-of-aldehydes-and-ketones-dry-distillation-of-carboxylic-acids</x:v>
       </x:c>
       <x:c r="K202" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-02-preparation-of-aldehydes-and-ketones-dry-distillation-of-carboxylic-acids</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-02-preparation-of-aldehydes-and-ketones-dry-distillation-of-carboxylic-acids</x:v>
       </x:c>
       <x:c r="L202" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-02-preparation-of-aldehydes-and-ketones-dry-distillation-of-carboxylic-acids/comments/comments-02-preparation-of-aldehydes-and-ketones-dry-distillation-of-carboxylic-acids.raw.json</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-02-preparation-of-aldehydes-and-ketones-dry-distillation-of-carboxylic-acids/comments/comments-02-preparation-of-aldehydes-and-ketones-dry-distillation-of-carboxylic-acids.raw.json</x:v>
       </x:c>
       <x:c r="M202" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-02-preparation-of-aldehydes-and-ketones-dry-distillation-of-carboxylic-acids/comments/comments-02-preparation-of-aldehydes-and-ketones-dry-distillation-of-carboxylic-acids.scrubbed.json</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-02-preparation-of-aldehydes-and-ketones-dry-distillation-of-carboxylic-acids/comments/comments-02-preparation-of-aldehydes-and-ketones-dry-distillation-of-carboxylic-acids.scrubbed.json</x:v>
       </x:c>
       <x:c r="N202" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-02-preparation-of-aldehydes-and-ketones-dry-distillation-of-carboxylic-acids/comments/comments-02-preparation-of-aldehydes-and-ketones-dry-distillation-of-carboxylic-acids.final.md</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-02-preparation-of-aldehydes-and-ketones-dry-distillation-of-carboxylic-acids/comments/comments-02-preparation-of-aldehydes-and-ketones-dry-distillation-of-carboxylic-acids.final.md</x:v>
       </x:c>
       <x:c r="O202" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -11058,7 +11075,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q202" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="203">
@@ -11072,13 +11089,13 @@
         <x:v>Aldehydes and Ketones (Organic Compounds containing Oxygen 2/3)</x:v>
       </x:c>
       <x:c r="D203" s="4" t="str">
-        <x:v>aldehydes-and-ketones</x:v>
+        <x:v>aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3</x:v>
       </x:c>
       <x:c r="E203" s="4" t="str">
         <x:v>03</x:v>
       </x:c>
       <x:c r="F203" s="4" t="str">
-        <x:v>aldehydes-and-ketones-lecture-03</x:v>
+        <x:v>aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3-lecture-03</x:v>
       </x:c>
       <x:c r="G203" s="4" t="str">
         <x:v>Preparation of Aldehydes: Rosenmund's Reduction &amp; Stephen's Reduction</x:v>
@@ -11093,16 +11110,16 @@
         <x:v>comments-03-preparation-of-aldehydes-rosenmunds-reduction-and-stephens-reduction</x:v>
       </x:c>
       <x:c r="K203" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-03-preparation-of-aldehydes-rosenmunds-reduction-and-stephens-reduction</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-03-preparation-of-aldehydes-rosenmunds-reduction-and-stephens-reduction</x:v>
       </x:c>
       <x:c r="L203" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-03-preparation-of-aldehydes-rosenmunds-reduction-and-stephens-reduction/comments/comments-03-preparation-of-aldehydes-rosenmunds-reduction-and-stephens-reduction.raw.json</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-03-preparation-of-aldehydes-rosenmunds-reduction-and-stephens-reduction/comments/comments-03-preparation-of-aldehydes-rosenmunds-reduction-and-stephens-reduction.raw.json</x:v>
       </x:c>
       <x:c r="M203" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-03-preparation-of-aldehydes-rosenmunds-reduction-and-stephens-reduction/comments/comments-03-preparation-of-aldehydes-rosenmunds-reduction-and-stephens-reduction.scrubbed.json</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-03-preparation-of-aldehydes-rosenmunds-reduction-and-stephens-reduction/comments/comments-03-preparation-of-aldehydes-rosenmunds-reduction-and-stephens-reduction.scrubbed.json</x:v>
       </x:c>
       <x:c r="N203" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-03-preparation-of-aldehydes-rosenmunds-reduction-and-stephens-reduction/comments/comments-03-preparation-of-aldehydes-rosenmunds-reduction-and-stephens-reduction.final.md</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-03-preparation-of-aldehydes-rosenmunds-reduction-and-stephens-reduction/comments/comments-03-preparation-of-aldehydes-rosenmunds-reduction-and-stephens-reduction.final.md</x:v>
       </x:c>
       <x:c r="O203" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -11111,7 +11128,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q203" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="204">
@@ -11125,13 +11142,13 @@
         <x:v>Aldehydes and Ketones (Organic Compounds containing Oxygen 2/3)</x:v>
       </x:c>
       <x:c r="D204" s="4" t="str">
-        <x:v>aldehydes-and-ketones</x:v>
+        <x:v>aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3</x:v>
       </x:c>
       <x:c r="E204" s="4" t="str">
         <x:v>04</x:v>
       </x:c>
       <x:c r="F204" s="4" t="str">
-        <x:v>aldehydes-and-ketones-lecture-04</x:v>
+        <x:v>aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3-lecture-04</x:v>
       </x:c>
       <x:c r="G204" s="4" t="str">
         <x:v>Preparation of Benzaldehyde: Etard's Reaction &amp; Gatterman Koch Reaction</x:v>
@@ -11146,16 +11163,16 @@
         <x:v>comments-04-preparation-of-benzaldehyde-etards-reaction-and-gatterman-koch-reaction</x:v>
       </x:c>
       <x:c r="K204" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-04-preparation-of-benzaldehyde-etards-reaction-and-gatterman-koch-reaction</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-04-preparation-of-benzaldehyde-etards-reaction-and-gatterman-koch-reaction</x:v>
       </x:c>
       <x:c r="L204" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-04-preparation-of-benzaldehyde-etards-reaction-and-gatterman-koch-reaction/comments/comments-04-preparation-of-benzaldehyde-etards-reaction-and-gatterman-koch-reaction.raw.json</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-04-preparation-of-benzaldehyde-etards-reaction-and-gatterman-koch-reaction/comments/comments-04-preparation-of-benzaldehyde-etards-reaction-and-gatterman-koch-reaction.raw.json</x:v>
       </x:c>
       <x:c r="M204" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-04-preparation-of-benzaldehyde-etards-reaction-and-gatterman-koch-reaction/comments/comments-04-preparation-of-benzaldehyde-etards-reaction-and-gatterman-koch-reaction.scrubbed.json</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-04-preparation-of-benzaldehyde-etards-reaction-and-gatterman-koch-reaction/comments/comments-04-preparation-of-benzaldehyde-etards-reaction-and-gatterman-koch-reaction.scrubbed.json</x:v>
       </x:c>
       <x:c r="N204" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-04-preparation-of-benzaldehyde-etards-reaction-and-gatterman-koch-reaction/comments/comments-04-preparation-of-benzaldehyde-etards-reaction-and-gatterman-koch-reaction.final.md</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-04-preparation-of-benzaldehyde-etards-reaction-and-gatterman-koch-reaction/comments/comments-04-preparation-of-benzaldehyde-etards-reaction-and-gatterman-koch-reaction.final.md</x:v>
       </x:c>
       <x:c r="O204" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -11164,7 +11181,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q204" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="205">
@@ -11178,13 +11195,13 @@
         <x:v>Aldehydes and Ketones (Organic Compounds containing Oxygen 2/3)</x:v>
       </x:c>
       <x:c r="D205" s="4" t="str">
-        <x:v>aldehydes-and-ketones</x:v>
+        <x:v>aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3</x:v>
       </x:c>
       <x:c r="E205" s="4" t="str">
         <x:v>05</x:v>
       </x:c>
       <x:c r="F205" s="4" t="str">
-        <x:v>aldehydes-and-ketones-lecture-05</x:v>
+        <x:v>aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3-lecture-05</x:v>
       </x:c>
       <x:c r="G205" s="4" t="str">
         <x:v>Preparation Of Ketones: From Acyl Chloride and From Benzene</x:v>
@@ -11199,16 +11216,16 @@
         <x:v>comments-05-preparation-of-ketones-from-acyl-chloride-and-from-benzene</x:v>
       </x:c>
       <x:c r="K205" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-05-preparation-of-ketones-from-acyl-chloride-and-from-benzene</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-05-preparation-of-ketones-from-acyl-chloride-and-from-benzene</x:v>
       </x:c>
       <x:c r="L205" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-05-preparation-of-ketones-from-acyl-chloride-and-from-benzene/comments/comments-05-preparation-of-ketones-from-acyl-chloride-and-from-benzene.raw.json</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-05-preparation-of-ketones-from-acyl-chloride-and-from-benzene/comments/comments-05-preparation-of-ketones-from-acyl-chloride-and-from-benzene.raw.json</x:v>
       </x:c>
       <x:c r="M205" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-05-preparation-of-ketones-from-acyl-chloride-and-from-benzene/comments/comments-05-preparation-of-ketones-from-acyl-chloride-and-from-benzene.scrubbed.json</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-05-preparation-of-ketones-from-acyl-chloride-and-from-benzene/comments/comments-05-preparation-of-ketones-from-acyl-chloride-and-from-benzene.scrubbed.json</x:v>
       </x:c>
       <x:c r="N205" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-05-preparation-of-ketones-from-acyl-chloride-and-from-benzene/comments/comments-05-preparation-of-ketones-from-acyl-chloride-and-from-benzene.final.md</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-05-preparation-of-ketones-from-acyl-chloride-and-from-benzene/comments/comments-05-preparation-of-ketones-from-acyl-chloride-and-from-benzene.final.md</x:v>
       </x:c>
       <x:c r="O205" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -11217,7 +11234,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q205" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="206">
@@ -11231,13 +11248,13 @@
         <x:v>Aldehydes and Ketones (Organic Compounds containing Oxygen 2/3)</x:v>
       </x:c>
       <x:c r="D206" s="4" t="str">
-        <x:v>aldehydes-and-ketones</x:v>
+        <x:v>aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3</x:v>
       </x:c>
       <x:c r="E206" s="4" t="str">
         <x:v>06</x:v>
       </x:c>
       <x:c r="F206" s="4" t="str">
-        <x:v>aldehydes-and-ketones-lecture-06</x:v>
+        <x:v>aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3-lecture-06</x:v>
       </x:c>
       <x:c r="G206" s="4" t="str">
         <x:v>Properties 1: Nucleophilic Addition - Addition of HCN, Alcohols</x:v>
@@ -11252,16 +11269,16 @@
         <x:v>comments-06-properties-1-nucleophilic-addition-addition-of-hcn-alcohols</x:v>
       </x:c>
       <x:c r="K206" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-06-properties-1-nucleophilic-addition-addition-of-hcn-alcohols</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-06-properties-1-nucleophilic-addition-addition-of-hcn-alcohols</x:v>
       </x:c>
       <x:c r="L206" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-06-properties-1-nucleophilic-addition-addition-of-hcn-alcohols/comments/comments-06-properties-1-nucleophilic-addition-addition-of-hcn-alcohols.raw.json</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-06-properties-1-nucleophilic-addition-addition-of-hcn-alcohols/comments/comments-06-properties-1-nucleophilic-addition-addition-of-hcn-alcohols.raw.json</x:v>
       </x:c>
       <x:c r="M206" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-06-properties-1-nucleophilic-addition-addition-of-hcn-alcohols/comments/comments-06-properties-1-nucleophilic-addition-addition-of-hcn-alcohols.scrubbed.json</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-06-properties-1-nucleophilic-addition-addition-of-hcn-alcohols/comments/comments-06-properties-1-nucleophilic-addition-addition-of-hcn-alcohols.scrubbed.json</x:v>
       </x:c>
       <x:c r="N206" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-06-properties-1-nucleophilic-addition-addition-of-hcn-alcohols/comments/comments-06-properties-1-nucleophilic-addition-addition-of-hcn-alcohols.final.md</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-06-properties-1-nucleophilic-addition-addition-of-hcn-alcohols/comments/comments-06-properties-1-nucleophilic-addition-addition-of-hcn-alcohols.final.md</x:v>
       </x:c>
       <x:c r="O206" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -11270,7 +11287,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q206" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="207">
@@ -11284,13 +11301,13 @@
         <x:v>Aldehydes and Ketones (Organic Compounds containing Oxygen 2/3)</x:v>
       </x:c>
       <x:c r="D207" s="4" t="str">
-        <x:v>aldehydes-and-ketones</x:v>
+        <x:v>aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3</x:v>
       </x:c>
       <x:c r="E207" s="4" t="str">
         <x:v>07</x:v>
       </x:c>
       <x:c r="F207" s="4" t="str">
-        <x:v>aldehydes-and-ketones-lecture-07</x:v>
+        <x:v>aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3-lecture-07</x:v>
       </x:c>
       <x:c r="G207" s="4" t="str">
         <x:v>Properties 2: Addition Of Ammonia &amp; Ammonia Derivatives</x:v>
@@ -11305,16 +11322,16 @@
         <x:v>comments-07-properties-2-addition-of-ammonia-and-ammonia-derivatives</x:v>
       </x:c>
       <x:c r="K207" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-07-properties-2-addition-of-ammonia-and-ammonia-derivatives</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-07-properties-2-addition-of-ammonia-and-ammonia-derivatives</x:v>
       </x:c>
       <x:c r="L207" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-07-properties-2-addition-of-ammonia-and-ammonia-derivatives/comments/comments-07-properties-2-addition-of-ammonia-and-ammonia-derivatives.raw.json</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-07-properties-2-addition-of-ammonia-and-ammonia-derivatives/comments/comments-07-properties-2-addition-of-ammonia-and-ammonia-derivatives.raw.json</x:v>
       </x:c>
       <x:c r="M207" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-07-properties-2-addition-of-ammonia-and-ammonia-derivatives/comments/comments-07-properties-2-addition-of-ammonia-and-ammonia-derivatives.scrubbed.json</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-07-properties-2-addition-of-ammonia-and-ammonia-derivatives/comments/comments-07-properties-2-addition-of-ammonia-and-ammonia-derivatives.scrubbed.json</x:v>
       </x:c>
       <x:c r="N207" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-07-properties-2-addition-of-ammonia-and-ammonia-derivatives/comments/comments-07-properties-2-addition-of-ammonia-and-ammonia-derivatives.final.md</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-07-properties-2-addition-of-ammonia-and-ammonia-derivatives/comments/comments-07-properties-2-addition-of-ammonia-and-ammonia-derivatives.final.md</x:v>
       </x:c>
       <x:c r="O207" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -11323,7 +11340,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q207" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="208">
@@ -11337,13 +11354,13 @@
         <x:v>Aldehydes and Ketones (Organic Compounds containing Oxygen 2/3)</x:v>
       </x:c>
       <x:c r="D208" s="4" t="str">
-        <x:v>aldehydes-and-ketones</x:v>
+        <x:v>aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3</x:v>
       </x:c>
       <x:c r="E208" s="4" t="str">
         <x:v>08</x:v>
       </x:c>
       <x:c r="F208" s="4" t="str">
-        <x:v>aldehydes-and-ketones-lecture-08</x:v>
+        <x:v>aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3-lecture-08</x:v>
       </x:c>
       <x:c r="G208" s="4" t="str">
         <x:v>Properties 3: Reduction Of Aldehydes and Ketones</x:v>
@@ -11358,16 +11375,16 @@
         <x:v>comments-08-properties-3-reduction-of-aldehydes-and-ketones</x:v>
       </x:c>
       <x:c r="K208" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-08-properties-3-reduction-of-aldehydes-and-ketones</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-08-properties-3-reduction-of-aldehydes-and-ketones</x:v>
       </x:c>
       <x:c r="L208" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-08-properties-3-reduction-of-aldehydes-and-ketones/comments/comments-08-properties-3-reduction-of-aldehydes-and-ketones.raw.json</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-08-properties-3-reduction-of-aldehydes-and-ketones/comments/comments-08-properties-3-reduction-of-aldehydes-and-ketones.raw.json</x:v>
       </x:c>
       <x:c r="M208" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-08-properties-3-reduction-of-aldehydes-and-ketones/comments/comments-08-properties-3-reduction-of-aldehydes-and-ketones.scrubbed.json</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-08-properties-3-reduction-of-aldehydes-and-ketones/comments/comments-08-properties-3-reduction-of-aldehydes-and-ketones.scrubbed.json</x:v>
       </x:c>
       <x:c r="N208" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-08-properties-3-reduction-of-aldehydes-and-ketones/comments/comments-08-properties-3-reduction-of-aldehydes-and-ketones.final.md</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-08-properties-3-reduction-of-aldehydes-and-ketones/comments/comments-08-properties-3-reduction-of-aldehydes-and-ketones.final.md</x:v>
       </x:c>
       <x:c r="O208" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -11376,7 +11393,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q208" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="209">
@@ -11390,13 +11407,13 @@
         <x:v>Aldehydes and Ketones (Organic Compounds containing Oxygen 2/3)</x:v>
       </x:c>
       <x:c r="D209" s="4" t="str">
-        <x:v>aldehydes-and-ketones</x:v>
+        <x:v>aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3</x:v>
       </x:c>
       <x:c r="E209" s="4" t="str">
         <x:v>09</x:v>
       </x:c>
       <x:c r="F209" s="4" t="str">
-        <x:v>aldehydes-and-ketones-lecture-09</x:v>
+        <x:v>aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3-lecture-09</x:v>
       </x:c>
       <x:c r="G209" s="4" t="str">
         <x:v>Properties 4: Tollen's Test (Silver Mirror Test) and Fehling's Test</x:v>
@@ -11411,16 +11428,16 @@
         <x:v>comments-09-properties-4-tollens-test-silver-mirror-test-and-fehlings-test</x:v>
       </x:c>
       <x:c r="K209" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-09-properties-4-tollens-test-silver-mirror-test-and-fehlings-test</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-09-properties-4-tollens-test-silver-mirror-test-and-fehlings-test</x:v>
       </x:c>
       <x:c r="L209" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-09-properties-4-tollens-test-silver-mirror-test-and-fehlings-test/comments/comments-09-properties-4-tollens-test-silver-mirror-test-and-fehlings-test.raw.json</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-09-properties-4-tollens-test-silver-mirror-test-and-fehlings-test/comments/comments-09-properties-4-tollens-test-silver-mirror-test-and-fehlings-test.raw.json</x:v>
       </x:c>
       <x:c r="M209" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-09-properties-4-tollens-test-silver-mirror-test-and-fehlings-test/comments/comments-09-properties-4-tollens-test-silver-mirror-test-and-fehlings-test.scrubbed.json</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-09-properties-4-tollens-test-silver-mirror-test-and-fehlings-test/comments/comments-09-properties-4-tollens-test-silver-mirror-test-and-fehlings-test.scrubbed.json</x:v>
       </x:c>
       <x:c r="N209" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-09-properties-4-tollens-test-silver-mirror-test-and-fehlings-test/comments/comments-09-properties-4-tollens-test-silver-mirror-test-and-fehlings-test.final.md</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-09-properties-4-tollens-test-silver-mirror-test-and-fehlings-test/comments/comments-09-properties-4-tollens-test-silver-mirror-test-and-fehlings-test.final.md</x:v>
       </x:c>
       <x:c r="O209" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -11429,7 +11446,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q209" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
@@ -11443,13 +11460,13 @@
         <x:v>Aldehydes and Ketones (Organic Compounds containing Oxygen 2/3)</x:v>
       </x:c>
       <x:c r="D210" s="4" t="str">
-        <x:v>aldehydes-and-ketones</x:v>
+        <x:v>aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3</x:v>
       </x:c>
       <x:c r="E210" s="4" t="str">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F210" s="4" t="str">
-        <x:v>aldehydes-and-ketones-lecture-10</x:v>
+        <x:v>aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3-lecture-10</x:v>
       </x:c>
       <x:c r="G210" s="4" t="str">
         <x:v>Haloform Reaction || Iodoform Reaction || Iodoform Test</x:v>
@@ -11464,16 +11481,16 @@
         <x:v>comments-10-haloform-reaction-iodoform-reaction-iodoform-test</x:v>
       </x:c>
       <x:c r="K210" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-10-haloform-reaction-iodoform-reaction-iodoform-test</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-10-haloform-reaction-iodoform-reaction-iodoform-test</x:v>
       </x:c>
       <x:c r="L210" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-10-haloform-reaction-iodoform-reaction-iodoform-test/comments/comments-10-haloform-reaction-iodoform-reaction-iodoform-test.raw.json</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-10-haloform-reaction-iodoform-reaction-iodoform-test/comments/comments-10-haloform-reaction-iodoform-reaction-iodoform-test.raw.json</x:v>
       </x:c>
       <x:c r="M210" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-10-haloform-reaction-iodoform-reaction-iodoform-test/comments/comments-10-haloform-reaction-iodoform-reaction-iodoform-test.scrubbed.json</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-10-haloform-reaction-iodoform-reaction-iodoform-test/comments/comments-10-haloform-reaction-iodoform-reaction-iodoform-test.scrubbed.json</x:v>
       </x:c>
       <x:c r="N210" s="4" t="str">
-        <x:v>content/chemistry/organic/aldehydes-and-ketones/lectures/lecture-10-haloform-reaction-iodoform-reaction-iodoform-test/comments/comments-10-haloform-reaction-iodoform-reaction-iodoform-test.final.md</x:v>
+        <x:v>content/03-organic/08-aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3/lectures/lecture-10-haloform-reaction-iodoform-reaction-iodoform-test/comments/comments-10-haloform-reaction-iodoform-reaction-iodoform-test.final.md</x:v>
       </x:c>
       <x:c r="O210" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -11482,7 +11499,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q210" s="4" t="str">
-        <x:v>Single lecture video from chapter list.</x:v>
+        <x:v>Single lecture video from chapter list. Reused existing content folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -11517,16 +11534,16 @@
         <x:v>comments-01-carboxylic-acids</x:v>
       </x:c>
       <x:c r="K211" s="4" t="str">
-        <x:v>content/chemistry/organic/carboxylic-acids/lectures/lecture-01-carboxylic-acids</x:v>
+        <x:v>content/03-organic/09-carboxylic-acids-organic-compounds-containing-oxygen-3-3/lectures/lecture-01-carboxylic-acids</x:v>
       </x:c>
       <x:c r="L211" s="4" t="str">
-        <x:v>content/chemistry/organic/carboxylic-acids/lectures/lecture-01-carboxylic-acids/comments/comments-01-carboxylic-acids.raw.json</x:v>
+        <x:v>content/03-organic/09-carboxylic-acids-organic-compounds-containing-oxygen-3-3/lectures/lecture-01-carboxylic-acids/comments/comments-01-carboxylic-acids.raw.json</x:v>
       </x:c>
       <x:c r="M211" s="4" t="str">
-        <x:v>content/chemistry/organic/carboxylic-acids/lectures/lecture-01-carboxylic-acids/comments/comments-01-carboxylic-acids.scrubbed.json</x:v>
+        <x:v>content/03-organic/09-carboxylic-acids-organic-compounds-containing-oxygen-3-3/lectures/lecture-01-carboxylic-acids/comments/comments-01-carboxylic-acids.scrubbed.json</x:v>
       </x:c>
       <x:c r="N211" s="4" t="str">
-        <x:v>content/chemistry/organic/carboxylic-acids/lectures/lecture-01-carboxylic-acids/comments/comments-01-carboxylic-acids.final.md</x:v>
+        <x:v>content/03-organic/09-carboxylic-acids-organic-compounds-containing-oxygen-3-3/lectures/lecture-01-carboxylic-acids/comments/comments-01-carboxylic-acids.final.md</x:v>
       </x:c>
       <x:c r="O211" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -11535,7 +11552,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q211" s="4" t="str">
-        <x:v>One-shot/timestamped chapter collapsed from 32 same-video links.</x:v>
+        <x:v>One-shot/timestamped chapter collapsed from 32 same-video links. Current final all-lectures page uses a one-shot; existing legacy folder 'lecture-01-methods-of-formation-of-carboxylic-acid' was not reused.</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -11546,7 +11563,7 @@
         <x:v>organic</x:v>
       </x:c>
       <x:c r="C212" s="4" t="str">
-        <x:v>Amines / Organic Compounds Containing Nitrogen</x:v>
+        <x:v>Amines</x:v>
       </x:c>
       <x:c r="D212" s="4" t="str">
         <x:v>amines</x:v>
@@ -11558,7 +11575,7 @@
         <x:v>amines-lecture-01</x:v>
       </x:c>
       <x:c r="G212" s="4" t="str">
-        <x:v>Amines / Organic Compounds Containing Nitrogen</x:v>
+        <x:v>Amines</x:v>
       </x:c>
       <x:c r="H212" s="4" t="str">
         <x:v>https://youtu.be/z-E_koEXP8k</x:v>
@@ -11567,19 +11584,19 @@
         <x:v>z-E_koEXP8k</x:v>
       </x:c>
       <x:c r="J212" s="4" t="str">
-        <x:v>comments-01-amines-organic-compounds-containing-nitrogen</x:v>
+        <x:v>comments-01-amines</x:v>
       </x:c>
       <x:c r="K212" s="4" t="str">
-        <x:v>content/chemistry/organic/amines/lectures/lecture-01-amines-organic-compounds-containing-nitrogen</x:v>
+        <x:v>content/03-organic/10-amines-organic-compounds-containing-nitrogen/lectures/lecture-01-amines</x:v>
       </x:c>
       <x:c r="L212" s="4" t="str">
-        <x:v>content/chemistry/organic/amines/lectures/lecture-01-amines-organic-compounds-containing-nitrogen/comments/comments-01-amines-organic-compounds-containing-nitrogen.raw.json</x:v>
+        <x:v>content/03-organic/10-amines-organic-compounds-containing-nitrogen/lectures/lecture-01-amines/comments/comments-01-amines.raw.json</x:v>
       </x:c>
       <x:c r="M212" s="4" t="str">
-        <x:v>content/chemistry/organic/amines/lectures/lecture-01-amines-organic-compounds-containing-nitrogen/comments/comments-01-amines-organic-compounds-containing-nitrogen.scrubbed.json</x:v>
+        <x:v>content/03-organic/10-amines-organic-compounds-containing-nitrogen/lectures/lecture-01-amines/comments/comments-01-amines.scrubbed.json</x:v>
       </x:c>
       <x:c r="N212" s="4" t="str">
-        <x:v>content/chemistry/organic/amines/lectures/lecture-01-amines-organic-compounds-containing-nitrogen/comments/comments-01-amines-organic-compounds-containing-nitrogen.final.md</x:v>
+        <x:v>content/03-organic/10-amines-organic-compounds-containing-nitrogen/lectures/lecture-01-amines/comments/comments-01-amines.final.md</x:v>
       </x:c>
       <x:c r="O212" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -11588,7 +11605,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q212" s="4" t="str">
-        <x:v>One-shot/timestamped chapter collapsed from 14 same-video links.</x:v>
+        <x:v>One-shot/timestamped chapter collapsed from 14 same-video links. Current final all-lectures page uses a one-shot; existing legacy folder 'lecture-01-methods-of-formation-of-amines-01' was not reused.</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
@@ -11623,16 +11640,16 @@
         <x:v>comments-01-biomolecules</x:v>
       </x:c>
       <x:c r="K213" s="4" t="str">
-        <x:v>content/chemistry/organic/biomolecules/lectures/lecture-01-biomolecules</x:v>
+        <x:v>content/03-organic/11-biomolecules/lectures/lecture-01-biomolecules</x:v>
       </x:c>
       <x:c r="L213" s="4" t="str">
-        <x:v>content/chemistry/organic/biomolecules/lectures/lecture-01-biomolecules/comments/comments-01-biomolecules.raw.json</x:v>
+        <x:v>content/03-organic/11-biomolecules/lectures/lecture-01-biomolecules/comments/comments-01-biomolecules.raw.json</x:v>
       </x:c>
       <x:c r="M213" s="4" t="str">
-        <x:v>content/chemistry/organic/biomolecules/lectures/lecture-01-biomolecules/comments/comments-01-biomolecules.scrubbed.json</x:v>
+        <x:v>content/03-organic/11-biomolecules/lectures/lecture-01-biomolecules/comments/comments-01-biomolecules.scrubbed.json</x:v>
       </x:c>
       <x:c r="N213" s="4" t="str">
-        <x:v>content/chemistry/organic/biomolecules/lectures/lecture-01-biomolecules/comments/comments-01-biomolecules.final.md</x:v>
+        <x:v>content/03-organic/11-biomolecules/lectures/lecture-01-biomolecules/comments/comments-01-biomolecules.final.md</x:v>
       </x:c>
       <x:c r="O213" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -11641,7 +11658,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q213" s="4" t="str">
-        <x:v>One-shot/timestamped chapter collapsed from 13 same-video links.</x:v>
+        <x:v>One-shot/timestamped chapter collapsed from 13 same-video links. Current final all-lectures page uses a one-shot; existing legacy folder 'lecture-01-carbohydrates-definition' was not reused.</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
@@ -11676,16 +11693,16 @@
         <x:v>comments-01-salt-analysis</x:v>
       </x:c>
       <x:c r="K214" s="4" t="str">
-        <x:v>content/chemistry/practical/salt-analysis/lectures/lecture-01-salt-analysis</x:v>
+        <x:v>content/04-practical/01-principles-related-to-practical-chemistry-qualitative-analysis/lectures/lecture-01-salt-analysis</x:v>
       </x:c>
       <x:c r="L214" s="4" t="str">
-        <x:v>content/chemistry/practical/salt-analysis/lectures/lecture-01-salt-analysis/comments/comments-01-salt-analysis.raw.json</x:v>
+        <x:v>content/04-practical/01-principles-related-to-practical-chemistry-qualitative-analysis/lectures/lecture-01-salt-analysis/comments/comments-01-salt-analysis.raw.json</x:v>
       </x:c>
       <x:c r="M214" s="4" t="str">
-        <x:v>content/chemistry/practical/salt-analysis/lectures/lecture-01-salt-analysis/comments/comments-01-salt-analysis.scrubbed.json</x:v>
+        <x:v>content/04-practical/01-principles-related-to-practical-chemistry-qualitative-analysis/lectures/lecture-01-salt-analysis/comments/comments-01-salt-analysis.scrubbed.json</x:v>
       </x:c>
       <x:c r="N214" s="4" t="str">
-        <x:v>content/chemistry/practical/salt-analysis/lectures/lecture-01-salt-analysis/comments/comments-01-salt-analysis.final.md</x:v>
+        <x:v>content/04-practical/01-principles-related-to-practical-chemistry-qualitative-analysis/lectures/lecture-01-salt-analysis/comments/comments-01-salt-analysis.final.md</x:v>
       </x:c>
       <x:c r="O214" s="4" t="str">
         <x:v>raw-to-scrubbed</x:v>
@@ -11694,7 +11711,7 @@
         <x:v>pending</x:v>
       </x:c>
       <x:c r="Q214" s="4" t="str">
-        <x:v>One-shot/timestamped chapter collapsed from 27 same-video links.</x:v>
+        <x:v>One-shot/timestamped chapter collapsed from 27 same-video links. Current final all-lectures page uses a one-shot; existing legacy folder 'lecture-01-introduction-of-qualitative-analysis' was not reused.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11705,12 +11722,18 @@
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="Q2:Q214">
     <x:cfRule type="expression" dxfId="1" priority="2">
-      <x:formula>ISNUMBER(SEARCH("collapsed",Q2))</x:formula>
+      <x:formula>ISNUMBER(SEARCH("One-shot",Q2))</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="2" priority="3">
+      <x:formula>ISNUMBER(SEARCH("legacy",Q2))</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="3" priority="4">
+      <x:formula>ISNUMBER(SEARCH("not found",Q2))</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ba1e7d3916a464b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6ea4212e7054b36"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11721,8 +11744,8 @@
   <x:cols>
     <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="44" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="38" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="45" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="36" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -11754,7 +11777,7 @@
         <x:v>Some Basic Concepts in Chemistry</x:v>
       </x:c>
       <x:c r="D2" s="4" t="str">
-        <x:v>some-basic-concepts-chemistry</x:v>
+        <x:v>some-basic-concepts-in-chemistry</x:v>
       </x:c>
       <x:c r="E2" s="4" t="n">
         <x:v>6</x:v>
@@ -11822,7 +11845,7 @@
         <x:v>Chemical Thermodynamics</x:v>
       </x:c>
       <x:c r="D6" s="4" t="str">
-        <x:v>thermodynamics</x:v>
+        <x:v>chemical-thermodynamics</x:v>
       </x:c>
       <x:c r="E6" s="4" t="n">
         <x:v>13</x:v>
@@ -11856,7 +11879,7 @@
         <x:v>Redox Reactions and Electrochemistry</x:v>
       </x:c>
       <x:c r="D8" s="4" t="str">
-        <x:v>redox-reactions-electrochemistry</x:v>
+        <x:v>redox-reactions-and-electrochemistry</x:v>
       </x:c>
       <x:c r="E8" s="4" t="n">
         <x:v>13</x:v>
@@ -11975,7 +11998,7 @@
         <x:v>Organic Chemistry: IUPAC nomenclature</x:v>
       </x:c>
       <x:c r="D15" s="4" t="str">
-        <x:v>iupac</x:v>
+        <x:v>organic-chemistry-iupac-nomenclature</x:v>
       </x:c>
       <x:c r="E15" s="4" t="n">
         <x:v>12</x:v>
@@ -11992,7 +12015,7 @@
         <x:v>Organic Chemistry: Isomerism</x:v>
       </x:c>
       <x:c r="D16" s="4" t="str">
-        <x:v>isomerism</x:v>
+        <x:v>organic-chemistry-isomerism</x:v>
       </x:c>
       <x:c r="E16" s="4" t="n">
         <x:v>13</x:v>
@@ -12009,7 +12032,7 @@
         <x:v>Organic Chemistry: GOC</x:v>
       </x:c>
       <x:c r="D17" s="4" t="str">
-        <x:v>goc</x:v>
+        <x:v>organic-chemistry-goc</x:v>
       </x:c>
       <x:c r="E17" s="4" t="n">
         <x:v>10</x:v>
@@ -12026,7 +12049,7 @@
         <x:v>Purification and Characterisation of Organic Compounds</x:v>
       </x:c>
       <x:c r="D18" s="4" t="str">
-        <x:v>purification-and-characterisation-organic-compounds</x:v>
+        <x:v>purification-and-characterisation-of-organic-compounds</x:v>
       </x:c>
       <x:c r="E18" s="4" t="n">
         <x:v>1</x:v>
@@ -12043,7 +12066,7 @@
         <x:v>Organic Chemistry: Reaction Mechanism</x:v>
       </x:c>
       <x:c r="D19" s="4" t="str">
-        <x:v>reaction-mechanism</x:v>
+        <x:v>organic-chemistry-reaction-mechanism</x:v>
       </x:c>
       <x:c r="E19" s="4" t="n">
         <x:v>15</x:v>
@@ -12077,7 +12100,7 @@
         <x:v>Haloalkanes and Haloarenes (Organic Compounds containing Halogens)</x:v>
       </x:c>
       <x:c r="D21" s="4" t="str">
-        <x:v>haloalkanes-and-haloarenes</x:v>
+        <x:v>haloalkanes-and-haloarenes-organic-compounds-containing-halogens</x:v>
       </x:c>
       <x:c r="E21" s="4" t="n">
         <x:v>9</x:v>
@@ -12094,7 +12117,7 @@
         <x:v>Alcohols, Phenols and Ethers (Organic Compounds containing Oxygen 1/3)</x:v>
       </x:c>
       <x:c r="D22" s="4" t="str">
-        <x:v>alcohols-phenols-and-ethers</x:v>
+        <x:v>alcohols-phenols-and-ethers-organic-compounds-containing-oxygen-1-3</x:v>
       </x:c>
       <x:c r="E22" s="4" t="n">
         <x:v>14</x:v>
@@ -12111,7 +12134,7 @@
         <x:v>Aldehydes and Ketones (Organic Compounds containing Oxygen 2/3)</x:v>
       </x:c>
       <x:c r="D23" s="4" t="str">
-        <x:v>aldehydes-and-ketones</x:v>
+        <x:v>aldehydes-and-ketones-organic-compounds-containing-oxygen-2-3</x:v>
       </x:c>
       <x:c r="E23" s="4" t="n">
         <x:v>10</x:v>
@@ -12142,7 +12165,7 @@
         <x:v>organic</x:v>
       </x:c>
       <x:c r="C25" s="4" t="str">
-        <x:v>Amines / Organic Compounds Containing Nitrogen</x:v>
+        <x:v>Amines</x:v>
       </x:c>
       <x:c r="D25" s="4" t="str">
         <x:v>amines</x:v>
@@ -12188,7 +12211,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d61a6c7dac142f2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7010a03368514702"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12244,7 +12267,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b275c506848418b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f69b8bd78794f6b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12254,85 +12277,133 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="32" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="100" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="110" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="12" t="str">
-        <x:v>Check</x:v>
+        <x:v>Item</x:v>
       </x:c>
       <x:c r="B1" s="12" t="str">
-        <x:v>Value</x:v>
+        <x:v>Note</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="16" t="str">
-        <x:v>Source file</x:v>
+      <x:c r="A2" s="18" t="str">
+        <x:v>Path basis</x:v>
       </x:c>
       <x:c r="B2" s="4" t="str">
-        <x:v>chemistry_all_lectures_reformatted(2).html</x:v>
+        <x:v>Revised from content/chemistry/{domain}/... to the existing repo structure: content/01-physical, content/02-inorganic, content/03-organic, content/04-practical.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="16" t="str">
+      <x:c r="A3" s="18" t="str">
+        <x:v>All-lectures source</x:v>
+      </x:c>
+      <x:c r="B3" s="4" t="str">
+        <x:v>chemistry_all_lectures_reformatted(3).html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="18" t="str">
+        <x:v>Content listing source</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="str">
+        <x:v>all_content_files.txt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="18" t="str">
         <x:v>Manifest rows</x:v>
       </x:c>
-      <x:c r="B3" s="4" t="n">
+      <x:c r="B5" s="4" t="n">
         <x:v>213</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="16" t="str">
+    <x:row r="6">
+      <x:c r="A6" s="18" t="str">
         <x:v>Unique video IDs</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="n">
+      <x:c r="B6" s="4" t="n">
         <x:v>213</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="16" t="str">
-        <x:v>One-shot/timestamped collapsed rows</x:v>
-      </x:c>
-      <x:c r="B5" s="4" t="n">
+    <x:row r="7">
+      <x:c r="A7" s="18" t="str">
+        <x:v>Existing lecture folders reused</x:v>
+      </x:c>
+      <x:c r="B7" s="4" t="n">
+        <x:v>205</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="18" t="str">
+        <x:v>One-shot collapsed rows</x:v>
+      </x:c>
+      <x:c r="B8" s="4" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="16" t="str">
-        <x:v>Processing mode default</x:v>
-      </x:c>
-      <x:c r="B6" s="4" t="str">
-        <x:v>raw-to-scrubbed</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="16" t="str">
-        <x:v>Initial status default</x:v>
-      </x:c>
-      <x:c r="B7" s="4" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="16" t="str">
-        <x:v>Folder rule</x:v>
-      </x:c>
-      <x:c r="B8" s="4" t="str">
-        <x:v>content/chemistry/{domain}/{chapter-slug}/lectures/lecture-{NN}-{lecture-title-slug}/comments</x:v>
-      </x:c>
-    </x:row>
     <x:row r="9">
-      <x:c r="A9" s="16" t="str">
-        <x:v>Domain rule</x:v>
-      </x:c>
-      <x:c r="B9" s="4" t="str">
-        <x:v>Derived from category placement in all-lectures HTML page</x:v>
-      </x:c>
+      <x:c r="A9" s="18" t="str">
+        <x:v>New/proposed lecture folders</x:v>
+      </x:c>
+      <x:c r="B9" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="18" t="str">
+        <x:v>Purification chapter</x:v>
+      </x:c>
+      <x:c r="B10" s="4" t="str">
+        <x:v>Present in all-lectures page but not in the current content listing; assigned content/03-organic/12-purification-and-characterisation-of-organic-compounds to avoid renaming existing organic folders.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="18" t="str">
+        <x:v>Legacy one-shot replacements</x:v>
+      </x:c>
+      <x:c r="B11" s="4" t="str">
+        <x:v>For Carboxylic Acids, Amines, Biomolecules, and Salt Analysis, the current all-lectures page uses one-shot rows. Existing legacy lecture-01 folders were not reused.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="18" t="str">
+        <x:v>Folder creation rule</x:v>
+      </x:c>
+      <x:c r="B12" s="4" t="str">
+        <x:v>Create each value in the Lecture folder column, then create comments/ and images/ inside it. Do not overwrite existing files.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="19"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="19"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="19"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="19"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="19"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="19"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="19"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="19"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84f022526e4c4216"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R390f300331494906"/>
   </x:tableParts>
 </x:worksheet>
 </file>